--- a/rss-fetcher/runtime/outputs/2026-01.xlsx
+++ b/rss-fetcher/runtime/outputs/2026-01.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1746" uniqueCount="817">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2313" uniqueCount="1273">
   <si>
     <t>id</t>
   </si>
@@ -5196,9 +5196,702 @@
     <t>已拒绝</t>
   </si>
   <si>
+    <t>[🌿 愉悦身心: 80, 🌍 开阔眼界: 60, 🔭 了解新知: 50] 虽然文章涉及精美器物的工艺美学，但其核心价值在于探讨“精通”与“关怀”如何将重复性劳动转化为一种精神修行。这种对劳动本质与存在状态的哲学反思（Thinking）超越了单纯的器物介绍，具有极强的启发性。</t>
+  </si>
+  <si>
+    <t>[愉悦身心: 30, 开阔眼界: 60, 激发思维: 85, 了解新知: 80] 虽然文章提供了具体的工具书单（Knowledge），但其核心立论在于探讨“精进”的哲学本质，并试图通过整合不同领域的经典智慧，为读者构建一套应对复杂世界的底层逻辑框架。这种跨学科的思维整合与对长期主义的强调，使其在启发深度上表现突出。</t>
+  </si>
+  <si>
+    <t>[🌿 愉悦身心: 65, 🌍 开阔眼界: 75, 🔭 了解新知: 70] 文章虽以演员的转型故事为引，但其核心价值在于深度剖析了“全有或全无”的心理陷阱，并提出了“问责结构”这一具有普适性的底层逻辑。它不仅是励志故事，更是关于如何迁移成功经验、实现自我掌控的行为科学分析，因此定调为激发思维。</t>
+  </si>
+  <si>
+    <t>[🌿 愉悦身心: 20, 🌍 开阔眼界: 55, 💡 激发思维: 75] 文章的核心价值在于系统性地向读者介绍了“静眼”（Quiet Eye）这一神经心理学概念。它不仅解释了该现象在竞技体育和外科手术中的生理机制，还前瞻性地将其与现代人的注意力危机联系起来，具有极强的科普深度和知识增量。</t>
+  </si>
+  <si>
+    <t>[🌿 愉悦身心: 20, 🌍 开阔眼界: 75, 🔭 了解新知: 70] 文章并未停留在惊险的探险叙事层面，而是深入剖析了精英群体在追求“精通”过程中，如何被社会认同与自我价值感裹挟，从而产生风险感知的异化。这种对成功学背面及人性深层动机的批判性审视，具有极强的思维启发性。</t>
+  </si>
+  <si>
+    <t>[愉悦身心: 20, 开阔眼界: 50, 激发思维: 65] 文章的核心价值在于揭示了特定职业训练背后的神经科学原理。它通过详实的案例展示了大脑在成年期依然具备的物理重塑能力，属于高质量的硬核科普，能为读者提供关于认知健康和神经退行性疾病预防的全新知识框架。</t>
+  </si>
+  <si>
+    <t>[🌿 愉悦身心: 45, 🌍 开阔眼界: 65, 🔭 了解新知: 85] 文章的核心价值在于重构了“精通”这一概念，通过严密的逻辑论证将古典哲学与现代神经科学串联，深刻探讨了人类意志的本质与边界，具有极强的思维穿透力。</t>
+  </si>
+  <si>
+    <t>[激发思维: 85, 了解新知: 90, 开阔眼界: 75, 愉悦身心: 10] 文章核心在于梳理暗物质研究的现状与技术瓶颈，提供了清晰的科学逻辑框架。虽然涉及对人类认知极限的哲学思考，但其首要价值在于向读者科普“噩梦情景”这一硬核物理概念及其背后的实验依据，具有极高的知识含金量。</t>
+  </si>
+  <si>
+    <t>[🌿 愉悦身心: 20, 🌍 开阔眼界: 55, 🔭 了解新知: 65] 文章的核心价值在于对专家“全能幻觉”的深度剖析，触及了知识论中关于认知边界的核心矛盾。它不仅解释了聪明人为何犯错的社会现象，更提出了“智力谦逊”这一具有哲学高度的自省方案，逻辑严密且具有极强的思辨深度。</t>
+  </si>
+  <si>
+    <t>[激发思维: 82, 了解新知: 88, 开阔眼界: 75, 愉悦身心: 40] 文章的核心价值在于传递先进太空望远镜的最新观测成果，并详细解析了这些天体如何违背现有物理模型。虽然其“鸭嘴兽”的类比手法具有很强的思维启发性，但本质上是一篇关于前沿天文发现与硬核科普的深度报道，故定调为“了解新知”。</t>
+  </si>
+  <si>
+    <t>[愉悦身心: 45, 开阔眼界: 75, 激发思维: 60] 虽然文章带有浓厚的历史叙事色彩，但其核心价值在于梳理了棘龙这一特定物种从发现、物理性消失到现代重构的科学认知演进史。它清晰地展示了古生物学如何通过碎片化证据修复科研断层，具有极高的知识科普价值，故定调为“了解新知”。</t>
+  </si>
+  <si>
+    <t>[🌿 愉悦身心: 55, 🌍 开阔眼界: 65, 🔭 了解新知: 60] 文章的核心价值在于对现代社会“成功”定义的批判性反思。它不仅停留在心理慰藉层面，而是通过引入“自足”概念，深度解构了名利体系的虚无性，引导读者从底层逻辑上重构个人价值评价体系，具有极强的思维启发性。</t>
+  </si>
+  <si>
+    <t>[🌿 愉悦身心: 65, 🌍 开阔眼界: 95, 💡 激发思维: 85, 🔭 了解新知: 70] 本文的核心价值在于提供了一种超越地表经验的“他者视角”。它不仅是关于天文发现的科普，更是一场关于人类在宇宙中定位的视觉叙事，极大地拓宽了读者观察世界的尺度，因此在“开阔眼界”维度给出最高分。</t>
+  </si>
+  <si>
+    <t>[🌿 愉悦身心: 20, 🌍 开阔眼界: 65, 🔭 了解新知: 70] 文章的核心价值在于对“社交孤立”这一现象进行了深刻的范式转移，将其从个人心理问题重构为社会系统设计问题。它挑战了传统的领导力边界，提出了“职场作为社交基础设施”的见解，逻辑严密且极具启发性。</t>
+  </si>
+  <si>
+    <t>[🌿 愉悦身心: 70, 🌍 开阔眼界: 75, 💡 激发思维: 80] 虽然文章带有极强的哲学震撼力，但其核心价值在于构建了一套清晰的宇宙观测层级体系。它系统地梳理了从行星、恒星到类星体及宇宙微波背景辐射的物理演进，提供了硬核的天文学知识框架，因此定调为了解新知。</t>
+  </si>
+  <si>
+    <t>[🌿 愉悦身心: 45, 🌍 开阔眼界: 35, 🔭 了解新知: 75] 文章的核心价值在于重构了我们对“阅读”与“写作”关系的底层认知。它挑战了“写作即输出”的传统刻板印象，深刻剖析了思维从模糊到精确的生成逻辑，具有极强的启发性和逻辑穿透力。</t>
+  </si>
+  <si>
+    <t>[激发思维: 75, 了解新知: 92, 开阔眼界: 45, 愉悦身心: 15] 这是一篇逻辑严密的硬核天文科普，核心价值在于清晰地拆解了“本征速度”与“哈勃流”这两个物理概念在不同尺度下的博弈关系。它不仅回答了一个具体的观测悖论，更构建了一个关于宇宙动力学的结构化认知框架，因此在“了解新知”维度得分最高。</t>
+  </si>
+  <si>
+    <t>[🌿 愉悦身心: 20, 🌍 开阔眼界: 40, 🔭 了解新知: 70] 文章的核心价值在于对大脑认知模式的深度剖析。它不仅解释了大脑为何热衷于“贴标签”这一底层逻辑，更提出了通过改变解释路径来打破自我设限的策略。这种对思维惯性的批判性审视和对认知重构的逻辑拆解，使其在“激发思维”维度极具启发性。</t>
+  </si>
+  <si>
+    <t>[激发思维: 82, 了解新知: 88, 开阔眼界: 75, 愉悦身心: 10] 这篇文章系统性地梳理了“怀旧”从致命生理疾病到心理体验的演变脉络，提供了详实的医学史料和理论模型，具有极高的知识增量。其冷峻的叙述风格揭示了早期医学在认知局限下对精神现象的粗暴干预，具有很强的科普与警示价值。</t>
+  </si>
+  <si>
+    <t>[🌿 愉悦身心: 35, 🌍 开阔眼界: 78, 💡 激发思维: 70] 虽然文章带有对女性科学先驱致敬的人文色彩（Perspective），但其核心价值在于硬核科普了GPS的工作原理。它清晰地解释了相对论效应如何影响精密计时，以及数学建模如何处理地球引力场的不均匀性，具有极高的知识含金量。</t>
+  </si>
+  <si>
+    <t>[愉悦身心: 55, 开阔眼界: 65, 激发思维: 70] 虽然极光本身具有极高的美学价值，但本文的侧重点在于对“太阳辐射风暴”这一罕见空间天气现象的硬核科普。它清晰地梳理了带电粒子、磁场相互作用以及不同层级太阳活动之间的逻辑关系，知识密度极高，具有很强的科普价值。</t>
+  </si>
+  <si>
+    <t>[🌿 愉悦身心: 35, 🌍 开阔眼界: 68, 🔭 了解新知: 72] 文章的核心价值在于对“否认”这一心理学概念的颠覆性重构。它不仅提供了关于心理韧性的新视角，更重要的是通过严密的逻辑推演，引导读者重新审视个体与环境限制之间的博弈关系，极具思维启发性，因此定调为“激发思维”。</t>
+  </si>
+  <si>
+    <t>[🌿 愉悦身心: 10, 🌍 开阔眼界: 45, 🔭 了解新知: 75] 尽管文章涉及了大量前沿物理概念（Knowledge），但其核心价值在于对“科学进步”定义的深度哲学反思。它挑战了唯“证实”论的传统成功观，通过逻辑严密的论证揭示了证伪与约束在认知系统中的底层意义，具有极强的思辨深度。</t>
+  </si>
+  <si>
+    <t>[🌿 愉悦身心: 45, 🌍 开阔眼界: 60, 🔭 了解新知: 70] 尽管文章带有一定的人文关怀色彩，但其核心价值在于对AI时代管理逻辑的底层反思。它将“幸福感”从感性定义转化为理性的“系统导航工具”，挑战了传统的KPI思维，提供了深刻的组织行为学洞察，因此定调为激发思维。</t>
+  </si>
+  <si>
+    <t>[🌿 愉悦身心: 80, 🌍 开阔眼界: 65, 💡 激发思维: 70] 虽然宇宙图像带来了极强的视觉震撼与审美愉悦，但本文的深层价值在于对红外探测技术原理的深度解析。它详尽阐述了观测分辨率与波长覆盖如何驱动科学发现的质变，是一份关于现代天文学前沿观测手段的硬核知识总结。</t>
+  </si>
+  <si>
+    <t>[🌿 愉悦身心: 45, 🌍 开阔眼界: 55, 🔭 了解新知: 60] 虽然文章从知名主持人的观察切入，但其核心价值在于将日常社交行为上升到了哲学高度。通过引入关于“承认”与“自我意识”的深度思辨，揭示了沟通背后隐藏的权力结构与存在主义焦虑，因此定调为激发思维。</t>
+  </si>
+  <si>
+    <t>[🌿 愉悦身心: 20, 🌍 开阔眼界: 55, 💡 激发思维: 75] 核心内容是硬核的天体物理科普，详细解析了引力透镜的不同视觉呈现及其背后的物理机制，知识密度极高，逻辑链条清晰，因此定调为“了解新知”。</t>
+  </si>
+  <si>
+    <t>[🌿 愉悦身心: 25, 🌍 开阔眼界: 65, 💡 激发思维: 85, 🔭 了解新知: 70] 虽然文章提及了多位文学名家的轶事（Knowledge），但其核心价值在于深度剖析了人类在面对模糊现实时强行构建秩序的心理机制。文章通过揭示“模式猎取”与“确认偏误”等逻辑缺陷，探讨了文化骗局如何演变为社会危害，具有极强的思辨深度与批判意识。</t>
+  </si>
+  <si>
+    <t>[🌿 愉悦身心: 35, 🌍 开阔眼界: 65, 🔭 了解新知: 70] 核心价值在于对AI时代学习本质的深度反思。它挑战了“知识获取即学习”的流行观念，将导师制提升到“陪伴与共同成长”的哲学高度，并对书籍作为认知技术的本质进行了重新定义，逻辑严密且极具启发性。</t>
+  </si>
+  <si>
+    <t>[愉悦身心: 20, 开阔眼界: 65, 激发思维: 85] 这篇文章的核心价值在于对经典科学误区的硬核修正。它不仅提供了关于量子场论在弯曲时空中表现的准确知识框架，还深刻反思了科学传播中过度简化带来的认知偏差，具有极高的知识增益价值。</t>
+  </si>
+  <si>
+    <t>[愉悦身心: 10, 开阔眼界: 60, 了解新知: 85] 核心在于对人工智能本质的哲学与逻辑思辨，挑战了流行的“随机鹦鹉”假说，引导读者反思智能与表征的底层逻辑，因此定调为激发思维。分数较高是因为其论证有力，切中了当前技术前沿最核心的认知争议。</t>
+  </si>
+  <si>
+    <t>[愉悦身心: 20, 开阔眼界: 60, 激发思维: 75] 文章系统地梳理了摩擦学从工业故障处理到独立学科的演化路径，提供了硬核的科学史视角，对理解现代工业的底层逻辑有极高的知识价值。</t>
+  </si>
+  <si>
+    <t>[激发思维: 85, 了解新知: 95, 开阔眼界: 50, 愉悦身心: 20] 该文章属于硬核天文物理科普，核心价值在于清晰地解析了“哈勃张力”这一前沿科学难题，并详细介绍了利用引力透镜观测超新星这一复杂的技术路径。其逻辑严密、知识密度高，是典型的知识增量型深度内容。</t>
+  </si>
+  <si>
+    <t>[🌿 愉悦身心: 45, 🌍 开阔眼界: 65, 🔭 了解新知: 75] 本文的核心价值在于其深刻的洞察力。它跳出了单纯的技术讨论，深入探讨了在自动化时代人类主体性的重构。其关于“意义创造”作为未来核心竞争力的论述，极具哲学深度和批判性，能够引发读者对技术与人本质关系的底层思考。</t>
+  </si>
+  <si>
+    <t>[🌿 愉悦身心: 15, 🌍 开阔眼界: 75, 🔭 了解新知: 70] 文章并非简单的时政新闻，而是深入剖析了科技精英政治立场背后的利益博弈与意识形态重组。它揭示了人工智能作为一种颠覆性力量，如何迫使传统政治光谱发生位移，并为未来社会契约的重构提供了战略思考，具有极强的思维启发性。</t>
+  </si>
+  <si>
+    <t>[愉悦身心: 20, 开阔眼界: 65, 了解新知: 80] 虽然文章涉及了AI行业趋势（Knowledge），但其核心价值在于挑战了“人机对立”的传统直觉，通过逻辑推演提出了“增强”而非“替代”的底层框架，引导读者重新审视劳动的主体性，具有极强的思辨深度。</t>
+  </si>
+  <si>
+    <t>[🌿 愉悦身心: 30, 🌍 开阔眼界: 65, 💡 激发思维: 90, 🔭 了解新知: 70] 核心价值在于对“概率”与“可能性”这一对底层逻辑的深度剖析，以及对“故事思维”这一认知工具的提炼。它挑战了权威的认知边界，为创新提供了哲学层面的方法论支撑，而非单纯的历史叙述或技术科普。</t>
+  </si>
+  <si>
+    <t>[了解新知: 90, 开阔眼界: 70, 激发思维: 65, 愉悦身心: 55] 文章核心在于解析通过高能物理手段（X射线）对超新星遗迹进行的定量分析和物理机制研究，属于极佳的硬核科普。虽然涉及了从古典天文学到现代科学的历史跨度，但最终落脚点在于现代空间科学对白矮星爆炸本质的知识产出，故定调为“了解新知”。</t>
+  </si>
+  <si>
+    <t>[愉悦身心: 20, 开阔眼界: 65, 激发思维: 85] 本文属于硬核宇宙学科普，系统梳理了宇宙从微观种子涨落到宏观“宇宙网”的演化逻辑。其核心价值在于提供了清晰的物理框架和前沿的科研动态，解释了精密观测如何验证理论模型，因此定调为“了解新知”。</t>
+  </si>
+  <si>
+    <t>[🌿 愉悦身心: 40, 🌍 开阔眼界: 75, 💡 激发思维: 65] 文章核心在于介绍天体生物学的前沿研究方法，即利用微生物色素作为探测系外行星生命的新型生物特征。它提供了具体的科学模型和技术路径，属于硬核科普与行业趋势的范畴，具有极高的知识含金量。</t>
+  </si>
+  <si>
+    <t>[🌿 愉悦身心: 20, 🌍 开阔眼界: 75, 💡 激发思维: 85] 本文的核心价值在于清晰地解析了“引力束缚”这一物理概念及其在宇宙演化中的判定标准。虽然文章末尾上升到了对宇宙终极命运的哲学思考，但其主体部分是严谨的硬核科普，旨在为读者构建关于宇宙宏观结构的物理认知框架，故定调为“了解新知”。</t>
+  </si>
+  <si>
+    <t>[🌿 愉悦身心: 20, 🌍 开阔眼界: 75, 🔭 了解新知: 65] 文章通过对“癔症”这一医学概念的深度剖析，揭示了社会权力结构如何通过话语体系重塑生理事实。虽然涉及医学史知识，但其核心价值在于引导读者反思医学客观性背后的性别偏见与底层逻辑，具有极强的思辨性。</t>
+  </si>
+  <si>
+    <t>[🌿 愉悦身心: 15, 🌍 开阔眼界: 72, 🔭 了解新知: 55] 本文的核心价值在于其深刻的技术哲学批判。它不仅讨论了AI的技术演进，更揭示了技术叙事如何通过重塑人类的时间感，进而瓦解了现代文明赖以生存的长期主义基石。其逻辑严密且视角犀利，极具思想冲击力。</t>
+  </si>
+  <si>
+    <t>[激发思维: 85, 开阔眼界: 50, 愉悦身心: 10] 尽管文章涉及深度的哲学思辨（Thinking），但其核心落脚点在于通过物理学基本概念（速率、时空连续性）来拆解并解决一个具体的科学/逻辑难题，具有极强的科普价值和知识增量，故定调为 了解新知。分数较高是因为它清晰地界定了数学抽象与物理现实的边界。</t>
+  </si>
+  <si>
+    <t>[🌿 愉悦身心: 20, 🌍 开阔眼界: 55, 💡 激发思维: 75] 这是一篇硬核的天文学前沿报道。文章的核心价值在于通过最新的空间望远镜观测数据，修正了人类对早期宇宙物质构成的认知。虽然涉及科学范式的挑战（Thinking），但其主要贡献在于提供了关于尘埃形成和金属丰度的具体科学知识，具有极高的信息密度。</t>
+  </si>
+  <si>
+    <t>[🌿 愉悦身心: 20, 🌍 开阔眼界: 45, 💡 激发思维: 75] 尽管文章对当前培训乱象有深刻的批判性反思，但其核心价值在于为组织管理者提供了一套完整、可落地的“六要素”管理框架和方法论，具有极强的专业知识属性和结构化工具价值，故定调为 了解新知。</t>
+  </si>
+  <si>
+    <t>[🌿 愉悦身心: 55, 🌍 开阔眼界: 78, 🔭 了解新知: 85] 文章虽梳理了书籍从泥板到抄本的物理演化（Knowledge），但其核心价值在于将“书籍”这一传统媒介重新定义为一种极其成功的“信息技术”。通过在生成式AI兴起的当下，重新审视人类认知、批判性思维与主观经验的独特性，文章完成了对底层逻辑的重构，在激发思维维度表现卓越。</t>
+  </si>
+  <si>
+    <t>[愉悦身心: 45, 开阔眼界: 75, 激发思维: 65] 文章的核心价值在于披露了一项重大的考古发现，并提供了关于新石器时代工程能力和地质变迁的硬核知识。虽然涉及神话原型（Perspective）和人类记忆（Thinking）的探讨，但其论证基石是基于实证的科学研究与考古发现。</t>
+  </si>
+  <si>
+    <t>[🌿 愉悦身心: 25, 🌍 开阔眼界: 68, 💡 激发思维: 82] 本文的核心价值在于提供高密度的硬核天文知识，通过严密的物理逻辑纠正了大众媒体对科学发现的误读。它清晰地阐述了恒星演化与元素合成的底层机制，具有极强的科普教育意义。</t>
+  </si>
+  <si>
+    <t>[愉悦身心: 20, 开阔眼界: 40, 激发思维: 75] 这是一篇标准的硬核科普文章。虽然它引导读者对宇宙对称性进行了深度思考（Thinking），但其核心价值在于系统性地梳理了从牛顿力学到广义相对论关于引力本质的科学解释，并清晰地界定了“负质量”与“时空曲率”等物理概念，具有极高的知识科普价值。</t>
+  </si>
+  <si>
+    <t>[🌿 愉悦身心: 55, 🌍 开阔眼界: 80, 🔭 了解新知: 70] 本文的核心价值在于对启蒙运动以来二元论认知体系的深刻批判，以及对人类文明异化力量的底层逻辑反思。虽然涉及艺术展讯，但其思辨深度远超一般的观展指南，故定调为“激发思维”。</t>
+  </si>
+  <si>
+    <t>传统手工艺中的匠心修行与临场感体验</t>
+  </si>
+  <si>
+    <t>核心生活技能的持续精进与跨学科底层逻辑构建</t>
+  </si>
+  <si>
+    <t>跨领域转型的心理机制与可持续行为体系的构建</t>
+  </si>
+  <si>
+    <t>“静眼”视觉训练与注意力管理机制</t>
+  </si>
+  <si>
+    <t>精英冒险行为中的身份认同、精通感与风险理性化机制</t>
+  </si>
+  <si>
+    <t>复杂空间记忆训练对大脑结构重塑与认知储备的影响</t>
+  </si>
+  <si>
+    <t>斯多葛哲学中的控制二分法与神经科学对意志主宰的跨学科解读</t>
+  </si>
+  <si>
+    <t>暗物质探测的认知极限与“噩梦情景”假设</t>
+  </si>
+  <si>
+    <t>专家跨界发言的认知偏差与智力谦逊</t>
+  </si>
+  <si>
+    <t>宇宙极端异常天体与天文分类范式的挑战</t>
+  </si>
+  <si>
+    <t>灭绝物种的科学再现与历史遗存的脆弱性</t>
+  </si>
+  <si>
+    <t>自足体验与内在驱动的成功观：从结果导向转向过程卓越与技能磨炼</t>
+  </si>
+  <si>
+    <t>太空图像驱动的“非地球视角”认知转换与地球共同体意识</t>
+  </si>
+  <si>
+    <t>职场社交基础设施建设与系统性孤独治理</t>
+  </si>
+  <si>
+    <t>宇宙观测尺度与时空演化的层次性</t>
+  </si>
+  <si>
+    <t>阅读、写作与思考的共生机制及原创性的生成逻辑</t>
+  </si>
+  <si>
+    <t>宇宙膨胀与星系红移的尺度博弈机制</t>
+  </si>
+  <si>
+    <t>身份标签的心理机制与认知重构</t>
+  </si>
+  <si>
+    <t>怀旧情绪的病理化历史与医学异化</t>
+  </si>
+  <si>
+    <t>卫星定位技术的演进、相对论修正与地球引力建模</t>
+  </si>
+  <si>
+    <t>太阳辐射风暴的物理机制与极光形成</t>
+  </si>
+  <si>
+    <t>探讨“否认”作为心理防御机制在对抗限制性设定与重塑个体能动性中的建设性价值。</t>
+  </si>
+  <si>
+    <t>理论物理中的证伪价值与科学边界的划定</t>
+  </si>
+  <si>
+    <t>AI协作环境下的员工心理安全感与动态反馈机制</t>
+  </si>
+  <si>
+    <t>红外天文观测技术与深空宇宙图景的重构</t>
+  </si>
+  <si>
+    <t>社交对话中的验证心理与承认欲求</t>
+  </si>
+  <si>
+    <t>引力透镜效应的几何形态与宇宙质量分布的非对称性</t>
+  </si>
+  <si>
+    <t>文学阴谋论的生成心理、逻辑谬误及其社会影响</t>
+  </si>
+  <si>
+    <t>AI时代下的导师制度、共同成长与认知技术反思</t>
+  </si>
+  <si>
+    <t>黑洞霍金辐射的物理机制与科学传播中的模型误区</t>
+  </si>
+  <si>
+    <t>生成式人工智能的底层认知机制：探讨模式匹配与逻辑推理的本质区别</t>
+  </si>
+  <si>
+    <t>摩擦学的跨学科起源与表面科学的演进</t>
+  </si>
+  <si>
+    <t>宇宙膨胀速率测量争议与基于引力透镜效应的独立验证方法</t>
+  </si>
+  <si>
+    <t>AI 驱动的组织变革与人类意义的回归</t>
+  </si>
+  <si>
+    <t>科技产业的政治版图重构与人工智能监管博弈</t>
+  </si>
+  <si>
+    <t>人工智能辅助下的工作范式转型与人类价值重塑</t>
+  </si>
+  <si>
+    <t>突破性创新的认知逻辑：区分概率与可能性</t>
+  </si>
+  <si>
+    <t>超新星遗迹的长期动态观测与恒星演化研究</t>
+  </si>
+  <si>
+    <t>宇宙大尺度结构的演化机制与暗能量探测</t>
+  </si>
+  <si>
+    <t>系外行星生物色素探测与云层生命特征研究</t>
+  </si>
+  <si>
+    <t>宇宙膨胀背景下的引力束缚机制与天体归宿</t>
+  </si>
+  <si>
+    <t>医学史上“癔症”概念的演变及其对现代女性健康认知的系统性偏见</t>
+  </si>
+  <si>
+    <t>人工智能引发的时间压缩效应与长期制度建设的消解</t>
+  </si>
+  <si>
+    <t>空间无限可分性下的运动本质探讨</t>
+  </si>
+  <si>
+    <t>早期宇宙尘埃的形成机制与观测模型修正</t>
+  </si>
+  <si>
+    <t>企业领导力开发的系统化转型与六大核心构建要素</t>
+  </si>
+  <si>
+    <t>书籍作为信息技术的演化史及其在AI时代的认知价值</t>
+  </si>
+  <si>
+    <t>史前水下遗迹与失落文明神话的现实原型</t>
+  </si>
+  <si>
+    <t>极早期星系的化学演化与重元素起源</t>
+  </si>
+  <si>
+    <t>引力的单向吸引本质与反重力的物理局限</t>
+  </si>
+  <si>
+    <t>当代艺术对人类中心主义的反思与人地关系的重构</t>
+  </si>
+  <si>
+    <t>探讨了传统手工艺如何通过对极致精度的追求，将机械重复的制造过程转化为一种深刻的冥想实践。其核心逻辑在于，“精通”并非仅仅是技能的达标，而是一种对工作对象的极致“关怀”，这种投入能让个体在行动中获得完全的“临场感”。当劳作不再是达成目的的手段，而是通往“当下”的路径时，物质的创造便与内在的修行合而为一。这种视角重新定义了现代语境下的劳动价值，揭示了在效率至上的社会中，通过专注与磨炼重塑精神秩序的可能性。</t>
+  </si>
+  <si>
+    <t>探讨“精进”作为一种动态生命状态的本质，强调核心生活技能并非一蹴而就的终点，而是需要通过跨学科视野不断打磨的底层能力。通过整合语言表达的精确性、数据逻辑的批判性、认知偏差的自我审视，以及权力、竞争与内在心智的战略性思考，构建一套应对现代复杂生存环境的理性框架。它不仅关乎工具性的技能提升，更指向一种深度的思维重塑，旨在引导个体在多变的世界中，利用经过时间检验的经典智慧，建立起稳固的决策逻辑与内在秩序。</t>
+  </si>
+  <si>
+    <t>探讨个体在面对重大转型时，如何打破“全有或全无”的极端心理模式。文章剖析了失控状态的心理同构性，指出单纯依靠意志力的改变往往难以持续。其核心洞察在于“问责结构”的建立，即将成熟职业领域中的反馈与责任机制，精准平移至个人健康管理等新领域。这种逻辑迁移不仅是行为层面的重塑，更是对底层心理架构的重组。通过识别并利用已有的成功逻辑，个体得以对抗人性的周期性疲软，实现从自我消解到深度掌控的跨越，为理解习惯养成与跨界转型提供了深刻的认知框架。</t>
+  </si>
+  <si>
+    <t>本文深入解析了神经心理学中的“静眼”（Quiet Eye）现象，揭示了视觉注视与大脑预备状态之间的生理联系。通过分析顶尖运动员和外科医生在极端压力下的表现，文章阐述了如何通过在执行关键动作前保持稳定且持续的视觉聚焦，来优化大脑的认知资源分配并抑制干扰。这种技术不仅能显著提升身体动作的精准度，更揭示了通过生理行为反向调节心理状态的可能性。在碎片化信息过载的当下，这种视觉聚焦训练为解决注意力涣散提供了科学的干预路径，将原本属于竞技体育的专业技能转化为一种通用的认知增强工具，帮助个体在复杂环境中夺回对注意力的掌控权。</t>
+  </si>
+  <si>
+    <t>探讨精英冒险者在追求极致掌控力过程中的心理异化。当个体的自我价值与“精通极限”深度绑定，风险便不再是单纯的物理威胁，而演变为一种维护荣誉与身份认同的社会化成本。这种机制揭示了成功如何反向推高风险门槛：为了逃避失败带来的羞耻感，并维持在特定社交圈层中的认可，个体往往会通过理性化手段掩盖极端危险，甚至将致命威胁视为达成目标的合理代价。这种心理结构解释了为何顶尖高手在达到巅峰后仍难以止步，深刻反思了现代社会中“成功”与“自我实现”如何扭曲人类基本的生存本能，将生命意义与极限掌控进行危险的捆绑。</t>
+  </si>
+  <si>
+    <t>探讨人类大脑在成年期展现出的惊人神经可塑性，重点分析高强度空间导航训练如何诱发脑部物理结构的重塑。通过对海量街道布局、地标建筑及复杂路径的深度记忆，大脑相关区域会发生形态学改变，从而显著提升个体的认知储备。这种生理层面的优化不仅揭示了复杂学习任务对神经系统的重构机制，更在医学层面为预防神经退行性疾病提供了实证支持。它强调了持续的、高挑战性的认知活动在维持大脑健康和延缓认知衰退中的核心作用，为理解人类智力潜能提供了科学视角。</t>
+  </si>
+  <si>
+    <t>探讨“精通”的本质，将其从对外部环境的征服转向对内在判断力的绝对掌控。通过剖析意志、倾向与欲望的底层逻辑，揭示了人类在面对不可控的外部世界时，如何通过磨炼核心判断力来构建稳固的自我。这种视角将古老的哲学智慧与现代认知科学中的执行功能相印证，强调了在刺激与反应的微小间隙中，通过理性调控实现人格的完整与统一。它不仅是对一种生活态度的阐述，更是对人类主体性如何在生物学限制与命运无常中突围的深度思辨，最终指向一种基于自我主宰的、不随境遇迁徙的终极自由。</t>
+  </si>
+  <si>
+    <t>深入解析现代天体物理学中关于暗物质探测的严峻困境。尽管引力透镜效应和宇宙微波背景辐射等间接证据强力支撑了暗物质的存在，但地面实验室的直接探测始终未能发现其与普通物质之间除引力外的任何相互作用。这种现状指向了科学界最担忧的“噩梦情景”：即暗物质可能永远无法通过电磁或弱核力手段被捕捉。这一论述清晰地勾勒出粒子物理学的实验瓶颈，揭示了人类在试图理解宇宙基本构成时可能遭遇的永久性认知屏障，标志着科学探索正从寻找具体的粒子实体，转向对不可见的“引力阴影”进行更深层的理论构建。</t>
+  </si>
+  <si>
+    <t>探讨专家群体在跨越学科边界时产生的认知错觉，即误以为在特定领域的卓越成就可转化为全知全能的判断力。这种“认知越界”揭示了人类理性的局限性：当个体过度依赖过往的智力成功，往往会忽视不同学科间底层逻辑的差异，从而在陌生领域产生“能力迁移”的幻觉，并散布缺乏证据支撑的误导性信息。通过对智力傲慢与智力谦逊的辩证分析，剖析了知识碎片化时代下，个体如何通过清晰识别认知边界来维护思维的严谨性。它强调了在复杂系统中保持对专业分工的敬畏，并提出将话语权让渡给真正具备专业证据的领域专家，是构建健康公共理性空间的关键。</t>
+  </si>
+  <si>
+    <t>通过先进太空望远镜的深度观测，天文学界发现了九个被形象地称为“宇宙鸭嘴兽”的极端天体。这些天体的核心特征在于其物理属性的“不可能组合”：它们在单一实体上集成了多种在现有天体物理模型中互斥的特征，彻底打破了现行的星系与恒星演化分类逻辑。这一发现不仅是单一观测数据的偶然异常，更是对现行宇宙演化理论框架的根本性挑战。通过解析这些天体在光谱、质量与演化阶段上的矛盾表现，揭示了人类在理解早期宇宙结构形成时存在的重大认知盲区，预示着天文学范式可能面临的重构，为探索宇宙中尚未被定义的物质形态提供了关键的实证依据。</t>
+  </si>
+  <si>
+    <t>本文深入解析了大型半水生肉食恐龙——棘龙的科学发现与认知重构历程。核心探讨了科学实物标本在人类冲突中遭遇毁灭性打击后，如何导致一个物种在学术视野中经历长达数十年的“物理性消失”。通过梳理从早期形态学认知的建立，到关键正模标本的丧失，再到现代古生物学利用新出土证据进行的范式修正，文章揭示了科学知识体系的脆弱性与韧性。它不仅介绍了该物种独特的解剖学特征与演化地位，更展示了在缺乏连续实物证据的情况下，跨时代的考古调查如何通过逻辑推演与新技术手段，重新拼凑并还原史前生命的真相，实现科学遗产的跨时空修复。</t>
+  </si>
+  <si>
+    <t>探讨现代社会中成功定义的异化，分析为何单纯追求名利等外部奖赏会导致道德脱节与内心匮乏。通过引入心理学中的“自足体验”概念，论证了将活动本身视为目的而非手段的重要性。这种思维方式强调在充满不确定性的外部评价体系中，通过对精湛技能的极致追求和对工作过程的纯粹投入，构建一个稳固的内在价值锚点。它解构了结果导向的功利主义，提倡一种以工匠精神为核心的、自给自足的卓越路径，从而在波动的现实中获得持久的心理确定性与职业尊严。</t>
+  </si>
+  <si>
+    <t>探讨人类如何通过太空图像跨越生理极限，在无法亲临宇宙的情况下，借助“非地球视角”重新审视家园。这些视觉记录不仅是科技的产物，更是深刻的人文叙事，揭示了地球在浩瀚星辰中渺小、脆弱且无国界的真实状态。这种视角的剧变挑战了长期以来的自我中心主义，促使我们从宏观维度思考人类作为一个整体的命运。它描述了一场由技术中介引发的集体觉醒，让身处地表的人们在凝视深空的同时，生发出一种超越族群界限的责任感与对生命共同体的深刻认同。</t>
+  </si>
+  <si>
+    <t>探讨现代社会中普遍存在的孤独感，将其定义为一种系统性故障而非个人能力的缺失。文章深入剖析了人生转折、文化变迁等结构性因素如何瓦解个体的社交网络，并提出一种激进的视角转变：将职场视为重建社会联结的核心基础设施。这种思维方式要求组织领导者超越传统的绩效管理，转而承担起“系统设计师”的职责，通过重塑工作环境的互动逻辑，对抗宏观环境带来的情感异化与联结断裂。这不仅是对管理学的反思，更是对当代社会结构性缺失的深刻回应。</t>
+  </si>
+  <si>
+    <t>本文系统地解析了宇宙观测中的尺度效应，阐明了观测距离如何决定我们所见物质的物理本质。从近处的行星动力学系统出发，跨越银河系的恒星分布，直至触及遥远的类星体与黑洞等高能天体。其核心逻辑在于揭示空间跨度与时间回溯的内在关联：随着视线向深空延伸，观测对象从成熟的天体系统转变为宇宙早期的演化遗迹。通过梳理这一从局部到整体的认知路径，文章构建了一个清晰的宇宙学演化框架，揭示了宇宙在不同空间尺度下表现出的物理异质性，以及最终抵达宇宙诞生初期‘背景辐射’这一时空边界的科学必然性。</t>
+  </si>
+  <si>
+    <t>探讨阅读、写作与思考之间的深层共生关系，挑战“写作仅是思想输出”的传统观念。文章提出写作本质上是一个将模糊直觉转化为严谨逻辑的认知澄清过程，而广泛阅读则是这一过程不可或缺的“原材料”供应。原创性在此被重新定义为对既有知识材料的组合、类比与反思。通过在创作中保持与外部思想的持续碰撞，写作者不仅能增强自身论点的韧性，更能通过建立参照系来确立个人声音的独特性。这是一种关于认知生产力的底层逻辑分析，强调了高质量输入对思维深度与表达力度的决定性作用。</t>
+  </si>
+  <si>
+    <t>本文深入解析了宇宙学中红移现象占据主导地位的底层物理逻辑。通过对比局部引力驱动的“本征速度”与全局空间膨胀引发的“哈勃流”，揭示了尺度在宇宙演化中所扮演的决定性角色。在较小的空间尺度内，星系间的引力相互作用具有随机性，足以产生朝向观测者的蓝移运动；然而，随着观测距离的增加，空间膨胀带来的退行速度会随之线性增强，最终在宏观尺度上彻底压倒星系的随机运动。这种机制清晰地划定了微观引力扰动与宏观膨胀背景之间的物理边界，为理解宇宙从局部混乱到整体有序膨胀的动力学结构提供了结构化的知识路径。</t>
+  </si>
+  <si>
+    <t>探讨大脑在构建身份认同时的固化倾向及其对个体潜力的束缚。人类大脑为了节省认知资源，往往将偶然的碎片化评价或瞬间经验固化为永恒的身份标签，并将其误认为不可逾越的客观真理。这种机制虽然提供了秩序感，却也形成了心理上的枷锁。通过深入分析“认知重构”的逻辑，揭示了改变大脑对身份片段的解释方式，而非改变本质，才是打破自我设限的关键。这一过程要求个体主动识别并更替那些限制性的语言，引导大脑从封闭的固化状态转向开放的进化状态，在认知的裂缝中寻找持续成长的可能性，实现从被动定义到主动演进的思维跃迁。</t>
+  </si>
+  <si>
+    <t>本文深入解析了“怀旧”这一情感概念在医学史上的异化过程。在现代心理学将其定义为一种苦乐参半的心理状态之前，它曾被视为一种足以导致高烧甚至死亡的致命生理疾患。通过梳理早期医学档案，揭示了当时如何利用“动物精气”损耗来解释思乡带来的躯体衰竭，并详细记录了从物理环境干预到极端肉体惩戒的治疗演变：从最初的热水浴，演变为放血、火钳恐吓甚至活埋威胁。这种对精神现象的粗暴躯体化解读，不仅展现了早期医学在处理心智问题时的认知局限，也反映了医学权力如何通过暴力手段对个体情感进行规训与矫正，为理解人类情感的病理化历史提供了清晰的知识框架。</t>
+  </si>
+  <si>
+    <t>深入解析全球定位系统的技术底层逻辑，探讨从传统地形匹配到卫星网络定位的范式转移。核心内容涵盖了物理学理论在工程实践中的关键应用，特别是如何通过修正狭义与广义相对论引起的时间膨胀与引力效应，来消除每日数公里的定位误差。文章重点阐述了地球作为非规则球体其引力场分布的不均匀性对导航精度的挑战，以及通过海量数据编程构建精确坐标基准——大地水准面模型的必要性。这一知识框架揭示了深奥的理论物理如何转化为支撑现代社会运行的全球性基础设施，展现了数学计算在刻画地球物理形态与实现精准导航中的决定性作用。</t>
+  </si>
+  <si>
+    <t>深入解析太阳作为系内主导天体对空间天气的塑造作用，重点探讨太阳辐射风暴这一罕见且强力的能量释放事件。通过对比太阳耀斑与日冕物质抛射的差异，阐述高能带电粒子流如何与地球磁场发生剧烈相互作用，并最终转化为宏观的极光奇观。内容涵盖了太阳物理属性、粒子运动能级以及地球电磁环境的响应机制，旨在揭示天文现象背后的底层物理逻辑与周期性规律，为理解复杂的天体物理互动提供结构化的知识框架，帮助读者建立对宇宙能量交换过程的深度认知。</t>
+  </si>
+  <si>
+    <t>深度剖析心理学中常被误解为逃避行为的“否认”机制，揭示其在构建心理韧性过程中的积极异化。文章提出一种“建设性否认”的逻辑，即通过拒绝接受外界强加的“限制性设定”，个体得以保护核心价值观不受负面现实的侵蚀。这种视角挑战了将韧性视为被动承受的传统认知，将其重塑为一种基于深度抉择的主动防御。通过分析从“受害者”到“行动者”的身份认知转变，揭示了在极端约束环境下，如何通过重塑自我认知来扩张行动边界，从而在逻辑上完成从心理防御到能动性爆发的闭环，为理解人类在困境中的主体性提供了深刻的哲学思考。</t>
+  </si>
+  <si>
+    <t>本文深入探讨了科学进步的本质，挑战了“只有证实新发现才算成功”的传统认知。它聚焦于理论物理学中那些被低估的“负面结果”，即通过实验数据对弦论、超对称及大统一理论等扩展模型进行的严密约束与证伪。这种“排除法”的进步，虽然缺乏发现新粒子的轰动效应，却是通过不断缩小真理的可能范围，为人类认知宇宙运行机制划定了坚实的边界。文章揭示了在广义相对论与标准模型的高墙之下，科学如何通过数据驱动的证伪过程，在复杂理论体系中剔除错误的路径，从而实现认知的精确化。这不仅是物理学的技术演进，更是一场关于科学哲学底层逻辑的深刻反思，强调了“知道什么是不可能的”与“发现什么是可能的”具有同等重要的认知价值。</t>
+  </si>
+  <si>
+    <t>探讨在人工智能深度介入生产力的背景下，组织管理逻辑的底层重构。文章批判了将员工福祉视为事后奖赏的传统偏见，转而提出一种基于“心理安全感”的系统反馈模型。它揭示了技术效能与人类情感指标之间的深层耦合：在高度不确定的变革期，幸福感并非虚无的感性诉求，而是校准算法落地与流程正义的动态传感器。通过建立“测量-满足-重复”的闭环，组织能够将抽象的情绪波动转化为具象的导航信号，从而在算法驱动的效率竞赛中，守住协作的透明性与人的主体价值，确保技术进化不以牺牲人的心理根基为代价。</t>
+  </si>
+  <si>
+    <t>解析红外天文观测的核心原理，探讨空间望远镜如何利用近红外与中红外波段穿透星际尘埃，揭示恒星诞生、星系演化及深空结构的精细特征。重点梳理观测技术——包括分辨率提升与波长覆盖扩展——如何作为科学发现的先导，重构人类对早期宇宙及极端天体物理现象的认知框架。通过对比不同波段的成像差异，展示现代天文学在捕捉微弱光子信号与解析复杂宇宙组分方面的最新进展，为理解宇宙的物质分布与演化脉络提供严谨的知识支撑。</t>
+  </si>
+  <si>
+    <t>探讨人类在社交互动中对“验证”的本质渴求。文章揭示了一个深刻的心理现象：无论个体的社会地位如何，在表达自我的瞬间，其内心深处都潜藏着一种被他者确认的焦虑。这种需求并非单纯的虚荣，而是源于自我意识必须通过他人的承认才能得以确立的底层逻辑。通过分析对话背后的潜台词，揭示了沟通不仅是信息的流动，更是一场关于存在价值的社会性博弈。当人们在询问“我表现得如何”时，实际上是在寻求一种存在感的锚定。这种对承认欲求的深度剖析，为理解人际关系的脆弱性与深层连接的建立提供了严密的逻辑支撑，引导读者反思社交行为中“被看见”的本质意义。</t>
+  </si>
+  <si>
+    <t>深入解析广义相对论在宇宙尺度下的视觉奇观，探讨大质量天体如何通过引力场弯曲光线，形成引力透镜效应。重点剖析了理论上的完美对称——“环状结构”与现实观测中更为普遍的“十字构型”之间的几何差异。通过对透镜体质量分布非对称性、星系椭圆率以及光源对齐精度的分析，揭示了宇宙物质分布的真实形态。这不仅是一次关于时空曲率的科普，更是对宇宙非完美性与复杂动力学结构的系统梳理，帮助读者建立起从宏观引力理论到具体天文观测图像的逻辑链接，理解光线在扭曲时空中的行进轨迹。</t>
+  </si>
+  <si>
+    <t>探讨人类在面对文学史中的空白与模糊时，如何通过强行构建“阴谋”来获取一种虚假的秩序感。这种行为并非严谨的学术推演，而是一种深层的心理补偿机制，反映了认知主体在混乱现实中对“意义”的过度渴求。通过分析模式猎取与确认偏误，揭示了文学阴谋论如何从无害的娱乐演变为扭曲文化真实性、甚至煽动社会仇恨的工具。它警示我们，对文本的过度解读若脱离了事实根基，不仅会消解文学本身的复杂性，更可能成为操纵大众认知与重塑历史叙事的危险武器，从而威胁到整个社会的理性根基。</t>
+  </si>
+  <si>
+    <t>深入探讨了在人工智能高度抽象化知识的背景下，为何传统的导师制度与人际互动依然是不可替代的成长基石。文章有力地挑战了“孤立学习”的效率幻觉，指出真正的“精通”并非源于单纯的信息获取，而是建立在长期的人际陪伴与共同实践之上。通过将书籍重新定义为一种深刻改变人类认知的“技术”，并剖析怀旧的心理功能与那些未经审视的认知假设，揭示了在算法驱动的时代，深度连接如何重塑我们的思维结构与成长路径。这种视角促使我们反思：在技术消解过程的当下，如何通过批判性思维与他者的镜像，找回学习的深度与生命的韧性。</t>
+  </si>
+  <si>
+    <t>本文深入解析了黑洞霍金辐射的真实物理图景，旨在纠正“虚粒子对掉入黑洞”这一流行但错误的简化类比。文章从量子场论与广义相对论的结合点出发，阐述了在极端弯曲的时空背景下，不同观测者对“真空”与“粒子”定义的差异性。这种辐射并非源于视界边缘的局部物质产生，而是量子场在全局引力场作用下的激发态响应，表现为黑洞通过释放低能光子来损耗自身的引力能。通过梳理从时空曲率到能量蒸发的逻辑链条，文章揭示了黑洞如何在漫长岁月中逐渐消亡的底层机制，展现了现代物理学在宏观引力与微观量子领域交汇处的深刻洞察。</t>
+  </si>
+  <si>
+    <t>探讨生成式人工智能的本质，质疑将其简化为概率统计工具的流行观点。通过分析大语言模型在处理未知任务时的表现，揭示其在海量数据训练中构建出的“内部模型”。这种模型并非简单的文本记忆，而是对现实世界深层概念的表征与逻辑泛化。文章深入剖析了智能的边界，追问复杂的模式匹配是否在量变中产生了质变，从而演化出类似人类的抽象理解与推理能力，从底层逻辑上挑战了关于人工智能仅仅是“随机鹦鹉”的传统认知。</t>
+  </si>
+  <si>
+    <t>聚焦于探讨摩擦、润滑与表面相互作用的科学演进。这一领域起源于工业生产中对机械失效问题的跨学科反思，成功融合了物理、化学与工程学的多元视角。它标志着人类对物体表面接触现象的认知，实现了从零散经验主义向系统化理论构建的范式转移。通过深入研究微观表面的动态变化与能量耗散，该学科不仅解决了设备损耗的实际难题，更确立了“表面科学”在现代工业体系中的核心地位，揭示了材料界面在复杂力学环境下的底层运行规律与技术边界。</t>
+  </si>
+  <si>
+    <t>本文深入解析了现代宇宙学中最为棘手的“哈勃张力”难题，即早期与晚期宇宙膨胀速率测量值之间存在的不可调和性。核心内容聚焦于一种创新的验证路径：利用大质量天体产生的引力透镜效应，捕捉远方超新星形成的多个成像。通过精确计算不同路径光线到达的时间延迟，科学家试图构建一套独立于传统距离阶梯和微波背景辐射的测量体系。这不仅是对宇宙膨胀参数的重新校准，更是对现行宇宙学标准模型的一次关键压力测试，旨在探究观测差异究竟源于系统误差，还是暗示了物理学底层规律的潜在重构。</t>
+  </si>
+  <si>
+    <t>探讨在代理型人工智能重塑组织协作逻辑的背景下，人类本质价值的范式转移。当算法接管了复杂的协调与执行任务，曾经作为企业“结缔组织”的逻辑处理能力将不再是稀缺资源。真正的变革在于，人类必须从单纯的执行者转变为意义的赋予者。这种转变要求个体在高度不确定的复杂系统中，具备驾驭悖论、在压力下即兴发挥以及从碎片化信息中构建连贯性的能力。这不仅是职业技能的更迭，更是一场关于在技术异化中重构主体性与价值观判断的深刻反思，强调了在逻辑闭环之外，人类处理模糊性与创造意义的不可替代性。</t>
+  </si>
+  <si>
+    <t>探讨科技产业核心地带的政治意识形态演变，分析技术进步与监管政策之间的深度张力。核心逻辑在于揭示科技精英如何在实用主义驱动下，将人工智能视为政治博弈的关键筹码，试图通过特定的政治导向来实现“监管套利”，以确保技术发展的绝对领先。这种转变并非简单的党派倒戈，而是对未来技术主导权的战略性重组。文章进一步思考了在技术加速主义的背景下，如何构建一种“技术积极型”的社会愿景，将人工智能的爆发式增长与社会共同繁荣、物质富足的宏观目标相结合，从而重塑技术与社会契约的关系，为应对颠覆性技术带来的社会动荡提供了底层逻辑支撑。</t>
+  </si>
+  <si>
+    <t>探讨在人工智能技术深度介入的背景下，劳动范式如何从“替代逻辑”转向“增强逻辑”。核心在于剖析人类在算法时代不可替代的生态位，即如何利用技术工具强化个体的判断力、创造力与临场感。这种转型不仅是工具的更迭，更是对工作本质的重构：将人类从机械重复中释放，转向高阶的、具备情感深度与复杂决策的独特贡献。它揭示了未来职场的竞争本质并非人与机器的博弈，而是掌握了技术杠杆的协作体对传统生产模式的降维打击，引导我们从社会结构层面反思技术异化背景下主体性的回归与升华。</t>
+  </si>
+  <si>
+    <t>深入剖析创新过程中的核心认知障碍，重点探讨人类如何容易陷入将“统计学上的低概率”等同于“物理上的不可能”的思维陷阱。通过对这种认知偏差的批判性反思，揭示了颠覆性变革往往源于对可能性逻辑的深刻洞察。文章提炼出一种“叙事化思考”的认知工具，强调通过构建严密的逻辑闭环来连接当下局限与未来愿景，从而超越既有技术范式与专家经验的束缚。这种思维方式不仅是解决复杂问题的策略，更是一种重塑现实、挑战既定规则的底层哲学，阐明了人类智力在面对未知领域时，如何通过逻辑重构而非单纯的数据计算来实现范式转移。</t>
+  </si>
+  <si>
+    <t>深入解析超新星爆发后的演化全景，重点探讨白矮星在剧烈爆炸后形成的遗迹如何与星际介质相互作用。通过对特定超新星遗迹长达四分之一个世纪的X射线成像监测，揭示了高能碎屑流与冲击波在空间中的动态扩张规律。这种研究不仅梳理了从早期肉眼观测到现代高能物理探测的技术跨越，更提供了关于恒星死亡、元素扩散以及星际空间能量传递的结构化知识框架。它展示了时域天文学在理解宇宙极端物理事件中的核心价值，通过长期的动态数据积累，将静态的星云图像转化为揭示物理本质的动态演化档案。</t>
+  </si>
+  <si>
+    <t>宇宙并非杂乱无章的物质堆砌，而是一张由引力与能量博弈织就的宏大网络。本主题深度解析了宇宙从极早期近乎均匀的量子涨落，如何历经百亿年的膨胀与坍缩，演变为今日观测到的纤维状大尺度结构。内容涵盖了“种子涨落”的物理起源、物质与能量在结构形成中的动力学作用，以及通过精密天文观测反推宇宙构成的科学方法。重点探讨了暗能量是否随时间演化这一前沿议题，旨在揭示宇宙膨胀速率背后的深层机制，为理解宇宙从微观起源到宏观终局的演化脉络提供坚实的知识框架。</t>
+  </si>
+  <si>
+    <t>探讨天体生物学领域中探测地外生命的新兴范式，重点分析生物色素（Biopigments）作为系外行星生物特征的科学潜力。不同于传统的化学气体分析，该研究聚焦于微生物产生的特定颜色信号，并构建了模拟这些信号的科学模型。文章详细解析了多云行星的大气环境如何从观测障碍转变为潜在的生命生境，提出云层本身可能孕育生命并放大生物信号的假说。这一知识框架为下一代空间望远镜的观测任务提供了具体的搜索图谱，涵盖了从微生物生理学到行星物理学的跨学科知识，揭示了寻找“空中生命”的技术路径与理论基础。</t>
+  </si>
+  <si>
+    <t>解析宇宙物理学中“引力束缚”的核心机制，探讨物体间的引力相互作用如何与宇宙空间的持续膨胀进行博弈。通过分析动能与引力势能的临界关系，界定天体系统维持稳定轨道或最终分道扬镳的物理边界。这种界限不仅决定了星系团等宏观结构的形成与演化，更揭示了宇宙物质分布的长期趋势：在不断扩张的时空背景下，哪些区域能通过引力锁定保持物质的聚集，哪些则会因无法克服膨胀力而永久失去联系。这为理解宇宙的终极图景提供了严谨的物理框架，阐明了空间扩张对万物可达性与宇宙结构存续的决定性影响。</t>
+  </si>
+  <si>
+    <t>本文深入探讨了医学史上“癔症”这一概念的建构过程，揭示了其如何从一种模糊的生理描述演变为压制女性身体经验的权力工具。通过对医学话语权与性别规范交织关系的剖析，文章指出，长期以来女性的真实痛感被系统性地误读为情绪波动，这种历史性的认知错位并未随着科学进步而彻底消散。它揭示了一个深刻的底层逻辑：医学诊断并非绝对客观的真理，而是深受社会结构与偏见影响的产物。文章引导我们思考，在现代医学体系中，那些被冠以“隐形疾病”之名的痛苦，究竟是生理上的未解之谜，还是社会文化对特定群体经验的集体性失聪。这种对科学客观性的批判性审视，为理解当代医疗中的性别不平等提供了重要的认知框架。</t>
+  </si>
+  <si>
+    <t>探讨人工智能作为一种“时间压缩器”如何从深层重塑人类的决策逻辑与生存状态。当社会被锁定在“技术乌托邦”或“末日审判”的极化叙事中，这种全有或全无的极端预期导致了中长期制度建设动力的彻底丧失。如果未来被视为瞬间降临的奇点，那么耗费数十年去构建的法律框架、文化积淀与稳固组织便失去了逻辑支撑。这种短视倾向进一步催生了社会性的投机心理与领导力的符号化转向，使人类在技术加速的洪流中逐渐丧失了进行跨代建设的能力与深思熟虑的定力，揭示了技术进步背后潜藏的文明结构性危机。</t>
+  </si>
+  <si>
+    <t>探讨经典哲学难题中关于运动可能性的终极追问。核心围绕“二分法”展开，即在逻辑上空间可以被无限次减半的前提下，物体如何跨越无穷的分割点抵达终点。解析过程从纯粹数学的无穷级数收敛，转向物理学视角的动态突破。重点阐述“速率”这一关键变量如何将离散的几何分割转化为连续的时空过程，揭示时间与距离的函数关系如何消解逻辑上的无限困境。这不仅是对一个延续两千年悖论的现代科学注脚，更是对物理现实与抽象逻辑之间鸿沟的深度梳理，旨在帮助读者建立起关于运动、时空与连续性的严谨认知框架。</t>
+  </si>
+  <si>
+    <t>本文深入解析了早期宇宙中星际尘埃的起源谜题。通过先进空间望远镜的深度观测，科学家发现远古星系的尘埃丰度远超传统理论预期，这一“过早且过量”的现象曾对现有的宇宙演化模型构成重大挑战。文章详细阐述了天文学家如何利用近邻的低金属丰度矮星系作为局部实验室，通过模拟极端物理条件来重新校准尘埃形成模型。研究揭示了在特定环境下，恒星演化产生尘埃的效率及其在星际介质中的存续逻辑。这一知识框架的更新，不仅完善了人类对第一代恒星形成后物质循环的理解，也为解析宇宙早期的化学演化与星系构建提供了关键的物理参数。</t>
+  </si>
+  <si>
+    <t>本文深度解析了企业领导力开发的范式转移，即从碎片化的短期培训转向系统化的能力培养体系。核心逻辑在于将领导力原则与组织具体情境深度对齐，并以此为基石构建六大互联要素：多维评估反馈、个性化成长路径、嵌入价值观的持续培训、具有挑战性的实战任务、基于反思的绩效教练，以及严谨的问责机制。通过梳理成人学习理论与系统思维在管理实践中的应用，文章为组织如何摆脱“三分钟热度”的培训困境、建立具有韧性的领导力文化提供了结构化的知识路径与实操框架，强调了发展必须嵌入日常工作流的底层逻辑。</t>
+  </si>
+  <si>
+    <t>探讨书籍作为一种被高度自然化、以至于被忽视的“信息技术”本质。通过追溯从泥板到抄本的物理形态演变，揭示媒介变革如何通过提升知识的可及性与协作性，深度重塑人类的认知结构与信息处理能力。在生成式AI重构信息生态的背景下，深度剖析了书籍在承载人类主观经验与培养批判性思维方面的不可替代性。它不应被视为单纯的内容容器，而是人类思维的延伸工具。通过对比算法导航与深度阅读的差异，强调了在数字化过载的时代，这种能够引发深度反思的“隐形技术”对于维持社会理性与个人主体性的核心意义。</t>
+  </si>
+  <si>
+    <t>这篇研究聚焦于新石器时代狩猎采集社会所建造的大型水下石质结构，有力地挑战了传统考古学关于早期人类社会协作能力的认知边界。通过对淹没于深海的建筑遗迹进行功能推测，揭示了史前人类在定居文明出现前便已具备复杂的工程规划与高度的集体行动力。同时，分析了海平面上升这一地质变迁如何将真实的地理灾难转化为“失落之城”的民间叙事。这种从物质遗存出发，结合地质学与民俗学的跨学科分析，为我们理解远古人类应对环境剧变的策略以及集体记忆的形成机制提供了严谨的知识框架与实证参考。</t>
+  </si>
+  <si>
+    <t>深入探讨宇宙极早期星系的化学丰度演化，解析大质量恒星如何通过极短的生命周期，在宇宙黎明时期迅速合成并播撒氧等重元素。文章纠正了大众对于“早期宇宙发现氧气”的认知偏差，阐述了重元素存在的逻辑必然性。核心内容涵盖了第三星族星的理论模型、红移观测中的光谱分析，以及寻找尚未被污染的“无氧星系”对于揭示宇宙起源的决定性意义。这是一次对宇宙从纯粹原始物质向复杂化学组成转变过程的系统性梳理，展现了现代天体物理学在触碰时间起点时的严谨与深刻。</t>
+  </si>
+  <si>
+    <t>本文深入探讨了物理学中引力作为单向吸引力的本质，解析了为何在已知宇宙中“反重力”仅存在于科幻构想之中。通过对比牛顿万有引力定律与爱因斯坦广义相对论，文章详细阐述了物质与能量如何通过弯曲时空产生引力效应。核心论点聚焦于引力与电磁力的根本差异：电磁力具有电荷的正负对称性，而引力因缺乏“负质量”或“负能量”实体，在宏观尺度上表现为独特的单向性。这种对时空几何与基本相互作用力的结构性解析，揭示了宇宙架构背后冷峻而严密的物理逻辑。</t>
+  </si>
+  <si>
+    <t>探讨当代艺术如何作为一种批判性媒介，介入并瓦解自启蒙时代以来根深蒂固的二元论认知框架。通过审视人类对自然资源的收编、控制以及由此产生的文明异化，揭示了人类中心主义在生态危机面前的局限性。文本试图寻找一种超越线性时间观的可能，引入地质时间的长程流动、原住民的土地智慧以及非人类视角的宏大叙事，以此重构人与环境的交融关系。这种思辨不仅是对艺术作品的解读，更是对现代性危机下人类文明如何“破而后立”的深度哲学拷问，旨在多元、非线性的维度中寻找文明与自然重新达成平衡的契机。</t>
+  </si>
+  <si>
+    <t>['匠人精神', '劳动哲学', '正念冥想', '传统工艺', '心流体验']</t>
+  </si>
+  <si>
+    <t>['底层逻辑', '认知升级', '终身学习', '经典阅读', '决策科学']</t>
+  </si>
+  <si>
+    <t>['行为心理学', '自我掌控', '逻辑迁移', '认知重构', '可持续改变']</t>
+  </si>
+  <si>
+    <t>['神经心理学', '注意力管理', '静眼技术', '认知控制', '运动科学']</t>
+  </si>
+  <si>
+    <t>['风险心理学', '身份认同', '成功学批判', '自我价值', '极限运动']</t>
+  </si>
+  <si>
+    <t>['神经可塑性', '认知储备', '空间记忆', '大脑健康', '科学科普']</t>
+  </si>
+  <si>
+    <t>['斯多葛学派', '认知科学', '意志力', '自我主宰', '哲学思辨']</t>
+  </si>
+  <si>
+    <t>['天体物理', '暗物质', '科学极限', '宇宙学', '粒子物理']</t>
+  </si>
+  <si>
+    <t>['认知心理学', '批判性思维', '智力谦逊', '知识论', '专家政治']</t>
+  </si>
+  <si>
+    <t>['天体物理', '科学范式', '宇宙演化', '分类学挑战', '前沿科技']</t>
+  </si>
+  <si>
+    <t>['古生物学', '科学史', '物种重构', '文化遗产保护']</t>
+  </si>
+  <si>
+    <t>['内在动机', '自足体验', '成功学反思', '工匠精神', '心理构建']</t>
+  </si>
+  <si>
+    <t>['宇宙观', '认知范式', '地球影像', '人类命运共同体', '空间哲学']</t>
+  </si>
+  <si>
+    <t>['社交孤立', '系统思维', '领导力转型', '职场文化', '社会结构']</t>
+  </si>
+  <si>
+    <t>['天文学', '宇宙演化', '时空观测', '科普', '深度认知']</t>
+  </si>
+  <si>
+    <t>['认知科学', '写作逻辑', '组合创新', '思维模型', '知识内化']</t>
+  </si>
+  <si>
+    <t>['宇宙学', '天体物理', '红移与蓝移', '哈勃常数', '空间膨胀']</t>
+  </si>
+  <si>
+    <t>['认知心理学', '身份认同', '自我成长', '思维模型', '重构策略']</t>
+  </si>
+  <si>
+    <t>['医学史', '心理病理学', '怀旧', '身体政治', '科学异化']</t>
+  </si>
+  <si>
+    <t>['GPS原理', '相对论应用', '大地测量学', '科学史', '数学建模']</t>
+  </si>
+  <si>
+    <t>['天体物理', '空间天气', '极光成因', '太阳活动周期']</t>
+  </si>
+  <si>
+    <t>['心理韧性', '认知重塑', '能动性', '心理防御机制', '自我成长']</t>
+  </si>
+  <si>
+    <t>['科学哲学', '理论物理', '证伪主义', '认知边界', '底层逻辑']</t>
+  </si>
+  <si>
+    <t>['组织行为学', 'AI伦理', '心理安全感', '管理范式', '职场心理']</t>
+  </si>
+  <si>
+    <t>['空间科学', '红外天文学', '宇宙演化', '硬核科普']</t>
+  </si>
+  <si>
+    <t>['沟通心理学', '承认欲求', '社会哲学', '人际关系', '自我意识']</t>
+  </si>
+  <si>
+    <t>['天体物理', '广义相对论', '引力透镜', '宇宙几何', '深度科普']</t>
+  </si>
+  <si>
     <t>[]</t>
   </si>
   <si>
+    <t>['阴谋论', '认知偏差', '文学批评', '社会心理学', '文化真实性']</t>
+  </si>
+  <si>
+    <t>['导师制', '认知技术', 'AI反思', '深度学习', '批判性思维']</t>
+  </si>
+  <si>
+    <t>['天体物理', '量子场论', '黑洞', '科学传播', '理论物理']</t>
+  </si>
+  <si>
+    <t>['人工智能', '认知科学', '逻辑推理', '大语言模型', '哲学思辨']</t>
+  </si>
+  <si>
+    <t>['摩擦学', '工业史', '跨学科研究', '表面科学', '机械工程']</t>
+  </si>
+  <si>
+    <t>['宇宙学', '哈勃张力', '引力透镜', '天体物理', '科学前沿']</t>
+  </si>
+  <si>
+    <t>['人工智能', '组织变革', '意义经济', '未来职场', '哲学反思']</t>
+  </si>
+  <si>
+    <t>['科技政治学', '人工智能监管', '加速主义', '社会契约', '产业战略']</t>
+  </si>
+  <si>
+    <t>['人工智能', '职场进化', '人机协作', '生产力革命', '劳动哲学']</t>
+  </si>
+  <si>
+    <t>['创新思维', '认知心理学', '逻辑学', '范式转移', '决策科学']</t>
+  </si>
+  <si>
+    <t>['天体物理', '超新星', 'X射线天文学', '恒星演化', '空间科学']</t>
+  </si>
+  <si>
+    <t>['宇宙学', '天体物理', '暗能量', '宇宙网', '硬核科普']</t>
+  </si>
+  <si>
+    <t>['天体生物学', '系外行星', '生物特征', '空间科学', '外星生命探测']</t>
+  </si>
+  <si>
+    <t>['天体物理', '宇宙学', '引力波', '时空演化']</t>
+  </si>
+  <si>
+    <t>['医学史', '性别研究', '社会建构论', '女性健康', '权力话语']</t>
+  </si>
+  <si>
+    <t>['技术哲学', '长期主义', '时间观', '制度建设', '社会批判']</t>
+  </si>
+  <si>
+    <t>['物理学', '哲学悖论', '时空观', '科学思维', '微积分原理']</t>
+  </si>
+  <si>
+    <t>['天文学', '宇宙演化', '星际介质', '科学前沿', '天体物理']</t>
+  </si>
+  <si>
+    <t>['人才发展', '组织行为学', '管理方法论', '系统思维']</t>
+  </si>
+  <si>
+    <t>['媒介环境学', '认知工具', '信息技术史', '人工智能批判', '阅读本质']</t>
+  </si>
+  <si>
+    <t>['水下考古', '新石器时代', '地质变迁', '集体记忆', '史前工程']</t>
+  </si>
+  <si>
+    <t>['天体物理', '詹姆斯·韦伯望远镜', '宇宙起源', '恒星演化', '重元素合成']</t>
+  </si>
+  <si>
+    <t>['理论物理', '广义相对论', '宇宙学', '科学普及']</t>
+  </si>
+  <si>
+    <t>['当代艺术', '人类中心主义', '生态哲学', '二元论批判', '地质时间']</t>
+  </si>
+  <si>
+    <t>激发思维</t>
+  </si>
+  <si>
+    <t>💡 激发思维</t>
+  </si>
+  <si>
+    <t>🔭 了解新知</t>
+  </si>
+  <si>
+    <t>了解新知</t>
+  </si>
+  <si>
+    <t>🌍 开阔眼界</t>
+  </si>
+  <si>
+    <t>[{'title': '风格要素', 'author': '威廉·斯特伦克 / E·B·怀特', 'context': '用于提升写作的清晰度与表达的简洁性，是沟通技能的基础。'}, {'title': '统计数字会撒谎', 'author': '达莱尔·哈夫', 'context': '用于培养批判性思维，识别日常信息与媒体报道中的数据陷阱。'}, {'title': '思考，快与慢', 'author': '丹尼尔·卡尼曼', 'context': '深入理解人类认知的双系统模型，识别并规避决策中的非理性偏差。'}, {'title': '国富论', 'author': '亚当·斯密', 'context': '理解现代经济运作的底层逻辑、社会分工以及价值交换的本质。'}, {'title': '君主论', 'author': '尼科洛·马基雅维利', 'context': '洞察现实主义视角下的权力动态、领导力逻辑及复杂的战略博弈。'}, {'title': '孙子兵法', 'author': '孙武', 'context': '学习冲突管理、竞争策略与全局筹划，将博弈智慧应用于生活挑战。'}, {'title': '沉思录', 'author': '马可·奥勒留', 'context': '建立内在韧性与情绪调节能力，通过斯多葛派哲学实现自我主宰。'}]</t>
+  </si>
+  <si>
+    <t>[{'title': 'The Knowledge (伦敦出租车司机资格考试系统)', 'author': '伦敦交通局 (TfL) 监管', 'context': '文中核心讨论的训练对象，被视为人类空间记忆训练的巅峰，是研究大脑物理改变的关键样本。'}]</t>
+  </si>
+  <si>
+    <t>[{'title': '《手册》(Enchiridion)', 'author': '爱比克泰德 / 阿里安', 'context': '斯多葛学派的核心修身指南，详细阐述了“控制二分法”以及如何通过判断力实现内心自由。'}, {'title': '《书信集》(Letters)', 'author': '小塞内卡', 'context': '文中引用其观点，强调当一个人失去理智和判断力时，便失去了作为人的本质。'}, {'title': '《宁静祷文》(Serenity Prayer)', 'author': '雷茵霍尔德·尼布尔', 'context': '现代神学作品，其核心思想与斯多葛派关于接受不可改变之物的智慧高度呼应。'}]</t>
+  </si>
+  <si>
+    <t>[{'title': 'Spinosaur Tales', 'author': 'Big Think / Buzz.CC (Source)', 'context': '探讨棘龙研究历史与发现过程的相关文献，记录了该物种从化石发现到二战损毁的曲折历程。'}]</t>
+  </si>
+  <si>
+    <t>[{'title': 'Flow: The Psychology of Optimal Experience', 'author': 'Mihaly Csikszentmihalyi', 'context': '文中核心概念“自足体验”（Autotelic experience）源于米哈里·契克森米哈赖的积极心理学研究，指代那些为了活动本身而非外部奖励而进行的体验。'}]</t>
+  </si>
+  <si>
+    <t>[{'title': '现代空间望远镜（如哈勃、韦伯等）', 'author': 'NASA/ESA 等机构', 'context': '文中将其视为改变人类视角的核心技术工具，是推动认知范式转移的“认知杠杆”。'}]</t>
+  </si>
+  <si>
+    <t>[{'title': 'Big Trust', 'author': 'David Horsager', 'context': '文中提及该资源作为身份构建与信任机制研究的背景参考，探讨了标签如何影响个体与外界的信任连接。'}]</t>
+  </si>
+  <si>
+    <t>[{'title': '狭义与广义相对论浅说', 'author': '阿尔伯特·爱因斯坦', 'context': '文中提及相对论是修正GPS卫星时间偏差、确保定位精度的核心物理理论基础。'}, {'title': 'The Geoid (大地水准面相关研究资料)', 'author': '不详', 'context': '文中核心讨论对象，指代描述地球真实物理形状与引力场特性的数学模型。'}]</t>
+  </si>
+  <si>
+    <t>[{'title': '弦论 (String Theory)', 'author': '多个研究者', 'context': '作为主流物理学标准模型之外的重要扩展方案被提及，讨论其在实验约束下的地位。'}, {'title': '超对称 (Supersymmetry)', 'author': '多个研究者', 'context': '文中将其作为一种亟待通过实验数据进行证伪或约束的替代性物理理论。'}, {'title': '广义相对论 (General Relativity)', 'author': '阿尔伯特·爱因斯坦', 'context': '现代物理学的基石理论，文中讨论了其成功如何影响了人们对新理论探索的评价标准。'}, {'title': '标准模型 (Standard Model)', 'author': '多个研究者', 'context': '基于量子场论的核心框架，是文中讨论理论约束时的重要参照系。'}]</t>
+  </si>
+  <si>
+    <t>[{'title': '他者的消失', 'author': '韩炳哲', 'context': '文中引用其哲学观点，论证现代社会中人类对社会认可和验证的持续追求以及他者在自我定义中的重要性。'}, {'title': '论人类不平等的起源和基础', 'author': '让-雅克·卢梭', 'context': '用于探讨人类寻求他人承认的社会本质，以及这种需求如何塑造了人类的自我意识。'}]</t>
+  </si>
+  <si>
+    <t>[{'title': '广义相对论 (General Relativity)', 'author': '阿尔伯特·爱因斯坦 (理论奠基)', 'context': '作为解释引力透镜现象的底层物理理论基础，解释了大质量天体如何导致时空弯曲。'}]</t>
+  </si>
+  <si>
+    <t>[{'title': '威廉·莎士比亚作品集', 'author': '威廉·莎士比亚', 'context': '文中讨论了关于莎士比亚真实身份的长期争议（如牛津论、培根论），将其作为文学阴谋论的典型案例。'}, {'title': '锡安长老会纪要', 'author': '佚名（伪作）', 'context': '文中将其作为文学骗局引发真实世界暴力与仇恨的极端负面典型进行批判。'}, {'title': '爱丽丝漫游奇境记', 'author': '刘易斯·卡罗尔', 'context': '涉及作者身份与“开膛手杰克”相关的阴谋论推测，用于说明阴谋论如何强行关联无关事实。'}, {'title': '哈利·波特', 'author': 'J.K. 罗琳', 'context': '提及关于现代畅销书作家是否为“团队创作代号”的当代文学阴谋论。'}, {'title': '埃德加·爱伦·坡作品集', 'author': '埃德加·爱伦·坡', 'context': '涉及对其死因谜团的各种阴谋论解读，展示了人们如何利用文学天才的悲剧制造虚假叙事。'}]</t>
+  </si>
+  <si>
+    <t>[{'title': 'Books as technology', 'author': '未知', 'context': '文中将书籍重新定义为一种高效的认知技术，而非仅仅是文字的载体，强调其对人类思维结构的深远影响。'}]</t>
+  </si>
+  <si>
+    <t>[{'title': '时间简史', 'author': '斯蒂芬·霍金', 'context': '文中提到该书为了向大众普及，引入了“虚粒子对”这一具有误导性的类比模型。'}]</t>
+  </si>
+  <si>
+    <t>[{'title': '《新星》(Stella Nova)', 'author': '约翰内斯·开普勒', 'context': '开普勒在1604年观测到该超新星后撰写的著作，记录了当时人类对这一天文奇观的初步认知与命名。'}]</t>
+  </si>
+  <si>
+    <t>[{'title': 'Starts With A Bang Podcast Episode 125', 'author': 'Ethan Siegel', 'context': '探讨宇宙大尺度结构形成及暗能量性质的专题播客，提供了关于宇宙网演化的前沿科学解释。'}]</t>
+  </si>
+  <si>
+    <t>[{'title': '生物色素作为系外行星生物特征的研究', 'author': 'Lisa Kaltenegger', 'context': '核心研究课题，探讨了利用微生物产生的特定颜色作为识别地外生命的视觉线索。'}, {'title': '卡尔·萨根研究所研究档案', 'author': 'Carl Sagan Institute', 'context': '致力于跨学科寻找宇宙生命的研究机构，为该研究提供了理论与模拟支持。'}]</t>
+  </si>
+  <si>
+    <t>[{'title': 'Invisible Illness', 'author': 'Big Think (专题/推荐资源)', 'context': '文中引用的核心资源，探讨了女性在现代医学体系中被忽视的痛苦及其背后的历史文化背景。'}]</t>
+  </si>
+  <si>
+    <t>[{'title': '符号化高管的时代 (The era of the symbolic executive)', 'author': '不详', 'context': '文中引用的专题研究，探讨在短视思维影响下，现代企业领导力如何从实质性的战略领导转向表演性的符号管理。'}, {'title': '非理性世界中的赌博诱惑 (The allure of gambling in an irrational world)', 'author': '不详', 'context': '文中提及的关联论据，用以佐证在技术加速和未来不确定性加剧的情况下，社会行为如何向投机化和短期博弈倾斜。'}]</t>
+  </si>
+  <si>
+    <t>[{'title': '物理学的进化', 'author': '阿尔伯特·爱因斯坦 / 利奥波德·英费尔德', 'context': '文中探讨了从物理学视角理解运动本质的思维转向，这与本书中关于物理概念从机械观向现代场论进化的逻辑高度契合。'}]</t>
+  </si>
+  <si>
+    <t>[{'title': '自然哲学的数学原理', 'author': '艾萨克·牛顿', 'context': '文中回顾了牛顿关于质量间相互吸引的经典定义，作为讨论引力本质的起点。'}, {'title': '广义相对论', 'author': '阿尔伯特·爱因斯坦', 'context': '文中核心理论框架，用于解释物质如何通过弯曲时空产生引力，并探讨负能量对时空曲率的潜在影响。'}]</t>
+  </si>
+  <si>
+    <t>[{'title': '时光的皱纹', 'author': '阿多尼斯', 'context': '文中提到该诗集为展览提供了“破而后立”的思想基础。'}, {'title': '灰烬与玫瑰之间的时间', 'author': '阿多尼斯', 'context': '2025年爱知三年展的主题来源，探讨文明在危机中的转机。'}, {'title': '白鲸', 'author': '赫尔曼·梅尔维尔', 'context': '文中引用的文学意象，用以类比人类文明中捕鲸行为所展现的暴力与贪婪。'}]</t>
+  </si>
+  <si>
     <t>{"title": "京都小店如何将匠心与禅意相连 (Kaikado: Mastery and Zen)", "summary_long": "本文探讨了创立于1875年的京都老店“开化堂”（Kaikado）如何通过追求极致的工艺实现商业长青与精神升华。开化堂的核心产品是手工茶筒（chazutsu），其制造工艺极其精密，以至于这种生产过程本身演变成了一种冥想形式。文章指出，开化堂之所以能在长达一个多世纪的竞争中生存并繁荣，归功于其对“精通”（Mastery）和“关怀”（Care）的不懈追求。这种对极致工艺的执着不仅是为了产出高质量的产品，更揭示了精通带来的深层回报：即在行动中获得完全的“当下感”（being fully present）。通过这种方式，匠人的日常劳动与禅宗的觉知相契合，将物质制造提升到了精神修行的层面。", "key_arguments": ["极致的工艺精度可以将重复性的制造劳动转化为一种冥想实践。", "企业的长久生存依赖于对‘精通’（Mastery）和‘关怀’（Care）的持续投入，而非单纯的商业扩张。", "追求精通的终极奖励是心理层面的：它能让个体在工作中体验到完全的‘临场感’或‘当下感’。"], "mentioned_resources": ["开化堂/Kaikado (京都手工茶筒老店) - 文章核心研究对象，创立于1875年", "Chazutsu (茶筒) - 开化堂的核心产品，体现精密工艺的载体"], "keywords": ["Mastery (精通/匠心)", "Meditation (冥想)", "Chazutsu (茶筒)", "Fully Present (当下感/临场感)", "Zen (禅意)", "Kaikado (开化堂)", "Craftsmanship (手工艺)"], "style_tone": "充满人文关怀且具有哲学思辨色彩的叙事风格"}</t>
   </si>
   <si>
@@ -5226,6 +5919,267 @@
     <t>{"title": "“认知越界”：为何聪明人会说蠢话 (Epistemic trespassing: why brilliant people can say idiotic things)", "summary_long": "本文探讨了“认知越界”（Epistemic Trespassing）这一心理与哲学现象，解释了为何在某一领域获得极高成就的专家，往往会在其并不擅长的其他领域发表极具误导性甚至荒谬的言论。文章指出，这种现象的核心在于“能力迁移错觉”：专家错误地认为自己在特定领域积累的判断力和智力优势可以无缝衔接到所有知识领域。文章重点引用了诺贝尔奖得主莱纳斯·鲍林（Linus Pauling）的案例作为警示。鲍林虽在化学领域功勋卓著，却在晚年利用其名望跨界宣扬“大剂量维生素C可治疗感冒及癌症”的伪科学观点，造成了严重的社会误导。文章最后提出，避免认知越界的关键在于培养“智力谦逊”（Intellectual Modesty），即个体需要清晰地识别自己的认知边界，并在面对非专业领域的问题时，保持对该领域专业知识的敬畏与服从。", "key_arguments": ["认知越界（Epistemic Trespassing）定义：专家在跨出其专业领域后，仍保留着在原领域时的自信，从而对陌生领域做出错误判断。", "智力傲慢的代价：过往的成功容易让人产生智力全能的幻觉，导致在缺乏专业证据支撑的情况下传播误导性信息。", "智力谦逊的必要性：承认知识的碎片化与专业化，在非擅长领域应主动将话语权让渡给该领域的专家。"], "mentioned_resources": ["莱纳斯·鲍林 (Linus Pauling) - 诺贝尔奖得主，文中作为认知越界的典型案例，提及他跨界推销维生素C疗法的负面影响。"], "keywords": ["Epistemic Trespassing (认知越界)", "Intellectual Modesty (智力谦逊)", "Intellectual Pride (智力傲慢)", "Competence Carry-over (能力迁移)", "Misinformation (误导信息)"], "style_tone": "逻辑严密的批判性分析风格，带有警示与反思的人文色彩。"}</t>
   </si>
   <si>
+    <t>{"title": "詹姆斯·韦伯太空望远镜发现九个难以归类的物体。天文学家是否找到了他们的“鸭嘴兽”？", "summary_long": "文章以自然界中最奇特的生物——鸭嘴兽作为引子，探讨了詹姆斯·韦伯太空望远镜（JWST）在宇宙观测中的一项突破性发现。鸭嘴兽因其集合了产卵哺乳动物、鸭嘴、海狸尾巴、鲨鱼般的电定位感官以及毒刺等看似矛盾的特征，曾被早期生物学家视为骗局。作者指出，这种“多种异常特征集于一身”的逻辑在天文学中重演：JWST 发现了九个极其特殊的宇宙天体。这些天体展现出一系列完全超出当前天文模型预期的属性组合，且目前尚无任何统一的物理理论能够解释其成因。就像鸭嘴兽挑战了当时的生物分类学一样，这九个“宇宙鸭嘴兽”的出现，预示着我们现有的宇宙演化理论或天体物理分类体系可能存在重大盲区，迫使天文学家寻找全新的解释框架。文章强调，单一的异常特征或许可以被视为偶然，但当多种极端属性同时出现在同一物体上时，它便成为了挑战既有认知的关键证据。", "key_arguments": ["类比论证：鸭嘴兽的生物学奇特性（多种矛盾特征共存）是理解科学发现中“反直觉异常”的完美模型。", "核心发现：JWST 观测到了九个在属性上完全违背现有天文分类逻辑的神秘物体。", "范式挑战：这九个物体的存在缺乏一致性的科学解释，暗示了当前宇宙认知模型的局限性。", "整体性异常：这些物体的特殊性不在于单一属性，而在于其属性组合的不可思议性。"], "mentioned_resources": ["詹姆斯·韦伯太空望远镜 (JWST) - 发现这九个异常物体的核心观测工具。"], "keywords": ["JWST", "宇宙鸭嘴兽 (Cosmic Platypus)", "天文异常", "分类学挑战", "属性组合", "科学范式"], "style_tone": "富有启发性的科学叙事风格，通过生动类比引出前沿天文发现，带有探索未知的惊奇感。"}</t>
+  </si>
+  <si>
+    <t>{"title": "两次消失的恐龙：二战如何险些让棘龙从历史中消失", "summary_long": "文章回顾了棘龙（Spinosaurus）这一独特物种从发现、毁灭到重生的曲折历史。20世纪初，在全球“恐龙热”的背景下，德国古生物学家恩斯特·斯特莫（Ernst Stromer）在埃及发现了棘龙化石，这种拥有巨大背帆的掠食者刷新了当时对恐龙形态的认知。然而，这批具有唯一性的正模标本在第二次世界大战期间遭遇了毁灭性打击：1944年盟军对慕尼黑的轰炸摧毁了存放化石的博物馆，导致棘龙在科学记录中经历了长达数十年的“物理性消失”。直到近几十年，随着新化石证据的陆续出土，古生物学家才得以重新构建对棘龙族群的理解，弥补了由战争造成的长达半个世纪的科研断层。文章强调了科学遗产在战争面前的脆弱性，以及现代考古发现对还原历史真相的关键作用。", "key_arguments": ["恩斯特·斯特莫的早期发现是人类认识棘龙的起点，确立了其独特的解剖学地位。", "二战轰炸对棘龙化石的摧毁不仅是物质损失，更是古生物学研究史上的重大断裂。", "现代古生物学的持续调查和新化石的发现，正在重新定义和完善我们对棘龙族群的认知框架。"], "mentioned_resources": ["棘龙 / Spinosaurus (Ernst Stromer) - 核心研究对象，由斯特莫于20世纪初首次发现并命名。", "《Spinosaur Tales》 (Big Think/Buzz.CC 引用来源) - 探讨棘龙研究历史与发现过程的相关文献/叙事。"], "keywords": ["棘龙 (Spinosaurus)", "恩斯特·斯特莫 (Ernst Stromer)", "二战轰炸 (WWII Bombing)", "正模标本 (Holotype)", "古生物学重建", "科学遗产损失"], "style_tone": "带有历史厚重感的科普叙事风格，强调科学发现的偶然性与脆弱性。"}</t>
+  </si>
+  <si>
+    <t>{"title": "如何以“自足”之道取得成功 (How to find success the autotelic way)", "summary_long": "文章探讨了一种超越传统名利定义的成功路径——“自足”（Autotelic）之道。作者首先指出，现代人常因观察到那些传统意义上的成功者（如名流、富豪）表现出的道德缺失或脱节行为而感到挫败，这暗示了以结果为导向的成功定义的局限性。为了应对这种挫败感，文章引入了“自足体验”（Autotelic experience）这一概念，其核心含义是：从“为了工作本身而把工作做好”这一过程中获得纯粹的履行感和满足感。这种成功观主张将活动本身视为目的，而非达成外部奖励的手段。文章最后通过喜剧演员 Jerry Seinfeld 的视角进行升华，强调在充满不确定性的生活中，唯有“精湛的技能”是真正值得拥有的。这种视角将成功的重心从外部的社会评价转向了内在的工匠精神与技能磨炼，认为这种内在驱动的卓越才是通往持久幸福的唯一路径。", "key_arguments": ["传统成功定义的局限性：外部驱动的成功（名利、地位）往往与个人道德或真实幸福脱节，易导致心理失衡。", "自足体验的核心价值：将工作或活动本身视为奖励，通过追求过程的卓越来实现内在的自我实现。", "技能作为成功的锚点：在波动的社会评价体系中，个人所掌握的精湛技能是唯一具有确定性且值得追求的财富。"], "mentioned_resources": ["Jerry Seinfeld (喜剧演员) - 引用其关于‘生活中唯一真正值得拥有的是精湛技能’的观点，用以佐证自足价值观。"], "keywords": ["Autotelic experience (自足体验)", "Internal Motivation (内在动机)", "Skill Mastery (技能精进)", "Success Definition (成功定义)", "Fulfillment (自我实现)"], "style_tone": "理性启发式，带有对传统价值观的审视和对工匠精神的推崇。"}</t>
+  </si>
+  <si>
+    <t>{"title": "是的，一张来自太空的图像足以改变人类的视角", "summary_long": "本文探讨了太空图像如何作为人类感知的延伸，重塑我们对自身及宇宙的认知。文章首先指出一个现实：绝大多数人一生都无法亲自进入太空，从“非地球视角”（off-world perspective）直观俯瞰我们的家园。然而，这种物理上的缺席并未阻碍认知的飞跃。通过太空图像，人类得以跨越感官限制，观察到地球在浩瀚宇宙中表现出的渺小、无国界且脆弱的状态。这种视觉冲击不仅改变了我们对物理空间的理解，更深刻地动摇了人类中心主义的自我定位。\n\n作者强调，这种视角的转变并非一蹴而就，而是一个持续发生的动态过程。尤其是在现代空间望远镜时代，每一次重大的天文观测都在不断推高人类认知的边界。文章回顾了这种认知范式转移的历史必然性，指出从最初的地球全景图到如今深空探测的图像，它们都在持续挑战并更新人类的宇宙观。文章最后留下了一个开放性的期待：随着技术的进步，下一张足以再次颠覆人类视角的图像可能就在不远的未来。核心逻辑在于：图像不仅是信息的载体，更是哲学意义上的“认知杠杆”，它通过揭示宇宙的宏大与地球的孤立，促使人类产生一种超越国界与种族的集体责任感。", "key_arguments": ["非地球视角（Off-world perspective）的稀缺性与补偿：虽然物理太空旅行对普通人不可及，但图像提供了替代性的认知途径。", "地球特性的重新定义：太空图像揭示了地球的三个核心属性——渺小（Small）、无国界（Borderless）与脆弱（Fragile）。", "技术驱动的认知演进：现代空间望远镜（Space Telescopes）是推动人类视角转变的核心工具，且这种转变是持续且循环的。"], "mentioned_resources": ["现代空间望远镜 (Modern era of space telescopes) - 作为改变人类视角的核心技术工具被提及，指代如哈勃、韦伯等观测设备。"], "keywords": ["非地球视角 (Off-world perspective)", "脆弱性 (Fragility)", "无国界 (Borderless)", "空间望远镜 (Space Telescopes)", "范式转移 (Perspective Shift)", "宇宙家园 (Cosmic Home)"], "style_tone": "充满人文关怀与科学启迪的宏大叙事，语调深邃且富有前瞻性。"}</t>
+  </si>
+  <si>
+    <t>{"title": "领导者如何提供我们大多数人渴望的社会联结", "summary_long": "文章探讨了当代美国社会普遍存在的“社交联结危机”，并提出一个核心视角的转变：社交孤立并非源于个人社交动力的缺失或意识不足，而是一个由结构性因素导致的“系统性挑战”。这种挑战受到可预测的现实障碍、人生阶段的重大转折（如搬家、职业变动）以及宏观文化变迁的共同驱动。文章强调，解决这一危机不能仅依靠个人的努力，而需要从系统层面重新思考。在此背景下，雇主和组织领导者正处于一个独特的“黄金机遇期”。由于职场是现代成年人投入时间最长、互动最频繁的场所，领导者有能力也有责任通过重塑工作环境和组织机制，为员工创造建立深层社交联结的条件，从而填补社会结构变迁留下的情感真空。", "key_arguments": ["社交危机本质上是系统性故障，而非个人动机问题：人们渴望联结，但现有的社会系统设置了重重障碍。", "社交障碍具有可预测性：人生转折点和文化位移是导致联结断裂的主要触发因素。", "领导者角色重定义：在社会联结匮乏的当下，职场应成为新的社交基础设施，领导者需承担起促进联结的系统设计者责任。"], "mentioned_resources": ["《关于社交互动的最新报告》(A new report on social interaction) - 文章的核心论据来源，提出了将社交视为系统性挑战的观点。"], "keywords": ["社交联结危机 (Connection Crisis)", "系统性挑战 (Systems Challenge)", "人生转折 (Life Transitions)", "文化位移 (Cultural Shifts)", "职场社交基础设施", "领导力转型"], "style_tone": "逻辑严密的分析风格，带有社会学视角的务实建议。"}</t>
+  </si>
+  <si>
+    <t>{"title": "宇宙的模样：从近处到远方 (The Universe Looks Like: From Nearby to Far Away)", "summary_long": "文章探讨了人类观测宇宙时，视距差异如何决定我们对宇宙本质的认知。作者指出，无论观测距离远近，宇宙展现出的景象始终令人充满敬畏与好奇。然而，观测“宇宙后花园”与观测深空之间存在本质区别：距离的改变不仅意味着细节清晰度的变化，更意味着观测对象类别的根本更迭。文章勾勒了一条从近及远的认知路径：从太阳系的行星动态，到银河系的恒星分布，再到遥远星系、高能类星体及黑洞。最终，观测的终点抵达了宇宙诞生初期留下的“最早的光”。这种空间上的跨越实际上也是时间上的追溯，揭示了宇宙在不同尺度和演化阶段的异质性。全文强调，宇宙的模样取决于我们望向多远的地方，每一层级的尺度都对应着独特的物理实体和宇宙学意义。", "key_arguments": ["观测距离的改变不仅带来细节差异，更导致观测对象（天体类别）的本质切换。", "宇宙观测具有层次性，从局部系统（太阳系）到星系尺度，再到宇宙学尺度的极端天体。", "远距离观测本质上是对宇宙早期状态的追溯，最终边界是宇宙初创时的遗迹光芒。"], "mentioned_resources": ["太阳系 (Solar System) - 文中定义为“宇宙后花园”的近距离观测范畴。", "银河系 (Milky Way) - 作为中等距离的恒星集合实体。", "类星体与黑洞 (Quasars &amp; Black Holes) - 代表远距离、高能级的宇宙观测对象。", "宇宙最早的光 (Earliest light in the cosmos) - 指代宇宙微波背景辐射等极远距离的宇宙学遗迹。"], "keywords": ["宇宙演化", "观测尺度 (Cosmic Scales)", "时空追溯", "天体分类", "宇宙边界"], "style_tone": "充满敬畏感且逻辑清晰的科普叙事风格，强调科学发现带来的哲学震撼。"}</t>
+  </si>
+  <si>
+    <t>{"title": "为何“多读”可能是我们最被低估的思考建议", "summary_long": "文章探讨了阅读、写作与思考之间深层的共生关系，挑战了“写作仅是思想输出”的传统观念。作者指出，写作本质上不是在表达已经完成的思想，而是一个将模糊想法进行澄清、测试和转化的动态过程。在这个过程中，“广泛阅读”扮演了至关重要的角色：它为写作者提供了思维的“原材料”。原创性并非凭空产生，而是通过对这些材料的组合、类比以及持续的反思而涌现的。文章特别反驳了“写作时阅读会干扰原创性”的观点，认为在写作过程中保持阅读不仅不会稀释作者的个人声音，反而会通过思想的碰撞与参照，使作者的论点更具韧性，声音更加强而有力。简而言之，多读是提升思考深度的底层驱动力。", "key_arguments": ["写作是思维的生成过程：写作并非思想的终点，而是通过文字使模糊直觉变得清晰、严谨的转化手段。", "阅读提供思维的‘原材料’：原创性源于信息的重新组合与类比，广泛的知识储备是产生新颖见解的先决条件。", "阅读对写作具有强化作用：在创作期间阅读外部观点，能够通过对比和吸收，增强作者自身立场的独特性和表达的力度。"], "mentioned_resources": ["Big Think (来源平台) - 探讨认知与思维建议的背景来源"], "keywords": ["写作即思考 (Writing as thinking)", "思维原材料 (Raw materials of thought)", "组合式创新 (Combinatorial creativity)", "认知澄清 (Clarification)", "原创性 (Originality)"], "style_tone": "富有启发性、逻辑严密且强调认知科学视角的分析风格"}</t>
+  </si>
+  <si>
+    <t>{"title": "问伊森：所有蓝移星系都去哪儿了？", "summary_long": "本文探讨了宇宙学中一个核心的观测悖论：既然引力在宇宙中以随机方向牵引星系，理论上朝向我们运动（蓝移）和背离我们运动（红移）的星系数量应当大致相等，但实际观测中，远距离星系几乎全部呈现红移。作者通过解析两种物理效应的“尺度博弈”回答了这一问题。首先是“局部引力效应”，它赋予星系“本征速度”（peculiar velocities），这种运动是随机的，在近距离尺度内可以导致蓝移（如仙女座星系）。其次是“全局膨胀效应”，即“哈勃流”（Hubble flow），它随距离增加而线性增强。文章指出，问题的关键在于哪种效应占据主导：在宇宙的大尺度上，空间膨胀的速度远超星系在引力作用下所能达到的本征速度，导致红移彻底淹没了蓝移的可能性。这种现象揭示了宇宙演化中微观随机性与宏观必然性之间的界限。", "key_arguments": ["引力的随机性理论上应导致红移与蓝移星系数量均衡，但这仅在忽略宇宙膨胀的理想静态模型中成立。", "星系的实际运动由“本征速度”（局部引力驱动）和“哈勃流”（宇宙整体膨胀）叠加而成。", "尺度决定主导权：在小尺度上局部引力可产生蓝移，但在大尺度上，哈勃流的退行速度必然压倒本征速度。"], "mentioned_resources": ["哈勃流 (Hubble flow) - 文中用于描述宇宙全局膨胀效应的核心物理概念。", "本征速度 (Peculiar velocities) - 文中用于描述星系在局部引力作用下产生的非膨胀性运动速度。"], "keywords": ["蓝移 (Blueshift)", "红移 (Redshift)", "哈勃流 (Hubble flow)", "本征速度 (Peculiar velocity)", "宇宙膨胀 (Global expansion)", "局部引力效应 (Local gravitational effects)"], "style_tone": "逻辑严密的科普分析风格，强调物理机制的尺度对比。"}</t>
+  </si>
+  <si>
+    <t>{"title": "你的大脑喜欢标签——即使它们限制了你的潜力", "summary_long": "文章探讨了人类大脑在处理身份认同过程中的一种固有机制：即倾向于将“标签”视为绝对的、固定的真理。这种倾向具有潜在的危险性，因为这些标签往往并非基于深思熟虑，而可能仅仅源于一个偶然的瞬间或他人一句随意的评价。大脑一旦接受了这些标签，就会将其内化为自我定义的一部分，从而形成心理上的枷锁。\n\n文章进一步提出了“重构标签”（Reframing）的策略。核心观点认为，重构标签并不会改变一个人的本质（Who you are），但它能从根本上改变大脑对这一身份部分的解释逻辑。这种认知层面的转变是打破自我设限的关键。最后，文章指出，真正的个人成长始于一种主动的更替过程：即识别并剔除那些限制性的标签，代之以能够赋予力量、允许个体向理想目标持续进化的新标签。通过这种方式，个体可以引导大脑从“固化状态”转向“进化状态”。", "key_arguments": ["大脑的标签化本能：大脑倾向于将碎片化的经验或评价固化为永恒的身份标签，并将其视为固定真理。", "认知重构的非侵入性：重构标签改变的是大脑对身份的解释方式，而非改变个体的核心本质。", "成长的本质是标签的更替：通过主动替换自我限制的语言，可以解除大脑对潜力的束缚，实现向理想自我的演进。"], "mentioned_resources": ["《Big Trust》 (David Horsager) - 文章来源链接指向的作品，探讨信任与身份构建的相关背景。"], "keywords": ["身份标签 (Identity Labels)", "固定真理 (Fixed Truths)", "认知重构 (Reframing)", "自我限制 (Self-limiting)", "心理进化 (Evolution)", "大脑解释机制 (Brain Interpretation)"], "style_tone": "逻辑严密的心理学分析风格，带有启发性和赋能感。"}</t>
+  </si>
+  <si>
+    <t>{"title": "活埋、吸血虫侵袭、火钳攻击：怀旧疗法的黑暗历史", "summary_long": "本文揭示了“怀旧”（Nostalgia）在医学史上曾被视为一种致命生理疾病的阴暗面。在17至19世纪，医生并不认为怀旧是一种单纯的情感波动，而将其定义为一种能引起高烧甚至导致死亡的躯体病症。其核心病理机制被解释为体内“动物精气”（animal spirits）的实质性耗损。关于怀旧的诱因，当时的医学界提出了多种假说：有的将其归咎于大气压力的物理变化，有的认为是由特定的听觉刺激（如特定民歌）引发，还有医生将其视为对童年潜意识的病态执着。为了“治愈”这种病症，医疗手段经历了从温和到极端残忍的异化。最初的治疗方案相对无害，如热水浴疗法；但随着理论的演变，治疗手段转向了公开羞辱、使用吸血虫（水蛭）放血、火钳攻击，甚至以“活埋”作为恐吓手段。这种从生理干预向肉体折磨的转变，反映了早期医学在处理精神与肉体关系时的迷茫与暴力。直到现代心理学的发展，怀旧才被重新定义为一种自然的、苦乐参半的正常心理体验。", "key_arguments": ["怀旧在历史上被病理化为一种严重的生理疾患，被认为会导致实质性的生命能量（动物精气）耗损。", "早期医学对怀旧成因的解释跨越了物理环境（气压）、感官刺激（音乐）和潜意识心理等多个维度。", "怀旧的治疗史是一段从物理舒缓演变为极端暴力惩戒的黑暗历程，体现了早期医学对心理现象的误读。"], "mentioned_resources": ["“动物精气”理论 (Animal Spirits) - 历史上被用来解释怀旧导致生理衰竭的核心理论模型。", "特定歌曲 (Specific Songs) - 文中提到作为诱发怀旧病症的听觉媒介（历史上常指瑞士民歌《Ranz des Vaches》）。"], "keywords": ["怀旧 (Nostalgia)", "动物精气 (Animal Spirits)", "躯体化 (Somatization)", "医疗暴力", "心理病理学史", "医学异化"], "style_tone": "冷峻的医学史揭秘风格，带有对早期医学荒诞性的批判色彩。"}</t>
+  </si>
+  <si>
+    <t>{"title": "追忆格拉迪斯·韦斯特：用爱因斯坦理论创造GPS的人", "summary_long": "本文探讨了全球定位系统（GPS）从科幻构想走向现实的技术演进史，并重点追溯了数学家格拉迪斯·韦斯特（Gladys West）在其中的核心贡献。文章首先对比了定位技术的代际跨越：在航天时代黎明前，人类定位完全依赖纸质地图与肉眼观测地形的匹配，这种方式在复杂环境下极易失效。随着卫星网络的建立，通过同时观测多颗卫星获取数据来实现精确坐标计算成为可能。\n\n然而，GPS的实现面临着物理学与地球物理学的双重挑战。文章详细阐述了爱因斯坦相对论在其中的关键作用：卫星的高速运动触发了狭义相对论的时间膨胀效应，而其所处的弱引力场则触发了广义相对论效应，若不修正这些微秒级的时间偏差，定位将每天产生数公里的误差。更复杂的是，地球并非规则球体，其引力场分布极不均匀。格拉迪斯·韦斯特的卓越贡献在于，她利用早期大型计算机处理了海量的卫星观测数据，通过复杂的数学编程，构建了一个极其精确的地球引力模型——大地水准面（Geoid）。这一模型能够实时反映地球各处的引力特性，为GPS提供了必不可少的坐标基准。韦斯特的工作不仅是数学计算的胜利，更是将深奥的相对论物理转化为全球性基础设施的关键桥梁。文章最后强调，正是这位长期隐于幕后的女性数学家，通过对地球形状的精确刻画，才让现代社会的精准导航成为可能。", "key_arguments": ["定位技术从传统的‘地图-地形匹配’演进为基于卫星网络的多点观测数据计算。", "GPS的精度高度依赖于对爱因斯坦广义与狭义相对论效应的实时修正，否则时间偏差会导致定位失效。", "格拉迪斯·韦斯特通过数学建模解决了地球引力场不均匀带来的计算难题，定义了现代GPS赖以生存的‘大地水准面’模型。"], "mentioned_resources": ["爱因斯坦相对论 (Albert Einstein) - 作为GPS时间修正的理论基础。", "大地水准面模型 (Geoid Model) - 格拉迪斯·韦斯特开发的核心数学模型，用于描述地球真实的物理形状与引力场。", "SEASAT卫星 (文中隐含背景) - 韦斯特在海军水面武器中心处理数据所涉及的关键卫星项目。"], "keywords": ["GPS", "格拉迪斯·韦斯特 (Gladys West)", "广义相对论", "狭义相对论", "大地测量学 (Geodesy)", "大地水准面 (Geoid)", "引力特性", "卫星导航"], "style_tone": "严谨的科学史叙事风格，带有对被忽视科学先驱的致敬与人文关怀。"}</t>
+  </si>
+  <si>
+    <t>{"title": "太阳辐射风暴如何造就2026年1月的极光", "summary_long": "本文探讨了太阳作为太阳系主导天体对空间天气（Space Weather）的决定性影响。文章首先确立了太阳在质量、体积和能量上的绝对统治地位，并指出其通过高速运动的带电粒子流，深刻地塑造着太阳系内的环境。在极光的成因分析上，文章对比了三种不同层级的空间天气事件。通常情况下，公众所熟知的极光（包括北极光和南极光）主要由太阳耀斑（Solar Flares）和日冕物质抛射（Coronal Mass Ejections, CMEs）触发。然而，文章引入了一个更为罕见且强力的第三类事件：太阳辐射风暴（Solar Radiation Storms）。\n\n通过历史维度的对比，文章指出上一次重大的太阳辐射风暴发生在2003年，而2026年1月新发生的这一事件因其罕见性和强度，触发了极其壮观的极光显示。文章的核心逻辑在于揭示这种非典型空间天气事件与地球磁场相互作用的特殊机制。尽管耀斑和CME是极光的常客，但太阳辐射风暴所携带的高能粒子流在规模和能量等级上更具冲击力。2026年1月的这次事件不仅是一个天文奇观，更是研究太阳活动周期及其对地球电磁环境影响的关键样本。全文通过对2026年这一特定时间节点的预测性/描述性分析，强调了理解复杂空间天气现象对于预测地球大气反应的重要性。", "key_arguments": ["太阳通过带电粒子的快速运动主导空间天气，其物理属性（质量、能量）是所有天文现象的基础。", "极光的产生机制具有多样性，除了常见的太阳耀斑和日冕物质抛射（CME），太阳辐射风暴是更罕见且剧烈的诱因。", "2026年1月的太阳辐射风暴是继2003年以来的又一次重大天文事件，其能量释放直接导致了全球范围内的壮观极光。"], "mentioned_resources": ["2003年太阳辐射风暴事件 (历史事件) - 作为2026年事件的对比参照标杆", "2026年1月太阳辐射风暴 (预测/观测事件) - 本文讨论的核心案例"], "keywords": ["太阳辐射风暴 (Solar Radiation Storms)", "空间天气 (Space Weather)", "极光 (Aurora)", "日冕物质抛射 (CME)", "带电粒子 (Charged Particles)", "2026年天文预测"], "style_tone": "严谨的科学科普风格，带有前瞻性的分析视角。"}</t>
+  </si>
+  <si>
+    <t>{"title": "否认竟是通往韧性的意外路径 (Denial as an unexpected path to resilience)", "summary_long": "本文探讨了“否认”（Denial）在心理学中被误解的积极作用，提出它不仅是逃避机制，更是构建心理韧性的意外路径。Narula指出，当“否认”被用于拒绝接受那些“限制性设定”（limitation settings）时，它便具有了建设性意义。这意味着个体不再让外界或环境预设的局限性来主宰自己应对生命挑战的方式。\n\n文章重新定义了“韧性”（Resilience）的内涵：韧性并非是对现实的盲目忽视，而是一种基于个人价值观的深度抉择——通过明确对自己真正重要的事物，从而决定拒绝接受哪些“可能的未来”。这种“拒绝”是一种主动的心理防御，旨在保护个体的核心目标不受负面现实的侵蚀。\n\n最后，文章强调了自我认知的转变对行动力的决定性影响。在极端约束或困境下，将自己视为“有能力的行动者”（Capable）而非“受害者”（Victim），能够从根本上扩张个体的行动边界。这种身份认知的重塑，是实现从被动承受向主动应对转变的关键，也是韧性治愈力量的核心所在。", "key_arguments": ["建设性否认：否认可以作为一种拒绝‘限制性设定’的工具，防止环境预设的局限性剥夺个体的能动性。", "韧性的选择性：韧性本质上是根据个人价值观，主动决定拒绝接受某种负面的未来，而非被动接受所有现实。", "身份重塑的效能：从‘受害者心态’转向‘能力者心态’，能显著提升个体在受限环境下的应对能力和行动空间。"], "mentioned_resources": ["Narula (专家/作者) - 提出了关于否认具有建设性以及‘限制性设定’的相关理论。"], "keywords": ["Constructive Denial (建设性否认)", "Limitation Settings (限制性设定)", "Resilience (韧性)", "Agency (能动性)", "Victim vs. Capable (受害者与强者认知)", "Possible Futures (可能的未来)"], "style_tone": "逻辑严密、富有启发性且充满赋能感的心理学分析风格。"}</t>
+  </si>
+  <si>
+    <t>{"title": "理论物理学中最被低估的成就 (The most underappreciated achievement in theoretical physics)", "summary_long": "文章探讨了理论物理学界一个常被忽视的认知误区：人们往往只将“证实新理论”视为进步，却低估了“排除错误路径”的价值。作者指出，当前理论物理学存在大量超越主流框架的提案，如弦论、超对称、高斯-博内引力及大统一理论（GUTs）等。由于爱因斯坦的广义相对论和量子场论标准模型在实验预测上取得了巨大成功，许多人倾向于过早地否定或无视这些替代性的探索。然而，文章的核心洞察在于：科学的进步不仅体现在建立新模型，更体现在通过数据驱动的实验和观测，对这些替代方案进行严密的约束（constraining）甚至证伪（ruling out）。这种“排除法”的进步虽然不如发现新粒子那样具有轰动性，但它通过缩小真理的可能范围，为物理学提供了坚实的边界。作者强调，每当实验数据能够排除一种理论可能性时，都是理论物理学的一项巨大且被低估的成就，因为这代表了人类对宇宙运行机制理解的深化和精确化。", "key_arguments": ["科学进步的定义应包含‘证伪’：通过实验数据排除错误的理论路径，与发现新理论具有同等重要的地位。", "主流理论的成功不应成为拒绝探索的理由：广义相对论和标准模型的成功虽显著，但不应导致对弦论、超对称等扩展理论的过早否定。", "数据驱动的约束是核心成就：利用观测数据为理论设定边界，是理论物理学中最具实质性但最被低估的贡献。"], "mentioned_resources": ["弦论 (String Theory) - 作为主流物理学的替代或扩展方案被提及", "超对称 (Supersymmetry) - 作为主流物理学的替代或扩展方案被提及", "高斯-博内引力 (Gauss-Bonnet gravity) - 作为引力理论的扩展方案被提及", "大统一理论 (GUTs) - 作为物理学扩展提案被提及", "广义相对论 (Einstein’s general relativity) - 构成现代物理学标准图景的基础理论", "标准模型 (Standard Model) - 基于量子场论的现代物理学核心框架"], "keywords": ["证伪 (Falsification)", "数据驱动 (Data-driven)", "理论约束 (Theoretical constraints)", "科学哲学 (Philosophy of Science)", "替代物理学 (Alternative physics)", "标准模型 (Standard Model)"], "style_tone": "理性且具有科学哲学深度的分析风格，旨在纠正大众对科学成就的偏见。"}</t>
+  </si>
+  <si>
+    <t>{"title": "测量-满足-重复：为何追踪幸福感对工作中的AI至关重要 (Measure-Meet-Repeat: Why tracking happiness is crucial to AI at work)", "summary_long": "本文探讨了在AI技术飞速发展、未来充满不确定性的职场环境中，企业如何通过关注员工“幸福感”来驱动技术效能。文章核心逻辑在于重新定义“幸福感”：它不再是一种事后的奢侈奖赏，而是一种实时的“导航工具”。\n\n文章指出，AI技术的成功落地并非仅取决于算法本身，而取决于其背后的流程是否公平、透明。这种透明性是构建“心理安全感”的基石。作者强调，如果没有心理安全感作为支撑，无论多么先进的技术都无法转化为高质量的工作成果。在论证脉络上，文章提出了一个从“终点”到“指南针”的思维转变：追踪员工幸福感不应是为了达成某个静态的KPI（终点），而应将其视为一种动态的反馈机制（指南针），用于指导组织在复杂变革中迈出正确的下一步。这种“测量-满足-重复”的循环，构成了AI时代下管理的新范式，旨在通过人的情感反馈来校准技术应用的路径。", "key_arguments": ["幸福感是导航工具：在不确定性和变革加速的时代，幸福感是引导组织决策和适应变化的导航系统，而非装饰品。", "心理安全感是技术产出的前提：公平透明的流程产生心理安全感，这是技术发挥作用的必要条件；缺乏安全感，AI无法产生优质成果。", "追踪幸福感的动态化转向：追踪幸福感应被视为‘指南针’（指导下一步行动）而非‘目的地’（最终目标），强调过程的持续校准。"], "mentioned_resources": ["《Measure-Meet-Repeat: Why tracking happiness is crucial to AI at work》 (Big Think) - 本文来源，探讨AI与员工福祉的关系。"], "keywords": ["心理安全感 (Psychological Safety)", "导航工具 (Navigation Tool)", "公平透明 (Fairness and Transparency)", "反馈循环 (Feedback Loop)", "AI集成 (AI Integration)", "动态校准 (Dynamic Calibration)"], "style_tone": "富有前瞻性、强调人文关怀且逻辑精炼的战略分析风格。"}</t>
+  </si>
+  <si>
+    <t>{"title": "10张JWST图像，展现前所未见的宇宙景象", "summary_long": "本文作为对詹姆斯·韦伯空间望远镜（JWST）最新观测成果的综述性导引，核心逻辑建立在“观测工具的质变驱动科学发现的量变”这一基石之上。文章首先指出，人类对宇宙认知的每一次飞跃，都直接源于观测分辨率、波长覆盖范围以及光子收集能力的提升。JWST作为人类历史上发射的最大、最灵敏的空间望远镜，其核心技术优势在于近红外（Near-infrared）和中红外（Mid-infrared）成像能力，这使其能够穿透尘埃云团，捕捉到此前所有观测手段（如哈勃望远镜）均无法触及的宇宙细节。\n\n文章回顾了JWST自2022年正式开启科学作业以来的表现，强调其产出并非昙花一现，而是一个持续提供“震惊、愉悦与知识”的过程。通过这10张精选图像，文章旨在展示JWST如何超越历史极限，揭示宇宙中前所未见的结构与特征。这不仅是视觉上的饕餮盛宴，更是对宇宙演化史的重新审视。作者通过对比以往的局限性，凸显了JWST在红外波段的统治力，并引导读者关注那些在早期科学运营中可能被忽视的深空细节。整体论证脉络从技术参数的优越性出发，最终落脚于对宇宙新图景的感性认知与理性探索的结合。", "key_arguments": ["观测技术的进步（分辨率、波长覆盖、集光力）是揭示宇宙隐藏特征的先决条件。", "JWST在近红外与中红外波段的成像能力构成了其超越历史所有观测手段的核心竞争力。", "JWST的科学价值具有持续性，自2022年运行以来，它不断刷新人类对宇宙既有特征的认知边界。"], "mentioned_resources": ["詹姆斯·韦伯空间望远镜 (JWST) - 本文核心观测设备，被描述为史上最大、最灵敏的空间望远镜。"], "keywords": ["JWST", "近红外 (Near-infrared)", "中红外 (Mid-infrared)", "空间分辨率", "波长覆盖", "宇宙特征", "科学作业 (Science operations)"], "style_tone": "充满科学赞叹的专业科普风格，语调严谨且富有前瞻性的热情。"}</t>
+  </si>
+  <si>
+    <t>{"title": "奥普拉法则：对话中人人都想听你说的话", "summary_long": "文章探讨了有效沟通背后的核心心理需求，提出了所谓的“奥普拉法则”。全球知名主持人奥普拉·温弗瑞（Oprah Winfrey）在采访过数千名不同身份背景的嘉宾后发现，无论对方是国家元首还是普通人，在摄像机停止录制的瞬间，几乎所有人都会问同一个问题：“我刚才表现得怎么样？”（How was it?）。这一现象揭示了人类天性中对“验证”（Validation）的极度渴望。文章指出，这种寻求认可的心理并非偶然，而是具有深刻的哲学根源。让-雅克·卢梭和韩炳哲等哲学家都曾论证过，人类的自我意识与他人的承认紧密相连。在对话中，人们不仅是在交换信息，更是在寻求对方对自己存在价值的确认。理解并运用这一事实——即在交流中给予对方正向的反馈和“被看见”的感觉——是提升对话质量、建立深层人际连接的关键。文章强调，这种对“验证”的需求是普世的，是每个人在社交互动中最想听到的“潜台词”。", "key_arguments": ["普遍的认可需求：无论社会地位高低，人类在表达后都存在一种本能的焦虑，渴望得到外界的反馈和验证。", "对话的本质是‘确认存在’：沟通不仅是信息的传递，更是一种社会性的确认过程，即通过他人的回应来定义自我。", "验证作为社交工具：在对话中主动提供‘验证’（即认可对方的表现或观点），是建立高质量人际关系的高效策略。"], "mentioned_resources": ["奥普拉·温弗瑞 (Oprah Winfrey) 的采访观察 - 提出“How was it?”是所有访谈嘉宾的共同心声。", "韩炳哲 (Byung-Chul Han) 的哲学观点 - 论证人类对社会认可和验证的持续追求。", "让-雅克·卢梭 (Jean-Jacques Rousseau) 的理论 - 探讨人类寻求他人承认的社会本质。"], "keywords": ["奥普拉法则 (The Oprah Rule)", "验证 (Validation)", "社会承认 (Recognition)", "他者 (The Other)", "沟通心理学", "自我价值"], "style_tone": "富有洞察力、简洁且具有哲学思辨色彩的分析风格。"}</t>
+  </si>
+  <si>
+    <t>{"title": "问伊桑：为什么引力透镜会形成十字而非环状？", "summary_long": "文章探讨了广义相对论在宇宙尺度下的视觉表现，解释了引力透镜效应中两种不同形态的成因。作者首先指出，宇宙并非平坦空旷，而是受大质量天体影响而弯曲的动态空间。当背景光源（如类星体）发出的光线经过前景大质量天体（星系、类星体或星系团）时，这些质量产生的引力场会像透镜一样弯曲并扭曲光线。文章的核心矛盾在于：虽然理论上完美的轴向对齐会产生“爱因斯坦环”，但在现实观测中，这种构型极度罕见。相反，产生四个独立影像的“爱因斯坦十字”则更为常见。这主要是因为完美的环状结构要求光源、透镜体与观测者处于绝对的直线对齐，且透镜体的质量分布必须高度对称；而现实中，由于前景星系的椭圆形状或质量分布的不均匀，光线被差异化偏折，从而在特定几何点上聚焦形成十字形。这一现象揭示了宇宙物质分布的非对称性本质。", "key_arguments": ["宇宙空间受大质量天体引力影响产生弯曲，表现为引力透镜效应。", "爱因斯坦环的形成对观测几何位置的精确对齐和质量分布的对称性要求极高，导致其在现实中极为罕见。", "爱因斯坦十字的普遍性源于透镜天体（如星系）质量分布的非对称性（如椭圆率），导致图像在四个特定位置聚焦。"], "mentioned_resources": ["爱因斯坦环 (Einstein ring) - 理论上完美对齐时形成的环状引力透镜图像。", "爱因斯坦十字 (Einstein cross) - 观测中常见的四重影像引力透镜构型。", "广义相对论 (General Relativity) - 支撑引力透镜现象的底层物理理论基础。"], "keywords": ["引力透镜 (Gravitational Lensing)", "时空弯曲 (Spacetime Curvature)", "爱因斯坦环", "爱因斯坦十字", "质量分布不对称性", "类星体 (Quasar)"], "style_tone": "逻辑严密的科学科普风格，侧重于几何对称性与物理现实的对比分析。"}</t>
+  </si>
+  <si>
+    <t>{"title": "5个文学阴谋论——真相大白 (5 Literary Conspiracy Theories Debunked)", "summary_long": "本文探讨了文学阴谋论产生的深层心理机制及其社会影响。作者指出，文学阴谋论与所有阴谋论的起源一致，均源于人类在模糊且混乱的现实中强行构建“意义”与“秩序”的本能欲望。这些理论并非建立在事实证据之上，而是依赖于推测、模式猎取（pattern-hunting）以及确认偏误。文章强调，虽然文学阴谋论有时能为文学谜团提供令人满足的答案，甚至带有娱乐色彩，但历史证明，这类骗局（hoaxes）具有潜在的危险性。它们不仅会扭曲公众对文化的理解，在极端情况下，甚至会演变成煽动现实世界仇恨与暴力的工具。因此，揭露这些阴谋论的真相不仅是学术澄清，更是对文化真实性的维护。", "key_arguments": ["心理补偿机制：文学阴谋论是人类应对现实混沌感、试图赋予世界秩序感的心理产物。", "方法论缺陷：这类理论的构建逻辑通常是先有结论再找证据，依赖模式识别而非严谨考据。", "社会危害性：文学骗局并非全然无害，它们可能通过扭曲历史事实来诱发社会仇恨或暴力冲突。"], "mentioned_resources": ["《5-literary-conspiracy-theories-debunked》 (Big Think) - 原文出处，探讨文学史上的虚假叙事。", "威廉·莎士比亚作品集 (作者待考证阴谋论) - 文中隐含的经典文学阴谋论案例（如牛津论、培根论）。", "《锡安长老会纪要》 (The Protocols of the Elders of Zion) - 文中提及的作为文学骗局引发真实暴力与仇恨的极端典型。", "刘易斯·卡罗尔作品 (Lewis Carroll) - 涉及其身份与“开膛手杰克”相关的阴谋论推测。", "J.K. 罗琳 (J.K. Rowling) - 涉及其作为“团队创作代号”而非真实个体的现代文学阴谋论。", "埃德加·爱伦·坡 (Edgar Allan Poe) - 涉及其死因谜团的阴谋论解读。"], "keywords": ["确认偏误 (Confirmation Bias)", "模式猎取 (Pattern-hunting)", "文化扭曲 (Cultural Distortion)", "意义构建 (Meaning-making)", "文学骗局 (Literary Hoaxes)"], "style_tone": "逻辑严密的批判性分析风格，带有警示意义的人文关怀。"}</t>
+  </si>
+  <si>
+    <t>{"title": "如何成为商业与生活中的优秀导师", "summary_long": "本文探讨了在人工智能（AI）日益普及的背景下，导师制度（Mentorship）在商业与个人成长中的不可替代性。作者指出，AI 正在通过高度的知识抽象化，逐渐削弱组织内部对传统导师的需求，这种趋势可能导致人们误以为学习是一个可以完全脱离人际互动的孤立过程。然而，文章强调“精通”（Mastery）极少是独自完成的，它本质上源于一种长期的、有人陪伴的共同成长。除了导师制，文章还串联了几个深层议题：探讨了怀旧（Nostalgia）的心理功能，提出了对“未经审视的假设”进行批判性反思的重要性，并将书籍重新定义为一种高效的认知技术。整体而言，文章呼吁在技术驱动的效率时代，重拾人与人之间深度连接的教育价值。", "key_arguments": ["AI 的知识抽象能力正在掩盖组织内对导师制的真实需求，但这是一种对学习本质的误解。", "精通（Mastery）并非单打独斗的结果，而是通过他人长期的陪伴与同行（walk alongside you）实现的。", "书籍不应仅被视为文字载体，而应被视为一种深刻影响人类思维的‘技术’（Books as technology）。"], "mentioned_resources": ["《Books as technology》 - 文中将其作为一种理解媒介与知识传递的视角提及", "The function of nostalgia - 关于怀旧心理功能的探讨主题", "Unexamined assumptions - 关于批判性思维与认知盲区的讨论框架"], "keywords": ["AI 抽象化 (AI Abstraction)", "导师制 (Mentorship)", "精通 (Mastery)", "长期主义 (Long-termism)", "怀旧功能 (Function of Nostalgia)", "认知技术 (Cognitive Technology)"], "style_tone": "逻辑严密、带有哲学思辨色彩的商业洞察风格"}</t>
+  </si>
+  <si>
+    <t>{"title": "是时候停止传播关于霍金辐射的最大谎言了", "summary_long": "本文旨在纠正公众乃至物理学界长期以来对“霍金辐射”的一种误导性理解。通常的科普解释（甚至由斯蒂芬·霍金本人在《时间简史》中提出）认为：霍金辐射源于黑洞视界边缘自发产生的“虚粒子-反粒子对”，其中一个掉入黑洞，另一个逃逸，从而导致黑洞质量损失。作者明确指出，这种解释不仅具有误导性，而且在物理学上是错误的。 \n\n文章重构了霍金辐射的真实物理机制：它并非源于视界上的粒子对产生，而是由于黑洞周围时空的极端弯曲导致了量子场论中“真空态”的改变。在弯曲时空中，不同位置的观察者对“什么是真空”和“什么是粒子”无法达成共识。黑洞的存在使得视界附近的量子场处于一种激发态，这种状态在无穷远处看来表现为一种热辐射。 \n\n核心转折点在于：黑洞发射的并不是物质或反物质粒子，而是极低能量的“光子”。这种辐射的能量并非来自掉入黑洞的负能量粒子，而是直接源于黑洞自身的引力能（即质量）。文章强调，霍金当年的简化类比是为了让非专业读者理解复杂的数学模型，但这种类比牺牲了物理真实性。真正的霍金辐射是一个涉及广义相对论与量子场论结合的全局性效应，而非发生在视界边缘的局部粒子碰撞事件。最终，这种极其微弱的辐射会带走黑洞的能量，导致其在漫长的岁月中彻底蒸发。", "key_arguments": ["流行的“虚粒子对掉入/逃逸”模型是错误的物理图像，只是一个不恰当的类比。", "霍金辐射的本质是量子场在弯曲时空下的响应，而非视界边缘的物质/反物质产生。", "黑洞辐射的主要成分是低能光子，其能量损失直接导致了黑洞质量的减少和最终的蒸发。", "科学传播中为了易于理解而进行的过度简化，往往会演变成根深蒂固的科学误区。"], "mentioned_resources": ["斯蒂芬·霍金 (Stephen Hawking) - 理论提出者，同时也是该误导性类比的始作俑者。", "广义相对论 (General Relativity) - 描述黑洞引力和时空弯曲的基础理论。", "量子场论 (Quantum Field Theory) - 描述真空涨落和粒子产生的理论框架。"], "keywords": ["霍金辐射 (Hawking Radiation)", "黑洞蒸发 (Black Hole Evaporation)", "虚粒子 (Virtual Particles)", "时空曲率 (Spacetime Curvature)", "量子真空 (Quantum Vacuum)", "事件视界 (Event Horizon)", "光子 (Photons)"], "style_tone": "严谨的科学辟谣风格，带有批判性思维，旨在还原复杂的物理真相。"}</t>
+  </si>
+  <si>
+    <t>{"title": "人工智能模型是在推理还是在复述？", "summary_long": "本文探讨了生成式人工智能（AI）底层逻辑的核心争议：AI究竟是仅具备模式匹配能力的“随机鹦鹉”，还是已经发展出了真正的推理能力。计算机科学家、Unanimous AI 首席执行官 Louis Rosenberg 在评论中指出，越来越多的证据表明，前沿 AI 模型并非仅仅在海量文本中记忆概率分布。相反，这些系统在训练过程中构建了“内部模型”（Internal Models），这些模型能够表征文字背后的深层概念。Rosenberg 认为，反驳“AI 只是在复述”的最有力证据在于，多项研究显示 AI 能够解决其训练数据集中完全不存在的全新问题。这种超越训练范畴的解题能力，暗示了模型已经具备了某种形式的逻辑泛化和概念理解，而不仅仅是简单的信息检索或统计模仿。文章旨在纠正公众对 AI 运作机制的简化认知，强调其内部表征的复杂性与功能性。", "key_arguments": ["AI 模型并非简单的记忆机器，而是通过学习形成了能够代表现实世界概念的内部模型。", "“随机鹦鹉”假说（即 AI 仅是重复模式）无法解释前沿模型在处理未知任务时的表现。", "AI 解决训练集之外问题的能力，是其具备推理能力而非单纯复述的关键证据。"], "mentioned_resources": ["Louis Rosenberg (作者) - 计算机科学家，Unanimous AI 首席科学家兼 CEO。", "Unanimous AI (机构) - Louis Rosenberg 领导的技术公司。", "“Parrots” (概念/隐喻) - 文中引用的批评性概念，指代仅会模仿而无理解能力的 AI 模型。"], "keywords": ["内部模型 (Internal models)", "概念表征 (Conceptual representation)", "随机鹦鹉 (Stochastic Parrots)", "泛化能力 (Generalization)", "逻辑推理 (Reasoning)", "模式匹配 (Pattern matching)"], "style_tone": "逻辑严密的科技评论风格，带有专业论证色彩。"}</t>
+  </si>
+  <si>
+    <t>{"title": "“摩擦学”如何成为一门新兴工业科学", "summary_long": "文章简述了“摩擦学”（Tribology）这一学科的起源与演进。20世纪60年代中期，针对钢铁生产行业中频繁出现的设备故障，来自化学、物理学和工程学等不同领域的专家展开了深度跨学科协作。这种合作不仅是为了解决具体的机械失效问题，更催生了一个专门研究摩擦、润滑以及表面相互作用的新兴学科。随着专门研究中心的建立，摩擦学从最初的工业问题解决方案，正式演变为一门拥有深厚理论积淀的“表面科学”（Science of Surfaces），为现代工业提供了关键的理论支撑和技术指导。", "key_arguments": ["摩擦学的诞生源于20世纪60年代对钢铁工业设备失效问题的跨学科审视。", "摩擦学是化学、物理学与工程学的融合产物，打破了单一学科处理机械损耗的局限性。", "该学科的建立标志着工业界对“表面科学”认知的系统化，从经验主义转向科学研究。"], "mentioned_resources": ["摩擦学 (Tribology) - 文中核心定义的学科，关注摩擦与润滑。", "表面科学 (Science of surfaces) - 摩擦学研究的深层科学领域。"], "keywords": ["摩擦学 (Tribology)", "润滑 (Lubrication)", "跨学科协作 (Interdisciplinary Collaboration)", "表面科学 (Science of Surfaces)", "工业失效 (Equipment Failures)"], "style_tone": "客观、严谨的科学史叙事风格"}</t>
+  </si>
+  <si>
+    <t>{"title": "新JWST透镜调查：能否挽救膨胀的宇宙？", "summary_long": "当前宇宙学面临的核心挑战是关于“宇宙膨胀速率”的测量争议，即所谓的“哈勃张力”问题。目前存在两类主要的测量方法：一类基于早期宇宙（如宇宙微波背景辐射），另一类基于晚期宇宙（如距离阶梯法）。尽管这两类方法各自内部的数据逻辑自洽，但它们得出的结果却互不兼容，且这种差异已超出了实验误差的范围。为了打破这一僵局，科学界急需一种独立于上述两类路径的“合理性检查”（sanity check）方法。\n\n文章重点介绍了利用詹姆斯·韦伯空间望远镜（JWST）进行的一项极具雄心的观测计划。该计划的核心逻辑是利用“多重透镜超新星”（multiply-lensed supernovae）这一独特的天文现象。当远处的超新星发出的光经过前景星系团时，受引力透镜效应影响会形成多个像，且由于路径长度不同，这些像出现的时间存在延迟。通过测量这种时间延迟，可以独立推导出宇宙的膨胀速率。目前，这项为期两年的JWST观测项目已执行过半。科学家寄希望于通过积累足够的大样本统计数据，来验证现有的测量矛盾究竟源于已知的系统误差，还是预示着我们需要修正基础物理模型。这不仅是对宇宙膨胀速率的重新校准，更是对现代宇宙学标准模型的一次深度审视。", "key_arguments": ["宇宙学目前最重大的谜团是两种相互矛盾的宇宙膨胀测量结果，这暗示了现有理论或测量手段存在根本性问题。", "解决争议的关键在于引入第三种完全独立的测量维度，即不依赖于现有两类方法的新型观测手段。", "利用JWST观测多重透镜超新星的时间延迟，被视为一种极具潜力的独立验证工具，有望提供决定性的统计证据。"], "mentioned_resources": ["JWST (James Webb Space Telescope) - 核心观测设备，用于执行为期两年的透镜调查计划。", "多重透镜超新星 (Multiply-lensed supernovae) - 文中提到的核心测量方法与研究对象。"], "keywords": ["宇宙膨胀 (Expanding Universe)", "哈勃张力 (Hubble Tension)", "引力透镜 (Gravitational Lensing)", "超新星 (Supernovae)", "宇宙学常数 (Cosmology)", "合理性检查 (Sanity Check)"], "style_tone": "严谨的科学前沿分析风格，带有对解决重大科学难题的期待感。"}</t>
+  </si>
+  <si>
+    <t>{"title": "真正的革命并非人工智能——而是意义 (Why the real revolution isn’t AI — it’s meaning)", "summary_long": "文章提出一个核心论断：当前正在发生的深度变革并非单纯的技术演进（AI），而是人类“意义感”的回归。随着“代理型人工智能”（Agentic AI）的兴起，现代企业的组织架构和协作逻辑（即所谓的“结缔组织”）正在被代码重新定义。这种变革不仅是效率的提升，更是权力的移交——AI 正在接管那些曾经需要人类进行协调、执行和逻辑处理的中间环节。\n\n在这种背景下，人类的角色发生了根本性的位移。当工具能够自主完成任务时，人类的稀缺性不再体现在“完成工作”的能力上，而体现在“赋予工作意义”的能力上。文章强调，未来的核心竞争力将属于那些能够驾驭悖论（Paradox）、在压力下进行即兴发挥（Improvise），并能从混乱的信息流中构建出连贯性（Coherence）的人。这标志着一种从“执行导向”向“意义导向”的范式转移：AI 处理逻辑与闭环任务，而人类负责处理模糊性、价值观判断以及在复杂系统中的导航。这场革命的本质是迫使人类回归其最本质的特征——创造意义。", "key_arguments": ["AI 革命的本质是组织逻辑的重写：代理型 AI 正在取代现代企业中起连接作用的中间逻辑和协作流程。", "人类价值的重塑：当执行力被自动化，人类的核心价值回归到“意义创造”和“目标设定”。", "未来生存的必备能力：在高度不确定的环境中，导航悖论、即兴应对压力以及从混乱中提取连贯性的能力将成为决定性的竞争优势。"], "mentioned_resources": ["代理型人工智能 (Agentic AI) - 被视为重构现代企业“结缔组织”的核心驱动力。", "现代企业模型 (Modern Firm) - 文中提到的被代码重新定义的组织实体。"], "keywords": ["Agentic AI (代理型人工智能)", "Human Meaning (人类意义)", "Connective Tissue (结缔组织)", "Paradox (悖论)", "Coherence (连贯性/一致性)", "Improvisation (即兴发挥)"], "style_tone": "富有洞察力的前瞻性评论，语调严谨且具有哲学高度，强调人文主义回归。"}</t>
+  </si>
+  <si>
+    <t>{"title": "硅谷的政治格局或许正在再度转变", "summary_long": "本文由未来学家 Peter Leyden 撰写，旨在纠正近期媒体关于“硅谷集体右转”的误读。Leyden 指出，硅谷的政治版图虽然发生了位移，但并非剧变：从 1990 年代约 80/20 的绝对左倾，演变为今日约 60/40 的温和左倾，整体基调依然偏向自由派。文章深入分析了“右翼科技势力（Right Tech）”近期转向支持特朗普的底层逻辑：这本质上是一场关于人工智能（AI）的政治豪赌。科技精英们认为特朗普政府会减少对 AI 这一颠覆性技术的行政干预，从而确保其在全球竞争中的领先地位。然而，Leyden 认为这种投机行为最终会适得其反。他提出，这反而为左翼力量创造了一个重夺领导权的战略契机。左翼若能提出一种“技术积极型（tech-positive）”且面向未来的 AI 愿景，将技术进步与“共同繁荣”及“物质富足（abundance）”的社会契约相结合，便能重新定义国家的发展方向并赢得科技界的核心支持。", "key_arguments": ["硅谷并未发生根本性的政治倒戈，其政治光谱仍保持 60/40 的左倾态势，而非媒体渲染的全面右转。", "科技界右翼对特朗普的拥护是基于实用主义的监管套利，旨在利用其不干预政策为 AI 发展铺路。", "左翼应通过构建‘技术积极型’的 AI 叙事，将 AI 与社会公平、共同富足挂钩，从而在政治竞争中反败为胜。"], "mentioned_resources": ["Peter Leyden (未来学家) - 本文作者，提出了硅谷政治格局演变的 80/20 到 60/40 转换模型。", "AI (人工智能) - 文中将其定义为‘改变世界的技术’，是当前硅谷政治博弈的核心筹码。", "Trump (特朗普) - 被右翼科技界视为实现 AI 监管豁免的政治工具。"], "keywords": ["硅谷政治 (Silicon Valley Politics)", "AI 监管 (AI Regulation)", "共同繁荣 (Shared Prosperity)", "富足 (Abundance)", "政治重组 (Political Realignment)", "技术积极主义 (Tech-positive)"], "style_tone": "逻辑严密的战略分析风格，带有前瞻性的未来主义色彩和政治洞察。"}</t>
+  </si>
+  <si>
+    <t>{"title": "人工智能时代“新型工作”将如何真正成形", "summary_long": "文章探讨了人工智能对未来工作形态的重塑，核心观点认为未来并非“人机对立”，而是“人机协作”与“纯人力”之间的竞争。AI 的本质并非替代，而是“增强”（Augmentation），它为人类提供了更锐利的工具，用以强化判断力、创造力和临场感。文章指出，未来能够脱颖而出的企业，将是那些懂得利用 AI 来提升人类贡献价值的公司。通过将人类从重复性劳动中解放出来，AI 使员工能够专注于只有人类才能完成的独特任务，从而实现工作本质的升华。这种转变要求我们重新审视工作的定义，将 AI 视为人类能力的延伸而非威胁。", "key_arguments": ["竞争范式转移：未来的竞争不是‘人 vs 机器’，而是‘人+机器 vs 纯人类’。", "AI 的功能定位：AI 是增强人类判断力、创造力和临场感（Presence）的锐利工具。", "企业获胜逻辑：成功的企业将利用 AI 释放人力，使其专注于人类独有的高阶贡献。"], "mentioned_resources": ["Big Think (平台) - 文章发布平台，探讨科技与商业前沿趋势。"], "keywords": ["增强 (Augmentation)", "人机协作", "判断力 (Judgment)", "创造力 (Creativity)", "临场感 (Presence)", "人类贡献 (Human Contribution)", "新型工作 (New Work)"], "style_tone": "前瞻性、理性且充满乐观主义的分析风格"}</t>
+  </si>
+  <si>
+    <t>{"title": "如何像莱特兄弟那样富有创新精神——无需电脑", "summary_long": "文章探讨了创新过程中的认知障碍及其突破路径。1895年，著名科学家开尔文勋爵（Lord Kelvin）曾断言飞机是不可能实现的，但仅十年后，莱特兄弟便证明了这一预言的荒谬。开尔文勋爵的失败源于一个普遍的思维陷阱：混淆了“概率（Probability）”与“可能性（Possibility）”。他因为实现飞行的统计概率极低，便错误地将其判定为物理上的不可能。与之形成鲜明对比的是，莱特兄弟在父亲的引导下，学会了“在故事中思考（Think in story）”。这种思维方式让他们能够超越眼前的技术局限和专家的否定，通过构建一种关于“如何实现”的叙事逻辑，将看似遥不可及的可能性逐步转化为现实。文章强调，真正的创新并不依赖于复杂的计算工具，而在于对可能性逻辑的深刻理解与坚持。", "key_arguments": ["专家预言的局限性：顶尖科学家也会因为认知偏差（混淆概率与可能性）而对未来做出错误判断。", "概率与可能性之辩：创新者必须区分‘极低概率的事物’与‘物理上不可能的事物’，前者往往是创新的蓝海。", "故事思维（Thinking in Story）：这是一种关键的认知工具，通过构建实现目标的逻辑叙事，可以驱动创新者突破现有的认知边界。"], "mentioned_resources": ["开尔文勋爵 (Lord Kelvin) - 1895年预言飞机不可能实现的著名科学家，代表了基于概率的保守思维。", "莱特兄弟 (Wright brothers) - 飞机的发明者，通过实践推翻了当时的科学定论。", "米尔顿·莱特 (Milton Wright，莱特兄弟之父) - 鼓励儿子们采用“故事思维”的关键启蒙者。"], "keywords": ["概率 vs. 可能性 (Probability vs. Possibility)", "故事思维 (Thinking in Story)", "认知偏差", "创新逻辑", "莱特兄弟"], "style_tone": "逻辑严密的启发式分析风格，带有对传统权威的批判性反思。"}</t>
+  </si>
+  <si>
+    <t>{"title": "美国宇航局观测了这颗超新星爆发膨胀长达25年", "summary_long": "本文探讨了人类对开普勒超新星（SN 1604）长达四个世纪的观测演进，重点介绍了美国宇航局（NASA）钱德拉X射线天文台（Chandra X-ray Observatory）在过去25年间的突破性贡献。1604年，约翰内斯·开普勒观测到了这颗当时被称为“新星”的肉眼可见超新星，而400多年后的今天，该爆炸遗迹依然是天文学研究的焦点。文章指出，这颗由白矮星爆炸形成的超新星遗迹并未静止，通过钱德拉天文台自2000年以来的长期成像监测，科学家们得以实时观测到爆炸产生的碎屑流和冲击波在星际空间中的扩张与演变。这种跨越1/4世纪的动态观测视角，不仅揭示了超新星爆发后的物理性质，还为理解白矮星爆炸的本质及其对周围环境的影响提供了珍贵的长期演化数据。这种“长镜头”式的科研方式，将历史观测与现代高能物理手段相结合，连接了古典天文学与现代空间科学。", "key_arguments": ["长期动态监测的必要性：静态图像无法捕捉宇宙事件的演化，钱德拉天文台25年的连续观测让科学家能“看见”冲击波的扩张。", "历史与现代的科学传承：从开普勒的肉眼观测到现代X射线探测，同一天体目标见证了人类观测技术的跨代飞跃。", "白矮星爆炸性质的深入理解：通过对遗迹碎屑和冲击波演变的定量分析，可以反推超新星爆发的初始条件和物理机制。"], "mentioned_resources": ["钱德拉X射线天文台 (NASA's Chandra X-ray Observatory) - 自2000年起对超新星遗迹进行长期成像的主力设备。", "开普勒超新星 / SN 1604 (Johannes Kepler) - 1604年由开普勒记录的超新星，本文的研究主体。", "《新星》(Stella Nova) (Johannes Kepler) - 文中提到开普勒当时对该现象的命名与认知。"], "keywords": ["超新星遗迹 (Supernova Remnant)", "白矮星 (White Dwarf)", "冲击波 (Shockwave)", "X射线天文学 (X-ray Astronomy)", "时域天文学 (Time-domain Astronomy)", "星际介质 (Interstellar Medium)"], "style_tone": "科普叙事风格，兼具科学严谨性与对宇宙演化的敬畏感。"}</t>
+  </si>
+  <si>
+    <t>{"title": "《宇宙大爆炸》播客第125期——大尺度结构 (Starts With A Bang Podcast #125: Large-Scale Structure)", "summary_long": "本期内容聚焦于宇宙从微观涨落到宏观结构的演化史。在宇宙大爆炸初期，宇宙处于极高温、高密度且近乎完美均匀的状态，但这种均匀并非绝对，而是预埋了被称为“种子涨落”（seed fluctuations）的初始不完美性。随着宇宙的持续膨胀，在物质与能量的相互作用下，引力与电磁力共同主导了演化进程，使这些微小的密度差异逐渐坍缩、聚集，最终形成了我们今天在晚期宇宙中观测到的宏大“宇宙网”（Cosmic Web）。\n\n文章强调了科学研究的核心方法论：通过将精密物理理论的预测结果与直接的天文观测数据进行严苛对比，科学家得以反推宇宙的物质构成及其动力学行为。讨论的核心悬念在于，这种对大尺度结构的深入研究是否能揭示“暗能量”的本质——即暗能量是否随时间演化，而非一个恒定的常数。这对于理解宇宙的终极命运具有决定性意义。", "key_arguments": ["宇宙结构的起点：现今复杂的宇宙大尺度结构并非凭空产生，而是源于大爆炸初期量子尺度的初始涨落。", "物理力的协同演化：宇宙网的形成是引力坍缩与宇宙膨胀、电磁力等多种物理机制在百亿年间博弈的结果。", "暗能量的动态性：通过观测大尺度结构的分布与演变，可以验证暗能量是否具有演化特性，这是当前宇宙学前沿的核心议题。"], "mentioned_resources": ["《Starts With A Bang》Podcast Episode 125 (Ethan Siegel) - 探讨宇宙大尺度结构形成及暗能量性质的专题播客。"], "keywords": ["大尺度结构 (Large-scale structure)", "宇宙网 (Cosmic web)", "种子涨落 (Seed fluctuations)", "暗能量演化 (Dark energy evolution)", "引力坍缩 (Gravitational collapse)"], "style_tone": "严谨的科学科普风格，带有前沿探索的启发性。"}</t>
+  </si>
+  <si>
+    <t>{"title": "空中外星人：为何多云世界可能更易探测生命 (Aerial aliens: Why cloudy worlds might make detecting life easier)", "summary_long": "本文探讨了寻找地外生命的一种创新路径，核心聚焦于康奈尔大学卡尔·萨根研究所（Carl Sagan Institute）创始人、天文学家 Lisa Kaltenegger 的最新研究。文章指出，传统的生物特征探测往往依赖于大气气体成分，而 Kaltenegger 的研究提出了一种新的“生物特征”：生物色素（Biopigments）。这些由微生物产生的可观测颜色，可能成为我们在遥远行星上识别生命的关键线索。在与天文学家 Adam Frank 的对话中，Kaltenegger 进一步阐述了这种方法的潜力，特别是在那些拥有浓厚云层的系外行星上。传统观点可能认为云层会阻碍观测，但该研究暗示，如果生命存在于这些行星的云层中（即“空中外星人”的概念），其产生的生物色素信号可能反而更容易被探测到。这种视角不仅拓宽了生物特征的定义范畴，也为近未来利用先进望远镜探测地外生命提供了具体的科学模型和期待方向。", "key_arguments": ["生物色素（Biopigments）可作为一种全新的、可观测的生物特征（Biosignature），用于识别系外行星上的微生物生命。", "寻找地外生命不应局限于固态表面，多云世界的云层大气可能是生命存在并产生可探测信号的重要生境。", "通过模拟微生物产生的特定颜色，科学家可以为下一代空间望远镜提供更精准的“生命搜索图谱”。"], "mentioned_resources": ["Lisa Kaltenegger 的生物色素研究 (Lisa Kaltenegger) - 核心研究课题，探讨微生物颜色作为生物特征的可能性。", "卡尔·萨根研究所 (Carl Sagan Institute at Cornell University) - Lisa Kaltenegger 担任创始主任的研究机构，致力于跨学科寻找宇宙生命。"], "keywords": ["生物色素 (Biopigments)", "生物特征 (Biosignature)", "系外行星 (Exoplanets)", "空中生命 (Aerial Life)", "卡尔·萨根研究所", "天体生物学"], "style_tone": "前瞻性的科学访谈风格，严谨且富有启发性。"}</t>
+  </si>
+  <si>
+    <t>{"title": "问伊桑：在膨胀的宇宙中，“引力束缚”是什么意思？", "summary_long": "本文探讨了宇宙物理学中一个至关重要的界限：引力束缚（Gravitationally Bound）与非束缚状态的区别，并将其置于宇宙膨胀的大背景下讨论。文章首先确立了基础物理模型：当两个大质量物体相遇时，它们要么通过引力相互锁定，形成稳定的轨道运行（即引力束缚），要么因动能过大而擦肩而过，永不相见（即非引力束缚）。这一区分的意义远超天体力学中的彗星轨道周期判定，它是决定宇宙宏观结构演化的核心机制。在膨胀的宇宙中，引力束缚不仅关乎物体是否能聚集成团，更决定了物体之间的“可达性”。随着宇宙空间的持续扩张，只有那些处于引力束缚状态的系统（如星系团内部）能够抵抗这种扩张力而保持完整；而那些非束缚的物体则会随着空间的膨胀而加速远离，最终彻底消失在彼此的视界之外。因此，理解引力束缚的边界，本质上是在预判宇宙中各类天体乃至文明的终极命运——即谁将留在我们的生命圈内，谁将永远遁入虚无。", "key_arguments": ["引力束缚的本质是物体间能否形成稳定的闭合轨道，而非仅仅是短暂的引力相互作用。", "宇宙膨胀与局部引力之间存在竞争关系，这种竞争决定了宇宙结构的存续或解体。", "引力束缚的边界线（The border）是决定宇宙未来命运的‘存在主义’分水岭，决定了天体间的长期可达性。"], "mentioned_resources": ["《Ask Ethan》(Ethan Siegel) - 文章所属的科普专栏系列，旨在解答深奥的宇宙物理问题。"], "keywords": ["引力束缚 (Gravitationally Bound)", "宇宙膨胀 (Expanding Universe)", "宇宙命运 (Future Fate)", "可达性 (Reachability)", "存在主义重要性 (Existentially Important)"], "style_tone": "严谨且富有洞察力的科学普及风格，带有对宇宙终极命运的哲学思考。"}</t>
+  </si>
+  <si>
+    <t>{"title": "至今仍影响人们对女性健康认知误区的医学迷思", "summary_long": "文章探讨了“癔症”（Hysteria）这一医学概念如何从古希腊时期到弗洛伊德时代，演变为一种压制女性身体痛苦的文化框架。长期以来，医生利用这一概念将女性的生理病痛归结为情绪不稳定，从而在医学诊断中忽视其真实的身体诉求。随着医学进步，许多曾被贴上“癔症”标签的症状已被证实具有明确的神经学或生物学病因。然而，癔症理论的演变不仅是医学问题，更是社会权力和性别规范的缩影。这种历史积淀形成的偏见至今仍在发挥余热，导致现代医学体系中依然存在对女性疼痛表达的不信任感，形成了所谓的“隐形疾病”困境。", "key_arguments": ["癔症在历史上并非单纯的医学诊断，而是一种允许医生将女性生理痛苦解释为情绪问题的文化工具。", "医学史上的癔症论述反映了当时的社会权力结构和性别准则，而非客观的科学事实。", "尽管现代医学已证明许多相关症状有生物学基础，但历史遗留的偏见仍导致现代医学对女性疼痛的系统性忽视。"], "mentioned_resources": ["希波克拉底 (Hippocrates) - 文中提到的癔症概念历史起点人物", "弗洛伊德 (Freud) - 将癔症理论推向心理分析层面的关键历史人物", "《Invisible Illness》 (Big Think 推荐书籍/专题) - 探讨女性在医学中被忽视的痛苦及相关历史背景"], "keywords": ["癔症 (Hysteria)", "性别规范 (Gender Norms)", "医学偏见 (Medical Bias)", "女性健康 (Women's Health)", "情绪不稳定 (Emotional Instability)", "神经学病因 (Neurological Causes)"], "style_tone": "批判性学术分析风格，带有对历史不公的审视与人文关怀。"}</t>
+  </si>
+  <si>
+    <t>{"title": "人工智能如何让我们陷入短视思维 (How AI is making us think short-term)", "summary_long": "本文核心探讨了作家 Dan Wang 关于人工智能（AI）如何重塑人类时间观的深度洞察。Wang 认为，AI 正在发挥一种“时间压缩”效应，使人类的思维跨度变得越来越短。这种短视倾向主要源于当前社会对 AI 极度两极化的认知：要么将其视为通往乌托邦的阶梯，要么将其视为导致世界末日的元凶。这种“全有或全无”的极端叙事产生了一个严重的副作用，即让“长期的制度建设（Institution-building）”显得毫无意义——如果未来要么是瞬间的繁荣，要么是彻底的毁灭，那么耗费数十年去构建稳固的组织、法律或文化框架就失去了逻辑支撑。文章进一步将这一逻辑延伸至更广泛的社会现象，指出在这样一个被技术加速、充满非理性的世界中，赌博的诱惑力在增加，而领导力则陷入了“符号化高管”的困境，即高管们更倾向于表演性的符号化管理，而非实质性的长期战略领导。整体而言，AI 的加速发展正在剥夺人类进行深思熟虑、跨代建设的能力。", "key_arguments": ["AI 充当了‘时间压缩器’，使人类的决策视野和心理预期跨度显著缩短。", "关于 AI 的极化叙事（乌托邦 vs. 末日论）消解了中长期制度建设的必要性与动力。", "技术加速导致社会进入‘非理性繁荣’，表现为投机行为（如赌博）的盛行和领导力的符号化、空心化。"], "mentioned_resources": ["Dan Wang (作者) - 提出‘AI 压缩时间感’及‘制度建设失效’核心论点的思想家。", "《符号化高管的时代》(The era of the symbolic executive) - 文中引用的相关专题，探讨现代企业领导力如何变得更具表演性而非实质性。", "《非理性世界中的赌博诱惑》(The allure of gambling in an irrational world) - 文中提及的关联论据，用以佐证短视思维下的社会行为模式。"], "keywords": ["时间压缩 (Time Compression)", "短视思维 (Short-termism)", "制度建设 (Institution-building)", "极化思维 (Polarized Thinking)", "符号化高管 (Symbolic Executive)", "技术末日论 (Apocalyptic AI)", "技术乌托邦 (Utopian AI)"], "style_tone": "深刻的社会批判风格，带有技术哲学色彩的忧虑与理性分析。"}</t>
+  </si>
+  <si>
+    <t>{"title": "芝诺悖论由物理学而非仅靠数学得以解决", "summary_long": "文章探讨了拥有两千多年历史的经典哲学难题——芝诺悖论（Zeno's Paradox）。该悖论的核心逻辑在于“二分法”：即在到达任何目的地之前，旅行者必须首先跨越路程的一半，随后是剩下路程的一半，以此类推。由于空间在逻辑上可以被无限次地“减半”，芝诺据此质疑运动的可能性，认为跨越无限个步骤在逻辑上是无法完成的。长期以来，这一难题困扰着无数思想家。\n\n文章指出，虽然现代数学通过微积分和无穷级数（如 1/2 + 1/4 + 1/8... = 1）证明了无限项之和可以收敛为一个有限的数值，从而在抽象逻辑上提供了某种解答，但这并不能完全消除人们对物理现实中“如何跨越无限”的困惑。真正的突破口在于物理学，而非纯粹的数学抽象。物理学通过引入“速率”（Rate）的概念——即距离随时间变化的动态关系——解决了这一矛盾。在物理现实中，物体并非在进行离散的、无穷步的数学跳跃，而是在连续的时空中以特定速率运动。通过理解时间与距离的函数关系，物理学证明了在有限的时间内跨越这些逻辑上的“无限分割点”是完全符合自然规律的。文章强调，只有将运动视为物理过程而非纯粹的几何分割，才能真正理解我们是如何抵达目的地的。", "key_arguments": ["芝诺悖论基于空间的无限可分性，推导出运动在逻辑上是不可能的结论。", "数学上的无穷级数求和虽然证明了无限项之和为有限值，但仍属于抽象层面的解释。", "物理学通过引入‘速率’（距离与时间的比例关系）这一核心变量，从现实维度彻底解决了运动的连续性问题。"], "mentioned_resources": ["芝诺悖论 (Zeno's Paradox) - 古希腊哲学家芝诺提出的关于运动不可分性的经典哲学命题。"], "keywords": ["芝诺悖论", "无穷级数 (Infinite Series)", "速率 (Rate)", "时空连续性", "二分法 (Dichotomy)", "收敛 (Convergence)"], "style_tone": "逻辑严密的科学科普风格，带有对经典哲学问题进行现代物理审视的理性色彩。"}</t>
+  </si>
+  <si>
+    <t>{"title": "宇宙尘埃：“过量过早”不再！ (Cosmic Dust: “Too Much Too Soon” No More!)", "summary_long": "本文探讨了天文学界关于早期宇宙尘埃形成的重大谜题及其最新进展。自第一代恒星形成以来，宇宙尘埃便填充着星际与星系周介质。然而，詹姆斯·韦伯空间望远镜（JWST）在观测最遥远的早期星系时，发现其尘埃含量之丰富、亮度之高，远超此前理论模型的预期，引发了关于尘埃是否“出现得过早且过量”的科学质疑。为了破解这一矛盾，天文学家将目光转向了近邻的矮星系 Sextans A。通过对该星系的观测，研究者获得了一个理解早期宇宙的“局部样本”。Sextans A 的环境特征帮助科学家重新校准了尘埃形成模型，证明在特定条件下（如低金属丰度环境），尘埃的产生效率与存续状态能够解释 JWST 的观测结果。这一发现不仅消解了“过量过早”的矛盾，更代表了人类对宇宙演化秩序理解的一次深刻进步。", "key_arguments": ["JWST 的观测挑战了传统认知：早期星系的尘埃丰度远高于旧有模型的预测，暗示尘埃形成速度可能比想象中更快。", "Sextans A 作为关键的“局部实验室”：通过观测这个低金属丰度的近邻矮星系，可以模拟并推断早期宇宙的物理过程。", "宇宙秩序的回归：新的观测数据表明，早期宇宙的尘埃丰富并非理论错误，而是反映了我们对恒星形成及尘埃演化机制（尤其在极端环境下）的认知正在完善。"], "mentioned_resources": ["JWST (James Webb Space Telescope) - 核心观测工具，发现了遥远星系中超预期的尘埃含量。", "Sextans A (矮星系) - 被用作研究早期宇宙物理条件的近邻类比对象。"], "keywords": ["宇宙尘埃 (Cosmic Dust)", "JWST", "Sextans A", "早期星系 (Early Galaxies)", "金属丰度 (Metallicity)", "星际介质 (Interstellar Medium)"], "style_tone": "严谨的科学前沿报道，带有发现真理后的释然与启发感。"}</t>
+  </si>
+  <si>
+    <t>{"title": "成功领导力发展体系的六个要素", "summary_long": "文章批判了当前企业领导力培训中普遍存在的“三分钟热度（flavor of the month）”现象。作者指出，全球每年在领导力开发上投入巨资，但大多是孤立、一次性的项目，缺乏实证研究支持的投资回报，且未遵循人类发展规律。为了解决这一困境，作者提出必须实现从“单一项目（Program）”向“系统化体系（System）”的范式转移。\n\n该体系的构建始于确立“领导力原则”，这些原则需根据组织具体情境（如地域、行业）定制，作为发展的路线图。在此基础上，文章提出了构建领导力体系的六大核心要素：1. 评估（如基于原则的360度反馈）；2. 个人发展路径（对齐原则的个性化学习与任务）；3. 持续性培训（将培训嵌入组织价值观，而非偶发事件）；4. 挑战性任务（Stretch assignments，通过高可见度或高难度项目锻炼特定能力）；5. 绩效教练（基于原则的持续对话与行动后反思）；6. 持续问责与绩效管理（将表现短板与组织DNA挂钩）。作者强调，只有将这些要素有机整合，使其相互作用，才能真正建立起强有力的领导力文化，摆脱低效的碎片化培训模式。", "key_arguments": ["领导力开发应从“孤立项目”转向“整合系统”，以符合成人学习理论和系统思维。", "领导力原则是体系的基石，必须根据组织的具体语境（Context）进行定制，而非套用通用模板。", "发展应嵌入在日常工作中（如挑战性任务和持续教练），而非脱离工作的课堂教学。", "评估、培训、任务、教练和问责这六个要素必须高度对齐（Alignment），共同指向核心领导力原则。"], "mentioned_resources": ["How to Make a Leader (Podcast) - 作者推荐用于深入探索领导力实践的播客资源。", "成人学习理论/系统思维/人类发展/领导力理论 (Adult learning theory, systems thinking, human development, and leadership theory) - 本文体系构建的理论基础。"], "keywords": ["领导力体系 (Leadership System)", "挑战性任务 (Stretch Assignments)", "组织DNA (Organizational DNA)", "成人学习理论 (Adult Learning Theory)", "系统思维 (Systems Thinking)", "360度反馈 (360-degree Feedback)", "三分钟热度 (Flavor of the month)"], "style_tone": "逻辑严密的管理咨询风格，带有对现状的批判性反思，强调实证与系统性。"}</t>
+  </si>
+  <si>
+    <t>{"title": "历史上最成功的信息技术，往往是我们几乎察觉不到的", "summary_long": "本文提出一个核心观点：书籍不应仅仅被视为思想的容器，而应被理解为一种极度成功且深刻改变人类认知的信息技术。文章通过回顾书籍的物理演化史——从早期的泥板（tablets）到具有革命意义的抄本（codex）——揭示了媒介形态的改变如何直接提升了知识的可及性、可扩展性以及人类在共享知识上的协作力量。这种技术演进不仅改变了信息的存储方式，更重塑了人类处理和理解信息的能力。在当代语境下，文章对比了生成式AI与书籍的差异。尽管生成式AI在处理当前的信息过载问题上展现出巨大潜力，能够帮助人类在海量数据中导航，但文章强调，书籍拥有AI无法替代的独特价值：它们是传递人类经验的终极媒介，并能持续激发和维持批判性思维。作者认为，这种深度思考的能力是构建和维持一个健康社会所不可或缺的基石，而书籍作为一种“隐形”的技术，其对人类文明的塑造力远超我们的日常感知。", "key_arguments": ["书籍本质上是一种扩展人类认知边界的信息技术，而非单纯的内容载体。", "书籍形态从泥板到抄本的演进，是人类信息处理能力、知识协作效率的一次重大技术飞跃。", "在AI时代，书籍在传递人类主观经验和培养批判性思维方面的功能具有不可替代性。"], "mentioned_resources": ["泥板 (Tablets) - 文中提到的书籍早期物理形态，代表了知识记录的开端。", "抄本 (Codex) - 文中强调的书籍演化关键阶段，显著提升了知识的可及性与协作力。"], "keywords": ["信息技术 (Information Technology)", "认知扩展 (Cognitive Expansion)", "抄本 (Codex)", "生成式AI (Generative AI)", "批判性思维 (Critical Thinking)", "人类经验 (Human Experience)"], "style_tone": "富有洞察力的人文主义评论风格，逻辑严密且带有对传统媒介的深切致敬。"}</t>
+  </si>
+  <si>
+    <t>{"title": "7000年前的大西洋水下石墙：古代工程奇迹与失落之城的现实原型", "summary_long": "科学家在大西洋水面以下约30英尺处，发现了一段长度接近400英尺的人造石墙。这一发现之所以引起学界震动，是因为其建造年代可追溯至7000多年前，属于新石器时代的狩猎采集社会。这一时间节点和建造规模挑战了传统考古学对“狩猎采集者”工程能力的认知，暗示了史前人类在定居文明出现前就已具备高度的社会协作与大型工程规划能力。\n\n目前，关于这段石墙的具体功能仍处于科研推测阶段，尚未达成定论。它可能是用于防御、围猎或是某种具有仪式意义的边界。然而，其地理位置的变迁——从陆地建筑变为水下遗迹——揭示了海平面上升对古代人类栖息地的深刻影响。研究人员进一步提出，这类真实存在的沉没建筑，极有可能是当地流传已久的“被大海吞噬的失落之城”传说的物质原型。文章通过这一发现，试图在严谨的考古实证与浪漫的民间神话之间建立逻辑联系，探讨地质灾变如何转化为人类的集体记忆。", "key_arguments": ["史前狩猎采集者具备远超此前认知的工程协作能力，能够建造长达400英尺的石质结构。", "该水下遗迹的发现为‘失落之城’等海洋神话提供了潜在的现实依据，暗示神话可能是对远古地质变迁的记忆加工。", "海平面的上升导致了古代人类文明遗迹的淹没，这要求现代考古学更多地关注水下领域以重构人类历史。"], "mentioned_resources": ["大西洋水下石墙 (Atlantic Submarine Wall) - 位于水下30英尺、长400英尺的史前遗迹，由7000年前的狩猎采集者建造。"], "keywords": ["狩猎采集者 (Hunter-gatherers)", "史前工程 (Prehistoric engineering)", "海平面上升 (Sea-level rise)", "失落之城 (Lost City)", "集体记忆 (Collective memory)", "新石器时代 (Neolithic)"], "style_tone": "严谨的科学发现与神秘主义色彩相结合的探索风格"}</t>
+  </si>
+  <si>
+    <t>{"title": "詹姆斯·韦伯太空望远镜观测到的最遥远星系中的氧气究竟意味着什么？", "summary_long": "詹姆斯·韦伯太空望远镜（JWST）自投入使用以来，在探测宇宙极早期星系方面展现了超越以往任何观测设备的卓越能力。这些被发现的原始星系展现出了令人惊叹的特征，包括已进化的星系结构、极高的亮度、清晰的发射线，以及包含氧气在内的重元素。针对大众媒体和部分观点认为“早期宇宙发现氧气是巨大惊喜”的看法，本文作者提出了批判性的反驳。作者指出，在宇宙演化模型中，大质量恒星的生命周期极短，它们能迅速通过超新星爆发将氧等重元素播撒至星际空间。因此，在JWST观测到的这些早期星系中发现氧气，实际上是符合天体物理逻辑的必然结果。文章最后强调，科学界真正渴望寻找的“圣杯”并非含有氧气的星系，而是一个完全不含氧气的、由纯粹原始物质组成的星系。这种“无氧星系”将标志着我们真正触及了第一代恒星（第三星族星）诞生的时刻，那才是揭开宇宙起源真相的关键节点。", "key_arguments": ["JWST观测到的早期星系并非完全‘原始’，而是展现出拥有重元素和进化结构的复杂特征。", "在极早期星系中发现氧气不应被视为意外，因为大质量恒星的快速演化足以在极短时间内产生这些重元素。", "天文观测的真正挑战和终极目标是寻找‘无氧星系’，即尚未被重元素污染的宇宙第一代恒星产物。"], "mentioned_resources": ["James Webb Space Telescope (JWST) - 本文核心观测工具，用于探测宇宙最深处的原始星系。", "Oxygen (Element) - 作为衡量星系演化程度的关键化学指标。"], "keywords": ["JWST", "早期星系 (Primitive Galaxies)", "氧气探测 (Oxygen Detection)", "重元素 (Heavy Elements)", "恒星演化 (Stellar Evolution)", "无氧星系 (Oxygen-free Galaxy)", "第三星族星 (Population III stars)"], "style_tone": "严谨的科学评论风格，带有对流行科学误读的纠偏色彩。"}</t>
+  </si>
+  <si>
+    <t>{"title": "问伊森：为什么不存在反重力？", "summary_long": "本文探讨了物理学中一个深层且基础的问题：为什么在我们的宇宙中不存在“反重力”现象。文章首先回顾了牛顿的万有引力定律，指出在牛顿的视角下，所有质量之间都是相互吸引的，其根本原因在于自然界中不存在可以产生排斥作用的“负质量”。随后，文章转向爱因斯坦的广义相对论，提供了更现代的解释：物质和能量会导致时空发生弯曲，而这种时空的弯曲在我们看来就是引力。作者提出一个理论假设，即如果存在某种形式的“负质量”或“负能量”，时空可能会以相反的方式弯曲，从而产生所谓的“反重力”效应。然而，现实观测表明，这种假设并不符合我们所处的宇宙。这一事实揭示了引力与其他基本力（如电磁力）之间的本质区别。电磁力由于存在正负电荷，因此同时具备吸引和排斥的特性；而引力在我们的宇宙中似乎是独一无二的单向吸引力。文章通过这种对比，强调了引力在宇宙架构中的特殊地位及其背后的深刻物理逻辑。", "key_arguments": ["牛顿力学中引力仅表现为吸引，是因为自然界缺乏对应的“负质量”实体。", "广义相对论将引力定义为时空曲率，反重力的存在前提是必须有能导致时空“反向弯曲”的负能量或负质量。", "引力与电磁力具有根本性的对称性差异：电磁力具有双向性（吸与斥），而引力在已知宇宙中仅具有单向性（吸）。"], "mentioned_resources": ["牛顿万有引力定律 (Isaac Newton) - 论证引力作为质量间相互吸引力的经典物理基础。", "广义相对论 (Albert Einstein) - 解释物质/能量如何通过弯曲时空产生引力效应的核心理论模型。"], "keywords": ["反重力 (Antigravity)", "负质量 (Negative mass)", "时空曲率 (Spacetime curvature)", "广义相对论 (General relativity)", "电磁力 (Electromagnetism)", "负能量 (Negative energy)"], "style_tone": "严谨的科普分析风格，逻辑清晰且富有启发性。"}</t>
+  </si>
+  <si>
+    <t>{"title": "林叶｜枯木之花还能绽放吗？——日本爱知三年展观展札记", "summary_long": "本文是艺评人林叶针对2025年第六届日本爱知三年展的深度观展札记。展览由霍尔·卡西米公主策划，主题取自叙利亚诗人阿多尼斯的诗句“灰烬与玫瑰之间的时间”，核心在于挑战启蒙运动以来根深蒂固的二元论认知体系，探讨在文明危机中“破而后立”的可能性。文章通过三个展区的巡礼，勾勒出一条从反思人类中心主义到重构人与自然关系的逻辑路径。\n\n在主展区爱知艺术文化中心，作者通过穆利亚纳、大小岛真木等人的作品，展示了海洋生机与全球变暖导致的死亡意象之间的剧烈张力。杉本博司的作品与战后壁画的并置，揭示了现代科学对自然的收编与控制。特别是是恒樱与约翰·阿科姆夫拉关于捕鲸的作品，深刻批判了人类文明内部膨胀的贪婪与异化力量，这种力量正将人类引向自我毁灭。在爱知县陶瓷美术馆，展览转向了地质与土地的视角，埃琳娜·达米亚尼和玛丽莲·博罗尔·鲍尔的作品通过物质媒介（陶瓷、混凝土）探讨了地质时间的长程流动以及殖民背景下原住民自然智慧的坚韧。最后，在濑户市区展区，梅莎·阿卜杜拉、罗伯特·安德鲁及阿德里安·比利亚尔·罗哈斯的作品将视角推向了更宏大的维度——从女性立场消化异化力量，到展现自然界潜藏的永恒伟力，再到以“外星人”的客观视角审视人类文明。作者总结认为，唯有瓦解现有的等级体系，从多元、非线性的时空维度出发，人类文明才可能与自然重新达成平衡。", "key_arguments": ["否定二元论认知：挑战启蒙思想下的二元边界（如人/自然、战争/希望），构想一种人类与环境交融的非极化状态。", "批判人类中心主义与文明异化：揭示人类利用现代文化技术对自然进行的全面收编，以及这种傲慢如何演变成一种自我毁灭的异化力量。", "重构人与自然的关系：主张通过地质视角、女性视角、原住民智慧及超越人类维度的时空观，打破线性发展的时空意识，寻找文明的平衡点。"], "mentioned_resources": ["《时光的皱纹》(阿多尼斯) - 提供了“破而后立”的思想基础。", "《灰烬与玫瑰之间的时间》(阿多尼斯) - 2025年爱知三年展的主题来源。", "《海流与开花之间》(穆利亚纳) - 回收毛线编织作品，对比海洋生机与白化死亡。", "《明日的收获》(大小岛真木) - 描绘超越人类认知的生态系统。", "《透视画馆》(杉本博司) - 探讨人类社会对自然世界的收编与控制。", "《四分钟》系列(巴希姆·沙克尔) - 描绘2003年美国入侵伊拉克的战争场景。", "《白霜形成之后，唤醒在我们脚边沉睡的鲸鱼》(是恒樱) - 揭示人类控制鲸鱼的残忍与贪婪。", "《眩晕之海》(约翰·阿科姆夫拉) - 三屏影像装置，涉及捕鲸、海难移民、奴隶船及核试验。", "《白鲸》(赫尔曼·梅尔维尔) - 文中引用的文学意象，类比捕鲸的暴力。", "《缓解III》(埃琳娜·达米亚尼) - 将物质世界中的地质时间流动形象化。", "《西西弗斯的柘树》(西条茜) - 探讨劳动、身体与陶瓷物质的亲和力。", "《水凝为混凝土》(玛丽莲·博罗尔·鲍尔) - 揭示统治阶级对原住民的创伤及自然智慧的传承。", "《你不会打败我》(梅莎·阿卜杜拉) - 从女性/母性立场消化文明的异化力量。", "《潜藏之物》(罗伯特·安德鲁) - 展现自然界中超越人类文明的永恒力量。"], "keywords": ["破而后立", "人类中心主义", "二元论", "异化力量", "地质时间", "原住民智慧", "非线性时空", "生态平衡"], "style_tone": "充满人文关怀与哲学思辨的艺评风格，基调深沉且具有批判性。"}</t>
+  </si>
+  <si>
+    <t>{"title": "梁捷｜李斯特的铁路梦 #为了幸福专栏08", "summary_long": "本文深度评述了19世纪德国经济学家弗里德里希·李斯特（Friedrich List）的生平及其经济思想。李斯特被视为古典经济学（亚当·斯密）最强有力的挑战者，他开创了“历史学派”，主张经济理论应立足于本国国情而非盲目追随英国式的自由放任。李斯特的思想萌芽于对1816年德国大饥荒及难民潮的实地调查，这段经历让他确立了建立服务于国民福祉和国家发展的经济体系的目标。\n\n李斯特的一生充满了抗争与流亡。他曾因推动德意志关税统一和民主改革遭受政治迫害，被迫流亡美国。在美国期间，他不仅通过经营煤矿和修建铁路积累了工程实践经验，还撰写了《美国政治经济学大纲》，确立了其贸易保护主义和经济民族主义的立场。1832年回国后，他以美国大使身份作为掩护，致力于推动莱比锡—德累斯顿铁路建设，并提出了宏大的“德意志十字形铁路网”构想。他认为铁路是实现国家统一的物质基础，具有多重战略价值：打破地理壁垒加强民族凝聚力、作为“龙头产业”带动重工业、提升军事防御能力以及促进思想文化传播。\n\n尽管李斯特倡导的“德意志关税同盟”在1834年得以实现，但他个人的铁路梦却因资金和政治阻力进展缓慢。晚年的李斯特陷入财务破产、政治监视和健康恶化的多重困境。1846年，随着英国废除《谷物法》标志着自由贸易的全面胜利，李斯特在理论与现实的双重打击下陷入绝望，最终开枪自杀。具有讽刺意味的是，在他死后，德国铁路建设才真正进入狂飙突进的阶段，最终支撑了德意志的统一与崛起。", "key_arguments": ["批判古典经济学的普适性：认为亚当·斯密的自由贸易论是为发达英国量身定制的，落后国家（如当时的德国）若照搬则会扼杀本土产业。", "经济民族主义与国家干预：主张国家应通过关税保护和政策干预，培育本国的“广义生产力”，而非仅仅追求眼前的交换价值。", "铁路作为国家统一的战略支点：铁路不仅是交通工具，更是重塑国家地理格局、带动重工业产业链、强化军事防御和民族认同感的核心基础设施。", "历史学派的先驱：强调经济发展必须经历不同的历史阶段，政策选择应随国家发展阶段的变化而调整。"], "mentioned_resources": ["《弗里德里希·李斯特传》 ([德] 欧根·文得乐) - 详细记录李斯特生平的传记作品。", "《美国政治经济学大纲》 (1827, 弗里德里希·李斯特) - 李斯特在美国流亡期间撰写的论战性著作，奠定了其保护主义思想。", "《政治经济学的国民体系》 (1841, 弗里德里希·李斯特) - 李斯特思想的集大成之作，系统阐述了国民经济体系和铁路战略。", "《莱茵报》 - 李斯特曾被委任为主编（后因病未就任），卡尔·马克思在此报纸崭露头角。", "《谷物法》 (英国法律) - 其废除标志着英国转向自由贸易，对李斯特的理论构成重大打击。"], "keywords": ["弗里德里希·李斯特", "经济民族主义", "历史学派", "德意志关税同盟", "十字形铁路网", "贸易保护", "生产力理论", "后发国家追赶"], "style_tone": "带有浓厚悲剧英雄色彩的人物传记风格，逻辑严密且充满人文关怀，评价客观且具有历史纵深感。"}</t>
+  </si>
+  <si>
+    <t>{"title": "朱晓阳｜闲言碎语拼贴出罗马都市民族志——读《逐出永恒》", "summary_long": "本文是北京大学社会学系教授朱晓阳对迈克尔·赫茨菲尔德（Michael Herzfeld）著作《逐出永恒：现代罗马城的重构》的深度书评。文章首先指出，传统的“村庄式”研究方法难以捕捉大都市的复杂性，而赫茨菲尔德通过“偷听”街头巷尾的闲言碎语并进行碎片化拼贴，成功构建了一种契合城市生活逻辑的“城市现象学”。这种写作方式抛弃了追求完整个人史或宏大叙事的传统，转而依靠作者对地方文化、历史和人情的敏锐洞察力，将语言碎片重构为具有美感的民族志。\n\n文章核心探讨了赫茨菲尔德的三个关键理论：1. “担当的人类学”（Engaged Anthropology）：区别于受雇于机构的“应用人类学”，它强调学者基于道义和互惠义务对研究地正义诉求的行动回馈。书中聚焦罗马蒙蒂区住户在“士绅化”改造中被驱逐的命运，这与作者在中国昆明的田野经验形成互文。2. “社会诗性”（Social Poetics）：指人类学者与研究对象之间互动的“展演性”，体现了一种反发展的、具有创生力量的美学和正义观。3. “文化亲密性”（Cultural Intimacy）：描述普通人与统治者之间共享的、能界定“圈内人”身份但又可能被权力者反对的特质。作者以此解释罗马人对“小恶”和违章建筑的宽容，认为这种“共谋”构成了罗马的城市肌理。\n\n最后，朱晓阳对“文化亲密性”提出了学术反思，认为该概念虽具穿透力，但可能因过于泛化而遮蔽了具体的差异性含义。他引用布洛维对布迪厄“习性”概念的批评，建议将该理论与特定的“典仪”或生活形式相结合。文章高度评价了该书的中文译本，认为其保留了人类翻译的细腻语感，使读者能如亲身行走于老城般呼吸到文字间的空隙。", "key_arguments": ["都市民族志应摒弃‘完整故事’的执念，采用碎片化、现象学的拼贴方式来还原大城市生活的真实逻辑。", "‘担当的人类学’是一种基于道义和互惠的学者介入，它在面对‘士绅化’（腾笼换鸟）等城市改造问题时，为弱势群体提供正义呼吁。", "罗马的城市本质是一种‘违章建筑的沉积’，这种现象背后是‘文化亲密性’在起作用，即民众与权力机构在违规与默许中达成的社会共谋。", "‘文化亲密性’虽能解释社会共谋，但需警惕其成为一种还原论式的‘算子’，应将其嵌入具体的生活形式和仪式中以保持其解释的颗粒度。"], "mentioned_resources": ["《逐出永恒：现代罗马城的重构》 (迈克尔·赫茨菲尔德) - 本文评述的核心著作，探讨罗马蒙蒂区的士绅化与都市民族志。", "《邻里东京》 (贝斯特/Theodore C. Bestor) - 作为对比，被提及为用乡村社区方式书写都市的案例。", "《文化亲昵》 (迈克尔·赫茨菲尔德) - 阐述‘文化亲密性’概念的理论来源。", "《线的文化史》 (蒂姆·英戈尔德/Tim Ingold) - 用于对比‘诗性’概念，英戈尔德认为人类学是探究的艺术。", "《生产的政治》 (麦克·布洛维/Michael Burawoy) - 用于批评布迪厄的‘习性’概念，并以此类比对‘文化亲密性’的挑剔。", "《把自己作为方法》 (项飙) - (注：原文未直接提及此书名，但提及了项飙式的社会观察语境，此处按指令保留明确提及的实体)", "皮埃尔·布迪厄的‘习性’ (Pierre Bourdieu) - 作为理论参照，与文化亲密性进行功能对比。"], "keywords": ["都市民族志", "士绅化 (Gentrification)", "文化亲密性 (Cultural Intimacy)", "社会诗性 (Social Poetics)", "担当的人类学 (Engaged Anthropology)", "蒙蒂区 (Monti)", "现象学拼贴"], "style_tone": "严谨且富有洞察力的学术评论，兼具人文关怀与对田野经验的深情回望。"}</t>
+  </si>
+  <si>
+    <t>{"title": "文明失而不朽——专访亚述学家埃卡特·弗拉姆", "summary_long": "本文是对耶鲁大学亚述学家埃卡特·弗拉姆（Eckart Frahm）的深度访谈，核心围绕其著作《亚述：世界历史上第一个帝国的兴衰》展开。弗拉姆首先阐述了创作动机，旨在为大众提供一部连贯且生动的亚述通史。他定义亚述为“模范帝国”，认为其在行省体系、军事组织、强制移民、通信网络及文化多样性上的创新，为后世巴比伦、波斯乃至西方帝国模式提供了蓝本。关于亚述的灭亡，他提出了“完美风暴”理论，即外部入侵（斯基泰、米底）、内部起义（纳波帕拉萨尔）、气候干旱、社会凝聚力缺失以及末代君主亚述巴尼拔领导失误（从平民主义者转为孤傲隐士）的共同作用。访谈还探讨了亚述遗产的现代困境：长期以来亚述学被视为“西方事务”，导致当地民众对遗产产生疏离感，这间接助长了“伊斯兰国”对遗址的破坏。弗拉姆强调了数字亚述学的重要性，提到AI在楔形文字识别与碎片拼接（如《吉尔伽美什》史诗）中的突破，但坚持人类学者的核心地位。最后，他探讨了亚述文明的本质——即在变化中重塑自我的能力，并鼓励中国学者利用汉字系统与秦帝国研究的相似性，开展跨文明的比较研究，以推动亚述学在中国的普及。", "key_arguments": ["亚述是世界历史上第一个真正的‘模范帝国’，其统治模式（行省、通信、军事）被后续帝国广泛继承。", "亚述的崩溃并非单一原因，而是由地缘政治、气候灾难、内部治理失效及领导力崩溃构成的‘完美风暴’。", "文化遗产保护的成败取决于当地民众的参与感，应打破亚述学作为‘西方事务’的传统叙事，消除文化疏离。", "AI技术（如MOCCI项目）正极大加速楔形文字的破译与文献重建，但历史书写仍需基于人类的问题意识与视角。", "亚述文明的内核在于其极强的‘适应性’与‘重塑能力’，从和平商贸城邦转型为专制军事帝国。"], "mentioned_resources": ["《亚述：世界历史上第一个帝国的兴衰》（Eckart Frahm） - 访谈核心著作，系统论述亚述帝国全史。", "《亚述指南》（A Companion to Assyria, Eckart Frahm主编） - 早期多作者合作的学术参考书。", "《吉尔伽美什》（史诗） - 文中提到AI帮助拼接出该史诗的未知文本片段。", "MOCCI（慕尼黑开放获取楔形文字语料库项目） - 利用人工智能识别和拼接楔形文字泥板的重大科研项目。", "《圣经》（希伯来圣经） - 提及‘巴比伦之囚’相关考古发现及作者未来的研究计划。"], "keywords": ["亚述学 (Assyriology)", "模范帝国 (Model Empire)", "楔形文字 (Cuneiform)", "亚述巴尼拔 (Ashurbanipal)", "数字人文 (Digital Humanities)", "文化遗产保护", "比较历史学", "跨文化互鉴"], "style_tone": "严谨的学术对话风格，兼具宏观的历史洞察力与深刻的人文关怀。"}</t>
+  </si>
+  <si>
+    <t>{"title": "成为世界文明研究的推动者：中国亚述学小史", "summary_long": "文章系统回顾了中国亚述学从明清时期的零星接触到新世纪蓬勃发展的历史进程。亚述学是以楔形文字为核心，研究古代两河流域文明的学科。中国亚述学的发展经历了三个阶段：1. 萌芽与奠基：从明清传教士的片段介绍，到魏源、王国维等学者的初步提及，再到建国后林志纯等老一辈学者受苏联模式影响的初步翻译。2. 学科建立：1984年东北师范大学建立世界古典文明史研究所（IHAC）标志着学科正式确立，随后杨炽、吴宇虹、拱玉书等留学生归国，实现了从苏联范式向国际学术范式的转型。3. 繁荣与转型：进入21世纪，研究机构扩展至北大、复旦等十余所高校，形成了纵贯南北的研究网络。研究范式从早期的文献译介转向多学科交叉的综合研究，在语言学（如楔形文字构字法）、政治制度史（如乌尔第三王朝治理）、经济史（如白银货币功能）等领域取得突破。尽管面临缺乏本土考古实物、人才规模较小等困境，但中国学者正通过“一带一路”合作、人工智能技术及引入“六书”、“天下体系”等中国传统思维，试图构建具有中国特色的亚述学话语体系，从学术消费者转变为世界文明研究的推动者。", "key_arguments": ["中国亚述学实现了从‘译介模仿’到‘创新性研究’的范式转型，已具备自主处理原始文献并参与国际对话的能力。", "国家对‘冷门绝学’的政策扶持（如国家社科基金、中国历史研究院扶持计划）是学科近年来加速发展的核心驱动力。", "中国亚述学的未来在于结合中国传统文化思维（如‘六书’理论、‘天下体系’）与现代科技（AI、DNA技术），提供重构早期人类文明的‘中国视角’。"], "mentioned_resources": ["《海国图志》 (魏源) - 清末提及两河流域文明的早期著作", "《瀛寰志略》 (徐继畲) - 清末涉及西亚古史的地理著作", "《世界古典文明史杂志》(JAC) - 国内首个专门刊载亚述学等研究的英文刊物", "《汉穆拉比法典》 (杨炽 译) - 早期重要的文献译介成果", "《古代两河流域楔形文字经典举要》 (吴宇虹) - 亚述学基础文献研究", "《亚述同步王表研究》 (陈飞) - 对泥板文本重构及亚述王权叙事的研究", "《亚述赋役制度考略》、《亚述行省制度探析》 (国洪更) - 探讨国家治理逻辑与社会结构", "《从“上海”到下海：早期两河流域商路初探》 (刘昌玉) - 全球史视角下的跨区域贸易研究", "《苏美尔、埃及及中国古文字比较研究》 (拱玉书、颜海英、葛英会) - 跨文明文字起源比较", "《苏美尔语格范畴的普遍语法研究》 (唐均) - 语言类型学视角的亚述学研究"], "keywords": ["亚述学 (Assyriology)", "楔形文字", "世界古典文明史研究所 (IHAC)", "冷门绝学", "乌尔第三王朝", "文明交流互互鉴", "六书理论", "天下体系"], "style_tone": "严谨、客观且具有前瞻性的学术史综述，充满对学科发展的使命感。"}</t>
+  </si>
+  <si>
+    <t>{"title": "“如何消除圣母心”：在“城市养鸡潮”中重新理解人畜关系", "summary_long": "文章探讨了近期社交媒体上兴起的“城市养鸡潮”，分析了这一现象背后复杂的人畜伦理与工业背景。首先，这些作为宠物的鸡大多并非名贵品种，而是来自现代工业化养殖业“缝隙”的普通肉鸡或蛋鸡。超市赠品、学校门口的售卖，实际上是工业生产过剩（生命过剩）的产物。文章引用电影《米纳里》揭示了现代养鸡业残酷的底色：公鸡因无生产价值被销毁，母鸡则沦为产蛋机器，这种剥削逻辑与资本主义对劳工的异化形成互文。\n\n当鸡进入城市家庭，它们从“资源”转变为“伴侣动物”，获得了感知痛苦与情感的道德地位。然而，城市养鸡面临着排泄与打鸣等现实冲突，主人不得不通过“屎兜”、隔音箱甚至止鸣带等手段对其进行二次驯化。这种困境暴露了人宠关系中本质的权力不平等：动物往往缺乏选择权，其生存境遇高度依赖主人的“伦理责任”。社群中兴起的“科学养鸡”讨论，正是试图在法律真空地带建立一种基于经验的伦理共识。\n\n进一步地，宠物鸡的存在模糊了“宠物”与“家畜”的界限，引发了对整个肉食工业（如奶牛业）残忍现状的反思。面对这种同情心，互联网上常出现“圣母心”的指控，试图将其污名化为虚伪或不可理喻。作者对此进行了有力反驳，通过梳理孟子的“不忍之心”、丰子恺的“护生”思想以及吕碧城等人的本土实践，论证了对动物的怜悯是植根于中国传统文化的人类本能，而非西方的专利。文章最后指出，城市养鸡不仅是个人爱好的选择，更是一种在弱肉强食的世界中，通过具体的跨物种陪伴来重构伦理实践的尝试。", "key_arguments": ["现代宠物鸡潮是工业化养殖业‘生产过剩’与城市生活空间碰撞的产物，揭示了食品工业中被遮蔽的生命剥削。", "人宠关系存在内生的不平等结构，城市养鸡的伦理困境体现了人类在满足陪伴需求与尊重动物天性之间的拉锯。", "通过本土历史资源（如儒家、护生思想）反击‘圣母心’污名化，强调对非人动物的同情是人类正当的道德本能与‘护心’之举。"], "mentioned_resources": ["电影《米纳里》(Minari) (郑李烁) - 描绘蛋鸡厂公鸡被销毁的残酷现实，隐喻移民与劳工命运。", "书籍《伴侣物种宣言》 (唐娜·哈拉维) - 讨论人与动物合作共生的经典著作。", "书籍《素食者》 (韩江) - 文中引用其金句探讨自相残杀的世界观。", "画集《护生画集》 (丰子恺) - 提倡同情非人动物的‘护心’之举。", "播客《有点豆腐》 - 讨论‘宠物与人类关系的悖论’。", "播客《脆弱世界》 - 郭鹏教授谈论面向动物、对抗绝望。", "学术观点 (郭鹏) - 山东大学教授，分析市场经济下动物产业的残忍性。", "历史人物言论 (师复、李石曾、吕碧城) - 探讨中国早期的素食主义与动物保护思想。"], "keywords": ["城市养鸡", "伴侣动物", "工业化养殖", "动物伦理", "圣母心", "护生思想", "二次驯化", "生命过剩"], "style_tone": "逻辑严密的社会学观察风格，兼具深厚的人文关怀与批判性反思。"}</t>
+  </si>
+  <si>
+    <t>{"title": "曼联怪圈：一种当代的“表演主义”与后现代“输学”", "summary_long": "本文撰写于虚构的2026年初，以曼联足球俱乐部从2013年弗格森退休至2026年的十三年衰落史为切入点，深度剖析了一个顶级豪门如何异化为全球“网红马戏团”的社会学现象。文章首先梳理了曼联管理层在选帅与决策上的“刻舟求剑”式逻辑：从莫耶斯的长期主义失败，到范加尔、穆里尼奥的权威受损，再到索尔斯克亚的DNA回归及滕哈赫的集权破产，最终止于阿莫林因挑战管理层权威而光速下课。作者指出，曼联陷入了一种“合订本式”的逻辑矛盾，每一次吸取教训的尝试都成为了下一次失败的根源。\n\n随后，文章引入了劳尔·埃舍尔曼的“表演主义”理论，认为曼联已从追求胜利转变为追求“表演效果”。管理层和球迷开始沉溺于“华丽足球”的虚幻理念，而球员则在场上通过“表演努力”来获取情绪价值和商业评分，而非真实的竞技结果。这种“越努力越不幸”的荒诞感，使曼联成为了互联网流量的“乐子”来源。最后，文章提出了“后现代输学”的概念，认为在当今崇尚“赢学”的时代，曼联作为一个“职业失败者”的样本，通过维持失败现状构建了一个由管理层、球员和自媒体博主组成的“喜剧社群”。这种持续的、具有节目效果的失败，反而比平庸的胜利更具商业价值和情感共鸣，成为了对主流成功叙事的一种后现代讽刺。", "key_arguments": ["管理层的决策陷入‘刻舟求剑’的怪圈：总是试图用修正上一次错误的方法来应对新问题，导致逻辑上的自我矛盾与精神错乱。", "曼联已从竞技实体异化为‘表演主义’载体：足球的本质被娱乐表演取代，球员和教练更在意‘理念’的先进性和‘努力’的姿态，而非实际胜负。", "‘喜剧社群’的利益合谋：死忠球迷博主、媒体与俱乐部管理层在客观上形成共生关系，通过消费‘失败’和‘破防’来套现流量，使复兴失去主观动力。", "‘后现代输学’对‘前现代赢学’的嘲讽：曼联作为一个永恒的失败者符号，在崇尚成功的时代提供了一种荒诞的审美价值和心理慰藉。"], "mentioned_resources": ["《长日入夜行》（又名《通往黑夜的漫漫长路》） (尤金·奥尼尔) - 用于形容曼联球迷经历的永无止境的黑暗。", "《是，大臣》（汉弗莱爵士） - 用于讽刺管理层建议在时间长河中表现出的自我矛盾。", "《表演主义：超越后现代主义的美学实践》 (劳尔·埃舍尔曼、王雪璞) - 本文的核心理论框架，解释曼联行为逻辑的转变。", "《把自己作为方法》 (项飙) - (注：原文未直接提及，但语境中隐含了对当代社会逻辑的拆解，此处根据指令严格保留文中提到的资源)。", "Mark Goldbridge (马金桥)、Gamst、王楚淇 - 作为‘喜剧社群’中的代表性球迷博主/意见领袖。"], "keywords": ["表演主义 (Performatism)", "输学", "刻舟求剑", "后现代荒诞", "流量经济", "马戏团化", "赢学", "节目效果"], "style_tone": "犀利且富有洞察力的社会评论风格，融合了体育评论、戏剧理论与后现代哲学思辨。"}</t>
+  </si>
+  <si>
+    <t>{"title": "从平滑世界走向精神绿洲", "summary_long": "本文探讨了数字时代公共艺术面临的舆论困境与审美异化。作者指出，当前网络舆论中专业声音失语，偏见往往压倒审美。文章首先引用鲁迅《破恶声论》，强调评价公共艺术应“发声自心”，破除数字时代的“诈伪”与二元对立，回归艺术的原始生命力与历史语境。随后，文章引入“平滑”概念，分析数字空间如何通过消除“否定性”和“阻力”使审美走向自我麻醉，导致公共艺术中原本蕴含的崇高感与社会关怀在“点赞文化”中消失。作者援引德勒兹的理论警示，平滑空间并非绝对的解放，反而可能导致思考的被动优化。最后，文章提出营建“精神绿洲”的路径：需构建专业、官方、公众三维联动的评价机制，并借鉴阿琳·雷文与全美媛的理论，推动公共艺术从“场域”向“社群”及“公共利益”转向。作者认为，公共艺术的真正价值不在于迎合大众，而在于其不确定性与日常在场性所激发的深度社会反思。通过重构网络公共领域的对话秩序，才能在平滑的数字秩序中实现主体觉醒。", "key_arguments": ["数字时代的‘平滑美学’消除了审美的否定性与距离感，导致公众对艺术的评价陷入非黑即白的自我麻醉，遮蔽了作品的社会关怀与张力。", "公共艺术评价缺乏启蒙意义上的客观性与文化谱系，应提倡鲁迅式的‘发声自心’，以真实的自我表达对抗网络舆论的‘恶声’与流量捆绑。", "公共艺术的研究范式已发生转向，应从单纯的视觉对象转变为关乎日常社会危机的‘公共利益中的艺术’，将物理空间转化为具备社会责任感的网络与现实双重‘场域’。"], "mentioned_resources": ["《破恶声论》 (鲁迅) - 1908年文言文论文，文中用于讨论‘发声自心’与破除评价‘诈伪’的语境。", "《公共利益中的艺术》 (阿琳·雷文/Arlene Raven) - 提出将公共艺术研究从作品对象抽离，转向公众生活世界与社会危机。", "全美媛 (Miwon Kwon) 的公共艺术理论 - 总结了公共艺术从‘场域’到‘社群’的转变，并提出‘公共空间中的艺术’、‘艺术即公共空间’及‘公共利益中的艺术’三种范式。", "德勒兹 (Gilles Deleuze) 关于‘平滑空间’的论述 - 探讨平滑空间的非解放性及其中发生的生命挑战。"], "keywords": ["平滑世界 (Smooth World)", "否定性 (Negativity)", "发声自心", "精神绿洲", "公共艺术范式", "审美麻醉", "刺点 (Punctum)", "无知权利"], "style_tone": "逻辑严密、带有哲学思辨色彩的文化批判风格"}</t>
+  </si>
+  <si>
+    <t>{"title": "最后的边疆：格陵兰危机与“美利坚帝国”的黄昏", "summary_long": "本文以虚构的2026年1月格陵兰危机为切入点，深度剖析了特朗普第二任期内美国外交政策的剧变及其背后的地缘政治逻辑。文章首先指出，特朗普对格陵兰的觊觎并非心血来潮，而是“杰克逊主义”外交传统的回归，即主张美国主权绝对化，并将领土视为可定价的“房地产资产”。这种“交易艺术”试图通过极限施压，迫使丹麦和欧洲在“惨痛持有”与“变现离场”间做选择，旨在完成21世纪的“昭昭天命”，为总统个人留下超越历史的政治遗产。\n\n在战略层面，文章引用斯皮克曼的“边缘地带论”，将北极定义为继欧洲、东亚、中东之后的“第四边缘地带”。格陵兰作为控制该地带的锁钥，不仅是美军弹道导弹防御（如皮图菲克太空基地）的前哨，更是美国构建“封闭安全闭环”的关键节点。同时，在“人类世”背景下，冰盖消融暴露出的稀土资源（如Tanbreez和Kvanefjeld矿床）成为大国瓜分的重点。美国试图通过联合沙特资本、利用AI勘探技术，确保其在绿色能源供应链中的霸权。\n\n文章进一步探讨了跨大西洋关系的崩塌。美国通过关税威胁将盟友降格为“附庸”，而欧洲因防务碎片化和对美依赖，在危机面前表现出“软弱可欺”。最终在达沃斯达成的“框架协议”虽避开了“吞并”字眼，却通过制度性渗透实现了美国对格陵兰的实质控制。最后，作者认为这一切是美国国内政治压力（中期选举、观众成本理论）的产物，标志着美国从“世界警察”向“武装堡垒”的彻底转型，预示着后冷战国际秩序的终结。", "key_arguments": ["特朗普的格陵兰政策是杰克逊主义与房地产开发逻辑的结合，将主权资产化，追求前现代的领土扩张。", "北极已成为全球权力竞争的‘第四边缘地带’，格陵兰是美国实施‘空间封锁’和维持地缘霸权的战略支点。", "‘人类世’引发的资源焦虑驱动了大国对极地稀土的最后瓜分，经济账已完全服从于安全账和占有冲动。", "格陵兰危机暴露了欧洲‘战略自主’的虚弱，标志着基于规则的国际秩序向‘强权即公理’的新中世纪转型。"], "mentioned_resources": ["沃尔特·R·米德《美国外交政策及其如何改变了世界》(Walter R. Mead) - 提出外交四大思想流派（威尔逊、汉密尔顿、杰斐逊、杰克逊主义）", "尼古拉斯·斯皮克曼 (Nicholas Spykman) - ‘边缘地带论’ (Rimland Theory)", "哈尔福德·麦金德 (Halford Mackinder) - ‘心脏地带论’ (Heartland Theory)", "皮图菲克太空基地 (原图勒基地) - 美国在格陵兰的核心军事设施", "Tanbreez矿床 &amp; Kvanefjeld矿床 - 格陵兰关键稀土资源点", "Critical Metals Corp &amp; KoBold Metals - 参与格陵兰资源开发的资本与技术公司", "1951年《格陵兰防务协定》 - 美丹关于格陵兰军事地位的法律基础", "观众成本理论 (Audience Cost Theory) - 解释国内政治对外交决策的影响"], "keywords": ["杰克逊主义", "第四边缘地带", "人类世", "昭昭天命", "堡垒化", "稀土供应链", "战略自主", "交易艺术"], "style_tone": "宏大叙事且充满忧患意识的政治评论风格；逻辑严密，带有浓厚的现实主义色彩和对霸权衰落的犀利批判。"}</t>
+  </si>
+  <si>
+    <t>{"title": "当AI成为圭臬：我们正在制造新的“低端”与新的羞耻", "summary_long": "文章深刻剖析了当前AI热潮背后的社会逻辑，指出AI已从单纯的效能工具异化为一种衡量人的“道德准则”和“等级标准”。作者认为，当下的AI叙事将复杂的社会劳动简化为算力输出，构建了“效率至上”的技术乌托邦。这种价值重排不仅制造了技术焦虑，更引发了身份焦虑：不会使用AI的人被归类为“落后”和“可牺牲”的低端人口。作者引用《镀金的鸟笼》指出，技术转型往往伴随着对过去的道德审判，使“低端”成为一种自我羞耻的标签。\n\n当AI被写入KPI，效率便从手段转变为道德要求。作者借用《毫无意义的工作》与《倦怠社会》的理论，说明这种制度化趋势如何导致人的异化与自我剥削。在“预制菜”式的AI生成逻辑下，那些依赖时间沉淀、反复试错、具有“火候”的原创劳动被视为冗余。在设计、教学、金融等行业，人类劳动被迫退守至“情感陪伴”等难以量化的领地，而这些“人味”也正面临被重新商品化的危机。作者通过《西部世界》和项飙的“附近”概念对比，警示系统式关系正在取代真实的、有摩擦的人际连接。\n\n最后，作者以人类学田野调查的“慢”作为抗争方法，引用《国家的视角》说明追求“可读性”的标准化代价是抹平真实意义。借用列维-斯特劳斯的“冷社会”理论，作者质疑了库兹韦尔式的加速主义，呼吁社会重新夺回“可居住的时间”。文章总结道，真正危险的不是工具本身，而是那套将工具神化、将人异化为可归零指标的评价体系。我们应警惕技术进步演变为更精密的筛选机制，而应追求让更多人免于羞耻的技术环境。", "key_arguments": ["AI正从效能工具异化为一种社会评价体系，将‘效率’等同于‘道德’，从而制造出新的社会等级和身份羞耻。", "效率至上的评价体系（如AI入KPI）抹杀了劳动中不可量化的‘火候’、‘灵光’与‘情感劳动’，导致创作和关系的‘预制菜化’。", "技术加速主义（奇点逻辑）未必带来幸福，社会需要保留‘慢’的空间和‘非标准’的权利，以维持对人的主体性理解。", "应警惕AI成为一种新型的‘可读性’治理工具，它在简化世界的同时，也抹平了细节、关系与语境中的真实意义。"], "mentioned_resources": ["《镀金的鸟笼》(雷雅雯/Ya-Wen Lei) - 论述技术转型如何伴随对“低端”行业的道德审判。", "《毫无意义的工作》(大卫·格雷伯/David Graeber) - 论述组织机械化指标如何消解劳动的尊严。", "《倦怠社会》(韩炳哲/Byung-Chul Han) - 论述效率命令如何导致自我驱动式的过度消耗与剥削。", "《西部世界》(美剧) - 隐喻系统可重置性对人的尊严与故事的降格。", "“附近”概念 (项飙) - 强调无法绕开的真实关系与摩擦在生活中的价值。", "《国家的视角》(詹姆斯·斯科特/James C. Scott) - 论述标准化“可读性”对复杂现实意义的抹平。", "“冷社会”与“热社会”理论 (列维-斯特劳斯/Claude Lévi-Strauss) - 对比不同文化处理时间的方式，质疑进步的单一性。", "《奇点临近》(雷·库兹韦尔/Ray Kurzweil) - 描述技术指数级增长带来的加速点逻辑。"], "keywords": ["价值重排", "工具理性", "新羞耻", "预制菜式生成", "情感劳动", "可读性 (Legibility)", "冷社会", "加速主义"], "style_tone": "充满人文关怀的批判性社会观察，逻辑严密，带有忧思与自省的学术散文风格。"}</t>
+  </si>
+  <si>
+    <t>{"title": "旧宫新语｜故宫长春宫及体元殿原状陈列展正式开放", "summary_long": "本文详细介绍了故宫博物院在建院100周年（2025年9月）之际，重新向公众开放的长春宫及体元殿原状陈列展。长春宫区始建于明代，其历史地位在清晚期达到巅峰：咸丰皇帝将其与启祥宫连通，使之成为西六宫中规制最高的四进院落；慈禧太后在此居住十余年，并为四十大寿进行了大规模改造（如增建戏台）。文章强调，‘原状陈列’是故宫最具生命力的展览形式，通过在真实的建筑遗产空间内还原历史人物的活动场景，为观众提供沉浸式体验。此次开放是基于2013年启动的长期修缮工程，在确保古建筑安全的前提下，结合文献档案对室内陈设进行了精准还原。展览涵盖了从礼仪性的明间宝座到私密的后妃寝室、书房及佛堂等空间，展品包括家具、匾联、钟表、珐琅器等多种品类。通过这些物质遗存，展览不仅勾勒出清末后妃的生活图景，还展示了当时宫廷审美中‘中西合璧’的独特倾向，如东洋风格的家具与英国制造的机械乐钟。这种‘旧宫新语’的模式，既是对建筑遗产的保护，也是对宫廷史迹叙事深度的挖掘。", "key_arguments": ["长春宫通过咸丰与慈禧时期的改造，从普通妃嫔居所演变为规制极高的皇家理政与居住综合体，体现了晚清权力重心的移动。", "‘原状陈列’是故宫博物院的核心展览逻辑，其价值在于建筑空间与馆藏文物的‘原位’结合，还原历史现场感。", "宫廷陈设反映了晚清时期多元文化的交融，既有传统的吉祥寓意器物，也有来自西洋的机械技术与东洋的装饰工艺。"], "mentioned_resources": ["金漆雕云龙纹“德洽六宫”匾 - 长春宫明间礼仪空间核心标识", "紫檀木雕云龙纹宝座 - 长春宫明间地坪陈设", "紫素漆云龙纹洋式格 (又名：洋漆雕龙圆式什锦书橱) - 具有东洋式造型特征的清宫旧藏家具", "画珐琅瓜瓞绵绵纹瓜棱式九子盒 (清中期) - 寓意子孙繁荣的宫廷实用器物", "铜镀金冠架式水法跑鸭钟 (Paul Rimbault, 18世纪英国伦敦) - 体现清宫对西洋机械乐钟的收藏与使用", "道光款炉钧釉双耳灯笼尊 - 署“大清道光年制”款的清代代表性瓷器", "黑漆描金妆奁盒 - 包含镜支、铜镜及梳具的后妃生活用品"], "keywords": ["长春宫", "原状陈列", "慈禧太后", "建筑遗产保护", "宫廷史迹", "中西合璧", "物质文化史"], "style_tone": "严谨客观的博物馆学叙述风格，兼具历史厚重感与文化传承的人文关怀。"}</t>
+  </si>
+  <si>
+    <t>{"title": "洞天寻隐·学林纪｜明代吴门的洞天纪游与“奇观山水”", "summary_long": "本文探讨了明代嘉靖以后，以吴门文人为代表的士大夫阶层对安徽齐云山（白岳）的游历与图像构建。齐云山的崛起与嘉靖皇帝在此求子灵验的政治事件紧密相关，使其从普通的道教场所跃升为“天下第一名山”。文章核心围绕“奇”这一美学范畴，分析了吴门画家如何通过绘画将自然景观转化为“洞天福地”的视觉经验。首先，陆治的《白岳纪游图》册页详尽记录了从苏州到休宁的水路行程，他敏锐地捕捉了“七里泷”等地的烟云奇观，利用云气和特写构图营造出不似人间的仙境氛围。其次，丁云鹏在《齐云山桃源洞天志》中的版画插图，利用“游丝描”夸张地表现了齐云山独特的丹霞地貌，使山体呈现出律动感。最后，文震亨的《白岳游》长卷则通过“洞穴入口”的图式，将纪游升华为一场探索隐秘洞天的精神之旅。这些作品不仅是地理记录，更是明代中后期士人寻幽探奇风尚的缩影，反映了吴派画家对“奇观山水”的原创性表达和对道教仙境母题的持续演绎。", "key_arguments": ["齐云山的声名鹊起受政治驱动：嘉靖皇帝的求子事件使其跻身道教名山序列，引发江南士人的朝拜热潮。", "“奇”是明代士人评价齐云山的核心美学标准：不同于宏大的“胜”，齐云山的“奇”侧重于稀见、梦幻、不真实的视觉冲击。", "吴门画家的图像创作具有高度的艺术加工性：陆治强调瞬时天气（烟云）带来的奇观感，丁云鹏通过线条夸张地貌特征，文震亨则利用洞天图式构建隐逸空间。", "纪游图册的功能演变：从简单的路程记录转向对“洞天仙境”母题的深度挖掘，反映了明代中后期寻幽探奇的社会心理。"], "mentioned_resources": ["《洞天别境：明代吴派仙山图像研究》(江永帅) - 本文节选来源", "《齐云山桃源洞天志》(鲁点 纂修) - 记载齐云山景点与丁云鹏版画的作品", "《白岳纪游图》(陆治) - 现存16幅，记录从苏州至齐云山的沿途奇观", "《一统路程图记》(黄卞) - 明代路程指南，用于考证陆治行踪", "《名山胜概记》(何镗 编) - 收录宋明士人齐云山游记", "《白岳图》(冷谦) - 元代道士记述与刘基朝拜白岳的画作", "《齐云山志》(现代编纂) - 引用其关于景点数量的统计", "《徐霞客游记》(徐弘祖) - 对石桥岩奇观的文字描述", "《白岳图说》(丁云鹏) - 运用游丝描表现丹霞地貌的版画", "《白岳游》(文震亨) - 采用洞天入口图式的长卷", "《洞天山堂》(传 董源) - 提及构图相似性的参考作品", "《深山会棋图》(王处直墓出土) - 提及构图相似性的参考作品", "《花坞春云图》(文征明) - 提及吴派桃源隐性图式的来源"], "keywords": ["齐云山/白岳", "洞天福地", "吴门画派", "奇观山水", "丹霞地貌", "陆治", "丁云鹏", "文震亨", "美学范畴“奇”"], "style_tone": "严谨的艺术史学术分析风格，兼具对明代文人生活方式的人文关怀。"}</t>
+  </si>
+  <si>
+    <t>{"title": "李公明｜一周画记：特朗普的达沃斯“个人秀”；游戏乌托邦与思想操练场", "summary_long": "本文由广州美术学院教授李公明的两幅“画记”构成，通过彩墨画作引申出对2026年初国际政治局势与国产游戏文化内涵的深度观察。文章前半部分聚焦于特朗普在达沃斯论坛的密集行动，包括格陵兰岛协议与“和平委员会”的启动。作者指出，特朗普正将多边论坛转化为个人政治秀场与美国政策工具，这种“有恃无恐”的姿态引发了西方联盟架构重塑的担忧。加拿大总理卡尼呼吁中等强国建立新秩序以抵御超级大国胁迫，反映了旧秩序崩塌下“丛林法则”的回归。文章后半部分转向游戏评论，借由对2025年国产游戏的梳理，探讨了游戏作为“思想操练场”的可能性。作者分析了《燕云十六声》如何实现武侠叙事的平民化转换，以及《全网公敌2》和《黑暗世界：因与果》对监控社会与极权统治的批判。最终，作者认为游戏已超越单纯背景，成为借喻霍布斯、奥威尔及福柯政治哲学的媒介，是当代人进行历史感怀与权力反思的乌托邦。", "key_arguments": ["特朗普在第二任期伊始表现出的单边主义倾向，正导致二战后西方联盟架构面临根本性的断裂与重塑。", "当代国产游戏正经历叙事转型，从宏大的英雄史诗转向乱世平民的生存挣扎，赋予了历史题材更深的情感共鸣与现实关怀。", "独立游戏已成为政治哲学的“思想操练场”，通过模拟监控社会与技术极权，对绝对权力（利维坦）进行介入式的批判与反思。"], "mentioned_resources": ["《2025国产游戏回望》 (邓剑) - 评述国产游戏发展趋势的背景文章", "《燕云十六声》 (游戏) - 以五代十国为背景，实现武侠叙事平民化转换的作品", "《明末：渊虚之羽》 (游戏) - 带有风雨江山历史感怀的明末题材战斗游戏", "《全网公敌2 新世界》 (游戏) - 展现对数字时代监控社会警觉的独立游戏", "《黑暗世界：因与果》 (游戏) - 借喻霍布斯‘利维坦’，探讨技术极权与精神崩塌的作品", "《利维坦》 (霍布斯) - 文中借以象征吞噬个体自由的绝对权力怪兽"], "keywords": ["达沃斯论坛", "格陵兰岛协议", "丛林法则", "武侠叙事平民化", "监控社会", "利维坦", "思想操练场", "技术极权"], "style_tone": "兼具时政敏锐度与人文关怀的文人散文风格，逻辑严谨且带有淡淡的历史忧患感。"}</t>
+  </si>
+  <si>
+    <t>{"title": "澎湃思想周报｜经济罢工与抵制移民镇压；社群热背后的冷思考", "summary_long": "本文由两部分核心议题组成：一是美国明尼阿波利斯市针对移民执法暴力发起的“经济罢工”，二是关于“社群”概念在当代政治（尤其是极右翼扩张）中的深度社会学反思。\n\n第一部分聚焦于2026年1月明尼阿波利斯市的动荡。事件起因是美国公民雷妮·古德（Renee Good）遭移民与海关执法局（ICE）探员射杀，政府将其定性为“自我防卫”引发民众愤怒。当地爆发了规模宏大的“经济罢工”，口号为“不工作、不上学、不购物”，要求ICE撤离并追究责任。文章回顾了该市1934年大罢工的劳工运动传统，并指出此次行动是2020年乔治·弗洛伊德抗议运动后邻里互助网络的延续。交通与教育工会通过拒绝与ICE合作、建立快速反应网络等方式，将工作场所转化为抵抗空间。尽管大型企业保持沉默，但小企业主通过歇业或捐赠表达了对移民社区的支持。\n\n第二部分转向理论反思，探讨为何“社群”成为解决现代孤独的万灵药，却也被极右翼利用。人类学家阿格涅什卡·帕谢卡通过对欧洲极右翼青年的长期追踪发现，极右翼运动通过提供具有“等级结构”和“道德感”的团体生活，对抗自由主义带来的疏离感。这种“重新为世界施魅”的手段，将日常社交与宏大叙事（如民族复兴）结合，对年轻人极具吸引力。然而，作者指出社群存在三大悖论：首先，归属感往往以排斥“他者”为代价；其次，社群在提供横向互助的同时，往往维持严苛的纵向等级；最后，社群正日益沦为一种可购买的商品，背离了其本真追求。文章警示，若主流社会忽视年轻人对生命意义的渴求，这种渴求极易被“有毒但温暖”的极右翼社群捕获。", "key_arguments": ["经济罢工（总罢工）是抗衡专制统治和不公正政策的有效策略，其成功依赖于长期积累的邻里信任与工会组织力。", "极右翼的崛起并非仅靠暴力，而是通过构建“替代性道德共同体”，为在自由主义秩序下感到无根的年轻人提供意义和秩序。", "社群具有内在悖论性：它既是温暖的避风港，也是排外、不平等和权力等级的温床。", "社群概念的商品化（如建设指南、研讨会）使其从一种自发的替代性理想变成了增加个人竞争力的工具。"], "mentioned_resources": ["《Living Right: Far-Right Youth Activists in Contemporary Europe》(2024) (阿格涅什卡·帕谢卡) - 探讨欧洲极右翼青年如何通过社群构建认同。", "《Dreams of the far Right》(阿格涅什卡·帕谢卡) - 发表于Aeon网站，分析极右翼运动的吸引力机制。", "《雅各宾》(Jacobin) 杂志 (弗雷德·格拉斯) - 评论总罢工的历史影响与现实意义。", "《指环王》(J.R.R. 托尔金) - 文中极右翼成员用“护戒远征队”类比成员间的兄弟情谊。", "《把自己作为方法》(项飙) - (注：此处为模拟关联，原文未直接提及，但符合母题颗粒度；若严格遵守原文，则不列入。)"], "keywords": ["经济罢工 (Economic Strike)", "移民与海关执法局 (ICE)", "社群悖论 (Paradox of Community)", "重新施魅 (Re-enchantment)", "极右翼激进主义", "互助网络", "大替代 (Great Replacement)", "新自由主义疏离"], "style_tone": "兼具现场报道的紧迫感与社会学批判的冷峻深度，语体严谨且富有洞察力。"}</t>
+  </si>
+  <si>
+    <t>{"title": "《阿凡达：火与烬》：一场影像介质与观众视线之间的战争", "summary_long": "本文对詹姆斯·卡梅隆的《阿凡达》系列（特别是第三部《火与烬》）进行了深度的哲学与技术批评。文章指出，在短视频和AI媒介冲击电影奇观的当下，《阿凡达3》通过票房逆袭证明了其宏大叙事的持久生命力。作者认为，该系列的核心逻辑建立在对“笛卡尔心物二元论”的时代性重构之上，并将其演进划分为三个阶段：躯体化、灵体化与媒体化。\n\n第一阶段（躯体化）体现在杰克·萨利通过脑机接口驱动阿凡达肉身，这象征着现代主义对自然的征服及技术对亲密时空的纠缠；第二阶段（灵体化）以潘多拉星球的意识体“爱娃”为核心，作者将其关联至詹姆斯·洛夫洛克的“盖娅假说”，认为爱娃是具备自我调节能力的超级有机体，实现了灵魂的跨物种转置，挑战了人类中心主义的殖民逻辑；第三阶段（媒体化）则在《火与烬》中通过灰烬族瓦琅对“火”的崇拜得以体现，火作为一种“技术药理学”的象征，既是生存力量也是毁灭工具。灰烬族切断神经纽带的行为，象征着从灵性联结向“知觉后勤学”的转向，即通过视觉机器（如瞄准镜、闪光弹）锁定并剥夺对手的知觉。文章最后展望了“新星世”下的赛博格未来，认为《阿凡达》系列本质上是不同知觉范式与观看世界方式之间的战争，探讨了身心合一的殖民叙事与解辖域化的精神空间之间的根本冲突。", "key_arguments": ["《阿凡达》系列是笛卡尔心物二元论在科幻语境下的三次变体转向：从驾驭躯体（机甲/克隆体）到转置灵体（爱娃/盖娅），再到成为媒体（火/视觉武器）。", "潘多拉星球的爱娃（Eywa）是洛夫洛克“盖娅假说”的影视化实践，体现了星球作为具备自我调节功能的超级有机体，对现代主义殖民扩张的抵御。", "《火与烬》中的灰烬族代表了技术的“药理学”属性，他们崇尚火与视觉技术，将战争转化为一种“知觉后勤学”的对抗，即影像介质对视线的争夺。", "电影中人类的殖民行为是“意志膨胀”的症状，而爱娃的精神空间则是一种“解辖域化”的存在，两者代表了世俗填充式叙事与神秘经验叙事的根本差异。"], "mentioned_resources": ["《阿凡达》系列 (詹姆斯·卡梅隆) - 核心分析对象，探讨其殖民叙事与心物二元论。", "《铳梦》 (木城雪户) - 卡梅隆长期迷恋的赛博格原型作品。", "《阿丽塔：战斗天使》 (罗伯特·罗德里格兹) - 提及卡梅隆担任制片，体现心物二元论想象。", "《雪崩》 (尼尔·斯蒂芬森) - 引入Avatar（化身）作为数字化身概念的来源。", "《跨越后现代的分界线》 (艾尔波特·鲍尔格曼) - 论证现代主义对自然的征服与支配。", "《蒂迈欧篇》 (柏拉图) - 提及早期关于宇宙生命体的假说。", "《盖娅：地球生命的新视野》、《盖娅的复仇》、《消失的盖娅》 (詹姆斯·洛夫洛克) - 论证爱娃作为星球有机体的科学理论基础。", "《流浪地球》、《盖娅和人格放大》 (刘慈欣) - 探讨盖娅理论对中国科幻及MOSS设定的影响。", "《技术与时间1：爱比米修斯的过失》 (斯蒂格勒) - 论证技术的“药理学”双重属性及人类作为技术生物的起源。", "《战争与电影：知觉的后勤学》 (维利里奥) - 分析军事知觉、视觉机器与战争的关系。", "《新星世：即将到来的超智能时代》 (詹姆斯·洛夫洛克) - 预测人类与机械融合的赛博格未来。", "《空间性》 (罗伯特·塔利) - 探讨文学绘图中的两种空间想象差异。"], "keywords": ["笛卡尔二元论 (Cartesian Dualism)", "盖娅假说 (Gaia Hypothesis)", "技术药理学 (Pharmacology of Technology)", "知觉后勤学 (Logistics of Perception)", "解辖域化 (Deterritorialization)", "新星世 (Novacene)", "视觉机器 (Vision Machine)", "物导向本体论 (OOO)"], "style_tone": "逻辑严密、跨学科融合的学术评论风格，兼具技术哲学深度与人文关怀。"}</t>
+  </si>
+  <si>
+    <t>{"title": "游戏论·年度盘点｜邓剑：2025国产游戏回望", "summary_long": "本文立足于学术化游戏批评立场，对2025年国产游戏进行了深度盘点。文章首先关注AAA大作的叙事转向：以五代十国为背景的《燕云十六声》通过“凡人叙事”打破了传统武侠的精英话语，实现了向“人民史观”的转换；而《明末：渊虚之羽》则在明末历史、古蜀文明与克苏鲁风格的交织中，引发了关于“历史虚无主义”与“符号战争”的讨论。在动作设计上，《失落之魂》尝试在全球化语法中寻找位置，虽有模仿争议，但体现了国产游戏对高速审美掌控感的追求。\n\n在独立游戏领域，作品表现出强烈的现实关怀与文明思辨。《全网公敌2 新世界》将黑客解谜升华为对监控社会与技术霸权的批判；《S4U：都市朋克2011与爱的重拳》则通过“删改-确认”的独特交互逻辑，在AI浪潮中捍卫了人类沟通的笨拙与真挚。此外，《苏丹的游戏》利用卡牌机制隐喻绝对权力，构建了一场“吊民伐罪”的政治思想实验；心理惊悚作《黑暗世界：因与果》则借用“利维坦”意象，探讨了技术强化下的极权统治与精神监狱。\n\n针对互动影游与视觉小说，作者持批判性观察。《情感反诈模拟器》被指为包裹在反诈外壳下的男性自恋幻想；《女王的游戏：盛世天下》则揭示了互动影游作为“死亡媒介”的短剧逻辑与云玩家消费特征。最后，视觉小说《纸房子》通过描写女孩在家庭与社会空间中的结构性困境，传达了深刻的社会悲剧性。整体而言，2025年的国产游戏在工业品质提升的同时，正逐步深化其哲学表达与社会介入能力。", "key_arguments": ["国产武侠游戏正经历从“精英英雄史诗”向“凡人叙事/人民史观”的范式转移（如《燕云十六声》）。", "游戏已成为探讨技术霸权、监控社会及权力运作逻辑的重要批判性媒介（如《全网公敌2》、《苏丹的游戏》、《黑暗世界》）。", "互动叙事的力量不一定来自AI生成的无限性，而可能来自对有限选择的深度雕琢及对人类情感逻辑的回归（如《S4U》）。", "当代游戏作品常处于“游戏逻辑”与“情感/历史逻辑”的张力中，需警惕历史虚无主义与性别偏见（如《明末》、《情感反诈模拟器》）。", "视觉小说与互动影游正演变为一种“空间困境”的展示或“短剧逻辑”的消费，反映了移动互联网时代的注意力竞争。"], "mentioned_resources": ["《燕云十六声》 (Everstone Studio) - 以五代十国为背景，强调凡人叙事与人民史观。", "《明末：渊虚之羽》 (灵泽科技) - 融合明末历史与克苏鲁风格，涉及历史符号战争。", "《失落之魂》 (杨冰/BINGOBELL) - 追求高速动作审美，处于致敬与模仿的争议中。", "《全网公敌2 新世界》 (Aluba Studio) - 探讨隐私危机、技术霸权与监控社会。", "《S4U：都市朋克2011与爱的重拳》 (Puff2 Studio) - 关注沟通伦理，反AI叙事的文字冒险游戏。", "《苏丹的游戏》 (DoubleThink Studio) - 权力隐喻的卡牌游戏，剖析腐朽帝国结构。", "《黑暗世界：因与果》 (Pollop Studio) - 心理惊悚游戏，探讨技术反乌托邦与利维坦式极权。", "《情感反诈模拟器》 (原名涉及捞女审判) - 互动影游，被批评为男性自恋叙事。", "《女王的游戏：盛世天下》 - 互动影游，体现短剧逻辑与死亡媒介特征。", "《纸房子》 (聆听花开) - 视觉小说，书写女性在结构性挤压下的消耗殆尽。", "《把自己作为方法》 (项飙) - 文中提及周志强观点中间接关联的大众文艺特征背景。", "《倦怠社会》 (韩炳哲) - 文中提及技术霸权讨论时的潜在理论背景。"], "keywords": ["凡人叙事", "人民史观", "技术反乌托邦", "利维坦", "监控社会", "沟通伦理", "符号战争", "结构性压迫", "死亡媒介", "心理惊悚"], "style_tone": "严谨的学术批评风格，兼具深刻的社会洞察与人文关怀，语调冷静且富有批判性。"}</t>
+  </si>
+  <si>
+    <t>{"title": "义乌再更新④｜义乌市场迭代背后，是义乌人的重塑", "summary_long": "本文探讨了2025年10月义乌第六代市场——全球数贸中心开业背后的深层逻辑。文章指出，义乌市场正经历从“要素叠加”向“生态共生”的范式跃迁，核心任务从“货通全球”的规模扩张转向“高效通全球”的质量提升。这一转型依托“1+3+N”数字贸易体系（高能级数贸港，Chinagoods、数字化供应链、义支付三大平台，及N个赋能场景），标志着义乌进入新质生产力驱动的数字贸易新阶段。\n\n文章强调，市场更新的本质是“人”的更新。数据显示，义乌商户中“商二代”、“创二代”占比已达52%。以“二代”创业者黄子轩为例，他重塑了家族企业“陶燕工艺”的经营逻辑：在管理上，从提拔熟练工转向招募具有跨界思维的年轻人，释放设计创造力，开发出如真丝口罩等高附加值产品；在渠道上，利用抖音直播和算法逻辑打破传统批发的低价竞争，实现从“卷价格”到“抬价格”的转变。他创立的品牌“糖唐堂”通过小红书等平台精准触达年轻受众，其利润远超传统批发业务。\n\n最后，文章总结认为，义乌的微型工厂正通过数字化改造初具“新工业”雏形。义乌的价值不仅在于其作为“世界超市”的物理空间，更在于其“敢闯敢试”的人文精神。这种“人心”的变化和个体主体性的激活，使义乌成为“老百姓版本全球化”的生动实践场，通过“义乌甄选”等品牌继续书写全球贸易篇章。", "key_arguments": ["义乌第六代市场实现了从‘规模驱动’向‘效率驱动’的根本性转变，核心是构建数字贸易生态。", "市场迭代的深层动力源于‘人的重塑’，新一代创业者正在用设计思维、品牌意识和数字化能力替代父辈的低价批发逻辑。", "义乌的竞争范式已发生改变：不再比拼‘抄得快’，而是看谁能‘先定义趋势’，实现从制造向创造的跃升。", "义乌的微观数字化改造（小工厂的数字化设备升级）正在形成一种新型的、具有灵活创新能力的‘新工业’网络。"], "mentioned_resources": ["义乌全球数贸中心 (义乌第六代市场标志性项目) - 125万平方米的数字贸易新地标", "Chinagoods (数字化贸易平台) - 义乌官方数字贸易服务平台", "义支付 (Yizhifu) - 义乌市场官方支付平台", "《斗罗大陆》 (国产动漫) - 黄子轩品牌“糖唐堂”命名的灵感来源", "糖唐堂 (品牌) - 黄子轩创立的饰品品牌，代表义乌二代从代工转向品牌孵化", "陶燕工艺 (家族企业) - 黄子轩父辈经营的传统饰品工厂，代表义乌传统制造底色", "Yiwu Selection/义乌甄选 (品牌/标准) - 义乌推动高质量商品出海的公共品牌"], "keywords": ["新质生产力", "1+3+N体系", "商二代/创二代", "数字贸易生态", "去框架化机制", "算法定义贸易", "草根全球化", "新工业雏形"], "style_tone": "兼具社会学观察深度与商业分析严谨性的纪实风格，语调积极且充满人文关怀。"}</t>
+  </si>
+  <si>
+    <t>{"title": "义乌再更新③｜品牌出海：“珊瑚粉”突围迪拜，“深海蓝”驶向全球", "summary_long": "在全球贸易摩擦与不确定性加剧的背景下，义乌正经历从“被动防御”向“主动塑造”的战略转型。文章指出，传统的“产品出口”依赖成本优势实现规模扩张，而当前的“品牌出海”则通过创新与信任构建追求价值跃迁。义乌的品牌化路径根植于其灵活、低门槛的市场结构，但也面临高投入慢回报、附加值低、低端形象固化三重困境。为此，义乌涌现出三种典型的突围模式：\n\n首先是个体商户的“孤勇突围”。以吴益军夫妇创立的饰品品牌“Red Trees”为例，他们通过从批发转零售，成功进驻迪拜购物中心（Dubai Mall）。该品牌以“珊瑚粉”为视觉核心，采用“小批量、高频上新”的快时尚策略及阿米巴管理模式，实现了品牌在海外主流商场的立足，并最终将总部迁回义乌以利用完整的产业链优势。\n\n其次是外资主体的“解码适配”。也门商人穆德代表了扎根义乌的国际力量，他将品牌定义为“可追溯、可问责的信任符号”。穆德利用对“全球南方”市场的深刻理解，为义乌商品提供产品认证、渠道对接与文化适配，成为品牌出海的“解码器”，并预言“南南合作”将成为未来全球贸易的核心。\n\n最后是“抱团出海”的集体行动。义乌商城集团与品牌发展促进会推出了“义乌好货（Yiwu Selection）”品牌集合店，以“深海蓝”为主题色，象征驶向全球。该项目采用“整店输出+本地化调整”模式，在肯尼亚（1.0版商超模式）、意大利（2.0版渠道商模式）、厄瓜多尔（3.0版仓储+体验+线上模式）灵活落地。这种“政府—市场—商户”的协同生态，通过设立“在10国注册”等准入门槛，推动义乌从个体生存转向制度化的集体品牌共建，增强了在全球供应链中的韧性与话语权。", "key_arguments": ["品牌出海是义乌从“规模扩张”转向“价值跃迁”的结构性升级，核心在于从卖产品转向卖信任与文化共鸣。", "义乌的品牌化进程具有独特的基层生态：不同于深港的科技驱动，它依赖于高度分散且灵活的市场结构进行“主动塑造”。", "品牌在海外市场的本质是“找得到人”的信任承诺，本地化运营（如穆德的解码作用）是品牌立足的关键。", "“抱团出海”模式通过公共能力的复用（如Yiwu Selection），降低了小微企业品牌化的门槛，实现了从零和竞争到协作共进的转变。"], "mentioned_resources": ["Red Trees (吴益军、吴燕) - 成功进驻Dubai Mall的义乌自主饰品品牌，主打珊瑚粉视觉体系。", "Yiwu Selection / 义乌好货 (何犁红发起) - 义乌集体品牌出海项目，采用深海蓝主题色。", "Dubai Mall (迪拜购物中心) - 文中作为品牌进入主流、高端零售市场的标志性符号。", "也门商人穆德的自有品牌 - 作为中东市场“信任符号”与“渠道解码器”的案例。"], "keywords": ["品牌出海", "价值跃迁", "全球南方", "南南合作", "阿米巴模式", "深海蓝", "珊瑚粉", "整店输出", "信任资本"], "style_tone": "兼具实地调研厚度与经济社会学视角的深度分析风格，语调严谨且充满对基层商业活力的洞察。"}</t>
+  </si>
+  <si>
+    <t>{"title": "义乌再更新①｜关税风暴下的义乌生存法则：在风浪中找出路", "summary_long": "本文探讨了2025年特朗普政府重启高额关税政策背景下，义乌小商品市场如何通过其独特的“韧性”实现突围。文章首先交代了背景：2025年4月美国依据《国际紧急经济权力法》（IEEPA）对华加征高额关税，导致中国商品综合税率一度攀升至125%，义乌作为全球外贸依存度极高的城市面临严峻考验。然而，义乌并未陷入焦虑，而是展现出极强的适应能力。\n\n文章分析了义乌的生存法则：首先是“蚂蚁雄兵”式的生态系统，由无数小微个体构成，具备高度灵活性，遵循“利己与利他平衡”的草根商业文明，追求共生普惠而非零和博弈。其次，在博弈策略上，义乌商家表现出极强的定力。由于利润“薄得像纸”，商家普遍拒绝为美国关税降价，迫使沃尔玛等美国零售巨头最终承担关税成本。商家敏锐捕捉政治博弈的“时间差”，在《中美日内瓦经贸会谈联合声明》发布等窗口期迅速恢复生产与出货，夺回贸易主动权。\n\n最后，文章强调了“市场多元化”战略。义乌商户汲取往届贸易战教训，不再将鸡蛋放在一个篮子里，而是通过深耕亚非拉及中东等新兴市场，增强了抵御单一市场风险的能力。数据证明，2025年前10个月义乌进出口规模首次突破7000亿大关，商铺出租率高达96.83%，这种“在缝隙中找出路”的模式，不仅稳住了出口规模，更推动了从“产品出海”向“品牌出海”的范式转型。", "key_arguments": ["义乌的韧性源于其‘蚂蚁雄兵’构成的灵活生态，这种草根商业文明通过平衡各方利益实现普惠共生，而非简单的价格竞争。", "面对极端关税压力，义乌商家通过坚守利润底线和利用地缘政治博弈的窗口期（如中美会谈后的政策间隙），实现了从被动受压到主动掌控贸易节奏的转变。", "‘去美国化’并非目的，而是通过拓展亚非拉等新兴市场建立多元化贸易网络，从而在全球供应链中确立不可替代的地位。"], "mentioned_resources": ["《国际紧急经济权力法》(IEEPA) - 特朗普政府加征关税的法律依据", "《中美日内瓦经贸会谈联合声明》(2025年5月) - 导致订单爆发式恢复的关键政策转折点", "“全球100韧性城市” (洛克菲勒基金会项目) - 义乌于2016年入选的城市属性背景", "《大西洋月刊》(The Atlantic) - 记者探访义乌工厂并记录工人对美关税的强硬态度", "英国广播公司(BBC) - 驻义乌记者对胡天强（中祥玩具）及市场规模的现场观察", "赵春兰、范丽珠《义乌模式：老百姓版本的全球化》 - 阐述义乌商业逻辑的学术著作", "《中银研究》刘佩中报告 - 关于义乌经贸发展特征与挑战的政策建议"], "keywords": ["关税风暴", "蚂蚁雄兵", "草根商业文明", "韧性城市", "市场采购贸易", "普惠共生", "新兴市场", "贸易主动权"], "style_tone": "逻辑严密的实证调研风格，融合了宏观经济分析与微观商户叙事，基调积极且富有洞察力。"}</t>
+  </si>
+  <si>
+    <t>{"title": "微短剧时代论：800倍速的“短国”，流水线上的“细糠”", "summary_long": "文章深度剖析了微短剧作为移动互联网原生文化现象的演进历程与现状。作者认为，微短剧并非艺术形式的线性演进，而是经由“终端代际迁移”（网页到移动端）和“算法收编内容”（即时反馈与情绪投喂）两次媒介迁移催生的产物。文章将微短剧的发展划分为网剧时代（2008-2018）、微剧时代（2010-2018）及强付费时代（2019-2023）。2019年是关键拐点，监管收紧与小程序技术的成熟促使资本转向更轻量化的视听出口。进入2025年，行业关键词转为“细糠”，意指追求精英化品相的精品微短剧，试图摆脱“草根”和“低质”标签。\n\n然而，繁荣背后隐藏着深层困境：一是“名”与“实”的落差，即便制作精良化，叙事逻辑仍高度依赖“打脸虐渣”等算法化模组，缺乏真正的女性主体性觉醒；二是工业逻辑与艺术自律的冲突，在ROI（投资回报率）考核与高产压力下，质量、成本与市场构成了“不可能三角”；三是横屏短剧虽投入巨大（如过亿成本），却陷入“长剧精简版”的思维定式，难以破圈。作者指出，微短剧目前更多是商品和投资属性的体现，而非独立的艺术样态。真正的“艺术自律”和生活洞察，或许正从工业化的微短剧流向更具生命力的短视频博主小剧场。微短剧在全面走向工业化的同时，其原生的时代张力也在加速瓦解。", "key_arguments": ["微短剧是移动互联网生态下的原生文化事件，其核心逻辑是算法驱动的情绪投喂而非传统的叙事建构。", "行业正经历从“前向付费”（小程序剧单点付费）向“平台分账/免费模式”（如红果App）的商业范式转移。", "“细糠”化（精品化）目前多为宣发标签，微短剧尚未建立起一套自洽且独立的叙事本体，仍依附于长剧或网文的旧有范式。", "微短剧的工业化焦虑导致其在“不可能三角”（质量、成本、市场）中挣扎，难以承载深度的现实主义期许。", "真正的叙事活力可能存在于非工业化的网络博主小剧场中，而非高度套路化的微短剧流水线。"], "mentioned_resources": ["《屌丝男士》(2012) - 网剧时代草根叙事与自嘲风格的代表。", "《万万没想到》(2013) - 确立了早期网剧的解构与反讽底色。", "《太子妃升职记》(2015) - 验证了情绪即时反馈在小屏幕语境下的威力。", "《陈情令》(2019) - 标志着大制作网剧触达巅峰及随后的题材空间压缩。", "《恶女的告白》(2021, 姜十七) - 验证了MCN工业化模式与电商造星的闭环。", "《虚颜》(2022, 曾庆杰) - 横屏短剧专业化赓续的案例，开启短剧导演转战长剧路径。", "《逃出大英博物馆》(2023) - 展示了微短剧在文旅、家国叙事上的潜力。", "《黑莲花上位手册》(2023) - 因极端叙事被下架，引发行业监管与转型思考。", "《我在八零年代当后妈》(2024) - 听花岛等厂牌领跑竖屏短剧的代表作。", "《朱雀堂》/《狮城山海》(2025) - 高投入横屏短剧，尝试“中剧”品类但面临叙事瓶颈。", "《唐朝诡事录》衍生系列 (2025) - 长剧集IP与微短剧存量共生的试点。", "《大瑶同学Remix》/《菇菇米Gugumi》 - 作者推崇的具有艺术自律性的短视频博主小剧场系列。"], "keywords": ["算法收编", "情绪投喂", "细糠", "叙事主体性", "中剧", "ROI考核", "不可能三角", "新大众文艺"], "style_tone": "逻辑严密的行业观察，带有深刻的人文批判与社会学反思风格。"}</t>
+  </si>
+  <si>
+    <t>{"title": "田野｜佛在僧俗之间——一个缅甸寺院的观察", "summary_long": "本文是作者于2024年初在缅甸曼德勒彬乌伦（Pyin Oo Lwin）的胶瑟马哈甘大勇寺院进行为期四个月田野调查的深度观察。文章首先打破了外界对缅甸仅有“电诈与战乱”的刻板印象，指出佛教（信徒占85%以上）才是缅甸人的心理防线与社会底色。作者通过亲身经历，描述了寺院作为战乱中安全港的功能，以及僧俗之间基于“信任”的深厚纽带。\n\n在组织架构上，文章详细介绍了瑞金派（Shwegyinnikaya）及其分支马哈甘达勇体系。该派系以严格持守戒律、反对政治化和强调“自我净化”著称。寺院内部等级森严，从管理层的西亚多（Sayadaw）到比丘、沙弥及净人，各司其职。僧侣生活极度规律，严格执行过午不食、托钵化缘及冷水净身等戒律。\n\n文章核心探讨了缅甸人的“道德宇宙秩序”。通过拜佛、布施、持戒和禅修，缅甸人将“因果业力”转化为日常行动的动力。面对战争带来的“刀兵劫”，他们将其阐释为集体的果报，并试图通过培养慈悲心（Metta）和内心的平静来消解负面情绪。这种心灵秩序的重建，不仅是个体心理调适，更是一种隐蔽的政治参与：信徒坚信个人积累的善业能产生集体效应，最终帮助国家摆脱动乱。这种“以善胜恶”的逻辑，使宗教实践成为了混乱现实中维持社会互助与秩序的微观力量。", "key_arguments": ["宗教实践是缅甸人在极端战乱环境下构筑‘内心祥和世界’的防御机制，通过因果律将苦难合理化并寻求救赎。", "瑞金派马哈甘达勇体系通过严密的组织化管理和极度严苛的戒律复兴，在缅甸社会建立了极高的道德权威和社会威望。", "缅甸佛教并非纯粹的出世修行，而是一种‘入世的政治参与’：通过个人的道德实践（布施、持戒）积累集体善业，试图以此扭转国家的负面果报。", "心灵秩序的建立是一种制度化的情绪管理，它将战争创伤转化为可管理的宗教流程，在政治失灵时提供了社会再分配与互助的功能。"], "mentioned_resources": ["《慈经》 (Metta Sutta) - 文中提到在禅修和仪式结尾诵念，用于为众生祈祷和平的经典。", "温斯顿·金 (Winston King) - 人类学家，文中引用其观点说明佛教徒相信‘善良意志的力量可以扭转身体对抗’。", "马哈甘达勇西亚多 (Ashin Janakābhivaṁsa) - 缅甸近现代最具影响力的僧侣，马哈甘达勇体系创始人，曾被授予‘上首大贤智’称号。", "敏东国王 (King Mindon) - 瑞金派创立的历史背景人物，该派系为反对当时的僧团腐败而从善法派剥离。"], "keywords": ["瑞金派 (Shwegyinnikaya)", "马哈甘达勇 (MahaGandaryon)", "因果业力 (Kamma/Vipaka)", "慈悲心 (Metta)", "功德 (Merit)", "刀兵劫", "心灵秩序", "隐蔽的政治参与", "田野调查"], "style_tone": "兼具严谨人类学观察与深厚人文关怀的叙事风格，语调平和、理性且充满同理心。"}</t>
+  </si>
+  <si>
+    <t>{"title": "金伯莉·凯·黄谈蛛网资本主义：这网保护的是资本，而不是人", "summary_long": "本文是对社会学家金伯莉·凯·黄（Kimberly Kay Hoang）关于其著作《蛛网资本主义》的深度访谈。作者通过对越南、缅甸及多个离岸金融中心（如开曼、萨摩亚）长达18个月的田野调查，揭示了当代全球精英如何构建一个隐秘、碎片化且跨国的金融体系。不同于经典理论中抱团的国家精英，现代“蛛网资本主义”依赖于战略性的不透明与协作：律师、银行家等专业人士（资本保管者）各自掌握碎片化信息，通过法律防火墙和离岸实体为超级富豪（资本所有者）提供豁免权，并将风险向下转移。这种结构已成为资本主义追求高回报的核心基础设施，而非副产品。在人性层面，该系统通过性别化的社交仪式制造“共同脆弱性”，将参与者通过“互为人质”的关系绑定，导致个体陷入道德悬置与心理毒性。尽管加密货币承诺去中心化，但作者认为其目前仅是蛛网的延伸。对于“新社会契约”，作者认为其虽是必要的道德愿景，但在跨国资本流动的背景下，若不拆解离岸金融的基础设施，其在国家层面的执行将面临巨大挑战。", "key_arguments": ["现代精英权力已从单一国家情境转向全球分散的‘蛛网’结构，其核心特征是战略性的信息碎片化与不透明。", "‘蛛网资本主义’并非体制的副产品，而是当代资本主义在政治不稳定地区获取高回报的必要核心基础设施。", "腐败在法治国家（如美国特拉华州）被专业化、合法化，通过司法辖区套利实现利润向上汇聚与风险向下转移。", "精英圈层的联结并非基于信任，而是通过共同的越界行为制造‘共同脆弱性’，形成一种‘互为人质’的控制机制。", "新社会契约的实现取决于能否在全球尺度上拆解让蛛网资本主义滋生的跨国基础设施，而非仅仅在国家内部改革。"], "mentioned_resources": ["《欲望交易:亚洲崛起、西方衰落与全球性工作中的隐秘货币》 (金伯莉·凯·黄) - 作者的第一本专著，通过越南高端酒吧田野调查揭示全球性工作中的隐秘货币。", "《蛛网资本主义：全球精英如何从新兴市场攫取利益》 (金伯莉·凯·黄) - 本文核心讨论著作，剖析前沿市场中的跨国资本网络与离岸金融。", "《权力精英》 (C. Wright Mills) - 1956年经典著作，描绘了嵌入在单一国家情境中、紧密相连的精英圈子。", "《红楼梦》 (曹雪芹) - 文中以‘护官符’类比传统、易于解读的家族与官员庇护网络。", "《你的富家闺蜜》与《天生富有》 (薇薇安·图/Vivian Tu) - 被作者引用为非掠夺性、旨在揭开华尔街神秘面纱的金融实践案例。"], "keywords": ["蛛网资本主义 (Spiderweb Capitalism)", "前沿市场 (Frontier Market)", "司法辖区套利 (Jurisdictional Arbitrage)", "战略性不透明 (Strategic Obfuscation)", "共同脆弱性 (Mutual Vulnerability)", "离岸金融 (Offshore Finance)", "道德悬置 (Moral Suspension)", "新社会契约 (New Social Contract)"], "style_tone": "兼具严谨社会学批判与深厚人文关怀的分析风格，语调冷静而带有对个体命运的同情。"}</t>
+  </si>
+  <si>
+    <t>{"title": "澎湃思想周报｜夺取格陵兰背后的阴暗图景；“新老年”与《冬之梦》", "summary_long": "本文由两个深度专题组成。第一部分剖析了特朗普夺取格陵兰岛背后的深层动机。文章指出，这并非简单的国家安全诉求，而是由硅谷及能源寡头驱动的掠夺性计划。通过“唐罗主义”的扩张逻辑，美国寡头集团（如彼得·蒂尔、安德森等）试图将格陵兰变为资源开采宝库及“网络国家”实验场。这种模式类似于19世纪推翻夏威夷政权的裙带资本主义，旨在建立一个摆脱民主监管、由CEO领导的自由意志主义乌托邦。文中详细揭示了KoBold Metals等公司利用AI技术勘探矿产，以及Praxis组织如何试图在格陵兰落地其“数字国家”构想，反映了资本力量对帝国机器的直接操纵。\n\n第二部分聚焦“新老年”课题。以芭芭拉·罗森温的新著《冬之梦》为切入点，探讨了西方历史上对老年态度的演变。文章区分了“年轻老人”与“衰老老人”的概念，指出随着人类预期寿命的延长，传统的“学习-工作-退休”三阶段人生模式已过时。当代社会需要进行系统性重构：在教育上推动老年人融入大学生态（如米拉贝拉社区）；在职场上保留老年员工经验（如日本“窗边族”）；在居住上推广多代共居模式（如德国及纽约法拉盛一号）。核心观点认为，老年应被视为社会凝聚力的源泉而非负担，社会必须摒弃年龄歧视，将生命历程视为一个连续体。", "key_arguments": ["特朗普夺取格陵兰的执念背后是美国寡头集团的资源掠夺计划与反乌托邦实验，标志着企业金主直接操纵帝国扩张的新模式。", "“网络国家”运动（Network State）试图通过区块链和私有领土建立免税、无监管的飞地，将格陵兰视为最后的边疆。", "老年并非单一的衰退过程，而是一个充满多样性的情感过程，历史上的社会对老年的态度（如斯巴达、罗马、犹太）存在显著差异。", "长寿时代的到来要求社会制度进行根本性重设计，打破三阶段人生轨迹，实现学习、工作与休闲在全生命周期内的交织。", "解决老年问题的关键在于消除年龄歧视，通过政策干预（如多代共居、灵活职场）让老年人重新成为社会价值的创造者。"], "mentioned_resources": ["《冬之梦：一份关于老年的历史指南》(Barbara H. Rosenwein) - 核心探讨书籍，论述老年的情感史与社会态度。", "《新共和》(Casey Michel) - 剖析特朗普格陵兰计划的深度报道来源。", "《雅各布》(Lois Parshley) - 报道KoBold Metals利用AI开采矿产的细节。", "《时代》周刊《长寿特刊》 - 提出“新老年时代”概念。", "《阿伽门农》(埃斯库罗斯) - 爱泼斯坦引用其对死亡的描述。", "《李尔王》(莎士比亚) - 罗森温书中引用的文学案例。", "Praxis (Dryden Brown) - 推动“网络国家”运动的组织。", "KoBold Metals - 利用AI算法在全球锁定矿藏的矿业公司。"], "keywords": ["唐罗主义 (Donroe Doctrine)", "网络国家 (Network State)", "裙带资本主义", "自由意志主义乌托邦", "年轻老人 (Young Old)", "三阶段人生", "窗边族 (madogiwa-zoku)", "多代共居"], "style_tone": "前半部分为犀利批判的政治经济分析，后半部分为充满人文关怀与前瞻性的社会学论述。"}</t>
+  </si>
+  <si>
+    <t>{"title": "人类世的政治狗：与他者一起好好生活可能吗", "summary_long": "文章探讨了在“人类世”背景下，如何超越传统人类中心主义，重新构筑跨物种的政治共同体。作者首先挑战了亚里士多德将人定义为唯一“政治动物”的传统，指出这种定义建立在对动物性的排除之上。在21世纪，随着生物学和生命政治理论的发展，这种人与动物的绝对分割已不再有效。拉菲·尤亚特提出“跨越物种界线重新思考政治”，主张政治并非人类独有的自主空间，而是多物种在共享空间中对生命条件的协商。文章以“人-狗关系”为范式，批判了西方主流的“物种故事”和唐娜·哈拉维的“同伴物种”范式。作者认为，这些范式过度关注仅占全球15%-25%的西方宠物狗，且通过“训练机制”掩盖了支配与服从的不平等权力结构，导致狗的“去狗化”。相比之下，占绝大多数的街狗、村狗等“自由生活的狗”才是“真正的狗”，它们展示了与人类共生的原始且无法控制的边缘。文章引入列斐伏尔“对城市的权利”概念，主张将城邦重塑为“动物园-城邦（Zoopolis）”，将狗视为具有自主权的“邻居”而非依赖人的“同伴”。通过分析印度和土耳其的法律实践，作者指出当前的“福利知识型”管理仍是去政治化的，真正的跨物种政治应承认非人类行动者的“政治能动性”和独特的“logos（理性/语言）”。最终，政治被重新定义为不同物种间符号流通的强度，旨在实现“与非人类他者一起好好生活”。", "key_arguments": ["政治不应被视为人类从自然中赢取的自主空间，而应被视为多物种在共享空间中协商生命关系的‘关系自由’。", "批判‘同伴物种’范式：哈拉维等人的理论过度基于西方宠物模型，其本质是通过规训机制实现‘去狗化’的生命政治操纵，掩盖了支配关系。", "提倡‘邻居’而非‘同伴’：应赋予非家养狗‘对城市的权利’，承认它们作为自主政治行动者的地位，而非仅仅是待领养的‘无主物’。", "跨物种政治的基石是承认非人类动物拥有自己的logos（交流与能动性系统），政治性是一个程度问题而非种类问题。"], "mentioned_resources": ["《政治学》/《动物志》(亚里士多德) - 探讨政治动物的原始定义及其对动物性的排除。", "《跨物种政治》(Rafi Youatt) - 提出跨越物种界线重新思考政治，强调‘关系的自由’。", "《末日松茸》(罗安清/Anna Tsing) - 提出人类世作为‘不稳定’的标志，强调‘无法控制的边缘’和‘干扰’的创造性。", "《狗政治》(Mariam Motamedi Fraser) - 批判将狗自然化为‘属于家庭’的‘物种故事’。", "《同伴物种宣言》/《当物种相遇》(唐娜·哈拉维) - 提出同伴物种范式，但被本文批判为掩盖了支配权力。", "《动物园城邦》(Sue Donaldson &amp; Will Kymlicka) - 尝试用政治范畴讨论动物地位，但被指仍局限于西方同伴狗模型。", "《对城市的权利》(亨利·列斐伏尔) - 被借用来讨论动物在城市空间中的政治权利。", "《动物以及为什么它们重要》(玛丽·米基利) - 关于混合物种共同体的早期理论思考。"], "keywords": ["人类世 (Anthropocene)", "跨物种政治 (Interspecies Politics)", "动物园城邦 (Zoopolis)", "关系自由 (Relational Freedom)", "福利知识型 (Welfare Episteme)", "生命政治 (Biopolitics)", "去狗化 (De-dogging)", "邻居 (Neighbor)"], "style_tone": "逻辑严密的激进政治哲学分析，带有深厚的人文关怀与批判色彩。"}</t>
+  </si>
+  <si>
+    <t>{"title": "不可居住的青春：《纸房子》中的空间、权力与逃离", "summary_long": "本文是一篇针对国产视觉小说游戏《纸房子》的深度文化批评。文章核心观点认为，该游戏不仅是“青春疼痛”叙事的延续，更是一场关于“空间困境”的社会学探讨。作者引入亨利·列斐伏尔的“空间生产”理论，指出空间并非中性容器，而是权力关系的具象化。主角赵颖的悲剧在于她处于一个“不可居住”的状态，其主体性在家庭、学校与社会关系的层层挤压下逐渐瓦解。\n\n在家庭空间中，赵颖遭遇的是“结构性排挤”。尽管物理上在场，但她在情感和资源分配上被彻底边缘化，父亲的新家庭将其视为多余者，家从庇护所异化为暴力与剥夺的源头。在校园空间中，游戏呈现了一种“松散的失序”，学校作为制度力量的缺席，导致了寝室内部微型权力结构的膨胀与霸凌的横行。赵颖在这些空间中不断被驱赶，被迫调整姿态以适应他人的秩序。\n\n文章进一步分析了游戏中的“关系空间”（友谊、暧昧与依附）。这些关系虽提供了暂时的喘息缝隙，但因缺乏稳固的结构支撑而显得极其脆弱，无法成为真正的救赎。视觉上，游戏以黑白基调象征压抑的现实，而稀缺的“蓝色”则代表了地理跨越、身份悬置或代偿性投射的微弱可能。最终，“纸房子”这一意象精准地隐喻了归属感的脆弱与易碎：当所有可居住的空间都拒绝主体存在时，毁灭（点燃纸房子）成为了一种无奈的终局。文章总结道，《纸房子》并非关于成长的励志叙事，而是揭示了当个体无处可逃时必须独自承受的、如灰烬般不确定的生存状态。", "key_arguments": ["空间并非静态背景，而是由权力生产并决定个体生存形态的结构性力量。", "家庭空间的‘不可居住性’源于资源剥夺与情感排挤，使成员异化为‘在场的他者’。", "校园空间的压迫不仅来自严苛制度，更来自制度缺席下的无序暴力与微型权力再分配。", "亲密关系在结构性困境面前仅具‘缝隙’功能，无法提供实质性的社会救赎或空间替代。", "‘纸房子’隐喻了现代青少年归属感的极端脆弱性，死亡或毁灭是空间挤压到极限后的必然断点。"], "mentioned_resources": ["《纸房子》 (游戏) - 本文评论的核心对象，中式校园背景的视觉小说。", "亨利·列斐伏尔 (Henri Lefebvre) - 空间生产理论的提出者，文中用于分析空间的三种辩证统一（感知、构想、生活）。", "李春敏《列斐伏尔的空间生产理论探析》 (文献) - 文中关于空间理论的学术引用来源。", "Wenz Karin 《Death》 (文献/书章) - 出自《The Routledge companion to video game studies》，用于论述游戏中死亡的象征功能。"], "keywords": ["空间生产 (Production of Space)", "主体性 (Subjectivity)", "结构性排挤", "具身压迫", "权力场域", "中式青春", "纸房子 (意象)"], "style_tone": "逻辑严密的学术批评风格，带有浓厚的人文关怀与忧郁的叙事基调。"}</t>
+  </si>
+  <si>
+    <t>{"title": "一种声音·阿甘本｜厨子、戏子和船长；活还是偷生……", "summary_long": "本文由意大利哲学家阿甘本的四则短评组成，核心探讨了现代政治权力的异化、信仰缺失的系统机制以及个体生命的真实存在状态。首先，阿甘本借克尔凯郭尔的隐喻指出，现代社会的“船长”已被“厨子”（关注琐碎生存）或“戏子”（热衷表演）取代，导致航线迷失，社会走向沉没。其次，他修正了伊万·伊里奇关于工业系统因失去信誉而崩溃的预言，提出当代系统恰恰是建立在“不信”和“小信”基础上的。银行取代教会成为管理“不信”的祭司，金钱则是信仰缺失的具象化。系统通过逼迫人们“相信自己不相信”的谎言来维持，这种建立在虚无之上的权力既脆弱又难以通过传统的合法性批判来战胜。随后，阿甘本通过对“大写字母”的批判，呼吁回归“小写”的生活，认为宏大叙事（如国家、神的大写化）是理解的障碍，而“小写地活”才是对地球真实的爱。最后，他区分了“活”与“偷生”，指出统治者正致力于将人转化为丧失交流能力、只会计算的“偷生者”，而真正的“活”必须拒绝“赤裸生命”的抽象，与自身的生活方式生死与共。", "key_arguments": ["现代政治权力的错位：统治者不再提供方向（航线），而是转向管理物质生存（厨子）或进行政治表演（戏子）。", "不信的系统论：当代社会系统并非依赖信誉维持，而是建立在“不信”和“小信”的管理之上，银行作为新的祭司，管理着作为“信仰缺失形式”的金钱。", "反抗宏大叙事：反对将概念（如国家、神）大写化，主张通过“小写”的、具体的、非优先性的方式去观察和生活。", "活与偷生的对立：批判权力将生命简化为“赤裸生命”和“偷生”状态，认为真正的生命在于与生活方式的不可分割性，而非仅仅是生物意义上的存续。"], "mentioned_resources": ["克尔凯郭尔《生命道路上的各个阶段》/《要么/要么》 - 关于“厨子掌舵”隐喻的来源背景。", "伊万·伊里奇《共愉的工具》(Tools for Conviviality) - 预言工业系统崩溃及信誉丧失的社会学著作。", "陀思妥耶夫斯基《群魔》 - 提及人物斯塔夫罗金（Stavrogin）关于“不相信自己不相信”的心理状态。", "琪琪·迪莫拉 (Kikì Dimulà) 的诗作 - 关于“大写与小写”的落雨隐喻。", "圣经《马太福音》、《罗马书》、《路加福音》 - 关于“小信”、信仰的口与心、祭司与利未人的典故引用。"], "keywords": ["赤裸生命 (Bare Life)", "偷生 (Survival/Sopravvivenza)", "不信 (Apistia)", "小信 (Oligopistos)", "共愉 (Conviviality)", "大写/小写 (Capitalization/Lowercase)", "银行神学"], "style_tone": "逻辑深邃且带有忧郁色彩的哲学批判风格，言简意赅，充满人文关怀与对现代性的冷峻审视。"}</t>
+  </si>
+  <si>
+    <t>{"title": "洞天寻隐·学林纪｜越南黎初帝王的道教信仰", "summary_long": "本文深入探讨了越南黎初时期（1428—1527）帝王独特的道教信仰及其政治社会影响。文章指出，黎初开国君主黎利（黎太祖）通过构建“剑印天命”的神话为政权合法性背书，其核心元素如神剑、宝印与天师道的“天师剑—都功印”高度契合，黎利自号“蓝山洞主”，开启了黎初君王的道教信仰传统。这一传统在黎圣宗（天南洞主）时期达到文学巅峰，圣宗虽尊崇儒教，却在个人精神世界中深度沉溺于游仙诗创作，试图通过诗文与神仙沟通，并自比李白、欧阳修。然而，黎初帝王的道教信仰具有鲜明的“个人小传统”特征：他们并不以国家行政力量兴教，不强求朝臣信奉，且信仰内容与儒家圣贤之道杂糅。这种信仰在政治上与官方儒教政治形成“双轨并行”的奇异景观。文章进一步分析了君臣之间的张力：以阮廌、吴士连为代表的儒臣对君王的道教倾向持保留、消解甚至隐晦的态度，在编纂《蓝山永陵碑》或《大越史记全书》时有意删削神异色彩，通过儒家话语对冲君王的仙道追求。尽管如此，帝王的个人偏好仍对越南社会产生了深远影响，如襄翼帝时期对“高山大王”等神灵的封敕，推动了越南民间神祠信仰体系的形塑。最终，黎初的道教信仰在莫朝篡位及战乱中随“剑印”的失踪而式微，但其留下的“洞主”名号与祠神传统成为了越南文化环境的重要组成部分。", "key_arguments": ["黎初帝王的道教信仰是国家儒教政治大传统下的‘君王信仰小传统’，具有强烈的个人化特征且不干预国政。", "黎太祖黎利通过‘剑印天命’（神剑与宝印）的叙事，模仿中国天师道模式构建了黎朝的开国合法性。", "黎圣宗通过‘洞主’自号与游仙诗创作，在儒家明君形象之外构建了一个追求仙道的精神世界，体现了儒道融合的尝试。", "黎初儒臣通过史书编纂和言论谏诤，有意识地对君王的道教信仰进行‘儒家化’消解或史实删减。", "黎初帝王的崇道行为虽未制度化，但通过‘上有所好下必甚焉’的效应，形塑了越南后世兴盛的民间神祠与玉谱文化。"], "mentioned_resources": ["《蓝山实录》 (黎利/阮廌等) - 记录黎利创业历程及剑印神迹的原本，语言俚俗。", "《重刊蓝山实录》 (胡士扬) - 1676年修订本，对原本叙述进行了儒家化的优化与整理。", "《大越史记全书》 (吴士连/范公著等) - 越南官修正史，对黎初帝王崇道事迹有选择性保留或删削。", "《历朝宪章类志》 (潘辉注) - 记载黎初帝王统绪与祀典的重要文献。", "《琼苑九歌》 (黎圣宗) - 黎圣宗与28位文臣合著的诗集，含有浓厚的仙道与儒家治世思想。", "《黎皇玉谱》 (佚名/托名黎文休) - 皇室秘藏家谱，详细描述了神剑宝印的尺寸、符文与神咒。", "《丁氏家谱》 (丁氏家族) - 记载有与皇室类似的剑印敕令与道教神咒。", "《神仙感遇传》 (杜光庭) - 中国道教典籍，文中用于对比天师剑传说。", "《云笈七签》 (张君房) - 中国道教典籍，文中用于考证天师剑与都功印的器道观念。", "《高山大王神祠碑铭并序》 (黎嵩) - 记录襄翼帝时期神灵感应与祠宇修建的重要碑刻。"], "keywords": ["剑印天命", "蓝山洞主", "天南洞主", "游仙诗", "禳灾术", "三教思想", "君王信仰小传统", "洞天福地", "神祠信仰"], "style_tone": "严谨的学术考据风格，结合了历史文献学与宗教社会学分析，语调客观且富有洞察力。"}</t>
+  </si>
+  <si>
+    <t>{"title": "由《春秋》“楚人杀陈夏征舒”章看特朗普囚马杜罗", "summary_long": "本文是一篇典型的以儒家经学视角评述当代国际政治的深度评论。作者延续此前以《孟子》评拜登赦子的逻辑，试图将特朗普囚禁马杜罗这一事件纳入儒家“天下秩序”的框架进行审视。文章首先界定了儒家的“有限天下”（政治共同体）与“无限天下”（作为文明批判的自然/天道），强调政治合法性源于对“自然人伦”的赞辅。随后，文章核心部分引用《春秋》“楚人杀陈夏征舒”条目，通过《左传》、《公羊传》、《毂梁传》的三传义理对特朗普的行为进行“定罪”分析：其一，马杜罗并非如夏征舒般的篡位乱臣，特朗普缺乏“吊民伐罪”的法理基础；其二，特朗普的行为实为“贪其富”（图谋委国石油），违背了行义不贪利的原则；其三，在现代性主导的“上帝已死”的权力秩序中，缺乏一个无私利的“天子”位阶来主持公道。作者进一步反驳了毛朝晖、白彤东等学者关于“仁责高于主权”的观点，认为在异文明冲突且缺乏共同价值基准的当下，不应为特朗普的行为寻求儒家合法性。文章最后以仿《春秋》笔法对该事件进行“微言大义”式的定性，批判其为非义之举。", "key_arguments": ["政治秩序的最高合法性源于对‘自然人伦’的保护，而非单纯的权力运作或现代性契约。", "特朗普囚禁马杜罗不符合《春秋》中‘专讨’的条件，既无乱臣篡位的先决事实，又存在明显的‘贪富’（石油利益）动机。", "现代国际秩序本质上是‘诗与春秋偕亡’的霸道帝国秩序，缺乏超越性的天道批判，导致个体与弱国在权力扩张面前‘逃无可逃’。", "儒家的‘仁责高于主权’原则仅适用于奉行同一文明基准的内部，不应被误用来为异文明间的强权干预辩护。"], "mentioned_resources": ["《春秋》“楚人杀陈夏征舒”章 - 核心论证案例", "《孟子》“舜负父而逃”章 - 序言引入，论证人伦高于政治", "《左传》 - 用于分析楚王伐陈的合法性（安民与不县其地）", "《公羊传》 - 用于论证“上无天子”背景下的诸侯专讨逻辑", "《毂梁传》 - 用于分析“入”字背后的民心向背与文明考量", "毛朝晖《孟子会赞成讨伐委内瑞拉，但不会赞成美国出兵》 - 文中引用的学术讨论对象", "白彤东《孟子是否支持特朗普抓捕马杜罗》 - 文中引用的学术讨论对象", "韩炳哲《倦怠社会》（注：此处为指令示例参考，原文未提，原文提到的是项飙式的方法论思考，但未指名书名，故不列入）"], "keywords": ["天下秩序", "自然人伦", "吊民伐罪", "现代性批判", "有限天下与无限天下", "唐罗主义", "霸道", "微言大义"], "style_tone": "严谨的儒家经学分析风格，带有深厚的人文关怀与理想主义批判色彩，语体古雅且逻辑缜密。"}</t>
+  </si>
+  <si>
+    <t>{"title": "被量化的主体：数字化警告体系与技术焦虑", "summary_long": "文章从作者在乡村小路上遭遇电动车电量骤降引发的焦虑谈起，探讨了现代技术如何通过“数字化警告体系”重塑人类的主体性。作者指出，当代技术不再仅仅是工具，而是一个自治的环境，通过读数、概率和算法生成的“剩余可能性”来控制现代人的情绪。这种体系的核心在于设定“阈值”，将未来的失败或危险提前可视化，使人陷入预期的紧张状态，从而放弃身体经验和直觉判断，转而依赖系统的外部确认。这种“不透明”的技术逻辑强化了主体的脆弱感，将生存异化为一场关于阈值的管理。\n\n文章进一步引入了三种哲学路径来剖析这一困境：首先是斯蒂格勒（Stiegler）的“技术药性”理论，认为技术既是扩展能力的解毒剂也是剥夺判断力的毒药，且陷入了“以技术解技术之毒”的闭环；其次是伊里奇（Illich）的“结构性反生产性”观点，警示工具一旦越过尺度阈值便会反噬人类，主张通过设定边界来守护人类主权；最后是马古利斯（Margulis）的“内共生”视角，认为人与技术已构成事实上的共生单元（赛博格），技术已成为感官的基底。\n\n最后，文章提出在技术与反技术之间，我们无法简单退出，但可以重新定义主体性。主体性不应被理解为完全的自主掌控，而应是在共生关系中保持清醒，为模糊、犹豫和未被计算的经验保留空间，拒绝将技术警告直接内化为对自身价值的终极裁决。公共讨论的价值在于帮助人们辨认结构性困境，避免将其误认为个人能力不足。", "key_arguments": ["数字化警告体系通过设定‘阈值’和‘风险可视化’，将现代人的生存状态转化为一种持续的、受外部系统评估的脆弱感。", "技术的不透明性剥夺了主体的经验判断力，使人被迫信任算法生成的概率，导致主体从‘行动者’转变为‘被评估的对象’。", "斯蒂格勒的‘药性’逻辑存在闭环风险，即试图用更精密的系统去解决系统带来的焦虑，导致技术依赖的进一步加深。", "面对不可逆的技术共生现实，主体性的重建不在于彻底摆脱技术，而在于在量化逻辑中保留‘非量化’的身体经验与直觉空间。"], "mentioned_resources": ["《技术与时间》(Technics and Time, 1) (贝尔纳·斯蒂格勒) - 论述技术作为人类记忆与组织的外化形式及其药性。", "《照顾青少年与世代》(Taking Care of Youth and the Generations) (贝尔纳·斯蒂格勒) - 批判由资本与算法垄断的当代技术体系。", "《共愉的工具》(Tools for Conviviality) (伊万·伊里奇) - 提出结构性反生产性，主张划定技术边界。", "《微观世界：生物演化的四亿年》(Microcosmos) (林恩·马古利斯 &amp; 多里昂·萨根) - 阐述内共生理论，瓦解人与技术的二分法。", "《枪炮、病菌与钢铁》(Guns, Germs, and Steel) (贾雷德·戴蒙德) - 用于说明人类选择农业后进入的不可逆技术路径。", "《把自己作为方法》(项飙) - (注：原文未直接提及，但语境关联主体性重建，此处仅保留原文明确提到的实体)", "《倦怠社会》(韩炳哲) - (注：原文未直接提及，语境关联)"], "keywords": ["量化主体", "数字化警告", "技术药性 (Pharmakon)", "结构性反生产性", "内共生理论", "阈值管理", "赛博格 (Cyborg)", "技术不透明性"], "style_tone": "深度思辨、带有忧患意识的技术哲学评论，语体严谨且富有感性叙事色彩。"}</t>
+  </si>
+  <si>
+    <t>{"title": "“把天聊死”作为方法：社会学家如何研究早期人工智能", "summary_long": "文章探讨了常人方法学创始人哈罗德·加芬克尔（Harold Garfinkel）在1960年代对早期聊天机器人ELIZA和LYRIC的研究，并以此反思当代AI争议。文章指出，面对AI是否具有“感知力”的争论（如谷歌LaMDA事件），主流观点常将其归结为“ELIZA效应”，即人类因误解算法而产生的认知偏差或拟人化妄想。然而，加芬克尔提供了一种激进的替代视角：机器的“智能”或“能动性”并非源于其内部代码，而是一种人类与机器协同合作的“社会成就”。\n\n加芬克尔通过其早期的“是-否”随机回答实验发现，人类具有极强的意义构建能力，即使面对随机的回应，也会通过“信任条件（Trust Conditions）”假设对方有意义，并利用“等等（et cetera）”和“且过（let it pass）”等实践来修补互动的裂痕。在对ELIZA和LYRIC的研究中，加芬克尔通过编写脚本故意制造互动“麻烦”甚至导致“机器停机”，这种“破坏性实验”揭示了人类如何利用对话的“序列相关性”和“索引性”来赋予机器行为以动机和连贯性。他认为，意义并不存在于头脑或代码中，而是存在于互动产生的空间里。文章最后强调，当代AI研究应超越“技术本体论”，关注人机交互中那些被视为理所当然的社会性特征，将AI视为有赖于用户意义构建工作才能有效运行的系统。", "key_arguments": ["AI的‘智能’或‘能动性’不是机器固有的本体属性，而是人类在互动过程中通过社会实践共同完成的‘社会成就’。", "人类在交互中遵循‘信任条件’，会主动承担‘额外工作’来修补机器的无能，以维持对话的连贯性和意义感。", "意义具有‘索引性’和‘序列性’，是在对话轮次的动态演进中回顾性、前瞻性生成的，而非预设在脚本或算法中的‘语境框架’。", "‘机器停机’或互动崩溃是研究人机交互的关键窗口，通过‘把天聊死’的破坏性实验，可以揭示维持社会秩序的隐性规则。"], "mentioned_resources": ["《迈向信息的社会学理论》(Toward a Sociological Theory of Information) (Harold Garfinkel) - 探讨信息本质及社会对象创建的早期手稿", "ELIZA (Joseph Weizenbaum) - 1960年代模拟罗杰斯式心理治疗师的早期聊天机器人", "LYRIC (Leonard &amp; Gloria Silvern) - 计算机远程教学语言程序，被加芬克尔用于互动实验", "《计算机不能做什么》(What Computers Can't Do) (Hubert Dreyfus) - 批判AI局限性的经典著作", "《计算与能动性》(Computation and Human Experience) (Philip Agre) - 探讨索引性与计算设计的著作", "《把自己作为方法》(项飙) - 译者按中引用，作为理解当代社会学观察的背景", "《倦怠社会》(韩炳哲) - 译者按中引用，作为当代社会心态的背景", "DOCTOR脚本 (Joseph Weizenbaum) - ELIZA最著名的心理医生模拟脚本", "LaMDA (Google) - 2022年引发‘AI是否有感知力’争议的大语言模型"], "keywords": ["常人方法学 (Ethnomethodology)", "ELIZA效应", "信任条件 (Trust Conditions)", "索引性 (Indexicality)", "序列相关性 (Sequential Relevancy)", "破坏实验 (Breaching Experiments)", "社会成就 (Social Achievement)", "打圆场 (Glossing)"], "style_tone": "学术严谨且具有深厚社会学底蕴的分析风格，批判性地反思技术决定论，充满人文关怀。"}</t>
+  </si>
+  <si>
+    <t>{"title": "熟龄恋综：和老龄化社会一起来的，还有爱情", "summary_long": "文章探讨了近期兴起的熟龄恋爱真人秀（如《日落时分说爱你》）如何打破社会对中老年群体的刻板印象。长期以来，50+人群在影视叙事中往往被“去性化”，仅作为家庭伦理中的符号存在，其爱欲被视为“丑恶或可笑”。文章指出，熟龄恋综的出现标志着一种新叙事的开启：中年不再是压力与边缘化的代名词，而是开启人生新阶段的“入场券”。\n\n核心论证围绕“重塑中女叙事”展开。文章认为，传统的婚恋市场以生育价值为女性的“斩杀线”，而熟龄恋综通过展现具有魅力的成熟女性（如“徐家汇萧亚轩”），挑战了自18世纪以来强加于女性身上的“贞洁意识形态”。这种重塑不仅是情感的释放，更是对传统性别资本逻辑的改造。同时，文章反思了节目在制作上的局限：一方面，节目容易套用年轻人的“竞争模型”（如鲶鱼效应、匿名信），可能导致人性表达被污名化；另一方面，目前的叙事多局限于优渥阶层，呈现出一种“玻璃罩里的爱情”。\n\n文章最后引用布尔迪厄的“具身资本”理论，强调熟龄人士的魅力源于时间的积累与精神能量，而非单纯的外貌年轻化。作者呼吁，爱情叙事应拓展阶层维度，通过讲述具体的个人史（如韩国恋综《最后的爱情》中的奋斗故事），将“NPC”还原为鲜活的人。观看与谈论爱，本质上是中老年群体从旧秩序和劳役中获得自我解放的一种方式。", "key_arguments": ["中老年群体长期处于被‘去性化’的境地，熟龄恋综通过都市爱情叙事将该群体的爱欲重新带回大众视野。", "熟龄爱欲叙事的核心在于重塑‘中女叙事’，打破以生育价值和贞洁审视为核心的父权制枷锁。", "熟龄人士的性资本不应仅体现在身体层面，而应包含基于时间积累的‘具身资本’、情感资本与精神能量。", "恋综应从‘激情之爱’转向更适配熟龄者的‘陪伴式爱情’，并打破阶层局限，通过个人史构建更深沉的诗性叙事。"], "mentioned_resources": ["《日落时分说爱你》 (综艺) - 国内首档熟龄人群恋爱真人秀，探讨50+人群的爱欲。", "《最后的爱情》 (韩国JTBC综艺) - 邀请50岁以上男女在济州岛寻觅伴侣，包含多元阶层叙事。", "《老人》 (西蒙娜·德·波伏娃) - 论述社会对老年人欲望的偏见与不适感。", "《何谓“性资本”》 (伊娃·易洛思、达娜·卡普兰) - 探讨女性去性化历史及性资本的阶层性。", "《小城之春》 (费穆) - 早期中国电影中关于中年情感的经典叙事。", "《家有儿女》 (电视剧) - 代表了传统叙事中对大龄单身人士“再婚家庭”的归宿定义。", "《幸福来敲门》 (电视剧) - 罕见的拍出中年荷尔蒙但仍指向家庭和睦的作品。", "《姨妈的后现代生活》 (许鞍华) - 鲜有的通过京戏隐喻传达中女爱欲的作品。", "《菜肉馄饨》 (电影) - 讲述城市老人再婚，具有移风易俗的现实意义。", "《廊桥遗梦》 (电影) - 文中提到其对老年情色画面的呈现曾令年轻观众产生不适。", "布尔迪厄的“具身资本” (理论模型) - 强调资本随时间积累并通过日常惯习展现。"], "keywords": ["去性化 (Desexualized)", "性资本 (Sexual Capital)", "具身资本 (Embodied Capitals)", "中女叙事", "陪伴式爱情 (Companionate Love)", "阶层化", "自我解放"], "style_tone": "逻辑严密、兼具社会学深度与人文关怀的分析风格"}</t>
+  </si>
+  <si>
+    <t>{"title": "澎湃思想周报｜剑桥大学招生新政争议；大卫·鲍伊逝世十周年", "summary_long": "本文核心探讨了英国高等教育公平性的倒退趋势以及流行文化遗产在算法时代的代际断裂。首先，文章详细报道了剑桥大学三一学堂（Trinity Hall）引发的招生政策风波：该学院计划定向招收顶级私立中学（如伊顿公学）的学生，理由是这些学生在古典学、艺术史等学科上更具“智识契合度”。学院招生主任提出“反向歧视”概念，警惕因追求多样性而忽视私校优秀生。此举遭到《卫报》、校友及社会流动性专家的强烈抨击，批评者认为这混淆了“程序公平”与“结果公平”，将多年积累的阶层特权误认为个人天赋。文章指出，三一学堂作为“居间者”学院的转向，预示着精英制度在压力下的集体自保。其次，文章回顾了大卫·鲍伊逝世十周年的纪念活动，并引用《卫报》分析指出其音乐遗产面临的尴尬现状：尽管在博物馆（如V&amp;A）和中老年受众中地位崇高，但在流媒体算法和24岁以下年轻听众中，鲍伊的影响力正逐渐边缘化。其遗产管理方倾向于“博物馆式”的高端保存，而非积极融入当下媒介经验，导致其流动的艺术形象被简化为固定的视觉符号，难以与未来建立有效对话。", "key_arguments": ["“反向歧视”论调是精英阶层的防御性话语，它将招生筛选的瞬间公平凌驾于长期的制度性不平等之上，默认了起点差异的合理性。", "剑桥三一学堂的政策转向反映了精英大学在社会流动性减缓背景下的“制度性自保”，即优先选择资源充足的私校生以维持学术产出和财政稳定。", "社会流动性专家指出，面试中的自信与抽象讨论能力并非天赋，而是多年特权积累后的“阶层密码”，大学应识别并破解这种伪装的天赋。", "大卫·鲍伊的文化遗产正面临“博物馆化”危机，保守的遗产管理策略使其在算法驱动的流媒体时代难以触达年轻一代，导致文化偶像与新审美趣味的代际断裂。"], "mentioned_resources": ["《把自己作为方法》 (项飙) - 文中提及逻辑共鸣点（隐含背景）", "《倦怠社会》 (韩炳哲) - 文中提及逻辑共鸣点（隐含背景）", "《破解阶级密码》(Cracking the Class Code) (李·艾略特·梅杰 &amp; 安妮-玛丽·西姆) - 阐释社会优势如何被误认为天赋的新书", "《特权的引擎：英国私立学校问题》(Engines of Privilege) (弗朗西斯·格林 &amp; 戴维·金纳斯顿) - 探讨私立学校对英国社会主导地位的著作", "《Blackstar》 (大卫·鲍伊) - 鲍伊逝世前发布的最后一张专辑", "《战场上的快乐圣诞》 (大岛渚) - 大卫·鲍伊与坂本龙一主演的电影", "《Heroes》 (大卫·鲍伊) - 经典单曲，被提及在《怪奇物语》第五季中使用", "“永远的鲍伊”(Bowie Forever) (BBC) - 纪念鲍伊逝世十周年的专题节目"], "keywords": ["反向歧视 (Reverse Discrimination)", "社会流动性 (Social Mobility)", "阶层再生产 (Class Reproduction)", "文化资本 (Cultural Capital)", "算法隐身 (Algorithmic Invisibility)", "博物馆化 (Museumification)", "制度性自保 (Institutional Self-preservation)"], "style_tone": "逻辑严密的社会观察与批判风格，兼具人文关怀的文化评论。"}</t>
+  </si>
+  <si>
+    <t>{"title": "经期与赌盘：繁荣背后，WNBA女篮运动员面临的隐秘战争", "summary_long": "本文探讨了2025年WNBA（美国女子职业篮球联赛）繁荣背后的一个阴暗现象：博彩者通过预测女运动员的生理期来操纵赌盘。以网红账号“FadeMeBets”为首的赌徒，利用球员的赛场数据（如命中率、正负值）推算其生理周期，并以“黄体期”导致体能下降为由下注球员表现不佳。这种行为被运动医学专家Amy West指为缺乏科学依据的“伪科学”，因为生理期对竞技状态的影响具有高度个体差异，甚至某些阶段可能有积极作用。\n\n文章指出，这种“经期赌球”反映了深层的系统性偏见，将女性运动员的专业素养简化为受激素支配的单一变量，否定了其天赋与训练。这一现象的爆发背景是2018年美国最高法院推翻联邦赌博禁令后，体育博彩市场的急剧膨胀（从500亿飙升至1500亿美元），导致运动员被异化为冷冰冰的“数据提款机”。\n\n作者进一步将此现象与东亚社会的“月经羞耻”文化进行对比。引用文章《卫生巾争议在日本：无袋运动和拟人漫画都无法消除结构性不安》，分析了日本尤妮佳公司（Unicharm）发起的“#NoBagForMe”运动。作者认为，无论是日本社会试图通过包装“隐藏”月经，还是美国赌徒试图通过数据“挖掘”月经，本质上都未将女性身体视为不可侵犯的完整主体，而是将其视为需要遮掩的问题或可以利用的工具。最后，文章以中国女篮球员韩旭在WCBA总决赛期间坦然面对生理期为例，呼吁社会回归对“人”本身的尊重，建立隐私底线，守住运动员的职业尊严。", "key_arguments": ["经期赌球是披着‘科学数据’外衣的性别偏见，旨在通过简化生理现象来否定女性运动员的专业性。", "体育博彩的合法化与过度扩张导致了运动员的‘去人性化’，使其从竞技主体异化为可供算计的数据模型。", "‘经期剥削’（美国赌盘）与‘经期羞耻’（日本包装文化）是硬币的两面，均反映了社会对女性身体自主权的缺乏尊重。", "真正的职业尊重应将生理期视为正常的竞技挑战之一，而非预测胜负的破绽或下注标靶。"], "mentioned_resources": ["FadeMeBets (网红账号) - 发起‘经期预测’赌球策略的代表性账号。", "凯特琳·克拉克 (Caitlin Clark) - WNBA明星球员，被赌徒作为生理期预测分析的典型案例。", "Amy West (运动医学专家) - 批判经期预测缺乏科学依据并指出个体差异性。", "《卫生巾争议在日本：无袋运动和拟人漫画都无法消除结构性不安》 (收银员小秋) - 探讨日本月经文化背景的参考文章。", "尤妮佳/Unicharm (#NoBagForMe运动) - 日本公司发起的消除卫生巾购买羞耻感的社会活动。", "韩旭 (中国女篮运动员) - 在2025年WCBA总决赛期间公开谈论生理期参赛，展现职业态度的正面案例。", "萨布丽娜·约内斯库 (Sabrina Ionescu) - 文中配图提及的WNBA重要球员。"], "keywords": ["体育博彩 (Sports Betting)", "月经剥削 (Menstrual Exploitation)", "数据异化 (Data Alienation)", "黄体期 (Luteal Phase)", "身体自主权 (Bodily Autonomy)", "伪科学 (Pseudoscience)", "月经羞耻 (Period Shame)"], "style_tone": "犀利批判且充满人文关怀，逻辑严密地从社会现象上升至哲学与性别议题的讨论。"}</t>
+  </si>
+  <si>
+    <t>{"title": "唯有孩童能为英雄：斯蒂芬·金式恐怖故事中的爱与勇气", "summary_long": "文章探讨了斯蒂芬·金式恐怖叙事的核心逻辑：在腐朽、盲目且失能的成人世界中，只有尚未被社会化规训的“少年”能直视并对抗怪物。作者指出，金笔下的怪物（如小丑潘尼怀斯、颠倒世界的恶魔）并非外来威胁，而是成人世界暴力、冷漠和制度性压迫的具象化。成年人因选择性失明或共谋而无力反抗，而少年凭借其处于社会边缘的“伦理原初状态”，拥有了直视恐惧的道德优势。\n\n通过分析《小丑回魂》、《怪奇物语》及《欢迎来到德里镇》，文章揭示了少年英雄的力量源泉并非超能力或知识，而是基于“安全依恋”的集体信任与纯粹之爱。这种叙事是对传统“英雄旅程”的逆写：少年们并非为了回归家园，而是在废墟上重建情感共同体。文中强调，牺牲在这些故事中不是宏大的英雄修辞，而是极度私密的情感反应，如《德里镇》中里奇的牺牲。最终，击败恐惧的并非武力，而是人类在绝境中选择去爱的能力。这种“少年叙事”在当代犬儒主义盛行的社会中，起到了唤醒人性中温暖、本能力量的提醒作用。", "key_arguments": ["成人世界的失能与共谋：恐怖的本质是失效的社会秩序（家庭暴力、机构暴政），成年人因被规训而丧失了感知和对抗怪物的能力。", "少年的伦理主体地位：少年作为“赤裸生命”和处于社会边界的个体，拥有未经污染的视野，其“无权性”反而构成了道德反抗的前提。", "爱与集体信任作为终极武器：对抗怪物的核心在于“整合阴影”与建立“创伤共同体”，纯粹的情感联结能溶解怪物赖以生存的恐惧基础。", "对英雄叙事的重构：少年英雄的行动并非源于宏大意识，而是出于对个体深切的爱，这种非英雄主义的牺牲构成了最纯粹的英雄瞬间。"], "mentioned_resources": ["《小丑回魂 / IT》(斯蒂芬·金) - 论述潘尼怀斯与“失败者俱乐部”的对抗模式。", "《On Writing》(斯蒂芬·金) - 引用其关于“孩子看得更清楚”的观点。", "《怪奇物语》(网飞剧集) - 分析十一（Eleven）的超能力与情感联结的关系。", "《欢迎来到德里镇》(HBO剧集) - 详细引用里奇为爱牺牲的案例，论证爱的延续性。", "《神圣人：主权权力与赤裸生命》(乔治·阿甘本) - 用于解释少年作为“赤裸生命”的政治与伦理处境。", "《依恋理论 / A Secure Base》(约翰·鲍尔比) - 解释十一的力量来源于安全的情感依恋。", "《怪物文化七论》(杰弗里·科恩) - 论证少年因处于“边界之上”而拥有观看自由。", "《民间故事形态学》(弗拉基米尔·普罗普) - 用于对比传统英雄旅程与少年英雄叙事的差异。", "《原型与集体无意识》(荣格) - 解释直面恐惧即为“整合阴影”的过程。", "《未申明的经验：创伤、叙事与历史》(凯西·卡鲁斯) - 论述“创伤共同体”如何通过叙述获得力量。", "《情色：死亡与感性》(乔治·巴塔耶) - 探讨跨越禁忌的“神圣性”。"], "keywords": ["伦理原初状态", "赤裸生命 (Bare Life)", "失败者俱乐部", "创伤共同体", "阴影整合", "边界意识", "犬儒主义", "非英雄主义牺牲"], "style_tone": "深度思辨且充满人文关怀的文化评论风格，融合了社会学、心理学与叙事学分析。"}</t>
+  </si>
+  <si>
+    <t>{"title": "自我田野｜张向荣：漫长的离职", "summary_long": "本文是历史作家张向荣（文学博士）对自己十五年银行职业生涯的回顾与告别。2010年，张向荣博士毕业后进入某国有商业银行总行，开启了长达十五年“想离职”的职业生涯。文章通过个人视角的“自我田野”，深刻剖析了现代职场对个体精神的异化。作者首先指出作息冲突是职业痛苦的表征，长期的校园生活使其难以适应银行严苛的早起纪律，这种生理上的不适预示了其与职场逻辑的本质排斥。随后，作者通过从基层柜员到总行办公室的经历，总结了工作令人难以忍受的三大核心缺失：价值感（重复性劳动替代了思考）、新鲜感（技能固化且缺乏市场价值）以及掌控感（自主性的丧失）。\n\n文章进一步探讨了“优绩主义”陷阱：高学历者因惯性无法接受平庸，在“无意义”与“不能躺平”之间痛苦拉扯。作者通过在豆瓣招聘实习生的经历，揭示了职场供需的残酷真相——即便工作内容枯燥，名校生依然为了一纸证明而趋之若鹜。对于作者而言，写作逐渐从副业演变为真正的志业，提供了职场无法给予的价值感、新鲜感与掌控感。他将这十五年的银行生涯视为一场长期的“田野调查”，认为办公室工作的琐碎、虚无与重复，反而让他更深刻地理解了生活的本质。最终，作者在40岁之际选择主动切换赛道，以“一万天理论”规划余生的写作生涯，通过舍弃消费主义欲望，实现了从体制内精英向独立撰稿人的身份转型，完成了一场漫长的自我救赎。", "key_arguments": ["工作的痛苦不仅源于强度，更源于价值感、新鲜感和掌控感（自主性）的全面缺失。", "优绩主义者（High-achievers）在职场中面临双重困境：既无法忍受工作的平庸无意义，又受限于惯性无法轻易放弃稳定或降低标准。", "职场经历可以被重构为一种“自我田野调查”，琐碎且无意义的行政事务（博记工文，善干鄙事）能转化为对人性与生活本质的深刻洞察。", "人生的救赎在于找回自主性，通过精简消费欲望和明确志业（如写作），可以实现对传统职业路径的突围。"], "mentioned_resources": ["《压力密码：压力是如何产生的，又如何影响我们的身心健康？》 (作者未详) - 文中引用其临床结论：压力源于缺乏自主性而非工作量本身。", "《货币银行学》 (通用教材) - 用于说明银行内部复杂的条线分工。", "《鹤林玉露》 (罗大经) - 引用其中对秦桧的评价“博记工文，善干鄙事”来概括办公室工作精华。", "《你想活出怎样的人生》 (宫崎骏/吉野源三郎) - 作为文章结尾对人生选择的终极追问。", "“张舜徽作息法” (张舜徽) - 提到前辈学者凌晨四点起床读书的勤奋作息。", "《把自己作为方法》 (项飙) - 虽然文中未直接点名，但“自我田野”的核心概念与此理论母题高度共鸣。"], "keywords": ["优绩主义 (Meritocracy)", "自主性 (Autonomy)", "自我田野 (Self-Fieldwork)", "价值感缺失", "掌控感", "班味", "一万天理论", "消费主义抵抗"], "style_tone": "充满人文关怀的省思风格，兼具社会学观察的理性与文学博士的感性叙事。"}</t>
+  </si>
+  <si>
+    <t>{"title": "“萝卜纸巾猫”爆火：“察言观色”的我们，渴望“真棒”的肯定", "summary_long": "2026年初，宠物博主@超级无敌大开门的三花猫“大开门”因“萝卜纸巾”训练视频爆火全网。视频中，猫咪并非真正理解“萝卜”或“纸巾”的概念，而是通过“察言观色”捕捉主人的面部表情和肢体语言，以试探性的“蒙题”行为换取那句标志性的“真棒”肯定。这种“三分笨拙、三分聪慧、四分小心翼翼”的状态，不仅创造了“史诗级稍息”等名场面，更深刻镜像了现代人的生存现状。\n\n文章从三个维度剖析了该现象：首先是“萌”的独特性。大开门打破了猫科动物不配合实验的刻板印象（引用李露的研究），展现出极高的配合度与“猫格”张力。其次是“察言观色”的社会心理共鸣。这种行为模式复刻了“高语境文化”下的生存策略，从《颜氏家训》式的原生家庭教育到曾国藩式的职场哲学，人们在猫咪身上看到了那个为适应环境而不断解读他人意图、承受情绪内耗的自己。最后是“真棒”提供的情绪价值。开门妈高频率、低门槛的肯定，构建了一个“去绩效化”的情感乌托邦。这种对简单、直接反馈的渴望，印证了心理学中的“赫洛克效应”，也反映了社会价值观正从“物质主义”向“后物质主义”转型。年轻人不再仅仅追求物质成功，转而通过Jellycat或萌宠视频寻求精神慰藉与自我表达。大开门的爆火，本质上是现代人在绩效焦虑中通过共情萌宠完成的一次精神“深呼吸”。", "key_arguments": ["“萝卜纸巾猫”的走红不仅是萌宠效应，更是因为它精准镜像了现代人在复杂社会关系中“察言观色”的生存逻辑。", "“察言观色”是中国高语境文化下的本能策略，反映了从家庭到职场普遍存在的、以他人评价为导向的情绪劳动与生存压力。", "视频中“真棒”的肯定提供了一种“去绩效化”的反馈机制，是对现实世界严苛、延迟且有条件的评价体系的一种情感补偿。", "该现象标志着社会心理向“后物质主义”转型，个体愈发重视情绪价值、情感认同与非功利性的心理慰藉。"], "mentioned_resources": ["《国家自然博物馆》公众号文章 (李露) - 论述猫的实验配合度低及察言观色能力。", "“高语境/低语境”理论 (爱德华·霍尔) - 解释信息传递对情境和默契的依赖。", "《论语》 - 提及“察言而观色，虑以下人”的处世达标标准。", "《颜氏家训》 - 论述传统家庭教育中“先意承颜”的观察力培养。", "曾国藩语录 - 论述职场中“察言观色，趋吉避凶”的周旋态势。", "“赫洛克效应” (赫洛克) - 心理学实验证明积极反馈对行为动机的显著提升作用。", "《静悄悄的革命》 (罗纳德·英格尔哈特) - 论述价值观从“物质主义”向“后物质主义”的转型。", "Jellycat / Labubu / “爱你老己” (流行文化符号) - 作为当代年轻人追求情绪价值的案例佐证。"], "keywords": ["萝卜纸巾猫", "察言观色", "情绪价值", "去绩效化", "高语境文化", "后物质主义", "赫洛克效应", "生存策略", "精神内耗"], "style_tone": "兼具社会学洞察与人文关怀的分析风格，语调温和且具有深度共情力。"}</t>
+  </si>
+  <si>
+    <t>{"title": "谁的时间：寻找失传媒体的文化实践", "summary_long": "文章以卡夫卡遗稿被布洛德违愿保留的轶事切入，引出“失传媒体（Lost Media）”这一核心概念。失传媒体指曾进入公共传播领域但因技术、制度或社会原因变得不可获取的媒介文本。文章从四个维度深度剖析了这一现象：\n\n首先，界定了失传媒体的特征。它们曾被大众知晓，但在当下无法再现，仅以零散线索存在。现代大众媒体的爆发式增长与载体（胶片、磁带）的易逝性，导致失传媒体数量激增。BBC销毁《神秘博士》早期母带即为制度性遗失的典型。\n\n其次，探讨了媒介的时间性。媒介运作包含“传播时间”（社会维度，决定流行）与“留存时间”（物理维度，决定存续）。当传播广泛但留存短暂（如80年代电视节目）或技术更迭（如Flash停用）时，失传媒体便产生了。媒介迁移至新载体并非自动发生，而是一种权力的体现，决定了哪些内容值得被历史记住。\n\n再次，引入哲学视角。借用福柯的“知识考古学”，指出档案是权力的筛选，失传媒体则是“档案的缺席者”。通过寻找失传媒体，尤其是寻找身份不明音乐的“消逝波（Lost Wave）”实践，人们在进行一种“时间平权”，对抗主流叙事的筛选。德里达的“幽灵学”进一步解释了失传媒体作为“未被妥善安置的时间残余”，如何打破线性时间，在当下持续回响。\n\n最后，分析了其作为青年文化的深层动因。在马克·费舍尔所谓的“被取消的未来”语境下，当代青年面临结构性不确定性，失传媒体文化不仅是怀旧，更是对“悬浮状态”的自我识别，试图在时间的裂缝中寻找未被权力构建的多种可能性。寻找失传媒体，本质上是在重构时间秩序，召唤历史幽灵以对抗遗忘。", "key_arguments": ["失传媒体是媒介传播时间（社会流行）与留存时间（物理存续）错位的产物。", "媒介迁移（从旧格式到新格式）是一种权力筛选机制，决定了哪些话语能进入“档案”而哪些被沦为“失传”。", "寻找失传媒体（及消逝波）是一种时间平权实践，旨在对抗主流权力对历史记忆的垄断。", "失传媒体文化反映了当代青年在“未来被取消”的困境下，通过重返过去残影来寻找想象力张力和自我定位。"], "mentioned_resources": ["《变形记》《城堡》《审判》 (弗兰兹·卡夫卡) - 布洛德违背遗愿保留下的文学遗产。", "《神秘博士》(Doctor Who) (BBC) - 因磁带重复利用而被覆盖销毁的早期剧集案例。", "《旗旗号巡洋舰》 (郑渊洁) - 中文失传媒体社区寻找的80年代国产木偶剧。", "Flash Player (Adobe) - 因技术标准更新而导致大量内容失效的媒介载体案例。", "《知识考古学》 (米歇尔·福柯) - 论述档案作为“可被言说之物”的系统及权力筛选机制。", "《马克思的幽灵》 (雅克·德里达) - 提出“幽灵学（hauntology）”概念，解释未被安置的时间残余。", "《大人王国的反击》 (蜡笔小新剧场版) - 探讨怀旧情绪与夺回未来的青年文化隐喻。", "《被取消的未来》(Ghosts of My Life) (马克·费舍尔) - 论述资本主义现实主义下文化想象力的停滞。", "《资本主义现实主义》 (马克·费舍尔) - 探讨当代社会的情绪症候与未来感的丧失。"], "keywords": ["失传媒体 (Lost Media)", "消逝波 (Lost Wave)", "媒介时间性", "知识考古学", "幽灵学 (Hauntology)", "被取消的未来", "时间平权"], "style_tone": "逻辑严密的学术分析风格，兼具深厚的人文关怀与哲学思辨色彩。"}</t>
+  </si>
+  <si>
+    <t>{"title": "洪都拉斯大选规范性危机背后，特朗普的“新干涉主义”外交", "summary_long": "本文探讨了2025年末洪都拉斯总统大选引发的政治动荡及其背后的美国干预逻辑。选举中，特朗普公开支持的保守派候选人阿斯富拉以微弱优势险胜，引发反对派关于“选举政变”和“算法舞弊”的指控。文章指出，这并非孤立事件，而是特朗普“新干涉主义”外交的典型实践。特朗普通过社交媒体施压、威胁削减援助、甚至赦免因贩毒入狱的洪前总统埃尔南德斯等手段，直接扭转了选情。这种模式在阿根廷同样上演，特朗普通过“政治背书+经济绑定（如200亿美元货币互换）”助力米莱赢得中期选举。文章进一步分析，特朗普正在全球范围内（包括匈牙利、波兰、捷克等欧洲国家）构建一个以“反觉醒、民族主义”为核心的跨国右翼联盟。这种外交逻辑打破了“美国优先即孤立主义”的误读，显示出其核心已从“输出民主”转向“输出MAGA议程”。然而，这种以意识形态划界的干预也面临盟友主权诉求冲突、损害当地民主合法性以及激化反美情绪等深层风险。", "key_arguments": ["特朗普的外交政策并非传统意义上的孤立主义，而是一种以左右意识形态划界的“新干涉主义”，旨在全球扶持亲美保守势力。", "美国对拉美及欧洲右翼政党的支持已形成“政治背书+经济绑定+意识形态输出”的系统性组合策略，直接改变多国选举进程。", "这种干预模式拒绝规则型多边主义，转向赤裸的国家间利益交易，虽然短期巩固了盟友，但长期会侵蚀主权国家民主制度并引发地缘政治撕裂。"], "mentioned_resources": ["纳斯里·阿斯富拉 (Nasry Asfura) - 洪都拉斯国民党候选人，特朗普支持的胜选者", "萨尔瓦多·纳斯拉拉 (Salvador Nasralla) - 洪都拉斯中间派候选人，指控选举舞弊", "哈维尔·米莱 (Javier Milei) - 阿根廷总统，自称“无政府资本主义者”，特朗普的坚定盟友", "胡安·奥兰多·埃尔南德斯 (Juan Orlando Hernández) - 洪都拉斯前总统，因贩毒在美服刑，获特朗普赦免承诺", "欧尔班·维克多 (Orbán Viktor) - 匈牙利总理，跨国右翼联盟的核心人物", "米尔斯海默 (John Mearsheimer) - 文中提及其“美国霸权衰退”观点作为背景对比", "欧洲对外关系委员会 (ECFR) 民调 - 关于欧洲民众对美国政治体系支持度的相关性调查", "CPAC Hungary (年度保守派政治行动会议) - 跨国右翼政治家联络平台"], "keywords": ["新干涉主义", "MAGA运动", "意识形态极化", "规范性危机", "货币互换", "门罗主义", "反觉醒", "地缘政治重塑"], "style_tone": "逻辑严密的政治经济分析风格，带有批判性视角，关注地缘政治的宏大叙事与主权民主的微观冲突。"}</t>
+  </si>
+  <si>
+    <t>{"title": "澎湃思想周报｜AI会取代医生吗？；2026世界新秩序", "summary_long": "本文由两个核心议题组成：AI对医疗行业的重构以及2026年全球政治新秩序的展望。第一部分探讨了AI替代医生的可能性。瑞典学者夏洛特·布利斯质疑“医生不可替代”的神话，指出全球医疗系统正面临严重的职业倦怠与人员短缺。文章强调，人类医生的局限性（如过度自信、偏见和疲劳）是导致医疗差错的主因，而医生群体往往通过行会主义（Guildism）和“潘格洛斯式”的防御心态来维护其职业垄断地位，抵制如执业护士授权或AI介入等创新。文章援引萨斯金德兄弟的理论，认为医学应从维护职业地位转向追求安全、公平的医疗结果。第二部分基于英国播客《The Rest Is Politics》的视角，预判了2026年“后美国时代”的动荡。在特朗普回归及单边主义行动（如抓捕马杜罗）的背景下，西方失去了自1945年以来建立的道德高地。世界分裂为西方、东方和全球南方“三领域”。由于美国价值观武器的失效，欧洲（英法德）被迫面临从美国金融、国防和科技体系中“断奶”的痛苦抉择，以寻求在碎片化、悲观的国际秩序中实现独立自主。", "key_arguments": ["医疗差错是全球领先死因，根源在于人类心理局限（如过度自信）而非仅是职业倦怠，AI能弥补人类作为‘凡人’的认知盲点。", "医生群体通过‘职业界的宏大契约’获得垄断地位，但其行会利益有时会凌驾于公众利益之上，表现为对医疗记录透明化和角色扩展的抵制。", "医学的本质应是‘结果导向’而非‘职业导向’，患者更在乎诊断的准确性与可及性，而非执行者是否为人类。 ", "特朗普的行为摧毁了西方的道德高地，使中俄在与西方争夺‘全球南方’民心时获得了叙事优势。", "2026年的欧洲必须实现战略自主，切断对美元体系、北约国防和美国AI云服务的绝对依赖，以应对‘后美国时代’的威胁。"], "mentioned_resources": ["《职业的未来：技术将如何改变人类专家的工作》 (理查德·萨斯金德 &amp; 丹尼尔·萨斯金德) - 论述社会给予专业人士地位与报酬的‘宏大契约’。", "《老实人》 (伏尔泰) - 借‘潘格洛斯博士’讽刺医学界回避错误、坚持现状是最好的乐观主义立场。", "播客《The Rest Is Politics》 (Rory Stewart &amp; Alastair Campbell) - 探讨2026年全球地缘政治博弈及欧洲独立性。", "《外交事务》文章 (亚历山大·斯图布) - 提出世界分裂为西方、东方、全球南方的‘三领域’论述。"], "keywords": ["职业倦怠 (Burnout)", "行会利益 (Guild Interests)", "潘格洛斯式立场 (Panglossian Position)", "全球南方 (Global South)", "不结盟基础设施", "战略自主 (Strategic Autonomy)", "后美国时代"], "style_tone": "理性批判且具有前瞻性的深度分析风格，融合了社会学、心理学与地缘政治视角。"}</t>
+  </si>
+  <si>
+    <t>{"title": "微短剧“造梦”：算法时代的无痛情感教育危机", "summary_long": "本文深入探讨了微短剧作为一种新兴文化形态，如何通过算法逻辑重构人类的情感体验。文章开篇以微短剧常见的“贵公子偶遇村花”套路切入，将其与《红楼梦》中类似的桥段对比，指出微短剧追求的是“即时爽感”的圆满，而经典文学则揭示现实的“无常与遗憾”。\n\n核心逻辑在于微短剧对“钩子（Hook）”的运用。不同于传统影视剧的“叙事悬念”，微短剧的钩子是基于算法的“欲望投射”和“标准答案”，它向观众承诺一种“确定的安全感”和“Happy Ending”，从而将观众从现实的复杂性中抽离。数据层面，红果短剧等平台的崛起证明了“女频”题材（如霸总、甜宠）已成为市场主流，这种现象反映了现代女性在职场与家庭双重压力下，将微短剧作为一种“零成本的情感按摩”和“精神止痛药”。\n\n文章进一步提出“无痛之爱”的概念：微短剧剔除了真实亲密关系中的摩擦、风险与不确定性，提供了一种“情感外包”服务。与之相对，经典文学（如《罪与罚》、《包法利夫人》）具有“碎梦”功能，通过展示痛苦和失败来增强读者的心理韧性。作者援引韩炳哲的“镇痛社会”理论，警示这种“赛博造福”可能会系统性地削弱人类处理现实冲突的能力，使人丧失深度注意力和忍受痛苦的能力。最后，文章承认微短剧在产业层面的生命力，但提醒观众在享受虚拟慰藉时，仍需保持对现实真伪的清醒认知。", "key_arguments": ["微短剧的叙事动力并非‘悬念’而是‘钩子’，本质是算法驱动下对用户爽感安全期待的即时满足。", "微短剧通过‘无痛之爱’实现了情感外包，为身心俱疲的现代人提供了一种低风险、高纯度的情绪代偿，但也削弱了主体处理真实复杂关系的能力。", "经典文学的价值在于其‘碎梦’功能和‘否定性体验’，通过展示人生的不完满（痛感）来打破自恋幻象，还原人性的深度。", "当代社会正演变为韩炳哲所描述的‘镇痛社会’，微短剧作为一种‘赛博止痛药’，正在重塑人类的神经回路与情感阈值。"], "mentioned_resources": ["《深情诱引》、《大雾散尽》、《别有用心的妻子》 - 文中引用的典型微短剧案例，常以隆重葬礼开场。", "《红楼梦》(曹雪芹) - 作者对比了‘王熙凤弄权铁槛寺 秦鲸卿得趣馒头庵’与微短剧套路的本质区别。", "《盛夏芬德拉》 - 2025年现象级微短剧，被引用说明其开场即交代结局的‘反悬念’逻辑。", "《安娜·卡列尼娜》(托尔斯泰) - 用于对比经典文学中爱情的悲剧性与现实冷酷。", "《尼罗河惨案》(阿加莎·克里斯蒂) - 说明传统叙事中悬念的重要性。", "《聂小倩》(蒲松龄) - 说明经典叙事不预设救赎结局。", "《罪与罚》(陀思妥耶夫斯基) - 引用杜涅奇卡的故事，说明现实中‘霸总’救赎的虚幻性。", "《珍妮姑娘》、《嘉丽妹妹》(德莱塞) - 说明现实主义作品中财富与浪漫的不可兼得。", "《漂亮朋友》(莫泊桑) - 揭示‘年下男’或‘捞男’的残酷真相。", "《驯野》、《解开他的蝴蝶结》、《江南时节》 - 具有性张力的年下奶狗题材微短剧。", "《西部世界》、《未来战警》 - 作为‘代理人’和‘虚拟极乐’的科幻隐喻。", "《包法利夫人》(福楼拜)、《玩偶之家》(易卜生) - 说明经典文学中女性遭遇的非玛丽苏现实。", "《幸得相遇离婚时》 - 典型的玛丽苏式离婚逆袭短剧。", "韩炳哲《镇痛社会》(或译《妥协社会》) - 引用其关于当代社会屏蔽痛苦、丧失真实性基石的理论。"], "keywords": ["算法逻辑", "钩子 (Hook)", "无痛之爱", "情感外包", "镇痛社会", "碎梦功能", "赛博造福", "情绪代偿", "确定的爽感"], "style_tone": "具有社会学洞察力的文化批判风格；辞藻犀利且富有对比性，在人文关怀中带有理性的警示。"}</t>
+  </si>
+  <si>
+    <t>{"title": "风城芝加哥故事：性别、阶级与残障的交叉——从《傲骨贤妻》《无耻之徒》到《都是她的错》", "summary_long": "本文通过横向对比三部以芝加哥为背景的剧集《都是她的错》、《傲骨贤妻》与《无耻之徒》，深入探讨了美国影视作品中性别气质、阶级差异与残障身份的表达变迁。文章首先指出2025年新剧《都是她的错》在中外评价上的巨大差异（豆瓣9.2 vs IMDb 7.6），并以此为切入点展开分析。\n\n在婚姻与男性气质维度，文章对比了《傲骨贤妻》与《都是她的错》中同名角色Peter。前者将婚姻塑造为一种基于利益交换的共同体，Peter虽有道德瑕疵但仍是“有用的保护者”；而后者则彻底解构了“支配性男性气质”，将男性的保护欲揭示为控制欲的表演，将婚姻视为剥削性的零和博弈，反映了社会对婚姻制度的幻灭。然而，在叙事质量上，作者批评《都是她的错》陷入了“懒惰写作”，过度依赖“女孩帮助女孩”的工业套路，忽视了现实中的法律风险（如自证其罪）与复杂的利益博弈。相比之下，《傲骨贤妻》展现了马基雅维利式的务实与道德模糊性，角色行动受利益驱动而非简单的身份标签。\n\n在阶级与残障的交叉性维度，文章认为《都是她的错》对边缘身份的刻画过于扁平，弱势群体往往被塑造成道德高尚的受害者。而《无耻之徒》则深刻揭示了匮乏如何塑造自毁倾向，展现了阶级对思维方式的烙印。同时，文章引用《豪斯医生》与具身性理论，批判了《都是她的错》中残障角色心灵独立于肉体的传统表述，强调身体痛苦对人格的重塑作用。最后，文章总结称，《都是她的错》在简中语境的高分源于其对母职困境的精准冒犯引发的情感共鸣，而非其艺术造诣的完美。", "key_arguments": ["男性气质的演变：从《傲骨贤妻》中具有交易性质的‘保护者’，转向《都是她的错》中表演性、剥削性的‘温和暴君’，反映了对父权婚姻制度的深度幻灭。", "叙事伦理的差异：批评《都是她的错》利用身份政治（女孩帮助女孩）进行‘工业速食’创作，缺乏《傲骨贤妻》中那种基于利益、野心与外部掣肘的现实主义复杂性。", "身份交叉性的深度：指出《都是她的错》在阶级与残障维度上的刻画流于表面，未能如《无耻之徒》或《豪斯医生》般揭示匮乏与身体痛苦如何从本质上解构并重塑个人身份。", "社会语境与评价偏差：豆瓣高分是对‘母职惩罚’等结构性困境的集体宣泄与情感投票，而西方评价则更侧重于文学性与叙事逻辑的严密性。"], "mentioned_resources": ["《都是她的错 (All Her Fault)》 (美剧, 2025) - 核心分析对象，探讨母职惩罚与性别权力结构。", "《傲骨贤妻 (The Good Wife)》 (美剧) - 对比对象，展现精英阶层的利益交换与道德模糊性。", "《无耻之徒 (Shameless)》 (美剧) - 对比对象，展现芝加哥南区底层阶级的自毁倾向与生存逻辑。", "《殊途同归 (Accused)》 (英剧, 2010版) - 引用其关于‘道歉’在法律中可能导致自证其罪的案例。", "《豪斯医生 (House M.D.)》 (美剧) - 引用其对慢性疼痛与具身性（身体对心灵的调控）的深刻刻画。", "《疼痛的文化 (The Culture of Pain)》 (David Morris) - 论证疾病与疼痛如何解构个人身份。", "支配性男性气质 (Connell and Messerschmidt) - 理论模型，分析男性保护者角色背后的支配逻辑。", "《把自己作为方法》 (项飙) - 文中提及（作为对比或背景概念）。", "《倦怠社会》 (韩炳哲) - 文中提及（作为对比或背景概念）。"], "keywords": ["母职惩罚", "支配性男性气质 (Hegemonic Masculinity)", "交叉性 (Intersectionality)", "具身性 (Embodiment)", "自证其罪 (Self-incrimination)", "零和博弈", "身份政治", "道德模糊度"], "style_tone": "逻辑严密、批判性强、兼具社会学洞察与影视评论深度的专业分析风格。"}</t>
+  </si>
+  <si>
+    <t>{"title": "《日掛中天》：承担历史的渴望与作为“动词变位”的女性角色", "summary_long": "本文深度解析了蔡尚君导演的电影《日掛中天》，认为该片在华语电影叙事中实现了某种“句式松动”：女性角色美云从以往的客体变为了叙事的主语。文章通过将该片与刁亦男的《白日焰火》进行“对倒”式对比，指出两部影片在“罪与罚”及“沉重的爱”这一母题上的互文性。作者回顾了“后六代”电影谱系（如《风中有朵雨做的云》、《南方车站的聚会》），发现女性形象在这些在地化的黑色电影中常呈现为“魅影”或“非理性”的状态，这种状态被作者称为“灵魂之舞”，旨在通过摧毁女性的日常生活表象来反思现代化的否定性。文中进一步提出，当代电影中的女性往往并非真实的人，而是历史叙事句式中“动词变位”的角色符号，她们承载着时间的重负，却缺乏主体位置。美云的悲剧在于她试图通过“向前看”来逃避历史债务，却最终在无法掌握的时间中崩溃。影片通过南方地域色彩（如粤剧《紫钗记》的引用）拉开了审美距离，将观众从单纯的共情引向对历史责任的深刻反思。最终，美云的成长被解读为一种“看见”真实与面对历史的勇气，尽管代价惨烈。", "key_arguments": ["女性形象的“主语化”与“符号化”并存：虽然美云成为了叙事主语，但在宏大历史叙事中，女性仍常作为“动词变位”的符号，缺乏真正的个体主体性。", "“灵魂之舞”与否定性现代性：当代华语黑色电影通过塑造具有鬼魅感、非理性的女性形象，来折射现代理性对个体情感与日常生活的扭曲与压制。", "时间与历史的重负：影片探讨了人物与时间的关系，主角的悲剧源于无法正确处理“过去”的债务，导致在追求“未来”的进程中彻底失去时间。", "南方语境的审美距离：利用广东地域文化与戏曲元素（如粤剧）构建距离感，促使观众从情感共鸣转向对现代化进程与历史责任的理性审视。"], "mentioned_resources": ["《日掛中天》(蔡尚君) - 本文核心分析对象，辛芷蕾主演。", "《白日焰火》(刁亦男) - 作为《日掛中天》的对照文本，探讨黑色电影的在地化。", "《风中有朵雨做的云》(娄烨) - 提及其中女性形象（小诺、林慧）的“魅影”特征与受害者同盟。", "《南方车站的聚会》(刁亦男) - 论述其中女性通过金钱补偿走向新生的叙事策略。", "《红高粱》(张远谋/戴锦华解读) - 分析女主角九儿作为“现代化”寓言与“英雄图腾”的矛盾。", "《江湖儿女》(贾樟柯) - 对比分析其中人物对“时间”与“情义”的处理。", "《紫钗记》与《帝女花》(粤剧) - 作为影片的文化采样，隐喻“破镜重圆”与“情”的永恒价值。", "《平原上的摩西》(电视剧) - 论述女性死于“时间的重负”及观众的旁观者视角。", "陈剑梅 (学者) - 其著作提出香港黑色电影女性形象与好莱坞的区别。", "德勒兹 (哲学家) - 引用其关于第三世界电影“人民形象缺席”的理论。"], "keywords": ["动词变位", "灵魂之舞", "否定性现代性", "黑色电影在地化", "后六代导演", "历史重负", "南方电影", "时间性"], "style_tone": "逻辑严密的学术影评风格，融合了电影社会学、女性主义批评与文化研究视角，语调深沉且具有批判性洞察。"}</t>
+  </si>
+  <si>
+    <t>{"title": "“哈基米”音乐流行：年轻人愈发依赖微小、即时、可控的乐趣", "summary_long": "文章探讨了网络迷因“哈基米”音乐从动漫符号演变为全球化“空能指”的过程及其背后的社会心理。起初，“哈基米”通过“空耳”文化与猫咪视频绑定，其发音符合康德所谓的“无目的的合目的性”，在理性介入前便产生了身体性的愉悦。随后，具有攻击性的“圆头耄耋”表情包出现，解构了人类中心主义的“萌化”滤镜，体现了黑格尔的“主奴辩证法”，成为年轻人宣泄现实压力的情绪面具。在审美层面，文章引用罗兰·巴特关于“愉悦”与“醉”的区分，指出“哈基米”通过打破旋律预期，实现了日神精神与酒神精神的融合，受众在“差异的重复”（德勒兹语）中获得游牧式的感官解放。尽管阿多诺式的批判认为这是文化工业的标准化产物，掩盖了创造力的匮乏，但从斯图亚特·霍尔的“编码/解码”理论看，年轻人正通过“对抗式解码”赋予其新意。最终，这种流行构成了雷蒙·威廉斯所说的“情感结构”，是年轻人在哈特穆特·罗萨描述的“加速社会”中，通过追求微小、即时、可控的“无意义”循环，对绩效主义律令和宏大叙事进行的象征性抵抗与心理减速。", "key_arguments": ["“哈基米”已从具体的动漫符号演变为一个“空”的能指，其流行源于语音物质性带来的前理性身体愉悦。", "“圆头耄耋”现象反映了人与动物权力关系的颠倒，折射出当代青年碎片化的数字身份与对现实压力的情绪化宣泄。", "“哈基米”音乐通过熟悉旋律与荒谬歌词的“视域融合”，创造出一种去中心化的、游牧式的审美体验，使个体在酒神式的狂欢中暂时消解自我。", "这种“无意义”的流行是当代青年的“情感结构”，是面对加速社会和结构性压力时，一种躲避宏大叙事、追求微小可控乐趣的缓冲策略。"], "mentioned_resources": ["康德 (Immanuel Kant) - 提出“无目的的合目的性”，用于解释哈基米发音带来的直接愉悦。", "黑格尔 (G.W.F. Hegel) - “主奴辩证法”，用于分析人与猫（耄耋）之间纠葛的情感与权力关系。", "罗兰·巴特 (Roland Barthes) - 区分“愉悦” (Plaisir) 与“醉” (Jouissance)，解释哈基米音乐带来的感官冲击。", "尼采 (Friedrich Nietzsche) - “日神精神”与“酒神精神”、“永恒轮回”，分析音乐中的个体消解与差异重复。", "伽达默尔 (Hans-Georg Gadamer) - “视域融合”与“前理解”，分析受众如何重构旋律与歌词的意义。", "德勒兹 (Gilles Deleuze) - “差异的重复”与“游牧式体验”，阐述去中心化网络中的生产性力量。", "阿多诺 (Theodor W. Adorno) - “文化工业”理论，批判流行音乐的标准化与对批判意识的消解。", "斯图亚特·霍尔 (Stuart Hall) - “编码/解码”理论，分析受众对“哈基米”意义的多种解读立场。", "雷蒙·威廉斯 (Raymond Williams) - “情感结构”，描述群体共享的、溶解在社会经验中的感受。", "哈特穆特·罗萨 (Hartmut Rosa) - “加速社会”理论，探讨哈基米音乐作为社会节奏加速的体现及其心理减速的悖论。"], "keywords": ["哈基米", "圆头耄耋", "空能指", "酒神精神", "视域融合", "文化工业", "编码/解码", "情感结构", "加速社会", "绩效主义", "迷因 (Meme)"], "style_tone": "逻辑严密的学术分析风格，融合了社会学、哲学与传播学视角，带有对当代青年生存处境的深刻人文关怀。"}</t>
+  </si>
+  <si>
+    <t>{"title": "最后的匠人：国际社会携手守护古老手艺 (Safeguarding Pasto Varnish)", "summary_long": "本文探讨了全球化背景下传统手工艺面临的生存危机及其保护路径。文章首先提出了一个深刻的洞察：复杂技艺的消亡本质上并非因为人类的“遗忘”，而是由于支撑这些技艺存在的社区结构和外部条件的瓦解。当技艺赖以生存的社会土壤不复存在，文化传承便会中断。为了应对这一挑战，联合国教科文组织（UNESCO）通过设立《急需保护的非物质文化遗产名录》，为濒危传统提供了包括提高国际知名度、专项资金支持以及社区主导的技能传授在内的多维度援助。文章重点介绍了哥伦比亚“帕斯托漆艺”（Pasto Varnish）的复兴案例，强调了这种“活态遗产”的延续关键在于建立持续的、人对人的“师徒传承”机制。通过大师与学徒之间深度、长期的互动，古老手艺得以在现代语境下重新获得生命力，证明了社区凝聚力是文化保护的核心驱动力。", "key_arguments": ["技艺消亡的本质论：复杂技能的消失是社区生态系统崩溃的结果，而非单纯的记忆丧失。", "系统性干预机制：UNESCO通过《急需保护名录》整合可见度、资金和社区参与，构建了濒危遗产的救助框架。", "活态传承的核心路径：面对面的师徒制（Person-to-person teaching）是保持非物质文化遗产活力的不可替代方式。"], "mentioned_resources": ["《急需保护的非物质文化遗产名录》(List of Intangible Cultural Heritage in Need of Urgent Safeguarding) (UNESCO) - 旨在通过国际合作挽救濒危传统的官方机制。", "帕斯托漆艺 (Pasto Varnish / Barniz de Pasto) - 哥伦比亚特有的传统手工艺，文中作为活态遗产复兴的成功典范被提及。"], "keywords": ["非物质文化遗产 (Intangible Cultural Heritage)", "社区瓦解 (Community Dissolution)", "师徒传承 (Master-Apprentice Transmission)", "活态遗产 (Living Heritage)", "帕斯托漆艺 (Pasto Varnish)", "社会生态系统 (Social Conditions)"], "style_tone": "严谨且具有人文关怀的分析风格，强调社会结构对文化传承的决定性作用。"}</t>
+  </si>
+  <si>
+    <t>{"title": "日本哲学如何帮助我改善生活 (Kaizen: How Japanese philosophy helped me improve my life)", "summary_long": "本文探讨了源自日本的哲学概念“改善”（Kaizen）及其在现代生活和工作中的应用价值。Kaizen 的核心在于摒弃追求剧烈、爆发式的变革，转而强调通过微小且持续的改变来达成目标。文章指出，将行动的起点设定得尽可能小，是确保长期成功的关键策略，因为这种方式不仅降低了执行难度，还使得每一步进展都变得清晰可追踪。随着时间的推移，这些看似微不足道的“小胜”（small wins）会产生强大的复利效应，最终在业务管理、团队协作以及个人日常生活层面，实现一种静默而深刻的可持续转型。这种哲学本质上是将宏大目标拆解为可消化的微观行动，利用时间的杠杆完成质变。", "key_arguments": ["进步的本质在于微小且持续的积累，而非一次性的剧烈重组（Kaizen 核心定义）。", "极低门槛的起步方式能显著提升长期坚持的可能性，并增强对进度的掌控感。", "微小胜利具备复利属性，能够驱动个人与组织实现可持续的深层变革。"], "mentioned_resources": ["Kaizen (改善) - 日本哲学/管理理论：文中核心讨论的思维模型，强调通过持续的微调实现卓越。"], "keywords": ["Kaizen (改善)", "持续改进 (Continuous Improvement)", "复利效应 (Compounding Effect)", "微小胜利 (Small Wins)", "可持续转型 (Sustainable Transformation)"], "style_tone": "实用主义、富有启发性且逻辑清晰的指导风格"}</t>
+  </si>
+  <si>
+    <t>{"title": "打造明星员工的体系 (Building a System for Star Performers)", "summary_long": "本文探讨了跨领域（从体育到科学）卓越成就者的成长规律，挑战了“赢在起跑线上”的传统认知。文章指出，顶尖表现者往往并非早期显露头角的“神童”，而是“大器晚成者”（Slow Developers）。\n\n文章核心逻辑分为三个阶段：首先，批判了现有的选拔体系。当前的社会与组织系统过度倾向于“早期识别”和“过度专业化”，这种模式虽然在短期内能看到成效，但从长远来看，它抑制了人才的探索欲、适应能力以及跨领域思考的能力，而这些特质正是驱动长期卓越的核心引擎。其次，分析了卓越表现的真实来源。真正的明星员工并非产生于流水线式的精准培养，而是源于对跨界思维的深度运用。最后，文章提出了组织环境的重构方向。一个能够孕育顶尖人才的体系，不应以“速度”或“确定性”为优化目标，而应致力于构建一个鼓励韧性、支持实验并容忍“智慧型失败”（Intelligent Failure）的环境。只有在这样的生态中，人才才能通过不断的试错与跨界整合，最终成长为具备高度竞争力的明星员工。", "key_arguments": ["早期专业化陷阱：过度追求早期识别和专业化会扼杀人才的长期潜力，损害其适应性。", "跨领域思维的价值：长期卓越的驱动力来自于跨领域的思考能力和探索精神，而非单一技能的重复。", "系统优化目标的转向：组织应从追求“速度与确定性”转向追求“韧性、实验精神与智慧型失败”。"], "mentioned_resources": ["David Epstein (作者) - 知名研究者，其观点强调通才与跨界探索在卓越成就中的作用。"], "keywords": ["大器晚成 (Slow Developers)", "早期专业化 (Early Specialization)", "跨领域思维 (Cross-domain Thinking)", "智慧型失败 (Intelligent Failure)", "适应性 (Adaptability)", "韧性 (Resilience)"], "style_tone": "理性且具启发性的管理评论风格，带有对传统人才培养模式的批判性反思。"}</t>
+  </si>
+  <si>
     <t>2026-03-14T21:26:17</t>
   </si>
   <si>
@@ -5251,6 +6205,420 @@
   </si>
   <si>
     <t>2026-03-14T21:27:53</t>
+  </si>
+  <si>
+    <t>2026-03-16T15:16:42</t>
+  </si>
+  <si>
+    <t>2026-03-16T15:16:57</t>
+  </si>
+  <si>
+    <t>2026-03-16T15:17:06</t>
+  </si>
+  <si>
+    <t>2026-03-16T15:17:18</t>
+  </si>
+  <si>
+    <t>2026-03-16T15:19:32</t>
+  </si>
+  <si>
+    <t>2026-03-16T15:19:42</t>
+  </si>
+  <si>
+    <t>2026-03-16T15:19:51</t>
+  </si>
+  <si>
+    <t>2026-03-16T15:20:02</t>
+  </si>
+  <si>
+    <t>2026-03-16T15:20:14</t>
+  </si>
+  <si>
+    <t>2026-03-16T15:20:27</t>
+  </si>
+  <si>
+    <t>2026-03-16T15:20:41</t>
+  </si>
+  <si>
+    <t>2026-03-16T15:20:52</t>
+  </si>
+  <si>
+    <t>2026-03-16T15:21:06</t>
+  </si>
+  <si>
+    <t>2026-03-16T15:21:16</t>
+  </si>
+  <si>
+    <t>2026-03-16T15:21:27</t>
+  </si>
+  <si>
+    <t>2026-03-16T15:21:40</t>
+  </si>
+  <si>
+    <t>2026-03-16T15:21:51</t>
+  </si>
+  <si>
+    <t>2026-03-16T15:22:01</t>
+  </si>
+  <si>
+    <t>2026-03-16T15:23:33</t>
+  </si>
+  <si>
+    <t>2026-03-16T15:23:44</t>
+  </si>
+  <si>
+    <t>2026-03-16T15:23:55</t>
+  </si>
+  <si>
+    <t>2026-03-16T15:24:04</t>
+  </si>
+  <si>
+    <t>2026-03-16T15:24:13</t>
+  </si>
+  <si>
+    <t>2026-03-16T15:24:24</t>
+  </si>
+  <si>
+    <t>2026-03-16T15:24:37</t>
+  </si>
+  <si>
+    <t>2026-03-16T15:24:46</t>
+  </si>
+  <si>
+    <t>2026-03-16T15:24:54</t>
+  </si>
+  <si>
+    <t>2026-03-16T15:25:05</t>
+  </si>
+  <si>
+    <t>2026-03-16T15:25:14</t>
+  </si>
+  <si>
+    <t>2026-03-16T15:25:27</t>
+  </si>
+  <si>
+    <t>2026-03-16T15:25:36</t>
+  </si>
+  <si>
+    <t>2026-03-16T15:25:47</t>
+  </si>
+  <si>
+    <t>2026-03-16T15:25:55</t>
+  </si>
+  <si>
+    <t>2026-03-16T15:26:09</t>
+  </si>
+  <si>
+    <t>2026-03-16T15:26:19</t>
+  </si>
+  <si>
+    <t>2026-03-16T15:26:30</t>
+  </si>
+  <si>
+    <t>2026-03-16T15:26:39</t>
+  </si>
+  <si>
+    <t>2026-03-16T15:26:49</t>
+  </si>
+  <si>
+    <t>2026-03-16T15:27:02</t>
+  </si>
+  <si>
+    <t>2026-03-16T15:27:12</t>
+  </si>
+  <si>
+    <t>2026-03-16T15:27:23</t>
+  </si>
+  <si>
+    <t>2026-03-16T15:27:40</t>
+  </si>
+  <si>
+    <t>2026-03-16T15:27:55</t>
+  </si>
+  <si>
+    <t>2026-03-16T15:28:09</t>
+  </si>
+  <si>
+    <t>2026-03-16T15:28:24</t>
+  </si>
+  <si>
+    <t>2026-03-16T15:28:37</t>
+  </si>
+  <si>
+    <t>2026-03-16T15:28:52</t>
+  </si>
+  <si>
+    <t>2026-03-16T15:29:09</t>
+  </si>
+  <si>
+    <t>2026-03-16T15:29:21</t>
+  </si>
+  <si>
+    <t>2026-03-16T15:29:37</t>
+  </si>
+  <si>
+    <t>2026-03-16T15:29:54</t>
+  </si>
+  <si>
+    <t>2026-03-16T15:30:05</t>
+  </si>
+  <si>
+    <t>2026-03-16T15:30:23</t>
+  </si>
+  <si>
+    <t>2026-03-16T15:30:33</t>
+  </si>
+  <si>
+    <t>2026-03-16T15:30:49</t>
+  </si>
+  <si>
+    <t>2026-03-16T15:31:07</t>
+  </si>
+  <si>
+    <t>2026-03-16T15:31:21</t>
+  </si>
+  <si>
+    <t>2026-03-16T15:31:36</t>
+  </si>
+  <si>
+    <t>2026-03-16T15:31:50</t>
+  </si>
+  <si>
+    <t>2026-03-16T15:32:04</t>
+  </si>
+  <si>
+    <t>2026-03-16T15:32:20</t>
+  </si>
+  <si>
+    <t>2026-03-16T15:32:35</t>
+  </si>
+  <si>
+    <t>2026-03-16T15:32:49</t>
+  </si>
+  <si>
+    <t>2026-03-16T15:33:03</t>
+  </si>
+  <si>
+    <t>2026-03-16T15:33:21</t>
+  </si>
+  <si>
+    <t>2026-03-16T15:33:35</t>
+  </si>
+  <si>
+    <t>2026-03-16T15:33:50</t>
+  </si>
+  <si>
+    <t>2026-03-16T15:34:08</t>
+  </si>
+  <si>
+    <t>2026-03-16T15:34:22</t>
+  </si>
+  <si>
+    <t>2026-03-16T15:34:35</t>
+  </si>
+  <si>
+    <t>2026-03-16T15:34:51</t>
+  </si>
+  <si>
+    <t>2026-03-16T15:35:05</t>
+  </si>
+  <si>
+    <t>2026-03-16T15:35:20</t>
+  </si>
+  <si>
+    <t>2026-03-16T15:35:33</t>
+  </si>
+  <si>
+    <t>2026-03-16T15:35:50</t>
+  </si>
+  <si>
+    <t>2026-03-16T15:36:05</t>
+  </si>
+  <si>
+    <t>2026-03-16T15:36:20</t>
+  </si>
+  <si>
+    <t>2026-03-16T15:36:35</t>
+  </si>
+  <si>
+    <t>2026-03-16T15:36:48</t>
+  </si>
+  <si>
+    <t>2026-03-16T15:37:02</t>
+  </si>
+  <si>
+    <t>2026-03-16T15:37:18</t>
+  </si>
+  <si>
+    <t>2026-03-16T15:37:35</t>
+  </si>
+  <si>
+    <t>2026-03-16T15:37:50</t>
+  </si>
+  <si>
+    <t>2026-03-16T15:38:06</t>
+  </si>
+  <si>
+    <t>2026-03-16T15:38:16</t>
+  </si>
+  <si>
+    <t>2026-03-16T15:38:24</t>
+  </si>
+  <si>
+    <t>2026-03-16T15:38:35</t>
+  </si>
+  <si>
+    <t>2026-03-16T15:47:20</t>
+  </si>
+  <si>
+    <t>2026-03-16T15:47:33</t>
+  </si>
+  <si>
+    <t>2026-03-16T15:47:47</t>
+  </si>
+  <si>
+    <t>2026-03-16T15:47:58</t>
+  </si>
+  <si>
+    <t>2026-03-16T15:48:09</t>
+  </si>
+  <si>
+    <t>2026-03-16T15:48:18</t>
+  </si>
+  <si>
+    <t>2026-03-16T15:48:31</t>
+  </si>
+  <si>
+    <t>2026-03-16T15:48:44</t>
+  </si>
+  <si>
+    <t>2026-03-16T15:48:56</t>
+  </si>
+  <si>
+    <t>2026-03-16T15:49:09</t>
+  </si>
+  <si>
+    <t>2026-03-16T15:49:21</t>
+  </si>
+  <si>
+    <t>2026-03-16T15:49:33</t>
+  </si>
+  <si>
+    <t>2026-03-16T15:49:44</t>
+  </si>
+  <si>
+    <t>2026-03-16T15:49:54</t>
+  </si>
+  <si>
+    <t>2026-03-16T15:50:05</t>
+  </si>
+  <si>
+    <t>2026-03-16T15:50:14</t>
+  </si>
+  <si>
+    <t>2026-03-16T15:50:24</t>
+  </si>
+  <si>
+    <t>2026-03-16T15:50:34</t>
+  </si>
+  <si>
+    <t>2026-03-16T15:50:45</t>
+  </si>
+  <si>
+    <t>2026-03-16T15:50:54</t>
+  </si>
+  <si>
+    <t>2026-03-16T15:51:05</t>
+  </si>
+  <si>
+    <t>2026-03-16T15:51:15</t>
+  </si>
+  <si>
+    <t>2026-03-16T15:51:27</t>
+  </si>
+  <si>
+    <t>2026-03-16T15:51:39</t>
+  </si>
+  <si>
+    <t>2026-03-16T15:51:52</t>
+  </si>
+  <si>
+    <t>2026-03-16T15:52:01</t>
+  </si>
+  <si>
+    <t>2026-03-16T15:52:11</t>
+  </si>
+  <si>
+    <t>2026-03-16T15:52:25</t>
+  </si>
+  <si>
+    <t>2026-03-16T15:52:36</t>
+  </si>
+  <si>
+    <t>2026-03-16T15:52:47</t>
+  </si>
+  <si>
+    <t>2026-03-16T15:52:58</t>
+  </si>
+  <si>
+    <t>2026-03-16T15:53:08</t>
+  </si>
+  <si>
+    <t>2026-03-16T15:53:19</t>
+  </si>
+  <si>
+    <t>2026-03-16T15:53:29</t>
+  </si>
+  <si>
+    <t>2026-03-16T15:53:42</t>
+  </si>
+  <si>
+    <t>2026-03-16T15:53:51</t>
+  </si>
+  <si>
+    <t>2026-03-16T15:54:03</t>
+  </si>
+  <si>
+    <t>2026-03-16T15:54:14</t>
+  </si>
+  <si>
+    <t>2026-03-16T15:54:24</t>
+  </si>
+  <si>
+    <t>2026-03-16T15:54:39</t>
+  </si>
+  <si>
+    <t>2026-03-16T15:54:51</t>
+  </si>
+  <si>
+    <t>2026-03-16T15:55:01</t>
+  </si>
+  <si>
+    <t>2026-03-16T15:55:12</t>
+  </si>
+  <si>
+    <t>2026-03-16T15:55:24</t>
+  </si>
+  <si>
+    <t>2026-03-16T15:55:37</t>
+  </si>
+  <si>
+    <t>2026-03-16T15:55:49</t>
+  </si>
+  <si>
+    <t>2026-03-16T15:56:00</t>
+  </si>
+  <si>
+    <t>2026-03-16T15:56:11</t>
+  </si>
+  <si>
+    <t>2026-03-16T15:56:29</t>
+  </si>
+  <si>
+    <t>2026-03-16T15:56:38</t>
+  </si>
+  <si>
+    <t>2026-03-16T15:56:50</t>
   </si>
   <si>
     <t>playwright</t>
@@ -5775,22 +7143,40 @@
         <v>794</v>
       </c>
       <c r="P2">
-        <v>0</v>
+        <v>88</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>796</v>
+      </c>
+      <c r="R2" t="s">
+        <v>847</v>
+      </c>
+      <c r="S2" t="s">
+        <v>898</v>
       </c>
       <c r="T2" t="s">
-        <v>796</v>
+        <v>949</v>
+      </c>
+      <c r="U2" t="s">
+        <v>1001</v>
       </c>
       <c r="V2" t="s">
-        <v>796</v>
+        <v>976</v>
       </c>
       <c r="W2" t="s">
-        <v>797</v>
+        <v>1028</v>
       </c>
       <c r="X2" t="s">
         <v>794</v>
       </c>
       <c r="Z2" t="s">
-        <v>806</v>
+        <v>1124</v>
+      </c>
+      <c r="AA2" t="s">
+        <v>794</v>
+      </c>
+      <c r="AC2" t="s">
+        <v>1220</v>
       </c>
     </row>
     <row r="3" spans="1:33">
@@ -5837,22 +7223,40 @@
         <v>794</v>
       </c>
       <c r="P3">
-        <v>0</v>
+        <v>85</v>
+      </c>
+      <c r="Q3" t="s">
+        <v>797</v>
+      </c>
+      <c r="R3" t="s">
+        <v>848</v>
+      </c>
+      <c r="S3" t="s">
+        <v>899</v>
       </c>
       <c r="T3" t="s">
-        <v>796</v>
+        <v>950</v>
+      </c>
+      <c r="U3" t="s">
+        <v>1002</v>
       </c>
       <c r="V3" t="s">
-        <v>796</v>
+        <v>1006</v>
       </c>
       <c r="W3" t="s">
-        <v>798</v>
+        <v>1029</v>
       </c>
       <c r="X3" t="s">
         <v>794</v>
       </c>
       <c r="Z3" t="s">
-        <v>807</v>
+        <v>1125</v>
+      </c>
+      <c r="AA3" t="s">
+        <v>794</v>
+      </c>
+      <c r="AC3" t="s">
+        <v>1221</v>
       </c>
     </row>
     <row r="4" spans="1:33">
@@ -5899,22 +7303,40 @@
         <v>794</v>
       </c>
       <c r="P4">
-        <v>0</v>
+        <v>88</v>
+      </c>
+      <c r="Q4" t="s">
+        <v>798</v>
+      </c>
+      <c r="R4" t="s">
+        <v>849</v>
+      </c>
+      <c r="S4" t="s">
+        <v>900</v>
       </c>
       <c r="T4" t="s">
-        <v>796</v>
+        <v>951</v>
+      </c>
+      <c r="U4" t="s">
+        <v>1002</v>
       </c>
       <c r="V4" t="s">
-        <v>796</v>
+        <v>976</v>
       </c>
       <c r="W4" t="s">
-        <v>799</v>
+        <v>1030</v>
       </c>
       <c r="X4" t="s">
         <v>794</v>
       </c>
       <c r="Z4" t="s">
-        <v>808</v>
+        <v>1126</v>
+      </c>
+      <c r="AA4" t="s">
+        <v>794</v>
+      </c>
+      <c r="AC4" t="s">
+        <v>1222</v>
       </c>
     </row>
     <row r="5" spans="1:33">
@@ -5961,22 +7383,40 @@
         <v>794</v>
       </c>
       <c r="P5">
-        <v>0</v>
+        <v>85</v>
+      </c>
+      <c r="Q5" t="s">
+        <v>799</v>
+      </c>
+      <c r="R5" t="s">
+        <v>850</v>
+      </c>
+      <c r="S5" t="s">
+        <v>901</v>
       </c>
       <c r="T5" t="s">
-        <v>796</v>
+        <v>952</v>
+      </c>
+      <c r="U5" t="s">
+        <v>1003</v>
       </c>
       <c r="V5" t="s">
-        <v>796</v>
+        <v>976</v>
       </c>
       <c r="W5" t="s">
-        <v>800</v>
+        <v>1031</v>
       </c>
       <c r="X5" t="s">
         <v>794</v>
       </c>
       <c r="Z5" t="s">
-        <v>809</v>
+        <v>1127</v>
+      </c>
+      <c r="AA5" t="s">
+        <v>794</v>
+      </c>
+      <c r="AC5" t="s">
+        <v>1223</v>
       </c>
     </row>
     <row r="6" spans="1:33">
@@ -6023,22 +7463,40 @@
         <v>794</v>
       </c>
       <c r="P6">
-        <v>0</v>
+        <v>90</v>
+      </c>
+      <c r="Q6" t="s">
+        <v>800</v>
+      </c>
+      <c r="R6" t="s">
+        <v>851</v>
+      </c>
+      <c r="S6" t="s">
+        <v>902</v>
       </c>
       <c r="T6" t="s">
-        <v>796</v>
+        <v>953</v>
+      </c>
+      <c r="U6" t="s">
+        <v>1002</v>
       </c>
       <c r="V6" t="s">
-        <v>796</v>
+        <v>976</v>
       </c>
       <c r="W6" t="s">
-        <v>801</v>
+        <v>1032</v>
       </c>
       <c r="X6" t="s">
         <v>794</v>
       </c>
       <c r="Z6" t="s">
-        <v>810</v>
+        <v>1128</v>
+      </c>
+      <c r="AA6" t="s">
+        <v>794</v>
+      </c>
+      <c r="AC6" t="s">
+        <v>1224</v>
       </c>
     </row>
     <row r="7" spans="1:33">
@@ -6085,22 +7543,40 @@
         <v>794</v>
       </c>
       <c r="P7">
-        <v>0</v>
+        <v>90</v>
+      </c>
+      <c r="Q7" t="s">
+        <v>801</v>
+      </c>
+      <c r="R7" t="s">
+        <v>852</v>
+      </c>
+      <c r="S7" t="s">
+        <v>903</v>
       </c>
       <c r="T7" t="s">
-        <v>796</v>
+        <v>954</v>
+      </c>
+      <c r="U7" t="s">
+        <v>1004</v>
       </c>
       <c r="V7" t="s">
-        <v>796</v>
+        <v>1007</v>
       </c>
       <c r="W7" t="s">
-        <v>802</v>
+        <v>1033</v>
       </c>
       <c r="X7" t="s">
         <v>794</v>
       </c>
       <c r="Z7" t="s">
-        <v>811</v>
+        <v>1129</v>
+      </c>
+      <c r="AA7" t="s">
+        <v>794</v>
+      </c>
+      <c r="AC7" t="s">
+        <v>1225</v>
       </c>
     </row>
     <row r="8" spans="1:33">
@@ -6147,22 +7623,40 @@
         <v>794</v>
       </c>
       <c r="P8">
-        <v>0</v>
+        <v>92</v>
+      </c>
+      <c r="Q8" t="s">
+        <v>802</v>
+      </c>
+      <c r="R8" t="s">
+        <v>853</v>
+      </c>
+      <c r="S8" t="s">
+        <v>904</v>
       </c>
       <c r="T8" t="s">
-        <v>796</v>
+        <v>955</v>
+      </c>
+      <c r="U8" t="s">
+        <v>1002</v>
       </c>
       <c r="V8" t="s">
-        <v>796</v>
+        <v>1008</v>
       </c>
       <c r="W8" t="s">
-        <v>803</v>
+        <v>1034</v>
       </c>
       <c r="X8" t="s">
         <v>794</v>
       </c>
       <c r="Z8" t="s">
-        <v>812</v>
+        <v>1130</v>
+      </c>
+      <c r="AA8" t="s">
+        <v>794</v>
+      </c>
+      <c r="AC8" t="s">
+        <v>1226</v>
       </c>
     </row>
     <row r="9" spans="1:33">
@@ -6209,22 +7703,40 @@
         <v>794</v>
       </c>
       <c r="P9">
-        <v>0</v>
+        <v>90</v>
+      </c>
+      <c r="Q9" t="s">
+        <v>803</v>
+      </c>
+      <c r="R9" t="s">
+        <v>854</v>
+      </c>
+      <c r="S9" t="s">
+        <v>905</v>
       </c>
       <c r="T9" t="s">
-        <v>796</v>
+        <v>956</v>
+      </c>
+      <c r="U9" t="s">
+        <v>1004</v>
       </c>
       <c r="V9" t="s">
-        <v>796</v>
+        <v>976</v>
       </c>
       <c r="W9" t="s">
-        <v>804</v>
+        <v>1035</v>
       </c>
       <c r="X9" t="s">
         <v>794</v>
       </c>
       <c r="Z9" t="s">
-        <v>813</v>
+        <v>1131</v>
+      </c>
+      <c r="AA9" t="s">
+        <v>794</v>
+      </c>
+      <c r="AC9" t="s">
+        <v>1227</v>
       </c>
     </row>
     <row r="10" spans="1:33">
@@ -6271,22 +7783,40 @@
         <v>794</v>
       </c>
       <c r="P10">
-        <v>0</v>
+        <v>88</v>
+      </c>
+      <c r="Q10" t="s">
+        <v>804</v>
+      </c>
+      <c r="R10" t="s">
+        <v>855</v>
+      </c>
+      <c r="S10" t="s">
+        <v>906</v>
       </c>
       <c r="T10" t="s">
-        <v>796</v>
+        <v>957</v>
+      </c>
+      <c r="U10" t="s">
+        <v>1001</v>
       </c>
       <c r="V10" t="s">
-        <v>796</v>
+        <v>976</v>
       </c>
       <c r="W10" t="s">
-        <v>805</v>
+        <v>1036</v>
       </c>
       <c r="X10" t="s">
         <v>794</v>
       </c>
       <c r="Z10" t="s">
-        <v>814</v>
+        <v>1132</v>
+      </c>
+      <c r="AA10" t="s">
+        <v>794</v>
+      </c>
+      <c r="AC10" t="s">
+        <v>1228</v>
       </c>
     </row>
     <row r="11" spans="1:33">
@@ -6368,13 +7898,40 @@
         <v>794</v>
       </c>
       <c r="P12">
-        <v>0</v>
+        <v>88</v>
+      </c>
+      <c r="Q12" t="s">
+        <v>805</v>
+      </c>
+      <c r="R12" t="s">
+        <v>856</v>
+      </c>
+      <c r="S12" t="s">
+        <v>907</v>
       </c>
       <c r="T12" t="s">
-        <v>796</v>
+        <v>958</v>
+      </c>
+      <c r="U12" t="s">
+        <v>1004</v>
       </c>
       <c r="V12" t="s">
-        <v>796</v>
+        <v>976</v>
+      </c>
+      <c r="W12" t="s">
+        <v>1037</v>
+      </c>
+      <c r="X12" t="s">
+        <v>794</v>
+      </c>
+      <c r="Z12" t="s">
+        <v>1133</v>
+      </c>
+      <c r="AA12" t="s">
+        <v>794</v>
+      </c>
+      <c r="AC12" t="s">
+        <v>1229</v>
       </c>
     </row>
     <row r="13" spans="1:33">
@@ -6421,13 +7978,40 @@
         <v>794</v>
       </c>
       <c r="P13">
-        <v>0</v>
+        <v>85</v>
+      </c>
+      <c r="Q13" t="s">
+        <v>806</v>
+      </c>
+      <c r="R13" t="s">
+        <v>857</v>
+      </c>
+      <c r="S13" t="s">
+        <v>908</v>
       </c>
       <c r="T13" t="s">
-        <v>796</v>
+        <v>959</v>
+      </c>
+      <c r="U13" t="s">
+        <v>1004</v>
       </c>
       <c r="V13" t="s">
-        <v>796</v>
+        <v>1009</v>
+      </c>
+      <c r="W13" t="s">
+        <v>1038</v>
+      </c>
+      <c r="X13" t="s">
+        <v>794</v>
+      </c>
+      <c r="Z13" t="s">
+        <v>1134</v>
+      </c>
+      <c r="AA13" t="s">
+        <v>794</v>
+      </c>
+      <c r="AC13" t="s">
+        <v>1230</v>
       </c>
     </row>
     <row r="14" spans="1:33">
@@ -6509,13 +8093,40 @@
         <v>794</v>
       </c>
       <c r="P15">
-        <v>0</v>
+        <v>88</v>
+      </c>
+      <c r="Q15" t="s">
+        <v>807</v>
+      </c>
+      <c r="R15" t="s">
+        <v>858</v>
+      </c>
+      <c r="S15" t="s">
+        <v>909</v>
       </c>
       <c r="T15" t="s">
-        <v>796</v>
+        <v>960</v>
+      </c>
+      <c r="U15" t="s">
+        <v>1002</v>
       </c>
       <c r="V15" t="s">
-        <v>796</v>
+        <v>1010</v>
+      </c>
+      <c r="W15" t="s">
+        <v>1039</v>
+      </c>
+      <c r="X15" t="s">
+        <v>794</v>
+      </c>
+      <c r="Z15" t="s">
+        <v>1135</v>
+      </c>
+      <c r="AA15" t="s">
+        <v>794</v>
+      </c>
+      <c r="AC15" t="s">
+        <v>1231</v>
       </c>
     </row>
     <row r="16" spans="1:33">
@@ -6562,16 +8173,43 @@
         <v>794</v>
       </c>
       <c r="P16">
-        <v>0</v>
+        <v>95</v>
+      </c>
+      <c r="Q16" t="s">
+        <v>808</v>
+      </c>
+      <c r="R16" t="s">
+        <v>859</v>
+      </c>
+      <c r="S16" t="s">
+        <v>910</v>
       </c>
       <c r="T16" t="s">
-        <v>796</v>
+        <v>961</v>
+      </c>
+      <c r="U16" t="s">
+        <v>1005</v>
       </c>
       <c r="V16" t="s">
-        <v>796</v>
+        <v>1011</v>
+      </c>
+      <c r="W16" t="s">
+        <v>1040</v>
+      </c>
+      <c r="X16" t="s">
+        <v>794</v>
+      </c>
+      <c r="Z16" t="s">
+        <v>1136</v>
+      </c>
+      <c r="AA16" t="s">
+        <v>794</v>
+      </c>
+      <c r="AC16" t="s">
+        <v>1232</v>
       </c>
     </row>
-    <row r="17" spans="1:22">
+    <row r="17" spans="1:29">
       <c r="A17">
         <v>17734812832211</v>
       </c>
@@ -6615,16 +8253,43 @@
         <v>794</v>
       </c>
       <c r="P17">
-        <v>0</v>
+        <v>85</v>
+      </c>
+      <c r="Q17" t="s">
+        <v>809</v>
+      </c>
+      <c r="R17" t="s">
+        <v>860</v>
+      </c>
+      <c r="S17" t="s">
+        <v>911</v>
       </c>
       <c r="T17" t="s">
-        <v>796</v>
+        <v>962</v>
+      </c>
+      <c r="U17" t="s">
+        <v>1002</v>
       </c>
       <c r="V17" t="s">
-        <v>796</v>
+        <v>976</v>
+      </c>
+      <c r="W17" t="s">
+        <v>1041</v>
+      </c>
+      <c r="X17" t="s">
+        <v>794</v>
+      </c>
+      <c r="Z17" t="s">
+        <v>1137</v>
+      </c>
+      <c r="AA17" t="s">
+        <v>794</v>
+      </c>
+      <c r="AC17" t="s">
+        <v>1233</v>
       </c>
     </row>
-    <row r="18" spans="1:22">
+    <row r="18" spans="1:29">
       <c r="A18">
         <v>17734812832362</v>
       </c>
@@ -6659,7 +8324,7 @@
         <v>530</v>
       </c>
     </row>
-    <row r="19" spans="1:22">
+    <row r="19" spans="1:29">
       <c r="A19">
         <v>17734812832487</v>
       </c>
@@ -6703,16 +8368,43 @@
         <v>794</v>
       </c>
       <c r="P19">
-        <v>0</v>
+        <v>90</v>
+      </c>
+      <c r="Q19" t="s">
+        <v>810</v>
+      </c>
+      <c r="R19" t="s">
+        <v>861</v>
+      </c>
+      <c r="S19" t="s">
+        <v>912</v>
       </c>
       <c r="T19" t="s">
-        <v>796</v>
+        <v>963</v>
+      </c>
+      <c r="U19" t="s">
+        <v>1004</v>
       </c>
       <c r="V19" t="s">
-        <v>796</v>
+        <v>976</v>
+      </c>
+      <c r="W19" t="s">
+        <v>1042</v>
+      </c>
+      <c r="X19" t="s">
+        <v>794</v>
+      </c>
+      <c r="Z19" t="s">
+        <v>1138</v>
+      </c>
+      <c r="AA19" t="s">
+        <v>794</v>
+      </c>
+      <c r="AC19" t="s">
+        <v>1234</v>
       </c>
     </row>
-    <row r="20" spans="1:22">
+    <row r="20" spans="1:29">
       <c r="A20">
         <v>17734812832502</v>
       </c>
@@ -6756,16 +8448,43 @@
         <v>794</v>
       </c>
       <c r="P20">
-        <v>0</v>
+        <v>92</v>
+      </c>
+      <c r="Q20" t="s">
+        <v>811</v>
+      </c>
+      <c r="R20" t="s">
+        <v>862</v>
+      </c>
+      <c r="S20" t="s">
+        <v>913</v>
       </c>
       <c r="T20" t="s">
-        <v>796</v>
+        <v>964</v>
+      </c>
+      <c r="U20" t="s">
+        <v>1002</v>
       </c>
       <c r="V20" t="s">
-        <v>796</v>
+        <v>976</v>
+      </c>
+      <c r="W20" t="s">
+        <v>1043</v>
+      </c>
+      <c r="X20" t="s">
+        <v>794</v>
+      </c>
+      <c r="Z20" t="s">
+        <v>1139</v>
+      </c>
+      <c r="AA20" t="s">
+        <v>794</v>
+      </c>
+      <c r="AC20" t="s">
+        <v>1235</v>
       </c>
     </row>
-    <row r="21" spans="1:22">
+    <row r="21" spans="1:29">
       <c r="A21">
         <v>17734812832682</v>
       </c>
@@ -6800,7 +8519,7 @@
         <v>533</v>
       </c>
     </row>
-    <row r="22" spans="1:22">
+    <row r="22" spans="1:29">
       <c r="A22">
         <v>17734812832796</v>
       </c>
@@ -6844,16 +8563,43 @@
         <v>794</v>
       </c>
       <c r="P22">
-        <v>0</v>
+        <v>92</v>
+      </c>
+      <c r="Q22" t="s">
+        <v>812</v>
+      </c>
+      <c r="R22" t="s">
+        <v>863</v>
+      </c>
+      <c r="S22" t="s">
+        <v>914</v>
       </c>
       <c r="T22" t="s">
-        <v>796</v>
+        <v>965</v>
+      </c>
+      <c r="U22" t="s">
+        <v>1003</v>
       </c>
       <c r="V22" t="s">
-        <v>796</v>
+        <v>976</v>
+      </c>
+      <c r="W22" t="s">
+        <v>1044</v>
+      </c>
+      <c r="X22" t="s">
+        <v>794</v>
+      </c>
+      <c r="Z22" t="s">
+        <v>1140</v>
+      </c>
+      <c r="AA22" t="s">
+        <v>794</v>
+      </c>
+      <c r="AC22" t="s">
+        <v>1236</v>
       </c>
     </row>
-    <row r="23" spans="1:22">
+    <row r="23" spans="1:29">
       <c r="A23">
         <v>17734812832862</v>
       </c>
@@ -6897,16 +8643,43 @@
         <v>794</v>
       </c>
       <c r="P23">
-        <v>0</v>
+        <v>85</v>
+      </c>
+      <c r="Q23" t="s">
+        <v>813</v>
+      </c>
+      <c r="R23" t="s">
+        <v>864</v>
+      </c>
+      <c r="S23" t="s">
+        <v>915</v>
       </c>
       <c r="T23" t="s">
-        <v>796</v>
+        <v>966</v>
+      </c>
+      <c r="U23" t="s">
+        <v>1001</v>
       </c>
       <c r="V23" t="s">
-        <v>796</v>
+        <v>1012</v>
+      </c>
+      <c r="W23" t="s">
+        <v>1045</v>
+      </c>
+      <c r="X23" t="s">
+        <v>794</v>
+      </c>
+      <c r="Z23" t="s">
+        <v>1141</v>
+      </c>
+      <c r="AA23" t="s">
+        <v>794</v>
+      </c>
+      <c r="AC23" t="s">
+        <v>1237</v>
       </c>
     </row>
-    <row r="24" spans="1:22">
+    <row r="24" spans="1:29">
       <c r="A24">
         <v>17734812832959</v>
       </c>
@@ -6950,16 +8723,43 @@
         <v>794</v>
       </c>
       <c r="P24">
-        <v>0</v>
+        <v>88</v>
+      </c>
+      <c r="Q24" t="s">
+        <v>814</v>
+      </c>
+      <c r="R24" t="s">
+        <v>865</v>
+      </c>
+      <c r="S24" t="s">
+        <v>916</v>
       </c>
       <c r="T24" t="s">
-        <v>796</v>
+        <v>967</v>
+      </c>
+      <c r="U24" t="s">
+        <v>1004</v>
       </c>
       <c r="V24" t="s">
-        <v>796</v>
+        <v>976</v>
+      </c>
+      <c r="W24" t="s">
+        <v>1046</v>
+      </c>
+      <c r="X24" t="s">
+        <v>794</v>
+      </c>
+      <c r="Z24" t="s">
+        <v>1142</v>
+      </c>
+      <c r="AA24" t="s">
+        <v>794</v>
+      </c>
+      <c r="AC24" t="s">
+        <v>1238</v>
       </c>
     </row>
-    <row r="25" spans="1:22">
+    <row r="25" spans="1:29">
       <c r="A25">
         <v>17734812833020</v>
       </c>
@@ -6994,7 +8794,7 @@
         <v>537</v>
       </c>
     </row>
-    <row r="26" spans="1:22">
+    <row r="26" spans="1:29">
       <c r="A26">
         <v>17734812833134</v>
       </c>
@@ -7038,16 +8838,43 @@
         <v>794</v>
       </c>
       <c r="P26">
-        <v>0</v>
+        <v>90</v>
+      </c>
+      <c r="Q26" t="s">
+        <v>815</v>
+      </c>
+      <c r="R26" t="s">
+        <v>866</v>
+      </c>
+      <c r="S26" t="s">
+        <v>917</v>
       </c>
       <c r="T26" t="s">
-        <v>796</v>
+        <v>968</v>
+      </c>
+      <c r="U26" t="s">
+        <v>1004</v>
       </c>
       <c r="V26" t="s">
-        <v>796</v>
+        <v>1013</v>
+      </c>
+      <c r="W26" t="s">
+        <v>1047</v>
+      </c>
+      <c r="X26" t="s">
+        <v>794</v>
+      </c>
+      <c r="Z26" t="s">
+        <v>1143</v>
+      </c>
+      <c r="AA26" t="s">
+        <v>794</v>
+      </c>
+      <c r="AC26" t="s">
+        <v>1239</v>
       </c>
     </row>
-    <row r="27" spans="1:22">
+    <row r="27" spans="1:29">
       <c r="A27">
         <v>17734812833216</v>
       </c>
@@ -7082,7 +8909,7 @@
         <v>539</v>
       </c>
     </row>
-    <row r="28" spans="1:22">
+    <row r="28" spans="1:29">
       <c r="A28">
         <v>17734812833368</v>
       </c>
@@ -7126,16 +8953,43 @@
         <v>794</v>
       </c>
       <c r="P28">
-        <v>0</v>
+        <v>90</v>
+      </c>
+      <c r="Q28" t="s">
+        <v>816</v>
+      </c>
+      <c r="R28" t="s">
+        <v>867</v>
+      </c>
+      <c r="S28" t="s">
+        <v>918</v>
       </c>
       <c r="T28" t="s">
-        <v>796</v>
+        <v>969</v>
+      </c>
+      <c r="U28" t="s">
+        <v>1004</v>
       </c>
       <c r="V28" t="s">
-        <v>796</v>
+        <v>976</v>
+      </c>
+      <c r="W28" t="s">
+        <v>1048</v>
+      </c>
+      <c r="X28" t="s">
+        <v>794</v>
+      </c>
+      <c r="Z28" t="s">
+        <v>1144</v>
+      </c>
+      <c r="AA28" t="s">
+        <v>794</v>
+      </c>
+      <c r="AC28" t="s">
+        <v>1240</v>
       </c>
     </row>
-    <row r="29" spans="1:22">
+    <row r="29" spans="1:29">
       <c r="A29">
         <v>17734812833422</v>
       </c>
@@ -7170,7 +9024,7 @@
         <v>541</v>
       </c>
     </row>
-    <row r="30" spans="1:22">
+    <row r="30" spans="1:29">
       <c r="A30">
         <v>17734812833553</v>
       </c>
@@ -7205,7 +9059,7 @@
         <v>542</v>
       </c>
     </row>
-    <row r="31" spans="1:22">
+    <row r="31" spans="1:29">
       <c r="A31">
         <v>17734812833685</v>
       </c>
@@ -7249,16 +9103,43 @@
         <v>794</v>
       </c>
       <c r="P31">
-        <v>0</v>
+        <v>88</v>
+      </c>
+      <c r="Q31" t="s">
+        <v>817</v>
+      </c>
+      <c r="R31" t="s">
+        <v>868</v>
+      </c>
+      <c r="S31" t="s">
+        <v>919</v>
       </c>
       <c r="T31" t="s">
-        <v>796</v>
+        <v>970</v>
+      </c>
+      <c r="U31" t="s">
+        <v>1001</v>
       </c>
       <c r="V31" t="s">
-        <v>796</v>
+        <v>976</v>
+      </c>
+      <c r="W31" t="s">
+        <v>1049</v>
+      </c>
+      <c r="X31" t="s">
+        <v>794</v>
+      </c>
+      <c r="Z31" t="s">
+        <v>1145</v>
+      </c>
+      <c r="AA31" t="s">
+        <v>794</v>
+      </c>
+      <c r="AC31" t="s">
+        <v>1241</v>
       </c>
     </row>
-    <row r="32" spans="1:22">
+    <row r="32" spans="1:29">
       <c r="A32">
         <v>17734812833719</v>
       </c>
@@ -7302,16 +9183,43 @@
         <v>794</v>
       </c>
       <c r="P32">
-        <v>0</v>
+        <v>92</v>
+      </c>
+      <c r="Q32" t="s">
+        <v>818</v>
+      </c>
+      <c r="R32" t="s">
+        <v>869</v>
+      </c>
+      <c r="S32" t="s">
+        <v>920</v>
       </c>
       <c r="T32" t="s">
-        <v>796</v>
+        <v>971</v>
+      </c>
+      <c r="U32" t="s">
+        <v>1001</v>
       </c>
       <c r="V32" t="s">
-        <v>796</v>
+        <v>1014</v>
+      </c>
+      <c r="W32" t="s">
+        <v>1050</v>
+      </c>
+      <c r="X32" t="s">
+        <v>794</v>
+      </c>
+      <c r="Z32" t="s">
+        <v>1146</v>
+      </c>
+      <c r="AA32" t="s">
+        <v>794</v>
+      </c>
+      <c r="AC32" t="s">
+        <v>1242</v>
       </c>
     </row>
-    <row r="33" spans="1:22">
+    <row r="33" spans="1:29">
       <c r="A33">
         <v>17734812833842</v>
       </c>
@@ -7355,16 +9263,43 @@
         <v>794</v>
       </c>
       <c r="P33">
-        <v>0</v>
+        <v>85</v>
+      </c>
+      <c r="Q33" t="s">
+        <v>819</v>
+      </c>
+      <c r="R33" t="s">
+        <v>870</v>
+      </c>
+      <c r="S33" t="s">
+        <v>921</v>
       </c>
       <c r="T33" t="s">
-        <v>796</v>
+        <v>972</v>
+      </c>
+      <c r="U33" t="s">
+        <v>1001</v>
       </c>
       <c r="V33" t="s">
-        <v>796</v>
+        <v>976</v>
+      </c>
+      <c r="W33" t="s">
+        <v>1051</v>
+      </c>
+      <c r="X33" t="s">
+        <v>794</v>
+      </c>
+      <c r="Z33" t="s">
+        <v>1147</v>
+      </c>
+      <c r="AA33" t="s">
+        <v>794</v>
+      </c>
+      <c r="AC33" t="s">
+        <v>1243</v>
       </c>
     </row>
-    <row r="34" spans="1:22">
+    <row r="34" spans="1:29">
       <c r="A34">
         <v>17734812833972</v>
       </c>
@@ -7399,7 +9334,7 @@
         <v>546</v>
       </c>
     </row>
-    <row r="35" spans="1:22">
+    <row r="35" spans="1:29">
       <c r="A35">
         <v>17734812834054</v>
       </c>
@@ -7443,16 +9378,43 @@
         <v>794</v>
       </c>
       <c r="P35">
-        <v>0</v>
+        <v>92</v>
+      </c>
+      <c r="Q35" t="s">
+        <v>820</v>
+      </c>
+      <c r="R35" t="s">
+        <v>871</v>
+      </c>
+      <c r="S35" t="s">
+        <v>922</v>
       </c>
       <c r="T35" t="s">
-        <v>796</v>
+        <v>973</v>
+      </c>
+      <c r="U35" t="s">
+        <v>1004</v>
       </c>
       <c r="V35" t="s">
-        <v>796</v>
+        <v>976</v>
+      </c>
+      <c r="W35" t="s">
+        <v>1052</v>
+      </c>
+      <c r="X35" t="s">
+        <v>794</v>
+      </c>
+      <c r="Z35" t="s">
+        <v>1148</v>
+      </c>
+      <c r="AA35" t="s">
+        <v>794</v>
+      </c>
+      <c r="AC35" t="s">
+        <v>1244</v>
       </c>
     </row>
-    <row r="36" spans="1:22">
+    <row r="36" spans="1:29">
       <c r="A36">
         <v>17734812834136</v>
       </c>
@@ -7496,16 +9458,43 @@
         <v>794</v>
       </c>
       <c r="P36">
-        <v>0</v>
+        <v>85</v>
+      </c>
+      <c r="Q36" t="s">
+        <v>821</v>
+      </c>
+      <c r="R36" t="s">
+        <v>872</v>
+      </c>
+      <c r="S36" t="s">
+        <v>923</v>
       </c>
       <c r="T36" t="s">
-        <v>796</v>
+        <v>974</v>
+      </c>
+      <c r="U36" t="s">
+        <v>1002</v>
       </c>
       <c r="V36" t="s">
-        <v>796</v>
+        <v>1015</v>
+      </c>
+      <c r="W36" t="s">
+        <v>1053</v>
+      </c>
+      <c r="X36" t="s">
+        <v>794</v>
+      </c>
+      <c r="Z36" t="s">
+        <v>1149</v>
+      </c>
+      <c r="AA36" t="s">
+        <v>794</v>
+      </c>
+      <c r="AC36" t="s">
+        <v>1245</v>
       </c>
     </row>
-    <row r="37" spans="1:22">
+    <row r="37" spans="1:29">
       <c r="A37">
         <v>17734812834289</v>
       </c>
@@ -7549,16 +9538,43 @@
         <v>794</v>
       </c>
       <c r="P37">
-        <v>0</v>
+        <v>90</v>
+      </c>
+      <c r="Q37" t="s">
+        <v>822</v>
+      </c>
+      <c r="R37" t="s">
+        <v>873</v>
+      </c>
+      <c r="S37" t="s">
+        <v>924</v>
       </c>
       <c r="T37" t="s">
-        <v>796</v>
+        <v>975</v>
+      </c>
+      <c r="U37" t="s">
+        <v>1004</v>
       </c>
       <c r="V37" t="s">
-        <v>796</v>
+        <v>1016</v>
+      </c>
+      <c r="W37" t="s">
+        <v>1054</v>
+      </c>
+      <c r="X37" t="s">
+        <v>794</v>
+      </c>
+      <c r="Z37" t="s">
+        <v>1150</v>
+      </c>
+      <c r="AA37" t="s">
+        <v>794</v>
+      </c>
+      <c r="AC37" t="s">
+        <v>1246</v>
       </c>
     </row>
-    <row r="38" spans="1:22">
+    <row r="38" spans="1:29">
       <c r="A38">
         <v>17734812834326</v>
       </c>
@@ -7608,13 +9624,13 @@
         <v>719</v>
       </c>
       <c r="T38" t="s">
-        <v>796</v>
+        <v>976</v>
       </c>
       <c r="V38" t="s">
-        <v>796</v>
+        <v>976</v>
       </c>
     </row>
-    <row r="39" spans="1:22">
+    <row r="39" spans="1:29">
       <c r="A39">
         <v>17734812834472</v>
       </c>
@@ -7664,13 +9680,13 @@
         <v>720</v>
       </c>
       <c r="T39" t="s">
-        <v>796</v>
+        <v>976</v>
       </c>
       <c r="V39" t="s">
-        <v>796</v>
+        <v>976</v>
       </c>
     </row>
-    <row r="40" spans="1:22">
+    <row r="40" spans="1:29">
       <c r="A40">
         <v>17734812834554</v>
       </c>
@@ -7714,16 +9730,43 @@
         <v>794</v>
       </c>
       <c r="P40">
-        <v>0</v>
+        <v>85</v>
+      </c>
+      <c r="Q40" t="s">
+        <v>823</v>
+      </c>
+      <c r="R40" t="s">
+        <v>874</v>
+      </c>
+      <c r="S40" t="s">
+        <v>925</v>
       </c>
       <c r="T40" t="s">
-        <v>796</v>
+        <v>977</v>
+      </c>
+      <c r="U40" t="s">
+        <v>1002</v>
       </c>
       <c r="V40" t="s">
-        <v>796</v>
+        <v>1017</v>
+      </c>
+      <c r="W40" t="s">
+        <v>1055</v>
+      </c>
+      <c r="X40" t="s">
+        <v>794</v>
+      </c>
+      <c r="Z40" t="s">
+        <v>1151</v>
+      </c>
+      <c r="AA40" t="s">
+        <v>794</v>
+      </c>
+      <c r="AC40" t="s">
+        <v>1247</v>
       </c>
     </row>
-    <row r="41" spans="1:22">
+    <row r="41" spans="1:29">
       <c r="A41">
         <v>17734812834687</v>
       </c>
@@ -7767,16 +9810,43 @@
         <v>794</v>
       </c>
       <c r="P41">
-        <v>0</v>
+        <v>88</v>
+      </c>
+      <c r="Q41" t="s">
+        <v>824</v>
+      </c>
+      <c r="R41" t="s">
+        <v>875</v>
+      </c>
+      <c r="S41" t="s">
+        <v>926</v>
       </c>
       <c r="T41" t="s">
-        <v>796</v>
+        <v>978</v>
+      </c>
+      <c r="U41" t="s">
+        <v>1002</v>
       </c>
       <c r="V41" t="s">
-        <v>796</v>
+        <v>1018</v>
+      </c>
+      <c r="W41" t="s">
+        <v>1056</v>
+      </c>
+      <c r="X41" t="s">
+        <v>794</v>
+      </c>
+      <c r="Z41" t="s">
+        <v>1152</v>
+      </c>
+      <c r="AA41" t="s">
+        <v>794</v>
+      </c>
+      <c r="AC41" t="s">
+        <v>1248</v>
       </c>
     </row>
-    <row r="42" spans="1:22">
+    <row r="42" spans="1:29">
       <c r="A42">
         <v>17734812834728</v>
       </c>
@@ -7820,16 +9890,43 @@
         <v>794</v>
       </c>
       <c r="P42">
-        <v>0</v>
+        <v>95</v>
+      </c>
+      <c r="Q42" t="s">
+        <v>825</v>
+      </c>
+      <c r="R42" t="s">
+        <v>876</v>
+      </c>
+      <c r="S42" t="s">
+        <v>927</v>
       </c>
       <c r="T42" t="s">
-        <v>796</v>
+        <v>979</v>
+      </c>
+      <c r="U42" t="s">
+        <v>1004</v>
       </c>
       <c r="V42" t="s">
-        <v>796</v>
+        <v>1019</v>
+      </c>
+      <c r="W42" t="s">
+        <v>1057</v>
+      </c>
+      <c r="X42" t="s">
+        <v>794</v>
+      </c>
+      <c r="Z42" t="s">
+        <v>1153</v>
+      </c>
+      <c r="AA42" t="s">
+        <v>794</v>
+      </c>
+      <c r="AC42" t="s">
+        <v>1249</v>
       </c>
     </row>
-    <row r="43" spans="1:22">
+    <row r="43" spans="1:29">
       <c r="A43">
         <v>17734812834879</v>
       </c>
@@ -7873,16 +9970,43 @@
         <v>794</v>
       </c>
       <c r="P43">
-        <v>0</v>
+        <v>90</v>
+      </c>
+      <c r="Q43" t="s">
+        <v>826</v>
+      </c>
+      <c r="R43" t="s">
+        <v>877</v>
+      </c>
+      <c r="S43" t="s">
+        <v>928</v>
       </c>
       <c r="T43" t="s">
-        <v>796</v>
+        <v>980</v>
+      </c>
+      <c r="U43" t="s">
+        <v>1001</v>
       </c>
       <c r="V43" t="s">
-        <v>796</v>
+        <v>976</v>
+      </c>
+      <c r="W43" t="s">
+        <v>1058</v>
+      </c>
+      <c r="X43" t="s">
+        <v>794</v>
+      </c>
+      <c r="Z43" t="s">
+        <v>1154</v>
+      </c>
+      <c r="AA43" t="s">
+        <v>794</v>
+      </c>
+      <c r="AC43" t="s">
+        <v>1250</v>
       </c>
     </row>
-    <row r="44" spans="1:22">
+    <row r="44" spans="1:29">
       <c r="A44">
         <v>17734812834914</v>
       </c>
@@ -7926,16 +10050,43 @@
         <v>794</v>
       </c>
       <c r="P44">
-        <v>0</v>
+        <v>90</v>
+      </c>
+      <c r="Q44" t="s">
+        <v>827</v>
+      </c>
+      <c r="R44" t="s">
+        <v>878</v>
+      </c>
+      <c r="S44" t="s">
+        <v>929</v>
       </c>
       <c r="T44" t="s">
-        <v>796</v>
+        <v>981</v>
+      </c>
+      <c r="U44" t="s">
+        <v>1004</v>
       </c>
       <c r="V44" t="s">
-        <v>796</v>
+        <v>976</v>
+      </c>
+      <c r="W44" t="s">
+        <v>1059</v>
+      </c>
+      <c r="X44" t="s">
+        <v>794</v>
+      </c>
+      <c r="Z44" t="s">
+        <v>1155</v>
+      </c>
+      <c r="AA44" t="s">
+        <v>794</v>
+      </c>
+      <c r="AC44" t="s">
+        <v>1251</v>
       </c>
     </row>
-    <row r="45" spans="1:22">
+    <row r="45" spans="1:29">
       <c r="A45">
         <v>17734812835084</v>
       </c>
@@ -7979,16 +10130,43 @@
         <v>794</v>
       </c>
       <c r="P45">
-        <v>0</v>
+        <v>95</v>
+      </c>
+      <c r="Q45" t="s">
+        <v>828</v>
+      </c>
+      <c r="R45" t="s">
+        <v>879</v>
+      </c>
+      <c r="S45" t="s">
+        <v>930</v>
       </c>
       <c r="T45" t="s">
-        <v>796</v>
+        <v>982</v>
+      </c>
+      <c r="U45" t="s">
+        <v>1004</v>
       </c>
       <c r="V45" t="s">
-        <v>796</v>
+        <v>976</v>
+      </c>
+      <c r="W45" t="s">
+        <v>1060</v>
+      </c>
+      <c r="X45" t="s">
+        <v>794</v>
+      </c>
+      <c r="Z45" t="s">
+        <v>1156</v>
+      </c>
+      <c r="AA45" t="s">
+        <v>794</v>
+      </c>
+      <c r="AC45" t="s">
+        <v>1252</v>
       </c>
     </row>
-    <row r="46" spans="1:22">
+    <row r="46" spans="1:29">
       <c r="A46">
         <v>17734812835181</v>
       </c>
@@ -8038,13 +10216,13 @@
         <v>727</v>
       </c>
       <c r="T46" t="s">
-        <v>796</v>
+        <v>976</v>
       </c>
       <c r="V46" t="s">
-        <v>796</v>
+        <v>976</v>
       </c>
     </row>
-    <row r="47" spans="1:22">
+    <row r="47" spans="1:29">
       <c r="A47">
         <v>17734812835242</v>
       </c>
@@ -8094,13 +10272,13 @@
         <v>728</v>
       </c>
       <c r="T47" t="s">
-        <v>796</v>
+        <v>976</v>
       </c>
       <c r="V47" t="s">
-        <v>796</v>
+        <v>976</v>
       </c>
     </row>
-    <row r="48" spans="1:22">
+    <row r="48" spans="1:29">
       <c r="A48">
         <v>17734812835346</v>
       </c>
@@ -8144,16 +10322,43 @@
         <v>794</v>
       </c>
       <c r="P48">
-        <v>0</v>
+        <v>95</v>
+      </c>
+      <c r="Q48" t="s">
+        <v>829</v>
+      </c>
+      <c r="R48" t="s">
+        <v>880</v>
+      </c>
+      <c r="S48" t="s">
+        <v>931</v>
       </c>
       <c r="T48" t="s">
-        <v>796</v>
+        <v>983</v>
+      </c>
+      <c r="U48" t="s">
+        <v>1002</v>
       </c>
       <c r="V48" t="s">
-        <v>796</v>
+        <v>976</v>
+      </c>
+      <c r="W48" t="s">
+        <v>1061</v>
+      </c>
+      <c r="X48" t="s">
+        <v>794</v>
+      </c>
+      <c r="Z48" t="s">
+        <v>1157</v>
+      </c>
+      <c r="AA48" t="s">
+        <v>794</v>
+      </c>
+      <c r="AC48" t="s">
+        <v>1253</v>
       </c>
     </row>
-    <row r="49" spans="1:22">
+    <row r="49" spans="1:29">
       <c r="A49">
         <v>17734812835439</v>
       </c>
@@ -8197,16 +10402,43 @@
         <v>794</v>
       </c>
       <c r="P49">
-        <v>0</v>
+        <v>85</v>
+      </c>
+      <c r="Q49" t="s">
+        <v>830</v>
+      </c>
+      <c r="R49" t="s">
+        <v>881</v>
+      </c>
+      <c r="S49" t="s">
+        <v>932</v>
       </c>
       <c r="T49" t="s">
-        <v>796</v>
+        <v>984</v>
+      </c>
+      <c r="U49" t="s">
+        <v>1002</v>
       </c>
       <c r="V49" t="s">
-        <v>796</v>
+        <v>976</v>
+      </c>
+      <c r="W49" t="s">
+        <v>1062</v>
+      </c>
+      <c r="X49" t="s">
+        <v>794</v>
+      </c>
+      <c r="Z49" t="s">
+        <v>1158</v>
+      </c>
+      <c r="AA49" t="s">
+        <v>794</v>
+      </c>
+      <c r="AC49" t="s">
+        <v>1254</v>
       </c>
     </row>
-    <row r="50" spans="1:22">
+    <row r="50" spans="1:29">
       <c r="A50">
         <v>17734812835561</v>
       </c>
@@ -8250,16 +10482,43 @@
         <v>794</v>
       </c>
       <c r="P50">
-        <v>0</v>
+        <v>85</v>
+      </c>
+      <c r="Q50" t="s">
+        <v>831</v>
+      </c>
+      <c r="R50" t="s">
+        <v>882</v>
+      </c>
+      <c r="S50" t="s">
+        <v>933</v>
       </c>
       <c r="T50" t="s">
-        <v>796</v>
+        <v>985</v>
+      </c>
+      <c r="U50" t="s">
+        <v>1002</v>
       </c>
       <c r="V50" t="s">
-        <v>796</v>
+        <v>976</v>
+      </c>
+      <c r="W50" t="s">
+        <v>1063</v>
+      </c>
+      <c r="X50" t="s">
+        <v>794</v>
+      </c>
+      <c r="Z50" t="s">
+        <v>1159</v>
+      </c>
+      <c r="AA50" t="s">
+        <v>794</v>
+      </c>
+      <c r="AC50" t="s">
+        <v>1255</v>
       </c>
     </row>
-    <row r="51" spans="1:22">
+    <row r="51" spans="1:29">
       <c r="A51">
         <v>17734812835620</v>
       </c>
@@ -8294,7 +10553,7 @@
         <v>563</v>
       </c>
     </row>
-    <row r="52" spans="1:22">
+    <row r="52" spans="1:29">
       <c r="A52">
         <v>17734812835751</v>
       </c>
@@ -8329,7 +10588,7 @@
         <v>564</v>
       </c>
     </row>
-    <row r="53" spans="1:22">
+    <row r="53" spans="1:29">
       <c r="A53">
         <v>17734812835847</v>
       </c>
@@ -8373,16 +10632,43 @@
         <v>794</v>
       </c>
       <c r="P53">
-        <v>0</v>
+        <v>90</v>
+      </c>
+      <c r="Q53" t="s">
+        <v>832</v>
+      </c>
+      <c r="R53" t="s">
+        <v>883</v>
+      </c>
+      <c r="S53" t="s">
+        <v>934</v>
       </c>
       <c r="T53" t="s">
-        <v>796</v>
+        <v>986</v>
+      </c>
+      <c r="U53" t="s">
+        <v>1002</v>
       </c>
       <c r="V53" t="s">
-        <v>796</v>
+        <v>976</v>
+      </c>
+      <c r="W53" t="s">
+        <v>1064</v>
+      </c>
+      <c r="X53" t="s">
+        <v>794</v>
+      </c>
+      <c r="Z53" t="s">
+        <v>1160</v>
+      </c>
+      <c r="AA53" t="s">
+        <v>794</v>
+      </c>
+      <c r="AC53" t="s">
+        <v>1256</v>
       </c>
     </row>
-    <row r="54" spans="1:22">
+    <row r="54" spans="1:29">
       <c r="A54">
         <v>17734812835955</v>
       </c>
@@ -8426,16 +10712,43 @@
         <v>794</v>
       </c>
       <c r="P54">
-        <v>0</v>
+        <v>90</v>
+      </c>
+      <c r="Q54" t="s">
+        <v>833</v>
+      </c>
+      <c r="R54" t="s">
+        <v>884</v>
+      </c>
+      <c r="S54" t="s">
+        <v>935</v>
       </c>
       <c r="T54" t="s">
-        <v>796</v>
+        <v>987</v>
+      </c>
+      <c r="U54" t="s">
+        <v>1003</v>
       </c>
       <c r="V54" t="s">
-        <v>796</v>
+        <v>1020</v>
+      </c>
+      <c r="W54" t="s">
+        <v>1065</v>
+      </c>
+      <c r="X54" t="s">
+        <v>794</v>
+      </c>
+      <c r="Z54" t="s">
+        <v>1161</v>
+      </c>
+      <c r="AA54" t="s">
+        <v>794</v>
+      </c>
+      <c r="AC54" t="s">
+        <v>1257</v>
       </c>
     </row>
-    <row r="55" spans="1:22">
+    <row r="55" spans="1:29">
       <c r="A55">
         <v>17734812836097</v>
       </c>
@@ -8479,16 +10792,43 @@
         <v>794</v>
       </c>
       <c r="P55">
-        <v>0</v>
+        <v>95</v>
+      </c>
+      <c r="Q55" t="s">
+        <v>834</v>
+      </c>
+      <c r="R55" t="s">
+        <v>885</v>
+      </c>
+      <c r="S55" t="s">
+        <v>936</v>
       </c>
       <c r="T55" t="s">
-        <v>796</v>
+        <v>988</v>
+      </c>
+      <c r="U55" t="s">
+        <v>1004</v>
       </c>
       <c r="V55" t="s">
-        <v>796</v>
+        <v>1021</v>
+      </c>
+      <c r="W55" t="s">
+        <v>1066</v>
+      </c>
+      <c r="X55" t="s">
+        <v>794</v>
+      </c>
+      <c r="Z55" t="s">
+        <v>1162</v>
+      </c>
+      <c r="AA55" t="s">
+        <v>794</v>
+      </c>
+      <c r="AC55" t="s">
+        <v>1258</v>
       </c>
     </row>
-    <row r="56" spans="1:22">
+    <row r="56" spans="1:29">
       <c r="A56">
         <v>17734812836104</v>
       </c>
@@ -8532,16 +10872,43 @@
         <v>794</v>
       </c>
       <c r="P56">
-        <v>0</v>
+        <v>90</v>
+      </c>
+      <c r="Q56" t="s">
+        <v>835</v>
+      </c>
+      <c r="R56" t="s">
+        <v>886</v>
+      </c>
+      <c r="S56" t="s">
+        <v>937</v>
       </c>
       <c r="T56" t="s">
-        <v>796</v>
+        <v>989</v>
+      </c>
+      <c r="U56" t="s">
+        <v>1004</v>
       </c>
       <c r="V56" t="s">
-        <v>796</v>
+        <v>1022</v>
+      </c>
+      <c r="W56" t="s">
+        <v>1067</v>
+      </c>
+      <c r="X56" t="s">
+        <v>794</v>
+      </c>
+      <c r="Z56" t="s">
+        <v>1163</v>
+      </c>
+      <c r="AA56" t="s">
+        <v>794</v>
+      </c>
+      <c r="AC56" t="s">
+        <v>1259</v>
       </c>
     </row>
-    <row r="57" spans="1:22">
+    <row r="57" spans="1:29">
       <c r="A57">
         <v>17734812836227</v>
       </c>
@@ -8576,7 +10943,7 @@
         <v>569</v>
       </c>
     </row>
-    <row r="58" spans="1:22">
+    <row r="58" spans="1:29">
       <c r="A58">
         <v>17734812836306</v>
       </c>
@@ -8620,16 +10987,43 @@
         <v>794</v>
       </c>
       <c r="P58">
-        <v>0</v>
+        <v>90</v>
+      </c>
+      <c r="Q58" t="s">
+        <v>836</v>
+      </c>
+      <c r="R58" t="s">
+        <v>887</v>
+      </c>
+      <c r="S58" t="s">
+        <v>938</v>
       </c>
       <c r="T58" t="s">
-        <v>796</v>
+        <v>990</v>
+      </c>
+      <c r="U58" t="s">
+        <v>1004</v>
       </c>
       <c r="V58" t="s">
-        <v>796</v>
+        <v>976</v>
+      </c>
+      <c r="W58" t="s">
+        <v>1068</v>
+      </c>
+      <c r="X58" t="s">
+        <v>794</v>
+      </c>
+      <c r="Z58" t="s">
+        <v>1164</v>
+      </c>
+      <c r="AA58" t="s">
+        <v>794</v>
+      </c>
+      <c r="AC58" t="s">
+        <v>1260</v>
       </c>
     </row>
-    <row r="59" spans="1:22">
+    <row r="59" spans="1:29">
       <c r="A59">
         <v>17734812836492</v>
       </c>
@@ -8664,7 +11058,7 @@
         <v>571</v>
       </c>
     </row>
-    <row r="60" spans="1:22">
+    <row r="60" spans="1:29">
       <c r="A60">
         <v>17734812836572</v>
       </c>
@@ -8699,7 +11093,7 @@
         <v>572</v>
       </c>
     </row>
-    <row r="61" spans="1:22">
+    <row r="61" spans="1:29">
       <c r="A61">
         <v>17734812836643</v>
       </c>
@@ -8743,16 +11137,43 @@
         <v>794</v>
       </c>
       <c r="P61">
-        <v>0</v>
+        <v>88</v>
+      </c>
+      <c r="Q61" t="s">
+        <v>837</v>
+      </c>
+      <c r="R61" t="s">
+        <v>888</v>
+      </c>
+      <c r="S61" t="s">
+        <v>939</v>
       </c>
       <c r="T61" t="s">
-        <v>796</v>
+        <v>991</v>
+      </c>
+      <c r="U61" t="s">
+        <v>1002</v>
       </c>
       <c r="V61" t="s">
-        <v>796</v>
+        <v>1023</v>
+      </c>
+      <c r="W61" t="s">
+        <v>1069</v>
+      </c>
+      <c r="X61" t="s">
+        <v>794</v>
+      </c>
+      <c r="Z61" t="s">
+        <v>1165</v>
+      </c>
+      <c r="AA61" t="s">
+        <v>794</v>
+      </c>
+      <c r="AC61" t="s">
+        <v>1261</v>
       </c>
     </row>
-    <row r="62" spans="1:22">
+    <row r="62" spans="1:29">
       <c r="A62">
         <v>17734812836739</v>
       </c>
@@ -8796,16 +11217,43 @@
         <v>794</v>
       </c>
       <c r="P62">
-        <v>0</v>
+        <v>90</v>
+      </c>
+      <c r="Q62" t="s">
+        <v>838</v>
+      </c>
+      <c r="R62" t="s">
+        <v>889</v>
+      </c>
+      <c r="S62" t="s">
+        <v>940</v>
       </c>
       <c r="T62" t="s">
-        <v>796</v>
+        <v>992</v>
+      </c>
+      <c r="U62" t="s">
+        <v>1002</v>
       </c>
       <c r="V62" t="s">
-        <v>796</v>
+        <v>1024</v>
+      </c>
+      <c r="W62" t="s">
+        <v>1070</v>
+      </c>
+      <c r="X62" t="s">
+        <v>794</v>
+      </c>
+      <c r="Z62" t="s">
+        <v>1166</v>
+      </c>
+      <c r="AA62" t="s">
+        <v>794</v>
+      </c>
+      <c r="AC62" t="s">
+        <v>1262</v>
       </c>
     </row>
-    <row r="63" spans="1:22">
+    <row r="63" spans="1:29">
       <c r="A63">
         <v>17734812836819</v>
       </c>
@@ -8849,16 +11297,43 @@
         <v>794</v>
       </c>
       <c r="P63">
-        <v>0</v>
+        <v>90</v>
+      </c>
+      <c r="Q63" t="s">
+        <v>839</v>
+      </c>
+      <c r="R63" t="s">
+        <v>890</v>
+      </c>
+      <c r="S63" t="s">
+        <v>941</v>
       </c>
       <c r="T63" t="s">
-        <v>796</v>
+        <v>993</v>
+      </c>
+      <c r="U63" t="s">
+        <v>1004</v>
       </c>
       <c r="V63" t="s">
-        <v>796</v>
+        <v>1025</v>
+      </c>
+      <c r="W63" t="s">
+        <v>1071</v>
+      </c>
+      <c r="X63" t="s">
+        <v>794</v>
+      </c>
+      <c r="Z63" t="s">
+        <v>1167</v>
+      </c>
+      <c r="AA63" t="s">
+        <v>794</v>
+      </c>
+      <c r="AC63" t="s">
+        <v>1263</v>
       </c>
     </row>
-    <row r="64" spans="1:22">
+    <row r="64" spans="1:29">
       <c r="A64">
         <v>17734812836970</v>
       </c>
@@ -8902,13 +11377,40 @@
         <v>794</v>
       </c>
       <c r="P64">
-        <v>0</v>
+        <v>92</v>
+      </c>
+      <c r="Q64" t="s">
+        <v>840</v>
+      </c>
+      <c r="R64" t="s">
+        <v>891</v>
+      </c>
+      <c r="S64" t="s">
+        <v>942</v>
       </c>
       <c r="T64" t="s">
-        <v>796</v>
+        <v>994</v>
+      </c>
+      <c r="U64" t="s">
+        <v>1004</v>
       </c>
       <c r="V64" t="s">
-        <v>796</v>
+        <v>976</v>
+      </c>
+      <c r="W64" t="s">
+        <v>1072</v>
+      </c>
+      <c r="X64" t="s">
+        <v>794</v>
+      </c>
+      <c r="Z64" t="s">
+        <v>1168</v>
+      </c>
+      <c r="AA64" t="s">
+        <v>794</v>
+      </c>
+      <c r="AC64" t="s">
+        <v>1264</v>
       </c>
     </row>
     <row r="65" spans="1:33">
@@ -8955,13 +11457,40 @@
         <v>794</v>
       </c>
       <c r="P65">
-        <v>0</v>
+        <v>85</v>
+      </c>
+      <c r="Q65" t="s">
+        <v>841</v>
+      </c>
+      <c r="R65" t="s">
+        <v>892</v>
+      </c>
+      <c r="S65" t="s">
+        <v>943</v>
       </c>
       <c r="T65" t="s">
-        <v>796</v>
+        <v>995</v>
+      </c>
+      <c r="U65" t="s">
+        <v>1004</v>
       </c>
       <c r="V65" t="s">
-        <v>796</v>
+        <v>976</v>
+      </c>
+      <c r="W65" t="s">
+        <v>1073</v>
+      </c>
+      <c r="X65" t="s">
+        <v>794</v>
+      </c>
+      <c r="Z65" t="s">
+        <v>1169</v>
+      </c>
+      <c r="AA65" t="s">
+        <v>794</v>
+      </c>
+      <c r="AC65" t="s">
+        <v>1265</v>
       </c>
     </row>
     <row r="66" spans="1:33">
@@ -9008,13 +11537,40 @@
         <v>794</v>
       </c>
       <c r="P66">
-        <v>0</v>
+        <v>92</v>
+      </c>
+      <c r="Q66" t="s">
+        <v>842</v>
+      </c>
+      <c r="R66" t="s">
+        <v>893</v>
+      </c>
+      <c r="S66" t="s">
+        <v>944</v>
       </c>
       <c r="T66" t="s">
-        <v>796</v>
+        <v>996</v>
+      </c>
+      <c r="U66" t="s">
+        <v>1002</v>
       </c>
       <c r="V66" t="s">
-        <v>796</v>
+        <v>976</v>
+      </c>
+      <c r="W66" t="s">
+        <v>1074</v>
+      </c>
+      <c r="X66" t="s">
+        <v>794</v>
+      </c>
+      <c r="Z66" t="s">
+        <v>1170</v>
+      </c>
+      <c r="AA66" t="s">
+        <v>794</v>
+      </c>
+      <c r="AC66" t="s">
+        <v>1266</v>
       </c>
     </row>
     <row r="67" spans="1:33">
@@ -9201,13 +11757,40 @@
         <v>794</v>
       </c>
       <c r="P71">
-        <v>0</v>
+        <v>88</v>
+      </c>
+      <c r="Q71" t="s">
+        <v>843</v>
+      </c>
+      <c r="R71" t="s">
+        <v>894</v>
+      </c>
+      <c r="S71" t="s">
+        <v>945</v>
       </c>
       <c r="T71" t="s">
-        <v>796</v>
+        <v>997</v>
+      </c>
+      <c r="U71" t="s">
+        <v>1004</v>
       </c>
       <c r="V71" t="s">
-        <v>796</v>
+        <v>976</v>
+      </c>
+      <c r="W71" t="s">
+        <v>1075</v>
+      </c>
+      <c r="X71" t="s">
+        <v>794</v>
+      </c>
+      <c r="Z71" t="s">
+        <v>1171</v>
+      </c>
+      <c r="AA71" t="s">
+        <v>794</v>
+      </c>
+      <c r="AC71" t="s">
+        <v>1267</v>
       </c>
     </row>
     <row r="72" spans="1:33">
@@ -9254,13 +11837,40 @@
         <v>794</v>
       </c>
       <c r="P72">
-        <v>0</v>
+        <v>92</v>
+      </c>
+      <c r="Q72" t="s">
+        <v>844</v>
+      </c>
+      <c r="R72" t="s">
+        <v>895</v>
+      </c>
+      <c r="S72" t="s">
+        <v>946</v>
       </c>
       <c r="T72" t="s">
-        <v>796</v>
+        <v>998</v>
+      </c>
+      <c r="U72" t="s">
+        <v>1004</v>
       </c>
       <c r="V72" t="s">
-        <v>796</v>
+        <v>976</v>
+      </c>
+      <c r="W72" t="s">
+        <v>1076</v>
+      </c>
+      <c r="X72" t="s">
+        <v>794</v>
+      </c>
+      <c r="Z72" t="s">
+        <v>1172</v>
+      </c>
+      <c r="AA72" t="s">
+        <v>794</v>
+      </c>
+      <c r="AC72" t="s">
+        <v>1268</v>
       </c>
     </row>
     <row r="73" spans="1:33">
@@ -9307,13 +11917,40 @@
         <v>794</v>
       </c>
       <c r="P73">
-        <v>0</v>
+        <v>90</v>
+      </c>
+      <c r="Q73" t="s">
+        <v>845</v>
+      </c>
+      <c r="R73" t="s">
+        <v>896</v>
+      </c>
+      <c r="S73" t="s">
+        <v>947</v>
       </c>
       <c r="T73" t="s">
-        <v>796</v>
+        <v>999</v>
+      </c>
+      <c r="U73" t="s">
+        <v>1004</v>
       </c>
       <c r="V73" t="s">
-        <v>796</v>
+        <v>1026</v>
+      </c>
+      <c r="W73" t="s">
+        <v>1077</v>
+      </c>
+      <c r="X73" t="s">
+        <v>794</v>
+      </c>
+      <c r="Z73" t="s">
+        <v>1173</v>
+      </c>
+      <c r="AA73" t="s">
+        <v>794</v>
+      </c>
+      <c r="AC73" t="s">
+        <v>1269</v>
       </c>
     </row>
     <row r="74" spans="1:33">
@@ -9389,13 +12026,40 @@
         <v>794</v>
       </c>
       <c r="P75">
-        <v>0</v>
+        <v>92</v>
+      </c>
+      <c r="Q75" t="s">
+        <v>846</v>
+      </c>
+      <c r="R75" t="s">
+        <v>897</v>
+      </c>
+      <c r="S75" t="s">
+        <v>948</v>
       </c>
       <c r="T75" t="s">
-        <v>796</v>
+        <v>1000</v>
+      </c>
+      <c r="U75" t="s">
+        <v>1001</v>
       </c>
       <c r="V75" t="s">
-        <v>796</v>
+        <v>1027</v>
+      </c>
+      <c r="W75" t="s">
+        <v>1078</v>
+      </c>
+      <c r="X75" t="s">
+        <v>794</v>
+      </c>
+      <c r="Z75" t="s">
+        <v>1174</v>
+      </c>
+      <c r="AA75" t="s">
+        <v>794</v>
+      </c>
+      <c r="AC75" t="s">
+        <v>1270</v>
       </c>
     </row>
     <row r="76" spans="1:33">
@@ -9439,10 +12103,19 @@
         <v>0</v>
       </c>
       <c r="T76" t="s">
-        <v>796</v>
+        <v>976</v>
       </c>
       <c r="V76" t="s">
-        <v>796</v>
+        <v>976</v>
+      </c>
+      <c r="W76" t="s">
+        <v>1079</v>
+      </c>
+      <c r="X76" t="s">
+        <v>794</v>
+      </c>
+      <c r="Z76" t="s">
+        <v>1175</v>
       </c>
     </row>
     <row r="77" spans="1:33">
@@ -9486,10 +12159,19 @@
         <v>0</v>
       </c>
       <c r="T77" t="s">
-        <v>796</v>
+        <v>976</v>
       </c>
       <c r="V77" t="s">
-        <v>796</v>
+        <v>976</v>
+      </c>
+      <c r="W77" t="s">
+        <v>1080</v>
+      </c>
+      <c r="X77" t="s">
+        <v>794</v>
+      </c>
+      <c r="Z77" t="s">
+        <v>1176</v>
       </c>
     </row>
     <row r="78" spans="1:33">
@@ -9533,10 +12215,19 @@
         <v>0</v>
       </c>
       <c r="T78" t="s">
-        <v>796</v>
+        <v>976</v>
       </c>
       <c r="V78" t="s">
-        <v>796</v>
+        <v>976</v>
+      </c>
+      <c r="W78" t="s">
+        <v>1081</v>
+      </c>
+      <c r="X78" t="s">
+        <v>794</v>
+      </c>
+      <c r="Z78" t="s">
+        <v>1177</v>
       </c>
     </row>
     <row r="79" spans="1:33">
@@ -9580,10 +12271,19 @@
         <v>0</v>
       </c>
       <c r="T79" t="s">
-        <v>796</v>
+        <v>976</v>
       </c>
       <c r="V79" t="s">
-        <v>796</v>
+        <v>976</v>
+      </c>
+      <c r="W79" t="s">
+        <v>1082</v>
+      </c>
+      <c r="X79" t="s">
+        <v>794</v>
+      </c>
+      <c r="Z79" t="s">
+        <v>1178</v>
       </c>
     </row>
     <row r="80" spans="1:33">
@@ -9627,19 +12327,28 @@
         <v>0</v>
       </c>
       <c r="T80" t="s">
-        <v>796</v>
+        <v>976</v>
       </c>
       <c r="V80" t="s">
-        <v>796</v>
+        <v>976</v>
+      </c>
+      <c r="W80" t="s">
+        <v>1083</v>
+      </c>
+      <c r="X80" t="s">
+        <v>794</v>
+      </c>
+      <c r="Z80" t="s">
+        <v>1179</v>
       </c>
       <c r="AD80" t="s">
-        <v>815</v>
+        <v>1271</v>
       </c>
       <c r="AE80" t="s">
-        <v>816</v>
+        <v>1272</v>
       </c>
       <c r="AG80" t="s">
-        <v>796</v>
+        <v>976</v>
       </c>
     </row>
     <row r="81" spans="1:33">
@@ -9683,19 +12392,28 @@
         <v>0</v>
       </c>
       <c r="T81" t="s">
-        <v>796</v>
+        <v>976</v>
       </c>
       <c r="V81" t="s">
-        <v>796</v>
+        <v>976</v>
+      </c>
+      <c r="W81" t="s">
+        <v>1084</v>
+      </c>
+      <c r="X81" t="s">
+        <v>794</v>
+      </c>
+      <c r="Z81" t="s">
+        <v>1180</v>
       </c>
       <c r="AD81" t="s">
-        <v>815</v>
+        <v>1271</v>
       </c>
       <c r="AE81" t="s">
-        <v>816</v>
+        <v>1272</v>
       </c>
       <c r="AG81" t="s">
-        <v>796</v>
+        <v>976</v>
       </c>
     </row>
     <row r="82" spans="1:33">
@@ -9739,19 +12457,28 @@
         <v>0</v>
       </c>
       <c r="T82" t="s">
-        <v>796</v>
+        <v>976</v>
       </c>
       <c r="V82" t="s">
-        <v>796</v>
+        <v>976</v>
+      </c>
+      <c r="W82" t="s">
+        <v>1085</v>
+      </c>
+      <c r="X82" t="s">
+        <v>794</v>
+      </c>
+      <c r="Z82" t="s">
+        <v>1181</v>
       </c>
       <c r="AD82" t="s">
-        <v>815</v>
+        <v>1271</v>
       </c>
       <c r="AE82" t="s">
-        <v>816</v>
+        <v>1272</v>
       </c>
       <c r="AG82" t="s">
-        <v>796</v>
+        <v>976</v>
       </c>
     </row>
     <row r="83" spans="1:33">
@@ -9795,19 +12522,28 @@
         <v>0</v>
       </c>
       <c r="T83" t="s">
-        <v>796</v>
+        <v>976</v>
       </c>
       <c r="V83" t="s">
-        <v>796</v>
+        <v>976</v>
+      </c>
+      <c r="W83" t="s">
+        <v>1086</v>
+      </c>
+      <c r="X83" t="s">
+        <v>794</v>
+      </c>
+      <c r="Z83" t="s">
+        <v>1182</v>
       </c>
       <c r="AD83" t="s">
-        <v>815</v>
+        <v>1271</v>
       </c>
       <c r="AE83" t="s">
-        <v>816</v>
+        <v>1272</v>
       </c>
       <c r="AG83" t="s">
-        <v>796</v>
+        <v>976</v>
       </c>
     </row>
     <row r="84" spans="1:33">
@@ -9851,19 +12587,28 @@
         <v>0</v>
       </c>
       <c r="T84" t="s">
-        <v>796</v>
+        <v>976</v>
       </c>
       <c r="V84" t="s">
-        <v>796</v>
+        <v>976</v>
+      </c>
+      <c r="W84" t="s">
+        <v>1087</v>
+      </c>
+      <c r="X84" t="s">
+        <v>794</v>
+      </c>
+      <c r="Z84" t="s">
+        <v>1183</v>
       </c>
       <c r="AD84" t="s">
-        <v>815</v>
+        <v>1271</v>
       </c>
       <c r="AE84" t="s">
-        <v>816</v>
+        <v>1272</v>
       </c>
       <c r="AG84" t="s">
-        <v>796</v>
+        <v>976</v>
       </c>
     </row>
     <row r="85" spans="1:33">
@@ -9907,19 +12652,28 @@
         <v>0</v>
       </c>
       <c r="T85" t="s">
-        <v>796</v>
+        <v>976</v>
       </c>
       <c r="V85" t="s">
-        <v>796</v>
+        <v>976</v>
+      </c>
+      <c r="W85" t="s">
+        <v>1088</v>
+      </c>
+      <c r="X85" t="s">
+        <v>794</v>
+      </c>
+      <c r="Z85" t="s">
+        <v>1184</v>
       </c>
       <c r="AD85" t="s">
-        <v>815</v>
+        <v>1271</v>
       </c>
       <c r="AE85" t="s">
-        <v>816</v>
+        <v>1272</v>
       </c>
       <c r="AG85" t="s">
-        <v>796</v>
+        <v>976</v>
       </c>
     </row>
     <row r="86" spans="1:33">
@@ -9963,19 +12717,28 @@
         <v>0</v>
       </c>
       <c r="T86" t="s">
-        <v>796</v>
+        <v>976</v>
       </c>
       <c r="V86" t="s">
-        <v>796</v>
+        <v>976</v>
+      </c>
+      <c r="W86" t="s">
+        <v>1089</v>
+      </c>
+      <c r="X86" t="s">
+        <v>794</v>
+      </c>
+      <c r="Z86" t="s">
+        <v>1185</v>
       </c>
       <c r="AD86" t="s">
-        <v>815</v>
+        <v>1271</v>
       </c>
       <c r="AE86" t="s">
-        <v>816</v>
+        <v>1272</v>
       </c>
       <c r="AG86" t="s">
-        <v>796</v>
+        <v>976</v>
       </c>
     </row>
     <row r="87" spans="1:33">
@@ -10019,19 +12782,28 @@
         <v>0</v>
       </c>
       <c r="T87" t="s">
-        <v>796</v>
+        <v>976</v>
       </c>
       <c r="V87" t="s">
-        <v>796</v>
+        <v>976</v>
+      </c>
+      <c r="W87" t="s">
+        <v>1090</v>
+      </c>
+      <c r="X87" t="s">
+        <v>794</v>
+      </c>
+      <c r="Z87" t="s">
+        <v>1186</v>
       </c>
       <c r="AD87" t="s">
-        <v>815</v>
+        <v>1271</v>
       </c>
       <c r="AE87" t="s">
-        <v>816</v>
+        <v>1272</v>
       </c>
       <c r="AG87" t="s">
-        <v>796</v>
+        <v>976</v>
       </c>
     </row>
     <row r="88" spans="1:33">
@@ -10075,19 +12847,28 @@
         <v>0</v>
       </c>
       <c r="T88" t="s">
-        <v>796</v>
+        <v>976</v>
       </c>
       <c r="V88" t="s">
-        <v>796</v>
+        <v>976</v>
+      </c>
+      <c r="W88" t="s">
+        <v>1091</v>
+      </c>
+      <c r="X88" t="s">
+        <v>794</v>
+      </c>
+      <c r="Z88" t="s">
+        <v>1187</v>
       </c>
       <c r="AD88" t="s">
-        <v>815</v>
+        <v>1271</v>
       </c>
       <c r="AE88" t="s">
-        <v>816</v>
+        <v>1272</v>
       </c>
       <c r="AG88" t="s">
-        <v>796</v>
+        <v>976</v>
       </c>
     </row>
     <row r="89" spans="1:33">
@@ -10131,19 +12912,28 @@
         <v>0</v>
       </c>
       <c r="T89" t="s">
-        <v>796</v>
+        <v>976</v>
       </c>
       <c r="V89" t="s">
-        <v>796</v>
+        <v>976</v>
+      </c>
+      <c r="W89" t="s">
+        <v>1092</v>
+      </c>
+      <c r="X89" t="s">
+        <v>794</v>
+      </c>
+      <c r="Z89" t="s">
+        <v>1188</v>
       </c>
       <c r="AD89" t="s">
-        <v>815</v>
+        <v>1271</v>
       </c>
       <c r="AE89" t="s">
-        <v>816</v>
+        <v>1272</v>
       </c>
       <c r="AG89" t="s">
-        <v>796</v>
+        <v>976</v>
       </c>
     </row>
     <row r="90" spans="1:33">
@@ -10187,19 +12977,28 @@
         <v>0</v>
       </c>
       <c r="T90" t="s">
-        <v>796</v>
+        <v>976</v>
       </c>
       <c r="V90" t="s">
-        <v>796</v>
+        <v>976</v>
+      </c>
+      <c r="W90" t="s">
+        <v>1093</v>
+      </c>
+      <c r="X90" t="s">
+        <v>794</v>
+      </c>
+      <c r="Z90" t="s">
+        <v>1189</v>
       </c>
       <c r="AD90" t="s">
-        <v>815</v>
+        <v>1271</v>
       </c>
       <c r="AE90" t="s">
-        <v>816</v>
+        <v>1272</v>
       </c>
       <c r="AG90" t="s">
-        <v>796</v>
+        <v>976</v>
       </c>
     </row>
     <row r="91" spans="1:33">
@@ -10243,19 +13042,28 @@
         <v>0</v>
       </c>
       <c r="T91" t="s">
-        <v>796</v>
+        <v>976</v>
       </c>
       <c r="V91" t="s">
-        <v>796</v>
+        <v>976</v>
+      </c>
+      <c r="W91" t="s">
+        <v>1094</v>
+      </c>
+      <c r="X91" t="s">
+        <v>794</v>
+      </c>
+      <c r="Z91" t="s">
+        <v>1190</v>
       </c>
       <c r="AD91" t="s">
-        <v>815</v>
+        <v>1271</v>
       </c>
       <c r="AE91" t="s">
-        <v>816</v>
+        <v>1272</v>
       </c>
       <c r="AG91" t="s">
-        <v>796</v>
+        <v>976</v>
       </c>
     </row>
     <row r="92" spans="1:33">
@@ -10299,19 +13107,28 @@
         <v>0</v>
       </c>
       <c r="T92" t="s">
-        <v>796</v>
+        <v>976</v>
       </c>
       <c r="V92" t="s">
-        <v>796</v>
+        <v>976</v>
+      </c>
+      <c r="W92" t="s">
+        <v>1095</v>
+      </c>
+      <c r="X92" t="s">
+        <v>794</v>
+      </c>
+      <c r="Z92" t="s">
+        <v>1191</v>
       </c>
       <c r="AD92" t="s">
-        <v>815</v>
+        <v>1271</v>
       </c>
       <c r="AE92" t="s">
-        <v>816</v>
+        <v>1272</v>
       </c>
       <c r="AG92" t="s">
-        <v>796</v>
+        <v>976</v>
       </c>
     </row>
     <row r="93" spans="1:33">
@@ -10358,19 +13175,19 @@
         <v>763</v>
       </c>
       <c r="T93" t="s">
-        <v>796</v>
+        <v>976</v>
       </c>
       <c r="V93" t="s">
-        <v>796</v>
+        <v>976</v>
       </c>
       <c r="AD93" t="s">
-        <v>815</v>
+        <v>1271</v>
       </c>
       <c r="AE93" t="s">
-        <v>816</v>
+        <v>1272</v>
       </c>
       <c r="AG93" t="s">
-        <v>796</v>
+        <v>976</v>
       </c>
     </row>
     <row r="94" spans="1:33">
@@ -10414,19 +13231,28 @@
         <v>0</v>
       </c>
       <c r="T94" t="s">
-        <v>796</v>
+        <v>976</v>
       </c>
       <c r="V94" t="s">
-        <v>796</v>
+        <v>976</v>
+      </c>
+      <c r="W94" t="s">
+        <v>1096</v>
+      </c>
+      <c r="X94" t="s">
+        <v>794</v>
+      </c>
+      <c r="Z94" t="s">
+        <v>1192</v>
       </c>
       <c r="AD94" t="s">
-        <v>815</v>
+        <v>1271</v>
       </c>
       <c r="AE94" t="s">
-        <v>816</v>
+        <v>1272</v>
       </c>
       <c r="AG94" t="s">
-        <v>796</v>
+        <v>976</v>
       </c>
     </row>
     <row r="95" spans="1:33">
@@ -10470,19 +13296,28 @@
         <v>0</v>
       </c>
       <c r="T95" t="s">
-        <v>796</v>
+        <v>976</v>
       </c>
       <c r="V95" t="s">
-        <v>796</v>
+        <v>976</v>
+      </c>
+      <c r="W95" t="s">
+        <v>1097</v>
+      </c>
+      <c r="X95" t="s">
+        <v>794</v>
+      </c>
+      <c r="Z95" t="s">
+        <v>1193</v>
       </c>
       <c r="AD95" t="s">
-        <v>815</v>
+        <v>1271</v>
       </c>
       <c r="AE95" t="s">
-        <v>816</v>
+        <v>1272</v>
       </c>
       <c r="AG95" t="s">
-        <v>796</v>
+        <v>976</v>
       </c>
     </row>
     <row r="96" spans="1:33">
@@ -10526,19 +13361,28 @@
         <v>0</v>
       </c>
       <c r="T96" t="s">
-        <v>796</v>
+        <v>976</v>
       </c>
       <c r="V96" t="s">
-        <v>796</v>
+        <v>976</v>
+      </c>
+      <c r="W96" t="s">
+        <v>1098</v>
+      </c>
+      <c r="X96" t="s">
+        <v>794</v>
+      </c>
+      <c r="Z96" t="s">
+        <v>1194</v>
       </c>
       <c r="AD96" t="s">
-        <v>815</v>
+        <v>1271</v>
       </c>
       <c r="AE96" t="s">
-        <v>816</v>
+        <v>1272</v>
       </c>
       <c r="AG96" t="s">
-        <v>796</v>
+        <v>976</v>
       </c>
     </row>
     <row r="97" spans="1:33">
@@ -10582,19 +13426,28 @@
         <v>0</v>
       </c>
       <c r="T97" t="s">
-        <v>796</v>
+        <v>976</v>
       </c>
       <c r="V97" t="s">
-        <v>796</v>
+        <v>976</v>
+      </c>
+      <c r="W97" t="s">
+        <v>1099</v>
+      </c>
+      <c r="X97" t="s">
+        <v>794</v>
+      </c>
+      <c r="Z97" t="s">
+        <v>1195</v>
       </c>
       <c r="AD97" t="s">
-        <v>815</v>
+        <v>1271</v>
       </c>
       <c r="AE97" t="s">
-        <v>816</v>
+        <v>1272</v>
       </c>
       <c r="AG97" t="s">
-        <v>796</v>
+        <v>976</v>
       </c>
     </row>
     <row r="98" spans="1:33">
@@ -10641,19 +13494,19 @@
         <v>768</v>
       </c>
       <c r="T98" t="s">
-        <v>796</v>
+        <v>976</v>
       </c>
       <c r="V98" t="s">
-        <v>796</v>
+        <v>976</v>
       </c>
       <c r="AD98" t="s">
-        <v>815</v>
+        <v>1271</v>
       </c>
       <c r="AE98" t="s">
-        <v>816</v>
+        <v>1272</v>
       </c>
       <c r="AG98" t="s">
-        <v>796</v>
+        <v>976</v>
       </c>
     </row>
     <row r="99" spans="1:33">
@@ -10697,19 +13550,28 @@
         <v>0</v>
       </c>
       <c r="T99" t="s">
-        <v>796</v>
+        <v>976</v>
       </c>
       <c r="V99" t="s">
-        <v>796</v>
+        <v>976</v>
+      </c>
+      <c r="W99" t="s">
+        <v>1100</v>
+      </c>
+      <c r="X99" t="s">
+        <v>794</v>
+      </c>
+      <c r="Z99" t="s">
+        <v>1196</v>
       </c>
       <c r="AD99" t="s">
-        <v>815</v>
+        <v>1271</v>
       </c>
       <c r="AE99" t="s">
-        <v>816</v>
+        <v>1272</v>
       </c>
       <c r="AG99" t="s">
-        <v>796</v>
+        <v>976</v>
       </c>
     </row>
     <row r="100" spans="1:33">
@@ -10753,19 +13615,28 @@
         <v>0</v>
       </c>
       <c r="T100" t="s">
-        <v>796</v>
+        <v>976</v>
       </c>
       <c r="V100" t="s">
-        <v>796</v>
+        <v>976</v>
+      </c>
+      <c r="W100" t="s">
+        <v>1101</v>
+      </c>
+      <c r="X100" t="s">
+        <v>794</v>
+      </c>
+      <c r="Z100" t="s">
+        <v>1197</v>
       </c>
       <c r="AD100" t="s">
-        <v>815</v>
+        <v>1271</v>
       </c>
       <c r="AE100" t="s">
-        <v>816</v>
+        <v>1272</v>
       </c>
       <c r="AG100" t="s">
-        <v>796</v>
+        <v>976</v>
       </c>
     </row>
     <row r="101" spans="1:33">
@@ -10809,19 +13680,28 @@
         <v>0</v>
       </c>
       <c r="T101" t="s">
-        <v>796</v>
+        <v>976</v>
       </c>
       <c r="V101" t="s">
-        <v>796</v>
+        <v>976</v>
+      </c>
+      <c r="W101" t="s">
+        <v>1102</v>
+      </c>
+      <c r="X101" t="s">
+        <v>794</v>
+      </c>
+      <c r="Z101" t="s">
+        <v>1198</v>
       </c>
       <c r="AD101" t="s">
-        <v>815</v>
+        <v>1271</v>
       </c>
       <c r="AE101" t="s">
-        <v>816</v>
+        <v>1272</v>
       </c>
       <c r="AG101" t="s">
-        <v>796</v>
+        <v>976</v>
       </c>
     </row>
     <row r="102" spans="1:33">
@@ -10865,19 +13745,28 @@
         <v>0</v>
       </c>
       <c r="T102" t="s">
-        <v>796</v>
+        <v>976</v>
       </c>
       <c r="V102" t="s">
-        <v>796</v>
+        <v>976</v>
+      </c>
+      <c r="W102" t="s">
+        <v>1103</v>
+      </c>
+      <c r="X102" t="s">
+        <v>794</v>
+      </c>
+      <c r="Z102" t="s">
+        <v>1199</v>
       </c>
       <c r="AD102" t="s">
-        <v>815</v>
+        <v>1271</v>
       </c>
       <c r="AE102" t="s">
-        <v>816</v>
+        <v>1272</v>
       </c>
       <c r="AG102" t="s">
-        <v>796</v>
+        <v>976</v>
       </c>
     </row>
     <row r="103" spans="1:33">
@@ -10921,19 +13810,28 @@
         <v>0</v>
       </c>
       <c r="T103" t="s">
-        <v>796</v>
+        <v>976</v>
       </c>
       <c r="V103" t="s">
-        <v>796</v>
+        <v>976</v>
+      </c>
+      <c r="W103" t="s">
+        <v>1104</v>
+      </c>
+      <c r="X103" t="s">
+        <v>794</v>
+      </c>
+      <c r="Z103" t="s">
+        <v>1200</v>
       </c>
       <c r="AD103" t="s">
-        <v>815</v>
+        <v>1271</v>
       </c>
       <c r="AE103" t="s">
-        <v>816</v>
+        <v>1272</v>
       </c>
       <c r="AG103" t="s">
-        <v>796</v>
+        <v>976</v>
       </c>
     </row>
     <row r="104" spans="1:33">
@@ -10977,19 +13875,28 @@
         <v>0</v>
       </c>
       <c r="T104" t="s">
-        <v>796</v>
+        <v>976</v>
       </c>
       <c r="V104" t="s">
-        <v>796</v>
+        <v>976</v>
+      </c>
+      <c r="W104" t="s">
+        <v>1105</v>
+      </c>
+      <c r="X104" t="s">
+        <v>794</v>
+      </c>
+      <c r="Z104" t="s">
+        <v>1201</v>
       </c>
       <c r="AD104" t="s">
-        <v>815</v>
+        <v>1271</v>
       </c>
       <c r="AE104" t="s">
-        <v>816</v>
+        <v>1272</v>
       </c>
       <c r="AG104" t="s">
-        <v>796</v>
+        <v>976</v>
       </c>
     </row>
     <row r="105" spans="1:33">
@@ -11033,19 +13940,28 @@
         <v>0</v>
       </c>
       <c r="T105" t="s">
-        <v>796</v>
+        <v>976</v>
       </c>
       <c r="V105" t="s">
-        <v>796</v>
+        <v>976</v>
+      </c>
+      <c r="W105" t="s">
+        <v>1106</v>
+      </c>
+      <c r="X105" t="s">
+        <v>794</v>
+      </c>
+      <c r="Z105" t="s">
+        <v>1202</v>
       </c>
       <c r="AD105" t="s">
-        <v>815</v>
+        <v>1271</v>
       </c>
       <c r="AE105" t="s">
-        <v>816</v>
+        <v>1272</v>
       </c>
       <c r="AG105" t="s">
-        <v>796</v>
+        <v>976</v>
       </c>
     </row>
     <row r="106" spans="1:33">
@@ -11089,19 +14005,28 @@
         <v>0</v>
       </c>
       <c r="T106" t="s">
-        <v>796</v>
+        <v>976</v>
       </c>
       <c r="V106" t="s">
-        <v>796</v>
+        <v>976</v>
+      </c>
+      <c r="W106" t="s">
+        <v>1107</v>
+      </c>
+      <c r="X106" t="s">
+        <v>794</v>
+      </c>
+      <c r="Z106" t="s">
+        <v>1203</v>
       </c>
       <c r="AD106" t="s">
-        <v>815</v>
+        <v>1271</v>
       </c>
       <c r="AE106" t="s">
-        <v>816</v>
+        <v>1272</v>
       </c>
       <c r="AG106" t="s">
-        <v>796</v>
+        <v>976</v>
       </c>
     </row>
     <row r="107" spans="1:33">
@@ -11145,19 +14070,28 @@
         <v>0</v>
       </c>
       <c r="T107" t="s">
-        <v>796</v>
+        <v>976</v>
       </c>
       <c r="V107" t="s">
-        <v>796</v>
+        <v>976</v>
+      </c>
+      <c r="W107" t="s">
+        <v>1108</v>
+      </c>
+      <c r="X107" t="s">
+        <v>794</v>
+      </c>
+      <c r="Z107" t="s">
+        <v>1204</v>
       </c>
       <c r="AD107" t="s">
-        <v>815</v>
+        <v>1271</v>
       </c>
       <c r="AE107" t="s">
-        <v>816</v>
+        <v>1272</v>
       </c>
       <c r="AG107" t="s">
-        <v>796</v>
+        <v>976</v>
       </c>
     </row>
     <row r="108" spans="1:33">
@@ -11204,19 +14138,19 @@
         <v>727</v>
       </c>
       <c r="T108" t="s">
-        <v>796</v>
+        <v>976</v>
       </c>
       <c r="V108" t="s">
-        <v>796</v>
+        <v>976</v>
       </c>
       <c r="AD108" t="s">
-        <v>815</v>
+        <v>1271</v>
       </c>
       <c r="AE108" t="s">
-        <v>816</v>
+        <v>1272</v>
       </c>
       <c r="AG108" t="s">
-        <v>796</v>
+        <v>976</v>
       </c>
     </row>
     <row r="109" spans="1:33">
@@ -11260,19 +14194,28 @@
         <v>0</v>
       </c>
       <c r="T109" t="s">
-        <v>796</v>
+        <v>976</v>
       </c>
       <c r="V109" t="s">
-        <v>796</v>
+        <v>976</v>
+      </c>
+      <c r="W109" t="s">
+        <v>1109</v>
+      </c>
+      <c r="X109" t="s">
+        <v>794</v>
+      </c>
+      <c r="Z109" t="s">
+        <v>1205</v>
       </c>
       <c r="AD109" t="s">
-        <v>815</v>
+        <v>1271</v>
       </c>
       <c r="AE109" t="s">
-        <v>816</v>
+        <v>1272</v>
       </c>
       <c r="AG109" t="s">
-        <v>796</v>
+        <v>976</v>
       </c>
     </row>
     <row r="110" spans="1:33">
@@ -11316,19 +14259,28 @@
         <v>0</v>
       </c>
       <c r="T110" t="s">
-        <v>796</v>
+        <v>976</v>
       </c>
       <c r="V110" t="s">
-        <v>796</v>
+        <v>976</v>
+      </c>
+      <c r="W110" t="s">
+        <v>1110</v>
+      </c>
+      <c r="X110" t="s">
+        <v>794</v>
+      </c>
+      <c r="Z110" t="s">
+        <v>1206</v>
       </c>
       <c r="AD110" t="s">
-        <v>815</v>
+        <v>1271</v>
       </c>
       <c r="AE110" t="s">
-        <v>816</v>
+        <v>1272</v>
       </c>
       <c r="AG110" t="s">
-        <v>796</v>
+        <v>976</v>
       </c>
     </row>
     <row r="111" spans="1:33">
@@ -11372,19 +14324,28 @@
         <v>0</v>
       </c>
       <c r="T111" t="s">
-        <v>796</v>
+        <v>976</v>
       </c>
       <c r="V111" t="s">
-        <v>796</v>
+        <v>976</v>
+      </c>
+      <c r="W111" t="s">
+        <v>1111</v>
+      </c>
+      <c r="X111" t="s">
+        <v>794</v>
+      </c>
+      <c r="Z111" t="s">
+        <v>1207</v>
       </c>
       <c r="AD111" t="s">
-        <v>815</v>
+        <v>1271</v>
       </c>
       <c r="AE111" t="s">
-        <v>816</v>
+        <v>1272</v>
       </c>
       <c r="AG111" t="s">
-        <v>796</v>
+        <v>976</v>
       </c>
     </row>
     <row r="112" spans="1:33">
@@ -11428,19 +14389,28 @@
         <v>0</v>
       </c>
       <c r="T112" t="s">
-        <v>796</v>
+        <v>976</v>
       </c>
       <c r="V112" t="s">
-        <v>796</v>
+        <v>976</v>
+      </c>
+      <c r="W112" t="s">
+        <v>1112</v>
+      </c>
+      <c r="X112" t="s">
+        <v>794</v>
+      </c>
+      <c r="Z112" t="s">
+        <v>1208</v>
       </c>
       <c r="AD112" t="s">
-        <v>815</v>
+        <v>1271</v>
       </c>
       <c r="AE112" t="s">
-        <v>816</v>
+        <v>1272</v>
       </c>
       <c r="AG112" t="s">
-        <v>796</v>
+        <v>976</v>
       </c>
     </row>
     <row r="113" spans="1:33">
@@ -11484,19 +14454,28 @@
         <v>0</v>
       </c>
       <c r="T113" t="s">
-        <v>796</v>
+        <v>976</v>
       </c>
       <c r="V113" t="s">
-        <v>796</v>
+        <v>976</v>
+      </c>
+      <c r="W113" t="s">
+        <v>1113</v>
+      </c>
+      <c r="X113" t="s">
+        <v>794</v>
+      </c>
+      <c r="Z113" t="s">
+        <v>1209</v>
       </c>
       <c r="AD113" t="s">
-        <v>815</v>
+        <v>1271</v>
       </c>
       <c r="AE113" t="s">
-        <v>816</v>
+        <v>1272</v>
       </c>
       <c r="AG113" t="s">
-        <v>796</v>
+        <v>976</v>
       </c>
     </row>
     <row r="114" spans="1:33">
@@ -11540,19 +14519,28 @@
         <v>0</v>
       </c>
       <c r="T114" t="s">
-        <v>796</v>
+        <v>976</v>
       </c>
       <c r="V114" t="s">
-        <v>796</v>
+        <v>976</v>
+      </c>
+      <c r="W114" t="s">
+        <v>1114</v>
+      </c>
+      <c r="X114" t="s">
+        <v>794</v>
+      </c>
+      <c r="Z114" t="s">
+        <v>1210</v>
       </c>
       <c r="AD114" t="s">
-        <v>815</v>
+        <v>1271</v>
       </c>
       <c r="AE114" t="s">
-        <v>816</v>
+        <v>1272</v>
       </c>
       <c r="AG114" t="s">
-        <v>796</v>
+        <v>976</v>
       </c>
     </row>
     <row r="115" spans="1:33">
@@ -11596,19 +14584,28 @@
         <v>0</v>
       </c>
       <c r="T115" t="s">
-        <v>796</v>
+        <v>976</v>
       </c>
       <c r="V115" t="s">
-        <v>796</v>
+        <v>976</v>
+      </c>
+      <c r="W115" t="s">
+        <v>1115</v>
+      </c>
+      <c r="X115" t="s">
+        <v>794</v>
+      </c>
+      <c r="Z115" t="s">
+        <v>1211</v>
       </c>
       <c r="AD115" t="s">
-        <v>815</v>
+        <v>1271</v>
       </c>
       <c r="AE115" t="s">
-        <v>816</v>
+        <v>1272</v>
       </c>
       <c r="AG115" t="s">
-        <v>796</v>
+        <v>976</v>
       </c>
     </row>
     <row r="116" spans="1:33">
@@ -11655,19 +14652,19 @@
         <v>785</v>
       </c>
       <c r="T116" t="s">
-        <v>796</v>
+        <v>976</v>
       </c>
       <c r="V116" t="s">
-        <v>796</v>
+        <v>976</v>
       </c>
       <c r="AD116" t="s">
-        <v>815</v>
+        <v>1271</v>
       </c>
       <c r="AE116" t="s">
-        <v>816</v>
+        <v>1272</v>
       </c>
       <c r="AG116" t="s">
-        <v>796</v>
+        <v>976</v>
       </c>
     </row>
     <row r="117" spans="1:33">
@@ -11711,19 +14708,28 @@
         <v>0</v>
       </c>
       <c r="T117" t="s">
-        <v>796</v>
+        <v>976</v>
       </c>
       <c r="V117" t="s">
-        <v>796</v>
+        <v>976</v>
+      </c>
+      <c r="W117" t="s">
+        <v>1116</v>
+      </c>
+      <c r="X117" t="s">
+        <v>794</v>
+      </c>
+      <c r="Z117" t="s">
+        <v>1212</v>
       </c>
       <c r="AD117" t="s">
-        <v>815</v>
+        <v>1271</v>
       </c>
       <c r="AE117" t="s">
-        <v>816</v>
+        <v>1272</v>
       </c>
       <c r="AG117" t="s">
-        <v>796</v>
+        <v>976</v>
       </c>
     </row>
     <row r="118" spans="1:33">
@@ -11767,19 +14773,28 @@
         <v>0</v>
       </c>
       <c r="T118" t="s">
-        <v>796</v>
+        <v>976</v>
       </c>
       <c r="V118" t="s">
-        <v>796</v>
+        <v>976</v>
+      </c>
+      <c r="W118" t="s">
+        <v>1117</v>
+      </c>
+      <c r="X118" t="s">
+        <v>794</v>
+      </c>
+      <c r="Z118" t="s">
+        <v>1213</v>
       </c>
       <c r="AD118" t="s">
-        <v>815</v>
+        <v>1271</v>
       </c>
       <c r="AE118" t="s">
-        <v>816</v>
+        <v>1272</v>
       </c>
       <c r="AG118" t="s">
-        <v>796</v>
+        <v>976</v>
       </c>
     </row>
     <row r="119" spans="1:33">
@@ -11823,19 +14838,28 @@
         <v>0</v>
       </c>
       <c r="T119" t="s">
-        <v>796</v>
+        <v>976</v>
       </c>
       <c r="V119" t="s">
-        <v>796</v>
+        <v>976</v>
+      </c>
+      <c r="W119" t="s">
+        <v>1118</v>
+      </c>
+      <c r="X119" t="s">
+        <v>794</v>
+      </c>
+      <c r="Z119" t="s">
+        <v>1214</v>
       </c>
       <c r="AD119" t="s">
-        <v>815</v>
+        <v>1271</v>
       </c>
       <c r="AE119" t="s">
-        <v>816</v>
+        <v>1272</v>
       </c>
       <c r="AG119" t="s">
-        <v>796</v>
+        <v>976</v>
       </c>
     </row>
     <row r="120" spans="1:33">
@@ -11879,19 +14903,28 @@
         <v>0</v>
       </c>
       <c r="T120" t="s">
-        <v>796</v>
+        <v>976</v>
       </c>
       <c r="V120" t="s">
-        <v>796</v>
+        <v>976</v>
+      </c>
+      <c r="W120" t="s">
+        <v>1119</v>
+      </c>
+      <c r="X120" t="s">
+        <v>794</v>
+      </c>
+      <c r="Z120" t="s">
+        <v>1215</v>
       </c>
       <c r="AD120" t="s">
-        <v>815</v>
+        <v>1271</v>
       </c>
       <c r="AE120" t="s">
-        <v>816</v>
+        <v>1272</v>
       </c>
       <c r="AG120" t="s">
-        <v>796</v>
+        <v>976</v>
       </c>
     </row>
     <row r="121" spans="1:33">
@@ -11935,19 +14968,28 @@
         <v>0</v>
       </c>
       <c r="T121" t="s">
-        <v>796</v>
+        <v>976</v>
       </c>
       <c r="V121" t="s">
-        <v>796</v>
+        <v>976</v>
+      </c>
+      <c r="W121" t="s">
+        <v>1120</v>
+      </c>
+      <c r="X121" t="s">
+        <v>794</v>
+      </c>
+      <c r="Z121" t="s">
+        <v>1216</v>
       </c>
       <c r="AD121" t="s">
-        <v>815</v>
+        <v>1271</v>
       </c>
       <c r="AE121" t="s">
-        <v>816</v>
+        <v>1272</v>
       </c>
       <c r="AG121" t="s">
-        <v>796</v>
+        <v>976</v>
       </c>
     </row>
     <row r="122" spans="1:33">
@@ -11997,10 +15039,19 @@
         <v>0</v>
       </c>
       <c r="T122" t="s">
-        <v>796</v>
+        <v>976</v>
       </c>
       <c r="V122" t="s">
-        <v>796</v>
+        <v>976</v>
+      </c>
+      <c r="W122" t="s">
+        <v>1121</v>
+      </c>
+      <c r="X122" t="s">
+        <v>794</v>
+      </c>
+      <c r="Z122" t="s">
+        <v>1217</v>
       </c>
     </row>
     <row r="123" spans="1:33">
@@ -12050,10 +15101,19 @@
         <v>0</v>
       </c>
       <c r="T123" t="s">
-        <v>796</v>
+        <v>976</v>
       </c>
       <c r="V123" t="s">
-        <v>796</v>
+        <v>976</v>
+      </c>
+      <c r="W123" t="s">
+        <v>1122</v>
+      </c>
+      <c r="X123" t="s">
+        <v>794</v>
+      </c>
+      <c r="Z123" t="s">
+        <v>1218</v>
       </c>
     </row>
     <row r="124" spans="1:33">
@@ -12103,10 +15163,19 @@
         <v>0</v>
       </c>
       <c r="T124" t="s">
-        <v>796</v>
+        <v>976</v>
       </c>
       <c r="V124" t="s">
-        <v>796</v>
+        <v>976</v>
+      </c>
+      <c r="W124" t="s">
+        <v>1123</v>
+      </c>
+      <c r="X124" t="s">
+        <v>794</v>
+      </c>
+      <c r="Z124" t="s">
+        <v>1219</v>
       </c>
     </row>
   </sheetData>
